--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C1255F-868D-4140-AC3D-913A0D5D6570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B506F823-0C24-5F41-8AA4-4418A3C362CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -638,12 +638,6 @@
 ~ Single Trip from chuk yuen to Temple Mall 19/08 - $2</t>
   </si>
   <si>
-    <t>Partial Food And Snack Prepaid on the Previous Month
-~ Food
-~ Snack And Drinks
-   ~ OK Store 20/08 - $8.5</t>
-  </si>
-  <si>
     <t>1. Top up $50 for Octopus</t>
   </si>
   <si>
@@ -664,6 +658,13 @@
   </si>
   <si>
     <t>~ iHerb Aveeno Lotion 23/08 - $136.64</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+   ~ HKTV mall 24/08 - $211.4
+~ Snack And Drinks
+   ~ OK Store 20/08 - $8.5</t>
   </si>
 </sst>
 </file>
@@ -1190,101 +1191,19 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1304,32 +1223,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1340,27 +1268,100 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1680,13 +1681,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1707,7 +1708,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>169.76</v>
+        <v>0</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1738,7 +1739,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1800,7 +1801,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>3.08</v>
+        <v>1.44</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1863,7 +1864,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>221.64000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1916,13 +1917,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1950,10 +1951,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="101"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1965,10 +1966,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="92"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1980,10 +1981,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="93" t="s">
+      <c r="C13" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1993,10 +1994,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2006,10 +2007,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="59"/>
+      <c r="D15" s="88"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2019,10 +2020,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2034,10 +2035,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="94"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2047,10 +2048,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2062,10 +2063,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="96"/>
+      <c r="D19" s="97"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2086,13 +2087,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2120,10 +2121,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="97"/>
+      <c r="D23" s="98"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2135,10 +2136,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2150,10 +2151,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2163,10 +2164,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="92" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="94"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2178,10 +2179,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="94"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2191,10 +2192,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="98" t="s">
+      <c r="C28" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="98"/>
+      <c r="D28" s="66"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2216,13 +2217,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2250,10 +2251,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="61"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2265,10 +2266,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2278,10 +2279,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="59"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2291,10 +2292,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="99" t="s">
+      <c r="C35" s="89" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="63"/>
+      <c r="D35" s="90"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2304,10 +2305,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="99" t="s">
+      <c r="C36" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="100"/>
+      <c r="D36" s="91"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2317,10 +2318,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="59"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2342,11 +2343,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2361,11 +2362,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2411,16 +2412,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="66"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
+      <c r="A48" s="87"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="87"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2469,11 +2470,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="65" t="s">
+      <c r="A54" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="65"/>
-      <c r="C54" s="65"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2508,11 +2509,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="65"/>
-      <c r="C58" s="65"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2536,11 +2537,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="83"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2564,11 +2565,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="84"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2645,11 +2646,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="67" t="s">
+      <c r="A72" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="67"/>
-      <c r="C72" s="67"/>
+      <c r="B72" s="84"/>
+      <c r="C72" s="84"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2699,167 +2700,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="69" t="s">
+      <c r="A80" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="69"/>
-      <c r="C80" s="69" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="69"/>
+      <c r="D80" s="85"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="101" t="s">
+      <c r="A81" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="101"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="71"/>
+      <c r="B81" s="78"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="71" t="s">
+      <c r="A82" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="71"/>
-      <c r="C82" s="102" t="s">
+      <c r="B82" s="56"/>
+      <c r="C82" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="102"/>
+      <c r="D82" s="79"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="71"/>
-      <c r="B83" s="71"/>
-      <c r="C83" s="102" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="102"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="71"/>
-      <c r="B84" s="71"/>
-      <c r="C84" s="102" t="s">
+      <c r="A84" s="56"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="102"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="71"/>
-      <c r="B85" s="71"/>
-      <c r="C85" s="103" t="s">
+      <c r="A85" s="56"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="103"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="71"/>
-      <c r="B86" s="71"/>
-      <c r="C86" s="76" t="s">
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="76"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="71"/>
-      <c r="B87" s="71"/>
-      <c r="C87" s="103" t="s">
+      <c r="A87" s="56"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="103"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="71"/>
-      <c r="B88" s="71"/>
-      <c r="C88" s="102" t="s">
+      <c r="A88" s="56"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="102"/>
+      <c r="D88" s="79"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="71"/>
-      <c r="B89" s="71"/>
-      <c r="C89" s="76" t="s">
+      <c r="A89" s="56"/>
+      <c r="B89" s="56"/>
+      <c r="C89" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="76"/>
+      <c r="D89" s="81"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="71"/>
-      <c r="B90" s="71"/>
-      <c r="C90" s="76" t="s">
+      <c r="A90" s="56"/>
+      <c r="B90" s="56"/>
+      <c r="C90" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="76"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="71"/>
-      <c r="B91" s="71"/>
-      <c r="C91" s="104" t="s">
+      <c r="A91" s="56"/>
+      <c r="B91" s="56"/>
+      <c r="C91" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="104"/>
+      <c r="D91" s="82"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="72" t="s">
+      <c r="A92" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="72"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="78" t="s">
+      <c r="C93" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="78"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2867,113 +2868,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="68" t="s">
+      <c r="A95" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="68" t="s">
+      <c r="A96" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="B96" s="72"/>
+      <c r="C96" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="68"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="70" t="s">
+      <c r="A97" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="70"/>
-      <c r="C97" s="79"/>
-      <c r="D97" s="79"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="71" t="s">
+      <c r="A98" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="71"/>
-      <c r="C98" s="75" t="s">
+      <c r="B98" s="56"/>
+      <c r="C98" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="75"/>
+      <c r="D98" s="73"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="71"/>
-      <c r="B99" s="71"/>
-      <c r="C99" s="73" t="s">
+      <c r="A99" s="56"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="74"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="71"/>
-      <c r="B100" s="71"/>
-      <c r="C100" s="73" t="s">
+      <c r="A100" s="56"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="74"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="71"/>
-      <c r="B101" s="71"/>
-      <c r="C101" s="73" t="s">
+      <c r="A101" s="56"/>
+      <c r="B101" s="56"/>
+      <c r="C101" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="73"/>
+      <c r="D101" s="74"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="71"/>
-      <c r="B102" s="71"/>
-      <c r="C102" s="84" t="s">
+      <c r="A102" s="56"/>
+      <c r="B102" s="56"/>
+      <c r="C102" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="105"/>
+      <c r="D102" s="70"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="71" t="s">
+      <c r="A103" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="71"/>
-      <c r="C103" s="79"/>
-      <c r="D103" s="79"/>
+      <c r="B103" s="56"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="82" t="s">
+      <c r="C104" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="82"/>
+      <c r="D104" s="58"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2994,91 +2995,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="83" t="s">
+      <c r="A107" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="83"/>
-      <c r="C107" s="83"/>
-      <c r="D107" s="83"/>
-      <c r="E107" s="83"/>
+      <c r="B107" s="71"/>
+      <c r="C107" s="71"/>
+      <c r="D107" s="71"/>
+      <c r="E107" s="71"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="68" t="s">
+      <c r="A108" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="68"/>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="72"/>
+      <c r="C108" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="68"/>
+      <c r="D108" s="72"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="70" t="s">
+      <c r="A109" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="70"/>
-      <c r="C109" s="79"/>
-      <c r="D109" s="79"/>
+      <c r="B109" s="59"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="57"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="87"/>
-      <c r="C110" s="98" t="s">
+      <c r="B110" s="61"/>
+      <c r="C110" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="98"/>
+      <c r="D110" s="66"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="88"/>
-      <c r="B111" s="89"/>
-      <c r="C111" s="106" t="s">
+      <c r="A111" s="62"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="107"/>
+      <c r="D111" s="68"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="90"/>
-      <c r="B112" s="91"/>
-      <c r="C112" s="84" t="s">
+      <c r="A112" s="64"/>
+      <c r="B112" s="65"/>
+      <c r="C112" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="105"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="79"/>
-      <c r="D113" s="79"/>
+      <c r="B113" s="56"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="82" t="s">
+      <c r="C114" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="82"/>
+      <c r="D114" s="58"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6830,35 +6831,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6872,42 +6880,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6947,13 +6948,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="99" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6975,7 +6976,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>169.76</v>
+        <v>0</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7007,7 +7008,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7071,7 +7072,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>3.08</v>
+        <v>1.44</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7135,7 +7136,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>221.64000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7188,13 +7189,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7222,10 +7223,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="101"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7237,10 +7238,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="57"/>
+      <c r="D12" s="112"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7252,10 +7253,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7267,10 +7268,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7291,13 +7292,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7325,10 +7326,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7340,10 +7341,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="88"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7355,23 +7356,23 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="62" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="63"/>
+      <c r="C20" s="111" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="90"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="109" t="s">
+      <c r="A21" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="109" t="s">
+      <c r="C21" s="109" t="s">
         <v>142</v>
-      </c>
-      <c r="C21" s="111" t="s">
-        <v>143</v>
       </c>
       <c r="D21" s="110"/>
       <c r="E21" s="29">
@@ -7381,8 +7382,8 @@
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
       <c r="E22" s="29">
         <v>0</v>
       </c>
@@ -7404,13 +7405,13 @@
       <c r="B24" s="24"/>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="60"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -7438,10 +7439,10 @@
       <c r="B26" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="61"/>
+      <c r="D26" s="96"/>
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
@@ -7453,10 +7454,10 @@
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="59"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="33">
         <v>2485</v>
       </c>
@@ -7464,8 +7465,8 @@
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="29">
         <v>0</v>
       </c>
@@ -7487,11 +7488,11 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
     </row>
     <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -7506,11 +7507,11 @@
       <c r="D32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="65" t="s">
+      <c r="A33" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="65"/>
-      <c r="C33" s="65"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
@@ -7556,16 +7557,16 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="87"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
     </row>
     <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -7614,11 +7615,11 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="65"/>
-      <c r="C45" s="65"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
@@ -7653,11 +7654,11 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="65" t="s">
+      <c r="A49" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="65"/>
-      <c r="C49" s="65"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -7681,11 +7682,11 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="65" t="s">
+      <c r="A52" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="65"/>
-      <c r="C52" s="65"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
@@ -7709,11 +7710,11 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="84"/>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
@@ -7790,11 +7791,11 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="67" t="s">
+      <c r="A63" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
+      <c r="B63" s="84"/>
+      <c r="C63" s="84"/>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
@@ -7844,91 +7845,91 @@
       <c r="B69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="72"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="69" t="s">
+      <c r="A71" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="69"/>
-      <c r="C71" s="69" t="s">
+      <c r="B71" s="85"/>
+      <c r="C71" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="69"/>
+      <c r="D71" s="85"/>
       <c r="E71" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="70" t="s">
+      <c r="A72" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="70"/>
-      <c r="C72" s="71"/>
-      <c r="D72" s="71"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
       <c r="E72" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="72" t="s">
+      <c r="A73" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="72"/>
-      <c r="C73" s="73" t="s">
+      <c r="B73" s="75"/>
+      <c r="C73" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="D73" s="73"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="72"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="74" t="s">
+      <c r="A74" s="75"/>
+      <c r="B74" s="75"/>
+      <c r="C74" s="108" t="s">
         <v>135</v>
       </c>
-      <c r="D74" s="75"/>
+      <c r="D74" s="73"/>
       <c r="E74" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="72"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="74" t="s">
+      <c r="A75" s="75"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="108" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="76"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="72" t="s">
+      <c r="A76" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="72"/>
-      <c r="C76" s="77"/>
-      <c r="D76" s="77"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="76"/>
+      <c r="D76" s="76"/>
       <c r="E76" s="46">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="78" t="s">
+      <c r="C77" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="78"/>
+      <c r="D77" s="77"/>
       <c r="E77" s="47">
         <f>(E15+E72)-SUM(E73:E76)</f>
         <v>24.599999999999909</v>
@@ -7936,105 +7937,105 @@
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68" t="s">
+      <c r="B80" s="72"/>
+      <c r="C80" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="68"/>
+      <c r="D80" s="72"/>
       <c r="E80" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="70" t="s">
+      <c r="A81" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="70"/>
-      <c r="C81" s="79"/>
-      <c r="D81" s="79"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="47">
         <f>E77</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="86" t="s">
+      <c r="A82" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="87"/>
-      <c r="C82" s="80" t="s">
+      <c r="B82" s="61"/>
+      <c r="C82" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="81"/>
+      <c r="D82" s="105"/>
       <c r="E82" s="48">
         <v>770.4</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="88"/>
-      <c r="B83" s="89"/>
-      <c r="C83" s="73" t="s">
-        <v>138</v>
-      </c>
-      <c r="D83" s="73"/>
+    <row r="83" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="62"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="D83" s="74"/>
       <c r="E83" s="48">
-        <v>8.5</v>
+        <v>219.9</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="88"/>
-      <c r="B84" s="89"/>
-      <c r="C84" s="84" t="s">
-        <v>140</v>
-      </c>
-      <c r="D84" s="85"/>
+      <c r="A84" s="62"/>
+      <c r="B84" s="63"/>
+      <c r="C84" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="106"/>
       <c r="E84" s="48">
         <v>254.5</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="90"/>
-      <c r="B85" s="91"/>
-      <c r="C85" s="112" t="s">
-        <v>144</v>
-      </c>
-      <c r="D85" s="85"/>
+      <c r="A85" s="64"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="107" t="s">
+        <v>143</v>
+      </c>
+      <c r="D85" s="106"/>
       <c r="E85" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="71" t="s">
+      <c r="A86" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="71"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
       <c r="E86" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="82" t="s">
+      <c r="C87" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D87" s="82"/>
+      <c r="D87" s="58"/>
       <c r="E87" s="47">
         <f>(E23+E81)-SUM(E82:E86)</f>
-        <v>221.63999999999987</v>
+        <v>10.239999999999782</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8052,72 +8053,72 @@
       <c r="E89" s="49"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="83" t="s">
+      <c r="A90" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="83"/>
-      <c r="C90" s="83"/>
-      <c r="D90" s="83"/>
-      <c r="E90" s="83"/>
+      <c r="B90" s="71"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="68" t="s">
+      <c r="A91" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B91" s="68"/>
-      <c r="C91" s="68" t="s">
+      <c r="B91" s="72"/>
+      <c r="C91" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D91" s="68"/>
+      <c r="D91" s="72"/>
       <c r="E91" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="79"/>
-      <c r="D92" s="79"/>
+      <c r="B92" s="59"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
       <c r="E92" s="47">
         <f>E87</f>
-        <v>221.63999999999987</v>
+        <v>10.239999999999782</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="71" t="s">
+      <c r="A93" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="B93" s="71"/>
-      <c r="C93" s="73" t="s">
+      <c r="B93" s="56"/>
+      <c r="C93" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="D93" s="73"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="71" t="s">
+      <c r="A94" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="71"/>
-      <c r="C94" s="79"/>
-      <c r="D94" s="79"/>
+      <c r="B94" s="56"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
       <c r="E94" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="82" t="s">
+      <c r="C95" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="82"/>
+      <c r="D95" s="58"/>
       <c r="E95" s="47">
         <f>(E29+E92)-SUM(E93:E94)</f>
-        <v>1535.6399999999999</v>
+        <v>1324.2399999999998</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11866,13 +11867,46 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A90:E90"/>
@@ -11884,46 +11918,13 @@
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A82:B85"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A73:B75"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E72">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B506F823-0C24-5F41-8AA4-4418A3C362CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940699EB-1EEB-4C45-B049-E94549ABA757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -641,13 +641,6 @@
     <t>1. Top up $50 for Octopus</t>
   </si>
   <si>
-    <t>~ Debit For Octopus Card ($50). 20/08
-~ OK Store buy additional 1 packet cigarette 20/08 - $78
-~ Mail Chuk Yuen Post Office - $2.4
-~ Additional transport fees for e-cigarette 20/08 - $50
-~ Paid Water Supplies Fees 20/08 - $74.1</t>
-  </si>
-  <si>
     <t>23rd August 2026</t>
   </si>
   <si>
@@ -665,6 +658,14 @@
    ~ HKTV mall 24/08 - $211.4
 ~ Snack And Drinks
    ~ OK Store 20/08 - $8.5</t>
+  </si>
+  <si>
+    <t>~ Debit For Octopus Card ($50). 20/08
+~ OK Store buy additional 1 packet cigarette 20/08 - $78
+~ Mail Chuk Yuen Post Office - $2.4
+~ Additional transport fees for e-cigarette 20/08 - $50
+~ Paid Water Supplies Fees 20/08 - $74.1
+~ Round Trip to East Kowloon hospital 31/08 - $4</t>
   </si>
 </sst>
 </file>
@@ -1193,17 +1194,110 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1223,41 +1317,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1268,101 +1353,17 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1681,13 +1682,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1832,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1864,7 +1865,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>10.24</v>
+        <v>6.24</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1917,13 +1918,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1951,10 +1952,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="101"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1966,10 +1967,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1981,10 +1982,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="103"/>
+      <c r="D13" s="98"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1994,10 +1995,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2007,10 +2008,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="88"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2020,10 +2021,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="88"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2035,10 +2036,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="93"/>
+      <c r="D17" s="99"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2048,10 +2049,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="94"/>
+      <c r="D18" s="100"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2063,10 +2064,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="97"/>
+      <c r="D19" s="101"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2087,13 +2088,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2121,10 +2122,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="98" t="s">
+      <c r="C23" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="98"/>
+      <c r="D23" s="102"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2136,10 +2137,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2151,10 +2152,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="88"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2164,10 +2165,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="93"/>
+      <c r="D26" s="99"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2179,10 +2180,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="94"/>
+      <c r="D27" s="100"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2192,10 +2193,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="66"/>
+      <c r="D28" s="103"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2217,13 +2218,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="95" t="s">
+      <c r="A31" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2251,10 +2252,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="96" t="s">
+      <c r="C32" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="96"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2266,10 +2267,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="88"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2279,10 +2280,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="88"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2292,10 +2293,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="90"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2305,10 +2306,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="89" t="s">
+      <c r="C36" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="91"/>
+      <c r="D36" s="105"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2318,10 +2319,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="88"/>
+      <c r="D37" s="61"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2343,11 +2344,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2362,11 +2363,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2412,16 +2413,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="87"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="87"/>
+      <c r="A48" s="70"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="70"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2470,11 +2471,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="83" t="s">
+      <c r="A54" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="69"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2509,11 +2510,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="83" t="s">
+      <c r="A58" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="69"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2537,11 +2538,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="83"/>
-      <c r="C61" s="83"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="69"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2565,11 +2566,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="84"/>
-      <c r="C64" s="84"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="71"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2646,11 +2647,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="84"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="71"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2709,158 +2710,158 @@
       <c r="E79" s="72"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="85" t="s">
+      <c r="B80" s="73"/>
+      <c r="C80" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="85"/>
+      <c r="D80" s="73"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="78" t="s">
+      <c r="A81" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="78"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
+      <c r="B81" s="106"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="75"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="56"/>
-      <c r="C82" s="79" t="s">
+      <c r="B82" s="75"/>
+      <c r="C82" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="79"/>
+      <c r="D82" s="107"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="56"/>
-      <c r="B83" s="56"/>
-      <c r="C83" s="79" t="s">
+      <c r="A83" s="75"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="79"/>
+      <c r="D83" s="107"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="56"/>
-      <c r="B84" s="56"/>
-      <c r="C84" s="79" t="s">
+      <c r="A84" s="75"/>
+      <c r="B84" s="75"/>
+      <c r="C84" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="79"/>
+      <c r="D84" s="107"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="56"/>
-      <c r="B85" s="56"/>
-      <c r="C85" s="80" t="s">
+      <c r="A85" s="75"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="80"/>
+      <c r="D85" s="108"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="56"/>
-      <c r="B86" s="56"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="75"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="81"/>
+      <c r="D86" s="80"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="56"/>
-      <c r="B87" s="56"/>
-      <c r="C87" s="80" t="s">
+      <c r="A87" s="75"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="80"/>
+      <c r="D87" s="108"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="56"/>
-      <c r="B88" s="56"/>
-      <c r="C88" s="79" t="s">
+      <c r="A88" s="75"/>
+      <c r="B88" s="75"/>
+      <c r="C88" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="79"/>
+      <c r="D88" s="107"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="56"/>
-      <c r="B89" s="56"/>
-      <c r="C89" s="81" t="s">
+      <c r="A89" s="75"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="81"/>
+      <c r="D89" s="80"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="56"/>
-      <c r="B90" s="56"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="75"/>
+      <c r="B90" s="75"/>
+      <c r="C90" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="81"/>
+      <c r="D90" s="80"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="56"/>
-      <c r="B91" s="56"/>
-      <c r="C91" s="82" t="s">
+      <c r="A91" s="75"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="82"/>
+      <c r="D91" s="109"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="75"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="82"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2890,91 +2891,91 @@
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="59" t="s">
+      <c r="A97" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="59"/>
-      <c r="C97" s="57"/>
-      <c r="D97" s="57"/>
+      <c r="B97" s="74"/>
+      <c r="C97" s="83"/>
+      <c r="D97" s="83"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="56" t="s">
+      <c r="A98" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="73" t="s">
+      <c r="B98" s="75"/>
+      <c r="C98" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="79"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="56"/>
-      <c r="B99" s="56"/>
-      <c r="C99" s="74" t="s">
+      <c r="A99" s="75"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="74"/>
+      <c r="D99" s="77"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="56"/>
-      <c r="B100" s="56"/>
-      <c r="C100" s="74" t="s">
+      <c r="A100" s="75"/>
+      <c r="B100" s="75"/>
+      <c r="C100" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="74"/>
+      <c r="D100" s="77"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="56"/>
-      <c r="B101" s="56"/>
-      <c r="C101" s="74" t="s">
+      <c r="A101" s="75"/>
+      <c r="B101" s="75"/>
+      <c r="C101" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="77"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="56"/>
-      <c r="B102" s="56"/>
-      <c r="C102" s="69" t="s">
+      <c r="A102" s="75"/>
+      <c r="B102" s="75"/>
+      <c r="C102" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="70"/>
+      <c r="D102" s="110"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="56" t="s">
+      <c r="A103" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="56"/>
-      <c r="C103" s="57"/>
-      <c r="D103" s="57"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="83"/>
+      <c r="D103" s="83"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="58" t="s">
+      <c r="C104" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="58"/>
+      <c r="D104" s="86"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2995,13 +2996,13 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="71" t="s">
+      <c r="A107" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="71"/>
-      <c r="C107" s="71"/>
-      <c r="D107" s="71"/>
-      <c r="E107" s="71"/>
+      <c r="B107" s="87"/>
+      <c r="C107" s="87"/>
+      <c r="D107" s="87"/>
+      <c r="E107" s="87"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="72" t="s">
@@ -3017,69 +3018,69 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="59" t="s">
+      <c r="A109" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="59"/>
-      <c r="C109" s="57"/>
-      <c r="D109" s="57"/>
+      <c r="B109" s="74"/>
+      <c r="C109" s="83"/>
+      <c r="D109" s="83"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="60" t="s">
+      <c r="A110" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="61"/>
-      <c r="C110" s="66" t="s">
+      <c r="B110" s="92"/>
+      <c r="C110" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="66"/>
+      <c r="D110" s="103"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="62"/>
-      <c r="B111" s="63"/>
-      <c r="C111" s="67" t="s">
+      <c r="A111" s="93"/>
+      <c r="B111" s="94"/>
+      <c r="C111" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="68"/>
+      <c r="D111" s="112"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="64"/>
-      <c r="B112" s="65"/>
-      <c r="C112" s="69" t="s">
+      <c r="A112" s="95"/>
+      <c r="B112" s="96"/>
+      <c r="C112" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="110"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="56" t="s">
+      <c r="A113" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="56"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
+      <c r="B113" s="75"/>
+      <c r="C113" s="83"/>
+      <c r="D113" s="83"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="58" t="s">
+      <c r="C114" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="58"/>
+      <c r="D114" s="86"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6831,42 +6832,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6880,35 +6874,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6948,13 +6949,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7104,7 +7105,7 @@
       </c>
       <c r="C7" s="9">
         <f>'April 2026 - June 2026'!C7</f>
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -7136,7 +7137,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>10.24</v>
+        <v>6.24</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7189,13 +7190,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7223,10 +7224,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="101"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7238,10 +7239,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="112" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="112"/>
+      <c r="D12" s="59"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7253,10 +7254,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="88"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7268,10 +7269,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7292,13 +7293,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7326,10 +7327,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="96" t="s">
+      <c r="C18" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="96"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7341,10 +7342,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="88"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7356,25 +7357,25 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="111" t="s">
+      <c r="C20" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="90"/>
+      <c r="D20" s="67"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="C21" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>142</v>
-      </c>
-      <c r="D21" s="110"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7405,13 +7406,13 @@
       <c r="B24" s="24"/>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="95"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -7439,10 +7440,10 @@
       <c r="B26" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="96" t="s">
+      <c r="C26" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="96"/>
+      <c r="D26" s="63"/>
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
@@ -7454,10 +7455,10 @@
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="88"/>
+      <c r="D27" s="61"/>
       <c r="E27" s="33">
         <v>2485</v>
       </c>
@@ -7465,8 +7466,8 @@
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="29">
         <v>0</v>
       </c>
@@ -7488,11 +7489,11 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
     </row>
     <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -7507,11 +7508,11 @@
       <c r="D32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
@@ -7557,16 +7558,16 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="87" t="s">
+      <c r="A38" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
     </row>
     <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -7615,11 +7616,11 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="83" t="s">
+      <c r="A45" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
@@ -7654,11 +7655,11 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="83" t="s">
+      <c r="A49" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="69"/>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -7682,11 +7683,11 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="83"/>
-      <c r="C52" s="83"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="69"/>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
@@ -7710,11 +7711,11 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="84" t="s">
+      <c r="A55" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="84"/>
-      <c r="C55" s="84"/>
+      <c r="B55" s="71"/>
+      <c r="C55" s="71"/>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
@@ -7791,11 +7792,11 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="84" t="s">
+      <c r="A63" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="84"/>
-      <c r="C63" s="84"/>
+      <c r="B63" s="71"/>
+      <c r="C63" s="71"/>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
@@ -7854,82 +7855,82 @@
       <c r="E70" s="72"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="85" t="s">
+      <c r="A71" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="85"/>
-      <c r="C71" s="85" t="s">
+      <c r="B71" s="73"/>
+      <c r="C71" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="85"/>
+      <c r="D71" s="73"/>
       <c r="E71" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="59" t="s">
+      <c r="A72" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="59"/>
-      <c r="C72" s="56"/>
-      <c r="D72" s="56"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
       <c r="E72" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="75"/>
-      <c r="C73" s="74" t="s">
+      <c r="B73" s="76"/>
+      <c r="C73" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="D73" s="74"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="75"/>
-      <c r="B74" s="75"/>
-      <c r="C74" s="108" t="s">
+      <c r="A74" s="76"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D74" s="73"/>
+      <c r="D74" s="79"/>
       <c r="E74" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="75"/>
-      <c r="B75" s="75"/>
-      <c r="C75" s="108" t="s">
+      <c r="A75" s="76"/>
+      <c r="B75" s="76"/>
+      <c r="C75" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="81"/>
+      <c r="D75" s="80"/>
       <c r="E75" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="75" t="s">
+      <c r="A76" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="75"/>
-      <c r="C76" s="76"/>
-      <c r="D76" s="76"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="46">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="77" t="s">
+      <c r="C77" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="77"/>
+      <c r="D77" s="82"/>
       <c r="E77" s="47">
         <f>(E15+E72)-SUM(E73:E76)</f>
         <v>24.599999999999909</v>
@@ -7959,83 +7960,83 @@
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="59" t="s">
+      <c r="A81" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="59"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="83"/>
+      <c r="D81" s="83"/>
       <c r="E81" s="47">
         <f>E77</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="61"/>
-      <c r="C82" s="104" t="s">
+      <c r="B82" s="92"/>
+      <c r="C82" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="105"/>
+      <c r="D82" s="85"/>
       <c r="E82" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="62"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="74" t="s">
-        <v>144</v>
-      </c>
-      <c r="D83" s="74"/>
+      <c r="A83" s="93"/>
+      <c r="B83" s="94"/>
+      <c r="C83" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" s="77"/>
       <c r="E83" s="48">
         <v>219.9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="62"/>
-      <c r="B84" s="63"/>
-      <c r="C84" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="D84" s="106"/>
+    <row r="84" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="93"/>
+      <c r="B84" s="94"/>
+      <c r="C84" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="D84" s="89"/>
       <c r="E84" s="48">
-        <v>254.5</v>
+        <v>258.5</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="64"/>
-      <c r="B85" s="65"/>
-      <c r="C85" s="107" t="s">
-        <v>143</v>
-      </c>
-      <c r="D85" s="106"/>
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="90" t="s">
+        <v>142</v>
+      </c>
+      <c r="D85" s="89"/>
       <c r="E85" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="56" t="s">
+      <c r="A86" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="56"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="83"/>
+      <c r="D86" s="83"/>
       <c r="E86" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="58" t="s">
+      <c r="C87" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="D87" s="58"/>
+      <c r="D87" s="86"/>
       <c r="E87" s="47">
         <f>(E23+E81)-SUM(E82:E86)</f>
-        <v>10.239999999999782</v>
+        <v>6.2399999999997817</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8053,13 +8054,13 @@
       <c r="E89" s="49"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="71" t="s">
+      <c r="A90" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="71"/>
-      <c r="C90" s="71"/>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
+      <c r="B90" s="87"/>
+      <c r="C90" s="87"/>
+      <c r="D90" s="87"/>
+      <c r="E90" s="87"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="72" t="s">
@@ -8075,50 +8076,50 @@
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="59" t="s">
+      <c r="A92" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="B92" s="59"/>
-      <c r="C92" s="57"/>
-      <c r="D92" s="57"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="47">
         <f>E87</f>
-        <v>10.239999999999782</v>
+        <v>6.2399999999997817</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="56" t="s">
+      <c r="A93" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B93" s="56"/>
-      <c r="C93" s="74" t="s">
+      <c r="B93" s="75"/>
+      <c r="C93" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="D93" s="74"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="56" t="s">
+      <c r="A94" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="56"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="57"/>
+      <c r="B94" s="75"/>
+      <c r="C94" s="83"/>
+      <c r="D94" s="83"/>
       <c r="E94" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="58" t="s">
+      <c r="C95" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="58"/>
+      <c r="D95" s="86"/>
       <c r="E95" s="47">
         <f>(E29+E92)-SUM(E93:E94)</f>
-        <v>1324.2399999999998</v>
+        <v>1320.2399999999998</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11867,46 +11868,13 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B75"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A90:E90"/>
@@ -11918,13 +11886,46 @@
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A82:B85"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E72">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940699EB-1EEB-4C45-B049-E94549ABA757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03639D5B-F0F2-114D-91F5-1A0ADD097EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="147">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -666,6 +666,12 @@
 ~ Additional transport fees for e-cigarette 20/08 - $50
 ~ Paid Water Supplies Fees 20/08 - $74.1
 ~ Round Trip to East Kowloon hospital 31/08 - $4</t>
+  </si>
+  <si>
+    <t>2nd September 2026</t>
+  </si>
+  <si>
+    <t>1. Borrow $60</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,112 +1198,18 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1317,32 +1229,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1353,17 +1274,107 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1682,13 +1693,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1740,7 +1751,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1865,7 +1876,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>6.24</v>
+        <v>66.239999999999995</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1918,13 +1929,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1952,10 +1963,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="100"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1967,10 +1978,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="97"/>
+      <c r="D12" s="101"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1982,10 +1993,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="98" t="s">
+      <c r="C13" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="98"/>
+      <c r="D13" s="102"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1995,10 +2006,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2008,10 +2019,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="61"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2021,10 +2032,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="87"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2036,10 +2047,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="99" t="s">
+      <c r="C17" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="99"/>
+      <c r="D17" s="92"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2049,10 +2060,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="100" t="s">
+      <c r="C18" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="100"/>
+      <c r="D18" s="93"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2064,10 +2075,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="101"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2088,13 +2099,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2122,10 +2133,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="102" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="102"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2137,10 +2148,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="87"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2152,10 +2163,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="87"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2165,10 +2176,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="99"/>
+      <c r="D26" s="92"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2180,10 +2191,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="100" t="s">
+      <c r="C27" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="100"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2193,10 +2204,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="103" t="s">
+      <c r="C28" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="103"/>
+      <c r="D28" s="65"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2218,13 +2229,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2252,10 +2263,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="95"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2267,10 +2278,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="87"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2280,10 +2291,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="87"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2293,10 +2304,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="104" t="s">
+      <c r="C35" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="67"/>
+      <c r="D35" s="89"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2306,10 +2317,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="104" t="s">
+      <c r="C36" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="105"/>
+      <c r="D36" s="90"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2319,10 +2330,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="87"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2344,11 +2355,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2363,11 +2374,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="82"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2413,16 +2424,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="70"/>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="70"/>
-      <c r="B48" s="70"/>
-      <c r="C48" s="70"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2471,11 +2482,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="69"/>
-      <c r="C54" s="69"/>
+      <c r="B54" s="82"/>
+      <c r="C54" s="82"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2510,11 +2521,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="69"/>
-      <c r="C58" s="69"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2538,11 +2549,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="69" t="s">
+      <c r="A61" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="69"/>
-      <c r="C61" s="69"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2566,11 +2577,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="71" t="s">
+      <c r="A64" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="83"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2647,11 +2658,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="71" t="s">
+      <c r="A72" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="71"/>
-      <c r="C72" s="71"/>
+      <c r="B72" s="83"/>
+      <c r="C72" s="83"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2659,7 +2670,7 @@
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="19">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2678,7 +2689,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2701,87 +2712,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="71"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73" t="s">
+      <c r="B80" s="84"/>
+      <c r="C80" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="73"/>
+      <c r="D80" s="84"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="106" t="s">
+      <c r="A81" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="106"/>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="75" t="s">
+      <c r="A82" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="75"/>
-      <c r="C82" s="107" t="s">
+      <c r="B82" s="55"/>
+      <c r="C82" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="107"/>
+      <c r="D82" s="78"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="75"/>
-      <c r="B83" s="75"/>
-      <c r="C83" s="107" t="s">
+      <c r="A83" s="55"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="107"/>
+      <c r="D83" s="78"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="75"/>
-      <c r="B84" s="75"/>
-      <c r="C84" s="107" t="s">
+      <c r="A84" s="55"/>
+      <c r="B84" s="55"/>
+      <c r="C84" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="107"/>
+      <c r="D84" s="78"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="75"/>
-      <c r="B85" s="75"/>
-      <c r="C85" s="108" t="s">
+      <c r="A85" s="55"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="108"/>
+      <c r="D85" s="79"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="75"/>
-      <c r="B86" s="75"/>
+      <c r="A86" s="55"/>
+      <c r="B86" s="55"/>
       <c r="C86" s="80" t="s">
         <v>89</v>
       </c>
@@ -2791,30 +2802,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="75"/>
-      <c r="B87" s="75"/>
-      <c r="C87" s="108" t="s">
+      <c r="A87" s="55"/>
+      <c r="B87" s="55"/>
+      <c r="C87" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="108"/>
+      <c r="D87" s="79"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="75"/>
-      <c r="B88" s="75"/>
-      <c r="C88" s="107" t="s">
+      <c r="A88" s="55"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="107"/>
+      <c r="D88" s="78"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="75"/>
-      <c r="B89" s="75"/>
+      <c r="A89" s="55"/>
+      <c r="B89" s="55"/>
       <c r="C89" s="80" t="s">
         <v>92</v>
       </c>
@@ -2824,8 +2835,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="75"/>
-      <c r="B90" s="75"/>
+      <c r="A90" s="55"/>
+      <c r="B90" s="55"/>
       <c r="C90" s="80" t="s">
         <v>93</v>
       </c>
@@ -2835,33 +2846,33 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="75"/>
-      <c r="B91" s="75"/>
-      <c r="C91" s="109" t="s">
+      <c r="A91" s="55"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="109"/>
+      <c r="D91" s="81"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="76"/>
-      <c r="C92" s="81"/>
-      <c r="D92" s="81"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="82" t="s">
+      <c r="C93" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="82"/>
+      <c r="D93" s="76"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2869,113 +2880,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="72" t="s">
+      <c r="A95" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="72"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
+      <c r="B95" s="71"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="71"/>
+      <c r="E95" s="71"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="72" t="s">
+      <c r="A96" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="72"/>
-      <c r="C96" s="72" t="s">
+      <c r="B96" s="71"/>
+      <c r="C96" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="72"/>
+      <c r="D96" s="71"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="74" t="s">
+      <c r="A97" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="74"/>
-      <c r="C97" s="83"/>
-      <c r="D97" s="83"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="75" t="s">
+      <c r="A98" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="75"/>
-      <c r="C98" s="79" t="s">
+      <c r="B98" s="55"/>
+      <c r="C98" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="79"/>
+      <c r="D98" s="72"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="75"/>
-      <c r="B99" s="75"/>
-      <c r="C99" s="77" t="s">
+      <c r="A99" s="55"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="77"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="75"/>
-      <c r="B100" s="75"/>
-      <c r="C100" s="77" t="s">
+      <c r="A100" s="55"/>
+      <c r="B100" s="55"/>
+      <c r="C100" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="77"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="75"/>
-      <c r="B101" s="75"/>
-      <c r="C101" s="77" t="s">
+      <c r="A101" s="55"/>
+      <c r="B101" s="55"/>
+      <c r="C101" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="77"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="75"/>
-      <c r="B102" s="75"/>
-      <c r="C102" s="88" t="s">
+      <c r="A102" s="55"/>
+      <c r="B102" s="55"/>
+      <c r="C102" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="110"/>
+      <c r="D102" s="69"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="75" t="s">
+      <c r="A103" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="75"/>
-      <c r="C103" s="83"/>
-      <c r="D103" s="83"/>
+      <c r="B103" s="55"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="86" t="s">
+      <c r="C104" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="86"/>
+      <c r="D104" s="57"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2996,91 +3007,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="87"/>
-      <c r="C107" s="87"/>
-      <c r="D107" s="87"/>
-      <c r="E107" s="87"/>
+      <c r="B107" s="70"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="72" t="s">
+      <c r="A108" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="72"/>
-      <c r="C108" s="72" t="s">
+      <c r="B108" s="71"/>
+      <c r="C108" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="72"/>
+      <c r="D108" s="71"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="74" t="s">
+      <c r="A109" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="74"/>
-      <c r="C109" s="83"/>
-      <c r="D109" s="83"/>
+      <c r="B109" s="58"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="56"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="91" t="s">
+      <c r="A110" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="92"/>
-      <c r="C110" s="103" t="s">
+      <c r="B110" s="60"/>
+      <c r="C110" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="103"/>
+      <c r="D110" s="65"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="93"/>
-      <c r="B111" s="94"/>
-      <c r="C111" s="111" t="s">
+      <c r="A111" s="61"/>
+      <c r="B111" s="62"/>
+      <c r="C111" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="112"/>
+      <c r="D111" s="67"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="95"/>
-      <c r="B112" s="96"/>
-      <c r="C112" s="88" t="s">
+      <c r="A112" s="63"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="110"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="75" t="s">
+      <c r="A113" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="75"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="83"/>
+      <c r="B113" s="55"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="86" t="s">
+      <c r="C114" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="86"/>
+      <c r="D114" s="57"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6832,35 +6843,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6874,42 +6892,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6949,13 +6960,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7009,7 +7020,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7137,7 +7148,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>6.24</v>
+        <v>66.239999999999995</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7190,13 +7201,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7224,10 +7235,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="100"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7239,10 +7250,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="111"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7254,10 +7265,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7269,10 +7280,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7293,13 +7304,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="94" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7327,10 +7338,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7342,10 +7353,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="87"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7357,36 +7368,42 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="67"/>
+      <c r="D20" s="89"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="108" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="65"/>
+      <c r="D21" s="109"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
+      <c r="A22" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="113" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="112"/>
       <c r="E22" s="29">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7398,7 +7415,7 @@
       </c>
       <c r="E23" s="26">
         <f>SUM(E19:E22)</f>
-        <v>2538.08</v>
+        <v>2598.08</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7406,13 +7423,13 @@
       <c r="B24" s="24"/>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -7440,10 +7457,10 @@
       <c r="B26" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="63"/>
+      <c r="D26" s="95"/>
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
@@ -7455,10 +7472,10 @@
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="61"/>
+      <c r="D27" s="87"/>
       <c r="E27" s="33">
         <v>2485</v>
       </c>
@@ -7466,8 +7483,8 @@
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
       <c r="E28" s="29">
         <v>0</v>
       </c>
@@ -7489,11 +7506,11 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
     </row>
     <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -7508,11 +7525,11 @@
       <c r="D32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
@@ -7558,16 +7575,16 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="70" t="s">
+      <c r="A38" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="70"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
+      <c r="A39" s="86"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="86"/>
     </row>
     <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -7616,11 +7633,11 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="69" t="s">
+      <c r="A45" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="82"/>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
@@ -7655,11 +7672,11 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="69" t="s">
+      <c r="A49" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="69"/>
-      <c r="C49" s="69"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="82"/>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -7683,11 +7700,11 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="69" t="s">
+      <c r="A52" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="69"/>
-      <c r="C52" s="69"/>
+      <c r="B52" s="82"/>
+      <c r="C52" s="82"/>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
@@ -7711,11 +7728,11 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="71" t="s">
+      <c r="A55" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="71"/>
-      <c r="C55" s="71"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
@@ -7792,11 +7809,11 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="71" t="s">
+      <c r="A63" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="71"/>
-      <c r="C63" s="71"/>
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
@@ -7804,7 +7821,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="19">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7823,7 +7840,7 @@
       </c>
       <c r="C66" s="19">
         <f>SUM(C64:C65)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7846,67 +7863,67 @@
       <c r="B69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="72" t="s">
+      <c r="A70" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B70" s="72"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="72"/>
-      <c r="E70" s="72"/>
+      <c r="B70" s="71"/>
+      <c r="C70" s="71"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="71"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="73" t="s">
+      <c r="A71" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="73"/>
-      <c r="C71" s="73" t="s">
+      <c r="B71" s="84"/>
+      <c r="C71" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="73"/>
+      <c r="D71" s="84"/>
       <c r="E71" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="74" t="s">
+      <c r="A72" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="74"/>
-      <c r="C72" s="75"/>
-      <c r="D72" s="75"/>
+      <c r="B72" s="58"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
       <c r="E72" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+      <c r="A73" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77" t="s">
+      <c r="B73" s="74"/>
+      <c r="C73" s="73" t="s">
         <v>122</v>
       </c>
-      <c r="D73" s="77"/>
+      <c r="D73" s="73"/>
       <c r="E73" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="76"/>
-      <c r="B74" s="76"/>
-      <c r="C74" s="78" t="s">
+      <c r="A74" s="74"/>
+      <c r="B74" s="74"/>
+      <c r="C74" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="D74" s="79"/>
+      <c r="D74" s="72"/>
       <c r="E74" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="76"/>
-      <c r="B75" s="76"/>
-      <c r="C75" s="78" t="s">
+      <c r="A75" s="74"/>
+      <c r="B75" s="74"/>
+      <c r="C75" s="107" t="s">
         <v>137</v>
       </c>
       <c r="D75" s="80"/>
@@ -7915,22 +7932,22 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="76" t="s">
+      <c r="A76" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="76"/>
-      <c r="C76" s="81"/>
-      <c r="D76" s="81"/>
+      <c r="B76" s="74"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
       <c r="E76" s="46">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="82" t="s">
+      <c r="C77" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="82"/>
+      <c r="D77" s="76"/>
       <c r="E77" s="47">
         <f>(E15+E72)-SUM(E73:E76)</f>
         <v>24.599999999999909</v>
@@ -7938,105 +7955,105 @@
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="71"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72" t="s">
+      <c r="B80" s="71"/>
+      <c r="C80" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="72"/>
+      <c r="D80" s="71"/>
       <c r="E80" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
+      <c r="B81" s="58"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
       <c r="E81" s="47">
         <f>E77</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="91" t="s">
+      <c r="A82" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="92"/>
-      <c r="C82" s="84" t="s">
+      <c r="B82" s="60"/>
+      <c r="C82" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="85"/>
+      <c r="D82" s="104"/>
       <c r="E82" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="93"/>
-      <c r="B83" s="94"/>
-      <c r="C83" s="77" t="s">
+      <c r="A83" s="61"/>
+      <c r="B83" s="62"/>
+      <c r="C83" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="77"/>
+      <c r="D83" s="73"/>
       <c r="E83" s="48">
         <v>219.9</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="93"/>
-      <c r="B84" s="94"/>
-      <c r="C84" s="88" t="s">
+      <c r="A84" s="61"/>
+      <c r="B84" s="62"/>
+      <c r="C84" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="D84" s="89"/>
+      <c r="D84" s="105"/>
       <c r="E84" s="48">
         <v>258.5</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="90" t="s">
+    <row r="85" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="63"/>
+      <c r="B85" s="64"/>
+      <c r="C85" s="106" t="s">
         <v>142</v>
       </c>
-      <c r="D85" s="89"/>
+      <c r="D85" s="105"/>
       <c r="E85" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="75" t="s">
+      <c r="A86" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="75"/>
-      <c r="C86" s="83"/>
-      <c r="D86" s="83"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="56"/>
       <c r="E86" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="86" t="s">
+      <c r="C87" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D87" s="86"/>
+      <c r="D87" s="57"/>
       <c r="E87" s="47">
         <f>(E23+E81)-SUM(E82:E86)</f>
-        <v>6.2399999999997817</v>
+        <v>66.239999999999782</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8054,72 +8071,72 @@
       <c r="E89" s="49"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="87" t="s">
+      <c r="A90" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="87"/>
-      <c r="C90" s="87"/>
-      <c r="D90" s="87"/>
-      <c r="E90" s="87"/>
+      <c r="B90" s="70"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="70"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B91" s="72"/>
-      <c r="C91" s="72" t="s">
+      <c r="B91" s="71"/>
+      <c r="C91" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D91" s="72"/>
+      <c r="D91" s="71"/>
       <c r="E91" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="74" t="s">
+      <c r="A92" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="B92" s="74"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
+      <c r="B92" s="58"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="56"/>
       <c r="E92" s="47">
         <f>E87</f>
-        <v>6.2399999999997817</v>
+        <v>66.239999999999782</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="75" t="s">
+      <c r="A93" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="B93" s="75"/>
-      <c r="C93" s="77" t="s">
+      <c r="B93" s="55"/>
+      <c r="C93" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="73"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="75" t="s">
+      <c r="A94" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="75"/>
-      <c r="C94" s="83"/>
-      <c r="D94" s="83"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="56"/>
       <c r="E94" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="86" t="s">
+      <c r="C95" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="86"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="47">
         <f>(E29+E92)-SUM(E93:E94)</f>
-        <v>1320.2399999999998</v>
+        <v>1380.2399999999998</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11867,14 +11884,48 @@
       <c r="B1031" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
+  <mergeCells count="59">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A90:E90"/>
@@ -11886,46 +11937,13 @@
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A82:B85"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A73:B75"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E72">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03639D5B-F0F2-114D-91F5-1A0ADD097EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A976F9A-FF4C-A74A-8BFD-856BF1101A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -660,18 +660,34 @@
    ~ OK Store 20/08 - $8.5</t>
   </si>
   <si>
+    <t>2nd September 2026</t>
+  </si>
+  <si>
+    <t>1. Borrow $60</t>
+  </si>
+  <si>
+    <t>~ Payback $60 to Mom</t>
+  </si>
+  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
 ~ Additional transport fees for e-cigarette 20/08 - $50
 ~ Paid Water Supplies Fees 20/08 - $74.1
-~ Round Trip to East Kowloon hospital 31/08 - $4</t>
-  </si>
-  <si>
-    <t>2nd September 2026</t>
-  </si>
-  <si>
-    <t>1. Borrow $60</t>
+~ Round Trip to East Kowloon hospital 31/08 - $4
+~ Round Trip to East Kowloon hospital 03/09 - $4</t>
+  </si>
+  <si>
+    <t>~ Additional transport fees for e-cigarette 17/09 - $50
+~ Round Trip to East Kowloon hospital 02/10 - $4
+~ Revlon color silk 17/09 - $59.9</t>
+  </si>
+  <si>
+    <t>~ Uniqlo (buy $300 - $30 discount)  - 17/09
+    ~ UNISEX CHINO SHORTS (INSEAM 20-23.5cm) 482944 - $99
+    ~ UNISEX REGULAR CHINO PANTS (INSEAM 74-77cm) 482880 / 487213 -$99
+    ~ MEN COTTON BOXER BRIEFS 482598 - $29 x 2
+    ~ MEN BRIEF 486880 - $49</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1199,17 +1215,116 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1229,41 +1344,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1274,107 +1380,23 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1693,13 +1715,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1929,13 +1951,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1963,10 +1985,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="C11" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="100"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1978,10 +2000,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="101"/>
+      <c r="D12" s="98"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1993,10 +2015,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="102"/>
+      <c r="D13" s="99"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2006,10 +2028,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2019,10 +2041,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="87"/>
+      <c r="D15" s="60"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2032,10 +2054,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="C16" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="87"/>
+      <c r="D16" s="60"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2047,10 +2069,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="92"/>
+      <c r="D17" s="100"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2060,10 +2082,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="93"/>
+      <c r="D18" s="101"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2075,10 +2097,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="96"/>
+      <c r="D19" s="102"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2099,13 +2121,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2133,10 +2155,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="97"/>
+      <c r="D23" s="103"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2148,10 +2170,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="87" t="s">
+      <c r="C24" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="87"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2163,10 +2185,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="87" t="s">
+      <c r="C25" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="87"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2176,10 +2198,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="92"/>
+      <c r="D26" s="100"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2191,10 +2213,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="93"/>
+      <c r="D27" s="101"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2204,10 +2226,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="65"/>
+      <c r="D28" s="104"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2229,13 +2251,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2263,10 +2285,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="95" t="s">
+      <c r="C32" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="95"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2278,10 +2300,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="87"/>
+      <c r="D33" s="60"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2291,10 +2313,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="87"/>
+      <c r="D34" s="60"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2304,10 +2326,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="88" t="s">
+      <c r="C35" s="105" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="89"/>
+      <c r="D35" s="66"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2317,10 +2339,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="88" t="s">
+      <c r="C36" s="105" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="90"/>
+      <c r="D36" s="106"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2330,10 +2352,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="91" t="s">
+      <c r="C37" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="87"/>
+      <c r="D37" s="60"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2355,11 +2377,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="85" t="s">
+      <c r="A40" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="85"/>
-      <c r="C40" s="85"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2374,11 +2396,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="82" t="s">
+      <c r="A42" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="82"/>
-      <c r="C42" s="82"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2424,16 +2446,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="86"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
+      <c r="A48" s="71"/>
+      <c r="B48" s="71"/>
+      <c r="C48" s="71"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2482,11 +2504,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="82" t="s">
+      <c r="A54" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="82"/>
-      <c r="C54" s="82"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2521,11 +2543,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="82" t="s">
+      <c r="A58" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2549,11 +2571,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="82" t="s">
+      <c r="A61" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="82"/>
-      <c r="C61" s="82"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2577,11 +2599,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="83" t="s">
+      <c r="A64" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="83"/>
-      <c r="C64" s="83"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="72"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2658,11 +2680,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="83"/>
-      <c r="C72" s="83"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="72"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2712,167 +2734,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="71"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="84"/>
-      <c r="C80" s="84" t="s">
+      <c r="B80" s="74"/>
+      <c r="C80" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="84"/>
+      <c r="D80" s="74"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="77" t="s">
+      <c r="A81" s="107" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="77"/>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
+      <c r="B81" s="107"/>
+      <c r="C81" s="76"/>
+      <c r="D81" s="76"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="55" t="s">
+      <c r="A82" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="55"/>
-      <c r="C82" s="78" t="s">
+      <c r="B82" s="76"/>
+      <c r="C82" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="78"/>
+      <c r="D82" s="108"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="55"/>
-      <c r="B83" s="55"/>
-      <c r="C83" s="78" t="s">
+      <c r="A83" s="76"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="78"/>
+      <c r="D83" s="108"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="55"/>
-      <c r="B84" s="55"/>
-      <c r="C84" s="78" t="s">
+      <c r="A84" s="76"/>
+      <c r="B84" s="76"/>
+      <c r="C84" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="78"/>
+      <c r="D84" s="108"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="55"/>
-      <c r="B85" s="55"/>
-      <c r="C85" s="79" t="s">
+      <c r="A85" s="76"/>
+      <c r="B85" s="76"/>
+      <c r="C85" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="79"/>
+      <c r="D85" s="109"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="55"/>
-      <c r="B86" s="55"/>
-      <c r="C86" s="80" t="s">
+      <c r="A86" s="76"/>
+      <c r="B86" s="76"/>
+      <c r="C86" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="80"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="55"/>
-      <c r="B87" s="55"/>
-      <c r="C87" s="79" t="s">
+      <c r="A87" s="76"/>
+      <c r="B87" s="76"/>
+      <c r="C87" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="79"/>
+      <c r="D87" s="109"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="55"/>
-      <c r="B88" s="55"/>
-      <c r="C88" s="78" t="s">
+      <c r="A88" s="76"/>
+      <c r="B88" s="76"/>
+      <c r="C88" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="78"/>
+      <c r="D88" s="108"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="55"/>
-      <c r="B89" s="55"/>
-      <c r="C89" s="80" t="s">
+      <c r="A89" s="76"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="80"/>
+      <c r="D89" s="81"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="55"/>
-      <c r="B90" s="55"/>
-      <c r="C90" s="80" t="s">
+      <c r="A90" s="76"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="80"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="55"/>
-      <c r="B91" s="55"/>
-      <c r="C91" s="81" t="s">
+      <c r="A91" s="76"/>
+      <c r="B91" s="76"/>
+      <c r="C91" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="81"/>
+      <c r="D91" s="110"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="74" t="s">
+      <c r="A92" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="74"/>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="76"/>
+      <c r="D93" s="83"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2880,113 +2902,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="71" t="s">
+      <c r="A95" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="71"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="71"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="71" t="s">
+      <c r="A96" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="71"/>
-      <c r="C96" s="71" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="71"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="58" t="s">
+      <c r="A97" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="58"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
+      <c r="B97" s="75"/>
+      <c r="C97" s="84"/>
+      <c r="D97" s="84"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="55" t="s">
+      <c r="A98" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="55"/>
-      <c r="C98" s="72" t="s">
+      <c r="B98" s="76"/>
+      <c r="C98" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="72"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="55"/>
-      <c r="B99" s="55"/>
-      <c r="C99" s="73" t="s">
+      <c r="A99" s="76"/>
+      <c r="B99" s="76"/>
+      <c r="C99" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="78"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="55"/>
-      <c r="B100" s="55"/>
-      <c r="C100" s="73" t="s">
+      <c r="A100" s="76"/>
+      <c r="B100" s="76"/>
+      <c r="C100" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="78"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="55"/>
-      <c r="B101" s="55"/>
-      <c r="C101" s="73" t="s">
+      <c r="A101" s="76"/>
+      <c r="B101" s="76"/>
+      <c r="C101" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="73"/>
+      <c r="D101" s="78"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="55"/>
-      <c r="B102" s="55"/>
-      <c r="C102" s="68" t="s">
+      <c r="A102" s="76"/>
+      <c r="B102" s="76"/>
+      <c r="C102" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="69"/>
+      <c r="D102" s="111"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="55" t="s">
+      <c r="A103" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="55"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
+      <c r="B103" s="76"/>
+      <c r="C103" s="84"/>
+      <c r="D103" s="84"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="57"/>
+      <c r="D104" s="87"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3007,91 +3029,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="70" t="s">
+      <c r="A107" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="70"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="70"/>
-      <c r="E107" s="70"/>
+      <c r="B107" s="88"/>
+      <c r="C107" s="88"/>
+      <c r="D107" s="88"/>
+      <c r="E107" s="88"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="71" t="s">
+      <c r="A108" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="71"/>
-      <c r="C108" s="71" t="s">
+      <c r="B108" s="73"/>
+      <c r="C108" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="71"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="58"/>
-      <c r="C109" s="56"/>
-      <c r="D109" s="56"/>
+      <c r="B109" s="75"/>
+      <c r="C109" s="84"/>
+      <c r="D109" s="84"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="59" t="s">
+      <c r="A110" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="60"/>
-      <c r="C110" s="65" t="s">
+      <c r="B110" s="93"/>
+      <c r="C110" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="65"/>
+      <c r="D110" s="104"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="61"/>
-      <c r="B111" s="62"/>
-      <c r="C111" s="66" t="s">
+      <c r="A111" s="94"/>
+      <c r="B111" s="95"/>
+      <c r="C111" s="112" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="67"/>
+      <c r="D111" s="113"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="63"/>
-      <c r="B112" s="64"/>
-      <c r="C112" s="68" t="s">
+      <c r="A112" s="96"/>
+      <c r="B112" s="97"/>
+      <c r="C112" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="111"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="55" t="s">
+      <c r="A113" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="55"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="56"/>
+      <c r="B113" s="76"/>
+      <c r="C113" s="84"/>
+      <c r="D113" s="84"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="57" t="s">
+      <c r="C114" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="57"/>
+      <c r="D114" s="87"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6843,42 +6865,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6892,35 +6907,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6945,7 +6967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y1031"/>
+  <dimension ref="A1:Y1034"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -6960,13 +6982,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7201,13 +7223,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7235,10 +7257,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="C11" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="100"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7250,10 +7272,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="111"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7265,10 +7287,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="87"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7280,10 +7302,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7304,13 +7326,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7338,10 +7360,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7353,10 +7375,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="87"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7368,10 +7390,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="110" t="s">
+      <c r="C20" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="89"/>
+      <c r="D20" s="66"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7383,25 +7405,25 @@
       <c r="B21" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="108" t="s">
+      <c r="C21" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="109"/>
+      <c r="D21" s="64"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="113" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="112"/>
+      <c r="C22" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="68"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7423,13 +7445,13 @@
       <c r="B24" s="24"/>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -7457,10 +7479,10 @@
       <c r="B26" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="95"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
@@ -7472,10 +7494,10 @@
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="87" t="s">
+      <c r="C27" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="87"/>
+      <c r="D27" s="60"/>
       <c r="E27" s="33">
         <v>2485</v>
       </c>
@@ -7483,8 +7505,8 @@
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="87"/>
-      <c r="D28" s="87"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
       <c r="E28" s="29">
         <v>0</v>
       </c>
@@ -7506,11 +7528,11 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="85" t="s">
+      <c r="A31" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
     </row>
     <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -7525,11 +7547,11 @@
       <c r="D32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="82" t="s">
+      <c r="A33" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
     </row>
     <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
@@ -7575,16 +7597,16 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="86" t="s">
+      <c r="A38" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="86"/>
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
+      <c r="A39" s="71"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
     </row>
     <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -7633,11 +7655,11 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="82" t="s">
+      <c r="A45" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="82"/>
-      <c r="C45" s="82"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
@@ -7672,11 +7694,11 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="82" t="s">
+      <c r="A49" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="82"/>
-      <c r="C49" s="82"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="70"/>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -7700,11 +7722,11 @@
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="82"/>
-      <c r="C52" s="82"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
@@ -7728,11 +7750,11 @@
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="83" t="s">
+      <c r="A55" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="83"/>
-      <c r="C55" s="83"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="72"/>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="17" t="s">
@@ -7809,11 +7831,11 @@
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="83" t="s">
+      <c r="A63" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="83"/>
-      <c r="C63" s="83"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="72"/>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
@@ -7863,91 +7885,91 @@
       <c r="B69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="71" t="s">
+      <c r="A70" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="B70" s="71"/>
-      <c r="C70" s="71"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="84" t="s">
+      <c r="A71" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="84"/>
-      <c r="C71" s="84" t="s">
+      <c r="B71" s="74"/>
+      <c r="C71" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="84"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="58" t="s">
+      <c r="A72" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="58"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
+      <c r="B72" s="75"/>
+      <c r="C72" s="76"/>
+      <c r="D72" s="76"/>
       <c r="E72" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="74" t="s">
+      <c r="A73" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="74"/>
-      <c r="C73" s="73" t="s">
+      <c r="B73" s="77"/>
+      <c r="C73" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="D73" s="73"/>
+      <c r="D73" s="78"/>
       <c r="E73" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="74"/>
-      <c r="B74" s="74"/>
-      <c r="C74" s="107" t="s">
+      <c r="A74" s="77"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="D74" s="72"/>
+      <c r="D74" s="80"/>
       <c r="E74" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="74"/>
-      <c r="B75" s="74"/>
-      <c r="C75" s="107" t="s">
+      <c r="A75" s="77"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="80"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="74" t="s">
+      <c r="A76" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="74"/>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
       <c r="E76" s="46">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="76" t="s">
+      <c r="C77" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="76"/>
+      <c r="D77" s="83"/>
       <c r="E77" s="47">
         <f>(E15+E72)-SUM(E73:E76)</f>
         <v>24.599999999999909</v>
@@ -7955,105 +7977,105 @@
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="71"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71" t="s">
+      <c r="B80" s="73"/>
+      <c r="C80" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="71"/>
+      <c r="D80" s="73"/>
       <c r="E80" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="58" t="s">
+      <c r="A81" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="58"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="84"/>
+      <c r="D81" s="84"/>
       <c r="E81" s="47">
         <f>E77</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="59" t="s">
+      <c r="A82" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="60"/>
-      <c r="C82" s="103" t="s">
+      <c r="B82" s="93"/>
+      <c r="C82" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="104"/>
+      <c r="D82" s="86"/>
       <c r="E82" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="61"/>
-      <c r="B83" s="62"/>
-      <c r="C83" s="73" t="s">
+      <c r="A83" s="94"/>
+      <c r="B83" s="95"/>
+      <c r="C83" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="73"/>
+      <c r="D83" s="78"/>
       <c r="E83" s="48">
         <v>219.9</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="61"/>
-      <c r="B84" s="62"/>
-      <c r="C84" s="68" t="s">
-        <v>144</v>
-      </c>
-      <c r="D84" s="105"/>
+    <row r="84" spans="1:5" ht="143" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="94"/>
+      <c r="B84" s="95"/>
+      <c r="C84" s="89" t="s">
+        <v>147</v>
+      </c>
+      <c r="D84" s="90"/>
       <c r="E84" s="48">
-        <v>258.5</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="63"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="106" t="s">
+      <c r="A85" s="96"/>
+      <c r="B85" s="97"/>
+      <c r="C85" s="91" t="s">
         <v>142</v>
       </c>
-      <c r="D85" s="105"/>
+      <c r="D85" s="90"/>
       <c r="E85" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="55" t="s">
+      <c r="A86" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="55"/>
-      <c r="C86" s="56"/>
-      <c r="D86" s="56"/>
+      <c r="B86" s="76"/>
+      <c r="C86" s="84"/>
+      <c r="D86" s="84"/>
       <c r="E86" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="57" t="s">
+      <c r="C87" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D87" s="57"/>
+      <c r="D87" s="87"/>
       <c r="E87" s="47">
         <f>(E23+E81)-SUM(E82:E86)</f>
-        <v>66.239999999999782</v>
+        <v>62.239999999999782</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8070,140 +8092,161 @@
       <c r="D89" s="49"/>
       <c r="E89" s="49"/>
     </row>
-    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="70" t="s">
+    <row r="90" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="70"/>
-      <c r="C90" s="70"/>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
+      <c r="B90" s="88"/>
+      <c r="C90" s="88"/>
+      <c r="D90" s="88"/>
+      <c r="E90" s="88"/>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71" t="s">
+      <c r="B91" s="73"/>
+      <c r="C91" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D91" s="71"/>
+      <c r="D91" s="73"/>
       <c r="E91" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="58" t="s">
+    <row r="92" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="B92" s="58"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="56"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="84"/>
       <c r="E92" s="47">
         <f>E87</f>
-        <v>66.239999999999782</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="55" t="s">
+        <v>62.239999999999782</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="B93" s="55"/>
-      <c r="C93" s="73" t="s">
+      <c r="B93" s="93"/>
+      <c r="C93" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D93" s="78"/>
+      <c r="E93" s="45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="94"/>
+      <c r="B94" s="95"/>
+      <c r="C94" s="114" t="s">
         <v>118</v>
       </c>
-      <c r="D93" s="73"/>
-      <c r="E93" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="55" t="s">
+      <c r="D94" s="115"/>
+      <c r="E94" s="45">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="94"/>
+      <c r="B95" s="95"/>
+      <c r="C95" s="114" t="s">
+        <v>148</v>
+      </c>
+      <c r="D95" s="115"/>
+      <c r="E95" s="45">
+        <v>113.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="92" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="96"/>
+      <c r="B96" s="97"/>
+      <c r="C96" s="114" t="s">
+        <v>149</v>
+      </c>
+      <c r="D96" s="115"/>
+      <c r="E96" s="45">
+        <v>274.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="55"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="45">
+      <c r="B97" s="76"/>
+      <c r="C97" s="84"/>
+      <c r="D97" s="84"/>
+      <c r="E97" s="45">
         <f>C67</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="57" t="s">
+    <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C98" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="57"/>
-      <c r="E95" s="47">
-        <f>(E29+E92)-SUM(E93:E94)</f>
-        <v>1380.2399999999998</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="24"/>
-      <c r="B96" s="24"/>
-    </row>
-    <row r="97" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="24"/>
-      <c r="B97" s="24"/>
-    </row>
-    <row r="98" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="24"/>
-      <c r="B98" s="24"/>
-    </row>
-    <row r="99" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D98" s="87"/>
+      <c r="E98" s="47">
+        <f>(E29+E92)-SUM(E93:E97)</f>
+        <v>127.83999999999969</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="24"/>
       <c r="B99" s="24"/>
     </row>
-    <row r="100" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="24"/>
       <c r="B100" s="24"/>
     </row>
-    <row r="101" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="24"/>
       <c r="B101" s="24"/>
     </row>
-    <row r="102" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="24"/>
       <c r="B102" s="24"/>
     </row>
-    <row r="103" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="24"/>
       <c r="B103" s="24"/>
     </row>
-    <row r="104" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="24"/>
       <c r="B104" s="24"/>
     </row>
-    <row r="105" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="24"/>
       <c r="B105" s="24"/>
     </row>
-    <row r="106" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="24"/>
       <c r="B106" s="24"/>
     </row>
-    <row r="107" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="24"/>
       <c r="B107" s="24"/>
     </row>
-    <row r="108" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="24"/>
       <c r="B108" s="24"/>
     </row>
-    <row r="109" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="24"/>
       <c r="B109" s="24"/>
     </row>
-    <row r="110" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="24"/>
       <c r="B110" s="24"/>
     </row>
-    <row r="111" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="24"/>
       <c r="B111" s="24"/>
     </row>
-    <row r="112" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="24"/>
       <c r="B112" s="24"/>
     </row>
@@ -11883,49 +11926,30 @@
       <c r="A1031" s="24"/>
       <c r="B1031" s="24"/>
     </row>
+    <row r="1032" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1032" s="24"/>
+      <c r="B1032" s="24"/>
+    </row>
+    <row r="1033" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1033" s="24"/>
+      <c r="B1033" s="24"/>
+    </row>
+    <row r="1034" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1034" s="24"/>
+      <c r="B1034" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B75"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
+  <mergeCells count="62">
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A93:B96"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A90:E90"/>
@@ -11937,13 +11961,47 @@
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A82:B85"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E72">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
@@ -11953,7 +12011,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E77 E81 E87 E92 E95">
+  <conditionalFormatting sqref="E77 E81 E87 E92 E98">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A976F9A-FF4C-A74A-8BFD-856BF1101A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F833D720-4424-B845-AD52-C535F3C36006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="152">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -543,10 +543,6 @@
    ~ Best Mart 360 16/07 - $25</t>
   </si>
   <si>
-    <t>~ Food
-~ Snack And Drinks</t>
-  </si>
-  <si>
     <t>1. Payback For Clothes Washing Detergent.
 2. Borrow $100 from Mom.</t>
   </si>
@@ -597,9 +593,6 @@
   </si>
   <si>
     <t>20th August 2026</t>
-  </si>
-  <si>
-    <t>20th September 2026</t>
   </si>
   <si>
     <t>1. Borrow $100
@@ -624,10 +617,6 @@
    ~ HKTVmall 18/08 - $670.4</t>
   </si>
   <si>
-    <t>~ Payback $100 to Mom
-~ Payback $670.4 to Mom (HKTVmall Online Shopping)</t>
-  </si>
-  <si>
     <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
 ~ Additional transport fees for e-cigarette 20/07 - $40
 ~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
@@ -650,9 +639,6 @@
     <t>A discount of $3.08 for iHerb payment</t>
   </si>
   <si>
-    <t>~ iHerb Aveeno Lotion 23/08 - $136.64</t>
-  </si>
-  <si>
     <t>Partial Food And Snack Prepaid on the Previous Month
 ~ Food
    ~ HKTV mall 24/08 - $211.4
@@ -664,9 +650,6 @@
   </si>
   <si>
     <t>1. Borrow $60</t>
-  </si>
-  <si>
-    <t>~ Payback $60 to Mom</t>
   </si>
   <si>
     <t>~ Debit For Octopus Card ($50). 20/08
@@ -678,16 +661,40 @@
 ~ Round Trip to East Kowloon hospital 03/09 - $4</t>
   </si>
   <si>
+    <t>18th September 2026</t>
+  </si>
+  <si>
+    <t>3rd September 2026</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>1. A gift for birthday $1000 from Lawrence</t>
+  </si>
+  <si>
+    <t>~ Payback $100 to Mom
+~ Payback $670.4 to Mom (HKTVmall Online Shopping)
+~ Payback $60 to Mom</t>
+  </si>
+  <si>
+    <t>~ Uniqlo (buy $300 - $30 discount)  - 03/09
+    ~ UNISEX EZY BARREL JEANS (INSEAM 72-78cm) 488630 / 492035 -$299
+    ~ UNISEX ULTRA STRETCH ACTIVE SHORTS (INSEAM 18-21.5cm) 482317 - $99
+    ~ MEN COTTON BOXER BRIEFS 482600- $29 x 2</t>
+  </si>
+  <si>
+    <t>~ Food
+   ~ HKTV mall 17/09 - $574.59
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>~ iHerb Aveeno Lotion 23/08 - $136.64
+~ Watsons Revlon color silk 17/09 - $59.9</t>
+  </si>
+  <si>
     <t>~ Additional transport fees for e-cigarette 17/09 - $50
-~ Round Trip to East Kowloon hospital 02/10 - $4
-~ Revlon color silk 17/09 - $59.9</t>
-  </si>
-  <si>
-    <t>~ Uniqlo (buy $300 - $30 discount)  - 17/09
-    ~ UNISEX CHINO SHORTS (INSEAM 20-23.5cm) 482944 - $99
-    ~ UNISEX REGULAR CHINO PANTS (INSEAM 74-77cm) 482880 / 487213 -$99
-    ~ MEN COTTON BOXER BRIEFS 482598 - $29 x 2
-    ~ MEN BRIEF 486880 - $49</t>
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1215,29 +1222,104 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1257,97 +1339,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1362,41 +1396,17 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1715,13 +1725,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1742,7 +1752,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>0</v>
+        <v>455.54</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1835,7 +1845,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>1.44</v>
+        <v>59.9</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1898,7 +1908,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>66.239999999999995</v>
+        <v>580.2399999999999</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1951,13 +1961,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1985,10 +1995,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="57"/>
+      <c r="D11" s="96"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2000,10 +2010,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="98"/>
+      <c r="D12" s="113"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2015,10 +2025,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="99"/>
+      <c r="D13" s="114"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2028,10 +2038,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="60"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2041,10 +2051,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="60"/>
+      <c r="D15" s="85"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2054,10 +2064,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="85"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2069,10 +2079,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="100" t="s">
+      <c r="C17" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="100"/>
+      <c r="D17" s="109"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2082,10 +2092,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="101"/>
+      <c r="D18" s="110"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2097,10 +2107,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="102"/>
+      <c r="D19" s="111"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2121,13 +2131,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2155,10 +2165,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="103"/>
+      <c r="D23" s="112"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2170,10 +2180,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="60"/>
+      <c r="D24" s="85"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2185,10 +2195,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="60"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2198,10 +2208,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="100"/>
+      <c r="D26" s="109"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2213,10 +2223,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="101"/>
+      <c r="D27" s="110"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2226,10 +2236,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="104" t="s">
+      <c r="C28" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="104"/>
+      <c r="D28" s="99"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2251,13 +2261,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2285,10 +2295,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="62"/>
+      <c r="D32" s="84"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2300,10 +2310,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="60" t="s">
+      <c r="C33" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="60"/>
+      <c r="D33" s="85"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2313,10 +2323,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="60"/>
+      <c r="D34" s="85"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2326,10 +2336,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="105" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="66"/>
+      <c r="C35" s="107" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="91"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2339,10 +2349,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="105" t="s">
+      <c r="C36" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="106"/>
+      <c r="D36" s="108"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2352,10 +2362,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="60"/>
+      <c r="C37" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="85"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2377,11 +2387,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2396,11 +2406,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2446,16 +2456,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="71" t="s">
+      <c r="A47" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
+      <c r="B47" s="82"/>
+      <c r="C47" s="82"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="71"/>
-      <c r="B48" s="71"/>
-      <c r="C48" s="71"/>
+      <c r="A48" s="82"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="82"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2504,11 +2514,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="70" t="s">
+      <c r="A54" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2543,11 +2553,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="70" t="s">
+      <c r="A58" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2571,11 +2581,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="83"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2599,11 +2609,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="72"/>
-      <c r="C64" s="72"/>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2680,11 +2690,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="72" t="s">
+      <c r="A72" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="72"/>
-      <c r="C72" s="72"/>
+      <c r="B72" s="80"/>
+      <c r="C72" s="80"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2734,167 +2744,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
+      <c r="A79" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="B79" s="71"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="71"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74" t="s">
+      <c r="B80" s="81"/>
+      <c r="C80" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="74"/>
+      <c r="D80" s="81"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="107" t="s">
+      <c r="A81" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="107"/>
-      <c r="C81" s="76"/>
-      <c r="D81" s="76"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="76" t="s">
+      <c r="A82" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="76"/>
-      <c r="C82" s="108" t="s">
+      <c r="B82" s="59"/>
+      <c r="C82" s="104" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="108"/>
+      <c r="D82" s="104"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="76"/>
-      <c r="B83" s="76"/>
-      <c r="C83" s="108" t="s">
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="108"/>
+      <c r="D83" s="104"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="76"/>
-      <c r="B84" s="76"/>
-      <c r="C84" s="108" t="s">
+      <c r="A84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="108"/>
+      <c r="D84" s="104"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="76"/>
-      <c r="B85" s="76"/>
-      <c r="C85" s="109" t="s">
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="109"/>
+      <c r="D85" s="105"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="76"/>
-      <c r="B86" s="76"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="81"/>
+      <c r="D86" s="78"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="76"/>
-      <c r="B87" s="76"/>
-      <c r="C87" s="109" t="s">
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="105" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="109"/>
+      <c r="D87" s="105"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="76"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="108" t="s">
+      <c r="A88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="108"/>
+      <c r="D88" s="104"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="76"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="81" t="s">
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="81"/>
+      <c r="D89" s="78"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="76"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="81"/>
+      <c r="D90" s="78"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="76"/>
-      <c r="B91" s="76"/>
-      <c r="C91" s="110" t="s">
+      <c r="A91" s="59"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="110"/>
+      <c r="D91" s="106"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="77" t="s">
+      <c r="A92" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="77"/>
-      <c r="C92" s="82"/>
-      <c r="D92" s="82"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="79"/>
+      <c r="D92" s="79"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="83" t="s">
+      <c r="C93" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="83"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2902,113 +2912,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="B95" s="73"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="73"/>
-      <c r="E95" s="73"/>
+      <c r="A95" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" s="71"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="71"/>
+      <c r="E95" s="71"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="73"/>
-      <c r="C96" s="73" t="s">
+      <c r="B96" s="71"/>
+      <c r="C96" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="73"/>
+      <c r="D96" s="71"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="75" t="s">
+      <c r="A97" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="75"/>
-      <c r="C97" s="84"/>
-      <c r="D97" s="84"/>
+      <c r="B97" s="56"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="76" t="s">
+      <c r="A98" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="76"/>
-      <c r="C98" s="80" t="s">
+      <c r="B98" s="59"/>
+      <c r="C98" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="80"/>
+      <c r="D98" s="77"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="76"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="78" t="s">
+      <c r="A99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="78"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="76"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="78" t="s">
+      <c r="A100" s="59"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="78"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="76"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="78" t="s">
+      <c r="A101" s="59"/>
+      <c r="B101" s="59"/>
+      <c r="C101" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="78"/>
+      <c r="D101" s="58"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="76"/>
-      <c r="B102" s="76"/>
-      <c r="C102" s="89" t="s">
+      <c r="A102" s="59"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="111"/>
+      <c r="D102" s="102"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="76" t="s">
+      <c r="A103" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="76"/>
-      <c r="C103" s="84"/>
-      <c r="D103" s="84"/>
+      <c r="B103" s="59"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="87" t="s">
+      <c r="C104" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="87"/>
+      <c r="D104" s="55"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3029,91 +3039,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="88" t="s">
-        <v>128</v>
-      </c>
-      <c r="B107" s="88"/>
-      <c r="C107" s="88"/>
-      <c r="D107" s="88"/>
-      <c r="E107" s="88"/>
+      <c r="A107" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B107" s="70"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="73" t="s">
+      <c r="A108" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="73"/>
-      <c r="C108" s="73" t="s">
+      <c r="B108" s="71"/>
+      <c r="C108" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="73"/>
+      <c r="D108" s="71"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="75" t="s">
+      <c r="A109" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="75"/>
-      <c r="C109" s="84"/>
-      <c r="D109" s="84"/>
+      <c r="B109" s="56"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="57"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="92" t="s">
+      <c r="A110" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="93"/>
-      <c r="C110" s="104" t="s">
+      <c r="B110" s="61"/>
+      <c r="C110" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="104"/>
+      <c r="D110" s="99"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="94"/>
-      <c r="B111" s="95"/>
-      <c r="C111" s="112" t="s">
+      <c r="A111" s="62"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="113"/>
+      <c r="D111" s="101"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="96"/>
-      <c r="B112" s="97"/>
-      <c r="C112" s="89" t="s">
-        <v>121</v>
-      </c>
-      <c r="D112" s="111"/>
+      <c r="A112" s="64"/>
+      <c r="B112" s="65"/>
+      <c r="C112" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="102"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="76" t="s">
+      <c r="A113" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="76"/>
-      <c r="C113" s="84"/>
-      <c r="D113" s="84"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="87" t="s">
+      <c r="C114" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="87"/>
+      <c r="D114" s="55"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6865,35 +6875,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6907,42 +6924,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6967,7 +6977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y1034"/>
+  <dimension ref="A1:Y1035"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -6982,13 +6992,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7010,7 +7020,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>0</v>
+        <v>455.54</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7106,7 +7116,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>1.44</v>
+        <v>59.9</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7170,7 +7180,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>66.239999999999995</v>
+        <v>580.2399999999999</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7223,13 +7233,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7257,10 +7267,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="57"/>
+      <c r="D11" s="96"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7272,40 +7282,40 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="58"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="60"/>
+      <c r="C13" s="85" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="85"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="60"/>
+      <c r="C14" s="98" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="85"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7326,13 +7336,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7360,441 +7370,445 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="84"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="60"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="D20" s="66"/>
+      <c r="C20" s="90" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="91"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="64"/>
+        <v>137</v>
+      </c>
+      <c r="C21" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="89"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="68"/>
+      <c r="C22" s="90" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="91"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="26">
-        <f>SUM(E19:E22)</f>
-        <v>2598.08</v>
+      <c r="A23" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="93"/>
+      <c r="E23" s="29">
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
       <c r="B24" s="24"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="26">
+        <f>SUM(E19:E23)</f>
+        <v>3598.08</v>
+      </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+    </row>
+    <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-    </row>
-    <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="31" t="s">
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+    </row>
+    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C27" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="62"/>
-      <c r="E26" s="2" t="s">
+      <c r="D27" s="84"/>
+      <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="6" t="s">
+    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="C28" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="60"/>
-      <c r="E27" s="33">
+      <c r="D28" s="85"/>
+      <c r="E28" s="33">
         <v>2485</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="29">
+    <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="35">
-        <f>SUM(E27:E28)</f>
-        <v>2485</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="24"/>
       <c r="B30" s="24"/>
-    </row>
-    <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="69" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="35">
+        <f>SUM(E28:E29)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+    </row>
+    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-    </row>
-    <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+    </row>
+    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C33" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="37"/>
-    </row>
-    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="70" t="s">
+      <c r="D33" s="37"/>
+    </row>
+    <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-    </row>
-    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="50" t="s">
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+    </row>
+    <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="50" t="s">
+      <c r="B35" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C35" s="33">
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="17" t="s">
+    <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B36" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C36" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
+    <row r="37" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B37" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="38">
+      <c r="C37" s="38">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="6" t="s">
+    <row r="38" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="7"/>
+      <c r="B38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="39">
-        <f>SUM(C34:C36)</f>
+      <c r="C38" s="39">
+        <f>SUM(C35:C37)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="71" t="s">
+    <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-    </row>
-    <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="71"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-    </row>
-    <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+    </row>
+    <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="82"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+    </row>
+    <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="29">
+      <c r="B41" s="6"/>
+      <c r="C41" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+    <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6" t="s">
+    <row r="44" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="39">
-        <f>SUM(C40:C43)</f>
+      <c r="C45" s="39">
+        <f>SUM(C41:C44)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="70" t="s">
+    <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-    </row>
-    <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+    </row>
+    <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="C46" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="C47" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="6"/>
+    <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="B48" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="39">
-        <f>SUM(C46:C47)</f>
+      <c r="C49" s="39">
+        <f>SUM(C47:C48)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="70" t="s">
+    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="70"/>
-      <c r="C49" s="70"/>
-    </row>
-    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="B50" s="83"/>
+      <c r="C50" s="83"/>
+    </row>
+    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17" t="s">
+    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="39">
-        <f>SUM(C50)</f>
+      <c r="C52" s="39">
+        <f>SUM(C51)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="70" t="s">
+    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="70"/>
-      <c r="C52" s="70"/>
-    </row>
-    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+      <c r="B53" s="83"/>
+      <c r="C53" s="83"/>
+    </row>
+    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B54" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
+    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="39">
-        <f>SUM(C53)</f>
+      <c r="C55" s="39">
+        <f>SUM(C54)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="72" t="s">
+    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="72"/>
-      <c r="C55" s="72"/>
-    </row>
-    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17" t="s">
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+    </row>
+    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="40">
+      <c r="C57" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
+    <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B59" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C58" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="C59" s="29">
         <v>0</v>
@@ -7802,401 +7816,406 @@
     </row>
     <row r="60" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="29">
+      <c r="B61" s="6"/>
+      <c r="C61" s="29">
         <v>55</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
+    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B62" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C61" s="19">
+      <c r="C62" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7" t="s">
+    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C62" s="39">
-        <f>SUM(C56:C61)</f>
+      <c r="C63" s="39">
+        <f>SUM(C57:C62)</f>
         <v>955</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="72" t="s">
+    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="72"/>
-      <c r="C63" s="72"/>
-    </row>
-    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="19">
-        <v>60</v>
-      </c>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7" t="s">
+    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="19">
-        <f>SUM(C64:C65)</f>
+      <c r="C67" s="19">
+        <f>SUM(C65:C66)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="6"/>
-      <c r="B67" s="34" t="s">
+    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6"/>
+      <c r="B68" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C67" s="41">
-        <f>C37+C44+C48+C51+C54+C62</f>
+      <c r="C68" s="41">
+        <f>C38+C45+C49+C52+C55+C63</f>
         <v>1171</v>
       </c>
-      <c r="H67" s="42"/>
-    </row>
-    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="24"/>
-      <c r="B68" s="24"/>
+      <c r="H68" s="42"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="24"/>
       <c r="B69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="B70" s="73"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" s="71"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="71"/>
+    </row>
+    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74" t="s">
+      <c r="B72" s="81"/>
+      <c r="C72" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="44" t="s">
+      <c r="D72" s="81"/>
+      <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="75" t="s">
+    <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="B72" s="75"/>
-      <c r="C72" s="76"/>
-      <c r="D72" s="76"/>
-      <c r="E72" s="47">
+      <c r="B73" s="56"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="77" t="s">
+    <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="77"/>
-      <c r="C73" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="D73" s="78"/>
-      <c r="E73" s="45">
+      <c r="B74" s="75"/>
+      <c r="C74" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="58"/>
+      <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="77"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="D74" s="80"/>
-      <c r="E74" s="45">
+    <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="75"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D75" s="77"/>
+      <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="77"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="D75" s="81"/>
-      <c r="E75" s="45">
+    <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="75"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="78"/>
+      <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="77" t="s">
+    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B76" s="77"/>
-      <c r="C76" s="82"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="46">
-        <f>C67</f>
+      <c r="B77" s="75"/>
+      <c r="C77" s="79"/>
+      <c r="D77" s="79"/>
+      <c r="E77" s="46">
+        <f>C68</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C77" s="83" t="s">
+    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="D77" s="83"/>
-      <c r="E77" s="47">
-        <f>(E15+E72)-SUM(E73:E76)</f>
+      <c r="D78" s="74"/>
+      <c r="E78" s="47">
+        <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="73" t="s">
+    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
+    </row>
+    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="71"/>
+      <c r="C81" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="71"/>
+      <c r="E81" s="43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82" s="56"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="47">
+        <f>E78</f>
+        <v>24.599999999999909</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" s="61"/>
+      <c r="C83" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="D83" s="69"/>
+      <c r="E83" s="48">
+        <v>830.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="62"/>
+      <c r="B84" s="63"/>
+      <c r="C84" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="58"/>
+      <c r="E84" s="48">
+        <v>219.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="125" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="62"/>
+      <c r="B85" s="63"/>
+      <c r="C85" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="D85" s="73"/>
+      <c r="E85" s="48">
+        <v>258.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="62"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D86" s="115"/>
+      <c r="E86" s="48">
+        <v>136.63999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="64"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="D87" s="73"/>
+      <c r="E87" s="116">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="59"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="45">
+        <f>C68</f>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" s="55"/>
+      <c r="E89" s="47">
+        <f>(E24+E82)-SUM(E83:E88)</f>
+        <v>580.23999999999978</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="49"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="49"/>
+      <c r="E90" s="49"/>
+    </row>
+    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="49"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="49"/>
+      <c r="E91" s="49"/>
+    </row>
+    <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
-    </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="73" t="s">
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="70"/>
+    </row>
+    <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73" t="s">
+      <c r="B93" s="71"/>
+      <c r="C93" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="73"/>
-      <c r="E80" s="43" t="s">
+      <c r="D93" s="71"/>
+      <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="B81" s="75"/>
-      <c r="C81" s="84"/>
-      <c r="D81" s="84"/>
-      <c r="E81" s="47">
-        <f>E77</f>
-        <v>24.599999999999909</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="92" t="s">
+    <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B94" s="56"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="47">
+        <f>E89</f>
+        <v>580.23999999999978</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="93"/>
-      <c r="C82" s="85" t="s">
-        <v>136</v>
-      </c>
-      <c r="D82" s="86"/>
-      <c r="E82" s="48">
-        <v>770.4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="94"/>
-      <c r="B83" s="95"/>
-      <c r="C83" s="78" t="s">
-        <v>143</v>
-      </c>
-      <c r="D83" s="78"/>
-      <c r="E83" s="48">
-        <v>219.9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="143" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="94"/>
-      <c r="B84" s="95"/>
-      <c r="C84" s="89" t="s">
-        <v>147</v>
-      </c>
-      <c r="D84" s="90"/>
-      <c r="E84" s="48">
-        <v>262.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="96"/>
-      <c r="B85" s="97"/>
-      <c r="C85" s="91" t="s">
-        <v>142</v>
-      </c>
-      <c r="D85" s="90"/>
-      <c r="E85" s="48">
-        <v>136.63999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="76" t="s">
+      <c r="B95" s="61"/>
+      <c r="C95" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="D95" s="67"/>
+      <c r="E95" s="45">
+        <v>574.59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="62"/>
+      <c r="B96" s="63"/>
+      <c r="C96" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D96" s="67"/>
+      <c r="E96" s="45">
+        <v>113.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="64"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="76"/>
-      <c r="C86" s="84"/>
-      <c r="D86" s="84"/>
-      <c r="E86" s="45">
-        <f>C67</f>
+      <c r="B98" s="59"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="45">
+        <f>C68</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="87" t="s">
+    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="D87" s="87"/>
-      <c r="E87" s="47">
-        <f>(E23+E81)-SUM(E82:E86)</f>
-        <v>62.239999999999782</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-    </row>
-    <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="49"/>
-      <c r="B89" s="49"/>
-      <c r="C89" s="49"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="49"/>
-    </row>
-    <row r="90" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="88" t="s">
-        <v>131</v>
-      </c>
-      <c r="B90" s="88"/>
-      <c r="C90" s="88"/>
-      <c r="D90" s="88"/>
-      <c r="E90" s="88"/>
-    </row>
-    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="D91" s="73"/>
-      <c r="E91" s="43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75" t="s">
-        <v>109</v>
-      </c>
-      <c r="B92" s="75"/>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
-      <c r="E92" s="47">
-        <f>E87</f>
-        <v>62.239999999999782</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="B93" s="93"/>
-      <c r="C93" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="D93" s="78"/>
-      <c r="E93" s="45">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="94"/>
-      <c r="B94" s="95"/>
-      <c r="C94" s="114" t="s">
-        <v>118</v>
-      </c>
-      <c r="D94" s="115"/>
-      <c r="E94" s="45">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="94"/>
-      <c r="B95" s="95"/>
-      <c r="C95" s="114" t="s">
-        <v>148</v>
-      </c>
-      <c r="D95" s="115"/>
-      <c r="E95" s="45">
-        <v>113.9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="96"/>
-      <c r="B96" s="97"/>
-      <c r="C96" s="114" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="115"/>
-      <c r="E96" s="45">
-        <v>274.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="84"/>
-      <c r="D97" s="84"/>
-      <c r="E97" s="45">
-        <f>C67</f>
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C98" s="87" t="s">
-        <v>96</v>
-      </c>
-      <c r="D98" s="87"/>
-      <c r="E98" s="47">
-        <f>(E29+E92)-SUM(E93:E97)</f>
-        <v>127.83999999999969</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="24"/>
-      <c r="B99" s="24"/>
+      <c r="D99" s="55"/>
+      <c r="E99" s="47">
+        <f>(E30+E94)-SUM(E95:E98)</f>
+        <v>1205.7499999999998</v>
+      </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="24"/>
@@ -11938,72 +11957,77 @@
       <c r="A1034" s="24"/>
       <c r="B1034" s="24"/>
     </row>
+    <row r="1035" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1035" s="24"/>
+      <c r="B1035" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A93:B96"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="A82:B85"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A73:B75"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A38:C39"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
+  <mergeCells count="63">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="A83:B87"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
   </mergeCells>
-  <conditionalFormatting sqref="C7:C8 E72">
+  <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -12011,7 +12035,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E77 E81 E87 E92 E98">
+  <conditionalFormatting sqref="E78 E82 E89 E94 E99">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F833D720-4424-B845-AD52-C535F3C36006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1280BC04-B72D-3942-9702-A9EEEAC22D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1222,20 +1222,119 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1261,127 +1360,10 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1396,17 +1378,35 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1725,13 +1725,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1961,13 +1961,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1995,10 +1995,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="96"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2010,10 +2010,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="113" t="s">
+      <c r="C12" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="113"/>
+      <c r="D12" s="101"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2025,10 +2025,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="114"/>
+      <c r="D13" s="102"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2038,10 +2038,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="85"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2051,10 +2051,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="85"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2064,10 +2064,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="85"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2079,10 +2079,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="109" t="s">
+      <c r="C17" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="109"/>
+      <c r="D17" s="103"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2092,10 +2092,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="110" t="s">
+      <c r="C18" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="110"/>
+      <c r="D18" s="104"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2107,10 +2107,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="C19" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="111"/>
+      <c r="D19" s="105"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2131,13 +2131,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2165,10 +2165,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="112" t="s">
+      <c r="C23" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="112"/>
+      <c r="D23" s="106"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2180,10 +2180,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="85" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="85"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2195,10 +2195,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="85"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2208,10 +2208,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="98" t="s">
+      <c r="C26" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="109"/>
+      <c r="D26" s="103"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2223,10 +2223,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="110" t="s">
+      <c r="C27" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="110"/>
+      <c r="D27" s="104"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2236,10 +2236,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="99" t="s">
+      <c r="C28" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="99"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2261,13 +2261,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2295,10 +2295,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="84" t="s">
+      <c r="C32" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="84"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2310,10 +2310,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="85" t="s">
+      <c r="C33" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="85"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2323,10 +2323,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="85"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2336,10 +2336,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="107" t="s">
+      <c r="C35" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="91"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2349,10 +2349,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="107" t="s">
+      <c r="C36" s="108" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="108"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2362,10 +2362,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="98" t="s">
+      <c r="C37" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="85"/>
+      <c r="D37" s="61"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2387,11 +2387,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2406,11 +2406,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2456,16 +2456,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="82" t="s">
+      <c r="A47" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="82"/>
-      <c r="C47" s="82"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="82"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="82"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2514,11 +2514,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="83" t="s">
+      <c r="A54" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2553,11 +2553,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="83" t="s">
+      <c r="A58" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2581,11 +2581,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="83"/>
-      <c r="C61" s="83"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2609,11 +2609,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="80" t="s">
+      <c r="A64" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2690,11 +2690,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="80" t="s">
+      <c r="A72" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="80"/>
-      <c r="C72" s="80"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="19">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2744,167 +2744,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="71"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="81" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="81"/>
-      <c r="C80" s="81" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="81"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="103" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="103"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="59" t="s">
+      <c r="A82" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="104" t="s">
+      <c r="B82" s="77"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="104"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="59"/>
-      <c r="B83" s="59"/>
-      <c r="C83" s="104" t="s">
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="104"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="59"/>
-      <c r="B84" s="59"/>
-      <c r="C84" s="104" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="104"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="59"/>
-      <c r="B85" s="59"/>
-      <c r="C85" s="105" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="105"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="59"/>
-      <c r="B86" s="59"/>
-      <c r="C86" s="78" t="s">
+      <c r="A86" s="77"/>
+      <c r="B86" s="77"/>
+      <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="78"/>
+      <c r="D86" s="82"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="59"/>
-      <c r="B87" s="59"/>
-      <c r="C87" s="105" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="105"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59"/>
-      <c r="B88" s="59"/>
-      <c r="C88" s="104" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="104"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="59"/>
-      <c r="B89" s="59"/>
-      <c r="C89" s="78" t="s">
+      <c r="A89" s="77"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="78"/>
+      <c r="D89" s="82"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="59"/>
-      <c r="B90" s="59"/>
-      <c r="C90" s="78" t="s">
+      <c r="A90" s="77"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="78"/>
+      <c r="D90" s="82"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="59"/>
-      <c r="B91" s="59"/>
-      <c r="C91" s="106" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="106"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="75"/>
-      <c r="C92" s="79"/>
-      <c r="D92" s="79"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="74" t="s">
+      <c r="C93" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="74"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2912,113 +2912,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="71" t="s">
+      <c r="A95" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="71"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="71"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="71" t="s">
+      <c r="A96" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="71"/>
-      <c r="C96" s="71" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="71"/>
+      <c r="D96" s="74"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="56" t="s">
+      <c r="A97" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="56"/>
-      <c r="C97" s="57"/>
-      <c r="D97" s="57"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="59" t="s">
+      <c r="A98" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="77" t="s">
+      <c r="B98" s="77"/>
+      <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="77"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="59"/>
-      <c r="B99" s="59"/>
-      <c r="C99" s="58" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="58"/>
+      <c r="D99" s="79"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="59"/>
-      <c r="B100" s="59"/>
-      <c r="C100" s="58" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="58"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="59"/>
-      <c r="B101" s="59"/>
-      <c r="C101" s="58" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="58"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="59"/>
-      <c r="B102" s="59"/>
-      <c r="C102" s="72" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="102"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="59" t="s">
+      <c r="A103" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="59"/>
-      <c r="C103" s="57"/>
-      <c r="D103" s="57"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="55" t="s">
+      <c r="C104" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="55"/>
+      <c r="D104" s="88"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3039,91 +3039,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="70" t="s">
+      <c r="A107" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="70"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="70"/>
-      <c r="E107" s="70"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
+      <c r="D107" s="89"/>
+      <c r="E107" s="89"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="71" t="s">
+      <c r="A108" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="71"/>
-      <c r="C108" s="71" t="s">
+      <c r="B108" s="74"/>
+      <c r="C108" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="71"/>
+      <c r="D108" s="74"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="56" t="s">
+      <c r="A109" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="56"/>
-      <c r="C109" s="57"/>
-      <c r="D109" s="57"/>
+      <c r="B109" s="76"/>
+      <c r="C109" s="85"/>
+      <c r="D109" s="85"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="60" t="s">
+      <c r="A110" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="61"/>
-      <c r="C110" s="99" t="s">
+      <c r="B110" s="94"/>
+      <c r="C110" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="99"/>
+      <c r="D110" s="107"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="62"/>
-      <c r="B111" s="63"/>
-      <c r="C111" s="100" t="s">
+      <c r="A111" s="95"/>
+      <c r="B111" s="96"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="101"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="64"/>
-      <c r="B112" s="65"/>
-      <c r="C112" s="72" t="s">
+      <c r="A112" s="97"/>
+      <c r="B112" s="98"/>
+      <c r="C112" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="102"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="59" t="s">
+      <c r="A113" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="59"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="85"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="55" t="s">
+      <c r="C114" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="55"/>
+      <c r="D114" s="88"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6875,42 +6875,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6924,35 +6917,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6992,13 +6992,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7233,13 +7233,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7267,10 +7267,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="96"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7282,10 +7282,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="97"/>
+      <c r="D12" s="59"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7297,10 +7297,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="85"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7312,10 +7312,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="85"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7336,13 +7336,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7370,10 +7370,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="84"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7385,10 +7385,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="85"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7400,10 +7400,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="91"/>
+      <c r="D20" s="67"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7415,10 +7415,10 @@
       <c r="B21" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="89"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7430,10 +7430,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="91"/>
+      <c r="D22" s="67"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7445,10 +7445,10 @@
       <c r="B23" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="93"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="29">
         <v>1000</v>
       </c>
@@ -7470,13 +7470,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="87" t="s">
+      <c r="A26" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7504,10 +7504,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="84"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7519,10 +7519,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="85" t="s">
+      <c r="C28" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="85"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7530,8 +7530,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7553,11 +7553,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="86" t="s">
+      <c r="A32" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7572,11 +7572,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="83" t="s">
+      <c r="A34" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7622,16 +7622,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="82" t="s">
+      <c r="A39" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="82"/>
-      <c r="C39" s="82"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="82"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
+      <c r="A40" s="72"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7680,11 +7680,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="83" t="s">
+      <c r="A46" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7719,11 +7719,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="83" t="s">
+      <c r="A50" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="71"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7747,11 +7747,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="83" t="s">
+      <c r="A53" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="71"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7775,11 +7775,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="80" t="s">
+      <c r="A56" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7856,11 +7856,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="80" t="s">
+      <c r="A64" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="B65" s="7"/>
       <c r="C65" s="19">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="C67" s="19">
         <f>SUM(C65:C66)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7910,91 +7910,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="71"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="71"/>
-      <c r="E71" s="71"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="81" t="s">
+      <c r="A72" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="81"/>
-      <c r="C72" s="81" t="s">
+      <c r="B72" s="75"/>
+      <c r="C72" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="81"/>
+      <c r="D72" s="75"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="56" t="s">
+      <c r="A73" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="56"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="59"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="75"/>
-      <c r="C74" s="58" t="s">
+      <c r="B74" s="78"/>
+      <c r="C74" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="58"/>
+      <c r="D74" s="79"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="75"/>
-      <c r="B75" s="75"/>
-      <c r="C75" s="76" t="s">
+      <c r="A75" s="78"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="77"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="75"/>
-      <c r="B76" s="75"/>
-      <c r="C76" s="76" t="s">
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="78"/>
+      <c r="D76" s="82"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="75" t="s">
+      <c r="A77" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="75"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="79"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="83"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="74" t="s">
+      <c r="C78" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="74"/>
+      <c r="D78" s="84"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8002,113 +8002,113 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="71" t="s">
+      <c r="A81" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="71"/>
-      <c r="C81" s="71" t="s">
+      <c r="B81" s="74"/>
+      <c r="C81" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="71"/>
+      <c r="D81" s="74"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="56"/>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
+      <c r="B82" s="76"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="68" t="s">
+      <c r="B83" s="94"/>
+      <c r="C83" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="D83" s="69"/>
+      <c r="D83" s="87"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="62"/>
-      <c r="B84" s="63"/>
-      <c r="C84" s="58" t="s">
+      <c r="A84" s="95"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="D84" s="58"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="48">
         <v>219.9</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="125" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="62"/>
-      <c r="B85" s="63"/>
-      <c r="C85" s="72" t="s">
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="D85" s="73"/>
+      <c r="D85" s="91"/>
       <c r="E85" s="48">
         <v>258.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="62"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="68" t="s">
+      <c r="A86" s="95"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="86" t="s">
         <v>150</v>
       </c>
-      <c r="D86" s="115"/>
+      <c r="D86" s="92"/>
       <c r="E86" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="64"/>
-      <c r="B87" s="65"/>
-      <c r="C87" s="72" t="s">
+      <c r="A87" s="97"/>
+      <c r="B87" s="98"/>
+      <c r="C87" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="D87" s="73"/>
-      <c r="E87" s="116">
+      <c r="D87" s="91"/>
+      <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59" t="s">
+      <c r="A88" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="59"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="57"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="85"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="55" t="s">
+      <c r="C89" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="55"/>
+      <c r="D89" s="88"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
         <v>580.23999999999978</v>
@@ -8129,89 +8129,89 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="70"/>
-      <c r="E92" s="70"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="89"/>
+      <c r="D92" s="89"/>
+      <c r="E92" s="89"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="71" t="s">
+      <c r="A93" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="71"/>
-      <c r="C93" s="71" t="s">
+      <c r="B93" s="74"/>
+      <c r="C93" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="71"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="56" t="s">
+      <c r="A94" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="56"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="57"/>
+      <c r="B94" s="76"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="47">
         <f>E89</f>
         <v>580.23999999999978</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="60" t="s">
+      <c r="A95" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="61"/>
-      <c r="C95" s="66" t="s">
+      <c r="B95" s="94"/>
+      <c r="C95" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="D95" s="67"/>
+      <c r="D95" s="100"/>
       <c r="E95" s="45">
         <v>574.59</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="62"/>
-      <c r="B96" s="63"/>
-      <c r="C96" s="66" t="s">
+      <c r="A96" s="95"/>
+      <c r="B96" s="96"/>
+      <c r="C96" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="D96" s="67"/>
+      <c r="D96" s="100"/>
       <c r="E96" s="45">
         <v>113.9</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="64"/>
-      <c r="B97" s="65"/>
-      <c r="C97" s="66"/>
-      <c r="D97" s="67"/>
+      <c r="A97" s="97"/>
+      <c r="B97" s="98"/>
+      <c r="C97" s="99"/>
+      <c r="D97" s="100"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="59" t="s">
+      <c r="A98" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="57"/>
-      <c r="D98" s="57"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
       <c r="E98" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="55" t="s">
+      <c r="C99" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="55"/>
+      <c r="D99" s="88"/>
       <c r="E99" s="47">
         <f>(E30+E94)-SUM(E95:E98)</f>
         <v>1205.7499999999998</v>
@@ -11963,48 +11963,15 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12017,15 +11984,48 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1280BC04-B72D-3942-9702-A9EEEAC22D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BC27A3-8741-AA40-8B6F-0EC90686FB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,13 +639,6 @@
     <t>A discount of $3.08 for iHerb payment</t>
   </si>
   <si>
-    <t>Partial Food And Snack Prepaid on the Previous Month
-~ Food
-   ~ HKTV mall 24/08 - $211.4
-~ Snack And Drinks
-   ~ OK Store 20/08 - $8.5</t>
-  </si>
-  <si>
     <t>2nd September 2026</t>
   </si>
   <si>
@@ -684,17 +677,25 @@
     ~ MEN COTTON BOXER BRIEFS 482600- $29 x 2</t>
   </si>
   <si>
-    <t>~ Food
-   ~ HKTV mall 17/09 - $574.59
-~ Snack And Drinks</t>
-  </si>
-  <si>
     <t>~ iHerb Aveeno Lotion 23/08 - $136.64
 ~ Watsons Revlon color silk 17/09 - $59.9</t>
   </si>
   <si>
     <t>~ Additional transport fees for e-cigarette 17/09 - $50
 ~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+   ~ HKTV mall 24/08 - $211.4
+   ~ HKTV mall 03/09 - $436.5
+~ Snack And Drinks
+   ~ OK Store 20/08 - $8.5</t>
   </si>
 </sst>
 </file>
@@ -1225,115 +1226,22 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1354,16 +1262,133 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1378,35 +1403,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1725,13 +1726,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1752,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>455.54</v>
+        <v>19.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>580.2399999999999</v>
+        <v>143.74</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1961,13 +1962,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1995,10 +1996,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2010,10 +2011,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="101"/>
+      <c r="D12" s="115"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2025,10 +2026,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="102"/>
+      <c r="D13" s="116"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2038,10 +2039,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2051,10 +2052,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="61"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2064,10 +2065,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="87"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2079,10 +2080,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="103"/>
+      <c r="D17" s="111"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2092,10 +2093,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="104"/>
+      <c r="D18" s="112"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2107,10 +2108,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="105"/>
+      <c r="D19" s="113"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2131,13 +2132,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2165,10 +2166,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="106"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2180,10 +2181,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="87"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2195,10 +2196,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="87"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2208,10 +2209,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="103"/>
+      <c r="D26" s="111"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2223,10 +2224,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="C27" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="104"/>
+      <c r="D27" s="112"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2236,10 +2237,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="107"/>
+      <c r="D28" s="101"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2261,13 +2262,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2295,10 +2296,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="86"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2310,10 +2311,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="87"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2323,10 +2324,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="87"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2336,10 +2337,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="108" t="s">
+      <c r="C35" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="67"/>
+      <c r="D35" s="93"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2349,10 +2350,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="108" t="s">
+      <c r="C36" s="109" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="110"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2362,10 +2363,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="87"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2387,11 +2388,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2406,11 +2407,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="85"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2456,16 +2457,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="84"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="84"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2514,11 +2515,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="85"/>
+      <c r="C54" s="85"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2553,11 +2554,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="85"/>
+      <c r="C58" s="85"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2581,11 +2582,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="85"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2609,11 +2610,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2690,11 +2691,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="82"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2744,167 +2745,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="71"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75" t="s">
+      <c r="B80" s="83"/>
+      <c r="C80" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="83"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
+      <c r="B81" s="105"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="59"/>
+      <c r="C82" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="106"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="106"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="106"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="107"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="82" t="s">
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="82"/>
+      <c r="D86" s="80"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="107"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="106"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="82" t="s">
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="82"/>
+      <c r="D89" s="80"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="82" t="s">
+      <c r="A90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="82"/>
+      <c r="D90" s="80"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="59"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="108"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="84"/>
+      <c r="D93" s="76"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2912,113 +2913,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="74"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
+      <c r="B95" s="71"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="71"/>
+      <c r="E95" s="71"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="74" t="s">
+      <c r="A96" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="74"/>
-      <c r="C96" s="74" t="s">
+      <c r="B96" s="71"/>
+      <c r="C96" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="74"/>
+      <c r="D96" s="71"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
+      <c r="A97" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="81" t="s">
+      <c r="B98" s="59"/>
+      <c r="C98" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="81"/>
+      <c r="D98" s="79"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79" t="s">
+      <c r="A99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="79"/>
+      <c r="D99" s="72"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79" t="s">
+      <c r="A100" s="59"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="79"/>
+      <c r="D100" s="72"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="77"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79" t="s">
+      <c r="A101" s="59"/>
+      <c r="B101" s="59"/>
+      <c r="C101" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="79"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="59"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="104"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="59"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="88"/>
+      <c r="D104" s="56"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3039,91 +3040,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
+      <c r="B107" s="70"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="70"/>
+      <c r="E107" s="70"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="74"/>
-      <c r="C108" s="74" t="s">
+      <c r="B108" s="71"/>
+      <c r="C108" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="74"/>
+      <c r="D108" s="71"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="76" t="s">
+      <c r="A109" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="76"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="93" t="s">
+      <c r="A110" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="94"/>
-      <c r="C110" s="107" t="s">
+      <c r="B110" s="63"/>
+      <c r="C110" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="107"/>
+      <c r="D110" s="101"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="95"/>
-      <c r="B111" s="96"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="64"/>
+      <c r="B111" s="65"/>
+      <c r="C111" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="103"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="66"/>
+      <c r="B112" s="67"/>
+      <c r="C112" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="104"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="88"/>
+      <c r="D114" s="56"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6875,35 +6876,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6917,42 +6925,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6992,13 +6993,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7020,7 +7021,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>455.54</v>
+        <v>19.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>580.2399999999999</v>
+        <v>143.74</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7233,13 +7234,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7267,10 +7268,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7282,10 +7283,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="99"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7297,10 +7298,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7312,10 +7313,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7336,13 +7337,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7370,10 +7371,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="86"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7385,10 +7386,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="87"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7400,10 +7401,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="67"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7415,40 +7416,40 @@
       <c r="B21" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="90" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="65"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" s="67"/>
+      <c r="C22" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="93"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="C23" s="94" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="69"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="29">
         <v>1000</v>
       </c>
@@ -7470,13 +7471,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7504,25 +7505,25 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="63"/>
+      <c r="D27" s="86"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="61"/>
+      <c r="D28" s="87"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7530,8 +7531,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7553,11 +7554,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7572,11 +7573,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="71" t="s">
+      <c r="A34" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7622,16 +7623,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="84"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
+      <c r="A40" s="84"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7680,11 +7681,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="85"/>
+      <c r="C46" s="85"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7719,11 +7720,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="71" t="s">
+      <c r="A50" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="71"/>
+      <c r="B50" s="85"/>
+      <c r="C50" s="85"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7747,11 +7748,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7775,11 +7776,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="82"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7856,11 +7857,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7910,91 +7911,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="71"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="75" t="s">
+      <c r="A72" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="75"/>
-      <c r="C72" s="75" t="s">
+      <c r="B72" s="83"/>
+      <c r="C72" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="75"/>
+      <c r="D72" s="83"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+      <c r="A73" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="78" t="s">
+      <c r="A74" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="79" t="s">
+      <c r="B74" s="77"/>
+      <c r="C74" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="79"/>
+      <c r="D74" s="72"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78"/>
-      <c r="B75" s="78"/>
-      <c r="C75" s="80" t="s">
+      <c r="A75" s="77"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="81"/>
+      <c r="D75" s="79"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="80" t="s">
+      <c r="A76" s="77"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="82"/>
+      <c r="D76" s="80"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78" t="s">
+      <c r="A77" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="81"/>
+      <c r="D77" s="81"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="84" t="s">
+      <c r="C78" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="84"/>
+      <c r="D78" s="76"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8002,116 +8003,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74" t="s">
+      <c r="B81" s="71"/>
+      <c r="C81" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="74"/>
+      <c r="D81" s="71"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="76" t="s">
+      <c r="A82" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="76"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="93" t="s">
+      <c r="A83" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="94"/>
-      <c r="C83" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="D83" s="87"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D83" s="69"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="89" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="95"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="D84" s="79"/>
+    <row r="84" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="64"/>
+      <c r="B84" s="65"/>
+      <c r="C84" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="72"/>
       <c r="E84" s="48">
-        <v>219.9</v>
+        <v>656.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="125" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="D85" s="91"/>
+      <c r="A85" s="64"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="D85" s="74"/>
       <c r="E85" s="48">
         <v>258.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="95"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="86" t="s">
-        <v>150</v>
-      </c>
-      <c r="D86" s="92"/>
+      <c r="A86" s="64"/>
+      <c r="B86" s="65"/>
+      <c r="C86" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" s="75"/>
       <c r="E86" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="97"/>
-      <c r="B87" s="98"/>
-      <c r="C87" s="90" t="s">
-        <v>148</v>
-      </c>
-      <c r="D87" s="91"/>
+      <c r="A87" s="66"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="D87" s="74"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77" t="s">
+      <c r="A88" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="77"/>
-      <c r="C88" s="85"/>
-      <c r="D88" s="85"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="88" t="s">
+      <c r="C89" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="88"/>
+      <c r="D89" s="56"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>580.23999999999978</v>
+        <v>143.73999999999978</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8129,92 +8130,92 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="89" t="s">
+      <c r="A92" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="89"/>
-      <c r="C92" s="89"/>
-      <c r="D92" s="89"/>
-      <c r="E92" s="89"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
+      <c r="E92" s="70"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="74" t="s">
+      <c r="A93" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="74"/>
-      <c r="C93" s="74" t="s">
+      <c r="B93" s="71"/>
+      <c r="C93" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="74"/>
+      <c r="D93" s="71"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="76" t="s">
+      <c r="A94" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="76"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>580.23999999999978</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="93" t="s">
+        <v>143.73999999999978</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="94"/>
-      <c r="C95" s="99" t="s">
+      <c r="B95" s="63"/>
+      <c r="C95" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="D95" s="61"/>
+      <c r="E95" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="64"/>
+      <c r="B96" s="65"/>
+      <c r="C96" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="D95" s="100"/>
-      <c r="E95" s="45">
-        <v>574.59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="95"/>
-      <c r="B96" s="96"/>
-      <c r="C96" s="99" t="s">
-        <v>151</v>
-      </c>
-      <c r="D96" s="100"/>
+      <c r="D96" s="61"/>
       <c r="E96" s="45">
-        <v>113.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="97"/>
-      <c r="B97" s="98"/>
-      <c r="C97" s="99"/>
-      <c r="D97" s="100"/>
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="61"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="85"/>
-      <c r="D98" s="85"/>
+      <c r="B98" s="59"/>
+      <c r="C98" s="58"/>
+      <c r="D98" s="58"/>
       <c r="E98" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="88" t="s">
+      <c r="C99" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="88"/>
+      <c r="D99" s="56"/>
       <c r="E99" s="47">
         <f>(E30+E94)-SUM(E95:E98)</f>
-        <v>1205.7499999999998</v>
+        <v>1403.7399999999998</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11963,15 +11964,48 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -11984,48 +12018,15 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BC27A3-8741-AA40-8B6F-0EC90686FB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115A6D1F-6E67-3A4D-B55F-2A83C010ADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -627,9 +627,6 @@
 ~ Single Trip from chuk yuen to Temple Mall 19/08 - $2</t>
   </si>
   <si>
-    <t>1. Top up $50 for Octopus</t>
-  </si>
-  <si>
     <t>23rd August 2026</t>
   </si>
   <si>
@@ -643,6 +640,46 @@
   </si>
   <si>
     <t>1. Borrow $60</t>
+  </si>
+  <si>
+    <t>18th September 2026</t>
+  </si>
+  <si>
+    <t>3rd September 2026</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>1. A gift for birthday $1000 from Lawrence</t>
+  </si>
+  <si>
+    <t>~ Payback $100 to Mom
+~ Payback $670.4 to Mom (HKTVmall Online Shopping)
+~ Payback $60 to Mom</t>
+  </si>
+  <si>
+    <t>~ Uniqlo (buy $300 - $30 discount)  - 03/09
+    ~ UNISEX EZY BARREL JEANS (INSEAM 72-78cm) 488630 / 492035 -$299
+    ~ UNISEX ULTRA STRETCH ACTIVE SHORTS (INSEAM 18-21.5cm) 482317 - $99
+    ~ MEN COTTON BOXER BRIEFS 482600- $29 x 2</t>
+  </si>
+  <si>
+    <t>~ iHerb Aveeno Lotion 23/08 - $136.64
+~ Watsons Revlon color silk 17/09 - $59.9</t>
+  </si>
+  <si>
+    <t>~ Additional transport fees for e-cigarette 17/09 - $50
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>1. Top up $50 for Octopus
+2. Top up $50 for Octopus 03/09</t>
   </si>
   <si>
     <t>~ Debit For Octopus Card ($50). 20/08
@@ -651,43 +688,8 @@
 ~ Additional transport fees for e-cigarette 20/08 - $50
 ~ Paid Water Supplies Fees 20/08 - $74.1
 ~ Round Trip to East Kowloon hospital 31/08 - $4
-~ Round Trip to East Kowloon hospital 03/09 - $4</t>
-  </si>
-  <si>
-    <t>18th September 2026</t>
-  </si>
-  <si>
-    <t>3rd September 2026</t>
-  </si>
-  <si>
-    <t>Brother</t>
-  </si>
-  <si>
-    <t>1. A gift for birthday $1000 from Lawrence</t>
-  </si>
-  <si>
-    <t>~ Payback $100 to Mom
-~ Payback $670.4 to Mom (HKTVmall Online Shopping)
-~ Payback $60 to Mom</t>
-  </si>
-  <si>
-    <t>~ Uniqlo (buy $300 - $30 discount)  - 03/09
-    ~ UNISEX EZY BARREL JEANS (INSEAM 72-78cm) 488630 / 492035 -$299
-    ~ UNISEX ULTRA STRETCH ACTIVE SHORTS (INSEAM 18-21.5cm) 482317 - $99
-    ~ MEN COTTON BOXER BRIEFS 482600- $29 x 2</t>
-  </si>
-  <si>
-    <t>~ iHerb Aveeno Lotion 23/08 - $136.64
-~ Watsons Revlon color silk 17/09 - $59.9</t>
-  </si>
-  <si>
-    <t>~ Additional transport fees for e-cigarette 17/09 - $50
-~ Round Trip to East Kowloon hospital 02/10 - $4</t>
-  </si>
-  <si>
-    <t>Partial Food And Snack Prepaid on the Previous Month
-~ Food
-~ Snack And Drinks</t>
+~ Round Trip to East Kowloon hospital 03/09 - $4
+~ Debit For Octopus Card ($50). 03/09</t>
   </si>
   <si>
     <t>Partial Food And Snack Prepaid on the Previous Month
@@ -695,7 +697,8 @@
    ~ HKTV mall 24/08 - $211.4
    ~ HKTV mall 03/09 - $436.5
 ~ Snack And Drinks
-   ~ OK Store 20/08 - $8.5</t>
+   ~ OK Store 20/08 - $8.5
+   ~ Ustore 03/09 - $55.2</t>
   </si>
 </sst>
 </file>
@@ -1226,22 +1229,115 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1262,133 +1358,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1403,11 +1382,35 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1726,13 +1729,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1784,7 +1787,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1877,7 +1880,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9">
-        <v>2.8</v>
+        <v>-6.4</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1909,7 +1912,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>143.74</v>
+        <v>84.539999999999992</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1962,13 +1965,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1996,10 +1999,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2011,10 +2014,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="115"/>
+      <c r="D12" s="101"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2026,10 +2029,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="116" t="s">
+      <c r="C13" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="116"/>
+      <c r="D13" s="102"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2039,10 +2042,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2052,10 +2055,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="87"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2065,10 +2068,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="C16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="87"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2080,10 +2083,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="111" t="s">
+      <c r="C17" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="111"/>
+      <c r="D17" s="103"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2093,10 +2096,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="C18" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="112"/>
+      <c r="D18" s="104"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2108,10 +2111,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="113"/>
+      <c r="D19" s="105"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2132,13 +2135,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2166,10 +2169,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="114"/>
+      <c r="D23" s="106"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2181,10 +2184,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="87" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="87"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2196,10 +2199,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="87" t="s">
+      <c r="C25" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="87"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2209,10 +2212,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="111"/>
+      <c r="D26" s="103"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2224,10 +2227,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="112"/>
+      <c r="D27" s="104"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2237,10 +2240,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="101"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2262,13 +2265,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2296,10 +2299,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="C32" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="86"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2311,10 +2314,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="87"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2324,10 +2327,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="87"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2337,10 +2340,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="109" t="s">
+      <c r="C35" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="93"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2350,10 +2353,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="109" t="s">
+      <c r="C36" s="108" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="110"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2363,10 +2366,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="100" t="s">
+      <c r="C37" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="87"/>
+      <c r="D37" s="61"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2388,11 +2391,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="88" t="s">
+      <c r="A40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="88"/>
-      <c r="C40" s="88"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2407,11 +2410,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2457,16 +2460,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="84"/>
-      <c r="C47" s="84"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="84"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="84"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2515,11 +2518,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="85" t="s">
+      <c r="A54" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="85"/>
-      <c r="C54" s="85"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2554,11 +2557,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="85" t="s">
+      <c r="A58" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="85"/>
-      <c r="C58" s="85"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2582,11 +2585,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="85" t="s">
+      <c r="A61" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2610,11 +2613,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="82" t="s">
+      <c r="A64" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2691,11 +2694,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="82" t="s">
+      <c r="A72" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="82"/>
-      <c r="C72" s="82"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2745,167 +2748,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="71"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="83" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="83"/>
-      <c r="C80" s="83" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="83"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="105" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="105"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="59" t="s">
+      <c r="A82" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="106" t="s">
+      <c r="B82" s="77"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="106"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="59"/>
-      <c r="B83" s="59"/>
-      <c r="C83" s="106" t="s">
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="106"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="59"/>
-      <c r="B84" s="59"/>
-      <c r="C84" s="106" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="106"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="59"/>
-      <c r="B85" s="59"/>
-      <c r="C85" s="107" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="107"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="59"/>
-      <c r="B86" s="59"/>
-      <c r="C86" s="80" t="s">
+      <c r="A86" s="77"/>
+      <c r="B86" s="77"/>
+      <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="80"/>
+      <c r="D86" s="82"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="59"/>
-      <c r="B87" s="59"/>
-      <c r="C87" s="107" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="107"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59"/>
-      <c r="B88" s="59"/>
-      <c r="C88" s="106" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="106"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="59"/>
-      <c r="B89" s="59"/>
-      <c r="C89" s="80" t="s">
+      <c r="A89" s="77"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="80"/>
+      <c r="D89" s="82"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="59"/>
-      <c r="B90" s="59"/>
-      <c r="C90" s="80" t="s">
+      <c r="A90" s="77"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="80"/>
+      <c r="D90" s="82"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="59"/>
-      <c r="B91" s="59"/>
-      <c r="C91" s="108" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="108"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="77" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="77"/>
-      <c r="C92" s="81"/>
-      <c r="D92" s="81"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="76"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2913,113 +2916,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="71" t="s">
+      <c r="A95" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="71"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="71"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="71" t="s">
+      <c r="A96" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="71"/>
-      <c r="C96" s="71" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="71"/>
+      <c r="D96" s="74"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="59" t="s">
+      <c r="A98" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="79" t="s">
+      <c r="B98" s="77"/>
+      <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="79"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="59"/>
-      <c r="B99" s="59"/>
-      <c r="C99" s="72" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="72"/>
+      <c r="D99" s="79"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="59"/>
-      <c r="B100" s="59"/>
-      <c r="C100" s="72" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="72"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="59"/>
-      <c r="B101" s="59"/>
-      <c r="C101" s="72" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="72"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="59"/>
-      <c r="B102" s="59"/>
-      <c r="C102" s="73" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="104"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="59" t="s">
+      <c r="A103" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="59"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="56" t="s">
+      <c r="C104" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="56"/>
+      <c r="D104" s="88"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3040,91 +3043,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="70" t="s">
+      <c r="A107" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="70"/>
-      <c r="C107" s="70"/>
-      <c r="D107" s="70"/>
-      <c r="E107" s="70"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
+      <c r="D107" s="89"/>
+      <c r="E107" s="89"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="71" t="s">
+      <c r="A108" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="71"/>
-      <c r="C108" s="71" t="s">
+      <c r="B108" s="74"/>
+      <c r="C108" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="71"/>
+      <c r="D108" s="74"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
+      <c r="B109" s="76"/>
+      <c r="C109" s="85"/>
+      <c r="D109" s="85"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="62" t="s">
+      <c r="A110" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="63"/>
-      <c r="C110" s="101" t="s">
+      <c r="B110" s="94"/>
+      <c r="C110" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="101"/>
+      <c r="D110" s="107"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="64"/>
-      <c r="B111" s="65"/>
-      <c r="C111" s="102" t="s">
+      <c r="A111" s="95"/>
+      <c r="B111" s="96"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="103"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="66"/>
-      <c r="B112" s="67"/>
-      <c r="C112" s="73" t="s">
+      <c r="A112" s="97"/>
+      <c r="B112" s="98"/>
+      <c r="C112" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="104"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="59" t="s">
+      <c r="A113" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="59"/>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="85"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="56" t="s">
+      <c r="C114" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="56"/>
+      <c r="D114" s="88"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6876,42 +6879,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6925,35 +6921,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6993,13 +6996,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7053,7 +7056,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7149,7 +7152,7 @@
       </c>
       <c r="C7" s="9">
         <f>'April 2026 - June 2026'!C7</f>
-        <v>2.8</v>
+        <v>-6.4</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -7181,7 +7184,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>143.74</v>
+        <v>84.539999999999992</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7234,13 +7237,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7268,10 +7271,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7283,10 +7286,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="99"/>
+      <c r="D12" s="59"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7298,10 +7301,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="87"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7313,10 +7316,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="100" t="s">
+      <c r="C14" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7337,13 +7340,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7371,10 +7374,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="86"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7386,70 +7389,70 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="87"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
         <v>131</v>
       </c>
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="93"/>
+      <c r="C20" s="108" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="67"/>
       <c r="E20" s="29">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="C21" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="90" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="91"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="93"/>
+      <c r="C22" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="67"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="94" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="95"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="29">
         <v>1000</v>
       </c>
@@ -7463,7 +7466,7 @@
       </c>
       <c r="E24" s="26">
         <f>SUM(E19:E23)</f>
-        <v>3598.08</v>
+        <v>3648.08</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7471,13 +7474,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7505,25 +7508,25 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="86"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="87" t="s">
+      <c r="C28" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="87"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7531,8 +7534,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7554,11 +7557,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="88"/>
-      <c r="C32" s="88"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7573,11 +7576,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7623,16 +7626,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="84" t="s">
+      <c r="A39" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="84"/>
-      <c r="C39" s="84"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="84"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
+      <c r="A40" s="72"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7681,11 +7684,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="85"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7720,11 +7723,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="85" t="s">
+      <c r="A50" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="85"/>
-      <c r="C50" s="85"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="71"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7748,11 +7751,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="85" t="s">
+      <c r="A53" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="71"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7776,11 +7779,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="82" t="s">
+      <c r="A56" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="82"/>
-      <c r="C56" s="82"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7857,11 +7860,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="82" t="s">
+      <c r="A64" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7911,91 +7914,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="71"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="71"/>
-      <c r="E71" s="71"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="83"/>
-      <c r="C72" s="83" t="s">
+      <c r="B72" s="75"/>
+      <c r="C72" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="83"/>
+      <c r="D72" s="75"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="57" t="s">
+      <c r="A73" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="57"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="59"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="77" t="s">
+      <c r="A74" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="77"/>
-      <c r="C74" s="72" t="s">
+      <c r="B74" s="78"/>
+      <c r="C74" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="72"/>
+      <c r="D74" s="79"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="77"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="78" t="s">
+      <c r="A75" s="78"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="79"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="77"/>
-      <c r="B76" s="77"/>
-      <c r="C76" s="78" t="s">
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="80"/>
+      <c r="D76" s="82"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="77" t="s">
+      <c r="A77" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="77"/>
-      <c r="C77" s="81"/>
-      <c r="D77" s="81"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="83"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="76" t="s">
+      <c r="C78" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="76"/>
+      <c r="D78" s="84"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8003,116 +8006,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="71" t="s">
+      <c r="A80" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="71" t="s">
+      <c r="A81" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="71"/>
-      <c r="C81" s="71" t="s">
+      <c r="B81" s="74"/>
+      <c r="C81" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="71"/>
+      <c r="D81" s="74"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
+      <c r="B82" s="76"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="62" t="s">
+      <c r="A83" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="63"/>
-      <c r="C83" s="68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D83" s="69"/>
+      <c r="B83" s="94"/>
+      <c r="C83" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="D83" s="87"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="64"/>
-      <c r="B84" s="65"/>
-      <c r="C84" s="72" t="s">
+    <row r="84" spans="1:5" ht="128" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="95"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="D84" s="72"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="48">
-        <v>656.4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="125" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="64"/>
-      <c r="B85" s="65"/>
-      <c r="C85" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="D85" s="74"/>
+        <v>711.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="137" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85" s="91"/>
       <c r="E85" s="48">
-        <v>258.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="64"/>
-      <c r="B86" s="65"/>
-      <c r="C86" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D86" s="75"/>
+      <c r="A86" s="95"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="D86" s="92"/>
       <c r="E86" s="48">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="66"/>
-      <c r="B87" s="67"/>
-      <c r="C87" s="73" t="s">
-        <v>147</v>
-      </c>
-      <c r="D87" s="74"/>
+      <c r="A87" s="97"/>
+      <c r="B87" s="98"/>
+      <c r="C87" s="90" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="91"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59" t="s">
+      <c r="A88" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="59"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="85"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="56" t="s">
+      <c r="C89" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="56"/>
+      <c r="D89" s="88"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>143.73999999999978</v>
+        <v>84.539999999999964</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8130,92 +8133,92 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="70"/>
-      <c r="E92" s="70"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="89"/>
+      <c r="D92" s="89"/>
+      <c r="E92" s="89"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="71" t="s">
+      <c r="A93" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="71"/>
-      <c r="C93" s="71" t="s">
+      <c r="B93" s="74"/>
+      <c r="C93" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="71"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="57" t="s">
+      <c r="A94" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="76"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>143.73999999999978</v>
+        <v>84.539999999999964</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="62" t="s">
+      <c r="A95" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="63"/>
-      <c r="C95" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="D95" s="61"/>
+      <c r="B95" s="94"/>
+      <c r="C95" s="99" t="s">
+        <v>148</v>
+      </c>
+      <c r="D95" s="100"/>
       <c r="E95" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="64"/>
-      <c r="B96" s="65"/>
-      <c r="C96" s="60" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="61"/>
+      <c r="A96" s="95"/>
+      <c r="B96" s="96"/>
+      <c r="C96" s="99" t="s">
+        <v>147</v>
+      </c>
+      <c r="D96" s="100"/>
       <c r="E96" s="45">
         <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="60"/>
-      <c r="D97" s="61"/>
+      <c r="A97" s="97"/>
+      <c r="B97" s="98"/>
+      <c r="C97" s="99"/>
+      <c r="D97" s="100"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="59" t="s">
+      <c r="A98" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
       <c r="E98" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="56" t="s">
+      <c r="C99" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="56"/>
+      <c r="D99" s="88"/>
       <c r="E99" s="47">
         <f>(E30+E94)-SUM(E95:E98)</f>
-        <v>1403.7399999999998</v>
+        <v>1344.54</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11964,48 +11967,15 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12018,15 +11988,48 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115A6D1F-6E67-3A4D-B55F-2A83C010ADAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3B1AC-2E57-7640-A58C-B9E66B88B29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -698,7 +698,8 @@
    ~ HKTV mall 03/09 - $436.5
 ~ Snack And Drinks
    ~ OK Store 20/08 - $8.5
-   ~ Ustore 03/09 - $55.2</t>
+   ~ Ustore 03/09 - $55.2
+   ~ Ustore 05/09 - $9.8</t>
   </si>
 </sst>
 </file>
@@ -1229,116 +1230,17 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1358,38 +1260,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1400,17 +1305,113 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1729,13 +1730,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1787,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>12</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1849,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>59.9</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1912,7 +1913,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>84.539999999999992</v>
+        <v>14.839999999999998</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1965,13 +1966,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1999,10 +2000,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="101"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2014,10 +2015,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="101"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2029,10 +2030,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="102"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2042,10 +2043,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2055,10 +2056,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="61"/>
+      <c r="D15" s="88"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2068,10 +2069,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2083,10 +2084,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="103"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2096,10 +2097,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="104"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2111,10 +2112,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="105"/>
+      <c r="D19" s="97"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2135,13 +2136,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2169,10 +2170,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="106"/>
+      <c r="D23" s="98"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2184,10 +2185,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2199,10 +2200,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2212,10 +2213,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="92" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="103"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2227,10 +2228,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="C27" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="104"/>
+      <c r="D27" s="94"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2240,10 +2241,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="107"/>
+      <c r="D28" s="66"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2265,13 +2266,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2299,10 +2300,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2314,10 +2315,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2327,10 +2328,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2340,10 +2341,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="108" t="s">
+      <c r="C35" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="67"/>
+      <c r="D35" s="90"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2353,10 +2354,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="108" t="s">
+      <c r="C36" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="91"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2366,10 +2367,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="92" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2391,11 +2392,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2410,11 +2411,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2460,16 +2461,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="A48" s="87"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="87"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2518,11 +2519,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2557,11 +2558,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2585,11 +2586,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="83"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2613,11 +2614,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="84"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2694,11 +2695,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
+      <c r="B72" s="84"/>
+      <c r="C72" s="84"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2748,167 +2749,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="85"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
+      <c r="B81" s="78"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="56"/>
+      <c r="C82" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="79"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="56"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="56"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="82" t="s">
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="82"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="56"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="56"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="79"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="82" t="s">
+      <c r="A89" s="56"/>
+      <c r="B89" s="56"/>
+      <c r="C89" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="82"/>
+      <c r="D89" s="81"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="82" t="s">
+      <c r="A90" s="56"/>
+      <c r="B90" s="56"/>
+      <c r="C90" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="82"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="56"/>
+      <c r="B91" s="56"/>
+      <c r="C91" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="82"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="84"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2916,113 +2917,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="74"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="74" t="s">
+      <c r="A96" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="74"/>
-      <c r="C96" s="74" t="s">
+      <c r="B96" s="72"/>
+      <c r="C96" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="74"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
+      <c r="A97" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="81" t="s">
+      <c r="B98" s="56"/>
+      <c r="C98" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="81"/>
+      <c r="D98" s="73"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79" t="s">
+      <c r="A99" s="56"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="79"/>
+      <c r="D99" s="74"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79" t="s">
+      <c r="A100" s="56"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="79"/>
+      <c r="D100" s="74"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="77"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79" t="s">
+      <c r="A101" s="56"/>
+      <c r="B101" s="56"/>
+      <c r="C101" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="79"/>
+      <c r="D101" s="74"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="56"/>
+      <c r="B102" s="56"/>
+      <c r="C102" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="70"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="56"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="88"/>
+      <c r="D104" s="58"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3043,91 +3044,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
+      <c r="B107" s="71"/>
+      <c r="C107" s="71"/>
+      <c r="D107" s="71"/>
+      <c r="E107" s="71"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="74"/>
-      <c r="C108" s="74" t="s">
+      <c r="B108" s="72"/>
+      <c r="C108" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="74"/>
+      <c r="D108" s="72"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="76" t="s">
+      <c r="A109" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="76"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="59"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="57"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="93" t="s">
+      <c r="A110" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="94"/>
-      <c r="C110" s="107" t="s">
+      <c r="B110" s="61"/>
+      <c r="C110" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="107"/>
+      <c r="D110" s="66"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="95"/>
-      <c r="B111" s="96"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="62"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="68"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="64"/>
+      <c r="B112" s="65"/>
+      <c r="C112" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="56"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="88"/>
+      <c r="D114" s="58"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6879,35 +6880,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6921,42 +6929,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6996,13 +6997,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="99" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7056,7 +7057,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>12</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7120,7 +7121,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>59.9</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7184,7 +7185,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>84.539999999999992</v>
+        <v>14.839999999999998</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7237,13 +7238,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7271,10 +7272,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="101"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7286,10 +7287,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7301,10 +7302,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7316,10 +7317,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7340,13 +7341,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7374,10 +7375,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7389,10 +7390,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="88"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7404,10 +7405,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="108" t="s">
+      <c r="C20" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="67"/>
+      <c r="D20" s="90"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7419,10 +7420,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="111" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="65"/>
+      <c r="D21" s="112"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7434,10 +7435,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="115" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="67"/>
+      <c r="D22" s="90"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7449,10 +7450,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="113" t="s">
         <v>143</v>
       </c>
-      <c r="D23" s="69"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="29">
         <v>1000</v>
       </c>
@@ -7474,13 +7475,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7508,10 +7509,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="63"/>
+      <c r="D27" s="96"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7523,10 +7524,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="61"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7534,8 +7535,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7557,11 +7558,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7576,11 +7577,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="71" t="s">
+      <c r="A34" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7626,16 +7627,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
+      <c r="A40" s="87"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7684,11 +7685,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7723,11 +7724,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="71" t="s">
+      <c r="A50" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="71"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="83"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7751,11 +7752,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
+      <c r="B53" s="83"/>
+      <c r="C53" s="83"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7779,11 +7780,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="84"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7860,11 +7861,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="84"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7914,91 +7915,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="72"/>
+      <c r="E71" s="72"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="75" t="s">
+      <c r="A72" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="75"/>
-      <c r="C72" s="75" t="s">
+      <c r="B72" s="85"/>
+      <c r="C72" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="75"/>
+      <c r="D72" s="85"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+      <c r="A73" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="78" t="s">
+      <c r="A74" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="79" t="s">
+      <c r="B74" s="75"/>
+      <c r="C74" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="79"/>
+      <c r="D74" s="74"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78"/>
-      <c r="B75" s="78"/>
-      <c r="C75" s="80" t="s">
+      <c r="A75" s="75"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="81"/>
+      <c r="D75" s="73"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="80" t="s">
+      <c r="A76" s="75"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="110" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="82"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78" t="s">
+      <c r="A77" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="76"/>
+      <c r="D77" s="76"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="84" t="s">
+      <c r="C78" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="84"/>
+      <c r="D78" s="77"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8006,116 +8007,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="74" t="s">
+      <c r="A80" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74" t="s">
+      <c r="B81" s="72"/>
+      <c r="C81" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="74"/>
+      <c r="D81" s="72"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="76" t="s">
+      <c r="A82" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="76"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="93" t="s">
+      <c r="A83" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="94"/>
-      <c r="C83" s="86" t="s">
+      <c r="B83" s="61"/>
+      <c r="C83" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="D83" s="87"/>
+      <c r="D83" s="107"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="128" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="95"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="79" t="s">
+    <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="62"/>
+      <c r="B84" s="63"/>
+      <c r="C84" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="D84" s="79"/>
+      <c r="D84" s="74"/>
       <c r="E84" s="48">
-        <v>711.6</v>
+        <v>721.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="137" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="90" t="s">
+      <c r="A85" s="62"/>
+      <c r="B85" s="63"/>
+      <c r="C85" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="D85" s="91"/>
+      <c r="D85" s="108"/>
       <c r="E85" s="48">
         <v>312.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="95"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="86" t="s">
+      <c r="A86" s="62"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="92"/>
+      <c r="D86" s="109"/>
       <c r="E86" s="48">
-        <v>136.63999999999999</v>
+        <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="97"/>
-      <c r="B87" s="98"/>
-      <c r="C87" s="90" t="s">
+      <c r="A87" s="64"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="91"/>
+      <c r="D87" s="108"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77" t="s">
+      <c r="A88" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="77"/>
-      <c r="C88" s="85"/>
-      <c r="D88" s="85"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="88" t="s">
+      <c r="C89" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="88"/>
+      <c r="D89" s="58"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>84.539999999999964</v>
+        <v>14.839999999999691</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8133,92 +8134,92 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="89" t="s">
+      <c r="A92" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="89"/>
-      <c r="C92" s="89"/>
-      <c r="D92" s="89"/>
-      <c r="E92" s="89"/>
+      <c r="B92" s="71"/>
+      <c r="C92" s="71"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="71"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="74" t="s">
+      <c r="A93" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="74"/>
-      <c r="C93" s="74" t="s">
+      <c r="B93" s="72"/>
+      <c r="C93" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="74"/>
+      <c r="D93" s="72"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="76" t="s">
+      <c r="A94" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="76"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>84.539999999999964</v>
+        <v>14.839999999999691</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="93" t="s">
+      <c r="A95" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="94"/>
-      <c r="C95" s="99" t="s">
+      <c r="B95" s="61"/>
+      <c r="C95" s="104" t="s">
         <v>148</v>
       </c>
-      <c r="D95" s="100"/>
+      <c r="D95" s="105"/>
       <c r="E95" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="95"/>
-      <c r="B96" s="96"/>
-      <c r="C96" s="99" t="s">
+      <c r="A96" s="62"/>
+      <c r="B96" s="63"/>
+      <c r="C96" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="D96" s="100"/>
+      <c r="D96" s="105"/>
       <c r="E96" s="45">
         <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="97"/>
-      <c r="B97" s="98"/>
-      <c r="C97" s="99"/>
-      <c r="D97" s="100"/>
+      <c r="A97" s="64"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="104"/>
+      <c r="D97" s="105"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="85"/>
-      <c r="D98" s="85"/>
+      <c r="B98" s="56"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
       <c r="E98" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="88" t="s">
+      <c r="C99" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="88"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="47">
         <f>(E30+E94)-SUM(E95:E98)</f>
-        <v>1344.54</v>
+        <v>1274.8399999999997</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11967,15 +11968,48 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -11988,48 +12022,15 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A3B1AC-2E57-7640-A58C-B9E66B88B29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DA9FCD-D7F1-3A46-8DC6-303761A161C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
     <sheet name="July 2026- September 2026" sheetId="2" r:id="rId2"/>
+    <sheet name="October 2026- December 2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="166">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -701,6 +702,48 @@
    ~ Ustore 03/09 - $55.2
    ~ Ustore 05/09 - $9.8</t>
   </si>
+  <si>
+    <t>20th October 2026</t>
+  </si>
+  <si>
+    <t>Balance Brought Forward From October 2026</t>
+  </si>
+  <si>
+    <t>Alan Tang's Income Expense For the Forecast Year 2026 October - December 2026</t>
+  </si>
+  <si>
+    <t>18th December 2026</t>
+  </si>
+  <si>
+    <t>Fixed Expense For the Year 2026 October - December 2026</t>
+  </si>
+  <si>
+    <t>October 20th - November 19th 2026 Revenue / Defered Debts Or Expenses</t>
+  </si>
+  <si>
+    <t>November 20th - December 17th 2026 Revenue / Defered Debts Or Expenses</t>
+  </si>
+  <si>
+    <t>20th November 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming October 20th - November 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming November 20th - December 17th 2026</t>
+  </si>
+  <si>
+    <t>Balance Brought Forward From November 2026</t>
+  </si>
+  <si>
+    <t>December 18th - January 19th 2027 Revenue / Defered Debts Or Expenses</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming December 18th - January 19th 2027</t>
+  </si>
+  <si>
+    <t>Blance Brough Forward From September 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1230,17 +1273,119 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1260,41 +1405,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1305,119 +1444,43 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4472C4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF2E75B6"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1730,13 +1793,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1966,13 +2029,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2000,10 +2063,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="101"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2043,10 +2106,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2056,10 +2119,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="88"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2069,10 +2132,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="88"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2084,10 +2147,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="93"/>
+      <c r="D17" s="104"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2097,10 +2160,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="94"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2112,10 +2175,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="97"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2136,13 +2199,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2170,10 +2233,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="98" t="s">
+      <c r="C23" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="98"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2185,10 +2248,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2200,10 +2263,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="88"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2213,10 +2276,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="93"/>
+      <c r="D26" s="104"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2228,10 +2291,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="94"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2241,10 +2304,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="66"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2266,13 +2329,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="95" t="s">
+      <c r="A31" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2300,10 +2363,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="96" t="s">
+      <c r="C32" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="96"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2315,10 +2378,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="88"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2328,10 +2391,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="88"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2341,10 +2404,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="90"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2354,10 +2417,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="89" t="s">
+      <c r="C36" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="91"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2367,10 +2430,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="88"/>
+      <c r="D37" s="61"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2392,11 +2455,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2411,11 +2474,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="83" t="s">
+      <c r="A42" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2461,16 +2524,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="87"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="87"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2519,11 +2582,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="83" t="s">
+      <c r="A54" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2558,11 +2621,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="83" t="s">
+      <c r="A58" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2586,11 +2649,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="83" t="s">
+      <c r="A61" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="83"/>
-      <c r="C61" s="83"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2614,11 +2677,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="84"/>
-      <c r="C64" s="84"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2695,11 +2758,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="84"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2749,167 +2812,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="75" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="85" t="s">
+      <c r="B80" s="76"/>
+      <c r="C80" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="85"/>
+      <c r="D80" s="76"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="78" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="78"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="56"/>
-      <c r="C82" s="79" t="s">
+      <c r="B82" s="78"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="79"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="56"/>
-      <c r="B83" s="56"/>
-      <c r="C83" s="79" t="s">
+      <c r="A83" s="78"/>
+      <c r="B83" s="78"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="79"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="56"/>
-      <c r="B84" s="56"/>
-      <c r="C84" s="79" t="s">
+      <c r="A84" s="78"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="79"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="56"/>
-      <c r="B85" s="56"/>
-      <c r="C85" s="80" t="s">
+      <c r="A85" s="78"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="80"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="56"/>
-      <c r="B86" s="56"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="78"/>
+      <c r="B86" s="78"/>
+      <c r="C86" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="81"/>
+      <c r="D86" s="83"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="56"/>
-      <c r="B87" s="56"/>
-      <c r="C87" s="80" t="s">
+      <c r="A87" s="78"/>
+      <c r="B87" s="78"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="80"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="56"/>
-      <c r="B88" s="56"/>
-      <c r="C88" s="79" t="s">
+      <c r="A88" s="78"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="79"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="56"/>
-      <c r="B89" s="56"/>
-      <c r="C89" s="81" t="s">
+      <c r="A89" s="78"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="81"/>
+      <c r="D89" s="83"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="56"/>
-      <c r="B90" s="56"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="78"/>
+      <c r="B90" s="78"/>
+      <c r="C90" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="81"/>
+      <c r="D90" s="83"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="56"/>
-      <c r="B91" s="56"/>
-      <c r="C91" s="82" t="s">
+      <c r="A91" s="78"/>
+      <c r="B91" s="78"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="82"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="75"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
+      <c r="B92" s="79"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="84"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="85"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2917,113 +2980,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="72" t="s">
+      <c r="A95" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="72"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="72" t="s">
+      <c r="A96" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="72"/>
-      <c r="C96" s="72" t="s">
+      <c r="B96" s="75"/>
+      <c r="C96" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="72"/>
+      <c r="D96" s="75"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="59" t="s">
+      <c r="A97" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="59"/>
-      <c r="C97" s="57"/>
-      <c r="D97" s="57"/>
+      <c r="B97" s="77"/>
+      <c r="C97" s="86"/>
+      <c r="D97" s="86"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="56" t="s">
+      <c r="A98" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="73" t="s">
+      <c r="B98" s="78"/>
+      <c r="C98" s="82" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="82"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="56"/>
-      <c r="B99" s="56"/>
-      <c r="C99" s="74" t="s">
+      <c r="A99" s="78"/>
+      <c r="B99" s="78"/>
+      <c r="C99" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="74"/>
+      <c r="D99" s="80"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="56"/>
-      <c r="B100" s="56"/>
-      <c r="C100" s="74" t="s">
+      <c r="A100" s="78"/>
+      <c r="B100" s="78"/>
+      <c r="C100" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="74"/>
+      <c r="D100" s="80"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="56"/>
-      <c r="B101" s="56"/>
-      <c r="C101" s="74" t="s">
+      <c r="A101" s="78"/>
+      <c r="B101" s="78"/>
+      <c r="C101" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="80"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="56"/>
-      <c r="B102" s="56"/>
-      <c r="C102" s="69" t="s">
+      <c r="A102" s="78"/>
+      <c r="B102" s="78"/>
+      <c r="C102" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="70"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="56" t="s">
+      <c r="A103" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="56"/>
-      <c r="C103" s="57"/>
-      <c r="D103" s="57"/>
+      <c r="B103" s="78"/>
+      <c r="C103" s="86"/>
+      <c r="D103" s="86"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="58" t="s">
+      <c r="C104" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="58"/>
+      <c r="D104" s="89"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3044,91 +3107,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="71" t="s">
+      <c r="A107" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="71"/>
-      <c r="C107" s="71"/>
-      <c r="D107" s="71"/>
-      <c r="E107" s="71"/>
+      <c r="B107" s="90"/>
+      <c r="C107" s="90"/>
+      <c r="D107" s="90"/>
+      <c r="E107" s="90"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="72" t="s">
+      <c r="A108" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="72"/>
-      <c r="C108" s="72" t="s">
+      <c r="B108" s="75"/>
+      <c r="C108" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="72"/>
+      <c r="D108" s="75"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="59" t="s">
+      <c r="A109" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="59"/>
-      <c r="C109" s="57"/>
-      <c r="D109" s="57"/>
+      <c r="B109" s="77"/>
+      <c r="C109" s="86"/>
+      <c r="D109" s="86"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="60" t="s">
+      <c r="A110" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="61"/>
-      <c r="C110" s="66" t="s">
+      <c r="B110" s="95"/>
+      <c r="C110" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="66"/>
+      <c r="D110" s="108"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="62"/>
-      <c r="B111" s="63"/>
-      <c r="C111" s="67" t="s">
+      <c r="A111" s="96"/>
+      <c r="B111" s="97"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="68"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="64"/>
-      <c r="B112" s="65"/>
-      <c r="C112" s="69" t="s">
+      <c r="A112" s="98"/>
+      <c r="B112" s="99"/>
+      <c r="C112" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="56" t="s">
+      <c r="A113" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="56"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
+      <c r="B113" s="78"/>
+      <c r="C113" s="86"/>
+      <c r="D113" s="86"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="58" t="s">
+      <c r="C114" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="58"/>
+      <c r="D114" s="89"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6880,42 +6943,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6929,49 +6985,56 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E93 E97 E104 E109 E114">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6997,13 +7060,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7238,13 +7301,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7272,10 +7335,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="101"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7287,10 +7350,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="59"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7302,10 +7365,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="88"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7317,10 +7380,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="92" t="s">
+      <c r="C14" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7341,13 +7404,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7375,10 +7438,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="96" t="s">
+      <c r="C18" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="96"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7390,10 +7453,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="88"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7405,10 +7468,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="89" t="s">
+      <c r="C20" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="90"/>
+      <c r="D20" s="67"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7420,10 +7483,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="111" t="s">
+      <c r="C21" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="112"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7435,10 +7498,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="90"/>
+      <c r="D22" s="67"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7450,10 +7513,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="D23" s="114"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="29">
         <v>1000</v>
       </c>
@@ -7475,13 +7538,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7509,10 +7572,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="96" t="s">
+      <c r="C27" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="96"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7524,10 +7587,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="88"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7535,8 +7598,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7558,11 +7621,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="86" t="s">
+      <c r="A32" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7577,11 +7640,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="83" t="s">
+      <c r="A34" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7627,16 +7690,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
+      <c r="A40" s="73"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7685,11 +7748,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="83" t="s">
+      <c r="A46" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7724,11 +7787,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="83" t="s">
+      <c r="A50" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7752,11 +7815,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="83" t="s">
+      <c r="A53" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7780,11 +7843,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="84" t="s">
+      <c r="A56" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="84"/>
-      <c r="C56" s="84"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7861,11 +7924,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="84"/>
-      <c r="C64" s="84"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7915,91 +7978,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="72" t="s">
+      <c r="A71" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="72"/>
-      <c r="C71" s="72"/>
-      <c r="D71" s="72"/>
-      <c r="E71" s="72"/>
+      <c r="B71" s="75"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="85" t="s">
+      <c r="A72" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="85" t="s">
+      <c r="B72" s="76"/>
+      <c r="C72" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="85"/>
+      <c r="D72" s="76"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="59" t="s">
+      <c r="A73" s="77" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="59"/>
-      <c r="C73" s="56"/>
-      <c r="D73" s="56"/>
+      <c r="B73" s="77"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="78"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="75"/>
-      <c r="C74" s="74" t="s">
+      <c r="B74" s="79"/>
+      <c r="C74" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="74"/>
+      <c r="D74" s="80"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="75"/>
-      <c r="B75" s="75"/>
-      <c r="C75" s="110" t="s">
+      <c r="A75" s="79"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="73"/>
+      <c r="D75" s="82"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="75"/>
-      <c r="B76" s="75"/>
-      <c r="C76" s="110" t="s">
+      <c r="A76" s="79"/>
+      <c r="B76" s="79"/>
+      <c r="C76" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="81"/>
+      <c r="D76" s="83"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="75" t="s">
+      <c r="A77" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="75"/>
-      <c r="C77" s="76"/>
-      <c r="D77" s="76"/>
+      <c r="B77" s="79"/>
+      <c r="C77" s="84"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="77" t="s">
+      <c r="C78" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="77"/>
+      <c r="D78" s="85"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8007,113 +8070,113 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="72" t="s">
+      <c r="A81" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72" t="s">
+      <c r="B81" s="75"/>
+      <c r="C81" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="72"/>
+      <c r="D81" s="75"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="59" t="s">
+      <c r="A82" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
+      <c r="B82" s="77"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="86"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="106" t="s">
+      <c r="B83" s="95"/>
+      <c r="C83" s="87" t="s">
         <v>144</v>
       </c>
-      <c r="D83" s="107"/>
+      <c r="D83" s="88"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="62"/>
-      <c r="B84" s="63"/>
-      <c r="C84" s="74" t="s">
+      <c r="A84" s="96"/>
+      <c r="B84" s="97"/>
+      <c r="C84" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="D84" s="74"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="48">
         <v>721.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="137" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="62"/>
-      <c r="B85" s="63"/>
-      <c r="C85" s="69" t="s">
+      <c r="A85" s="96"/>
+      <c r="B85" s="97"/>
+      <c r="C85" s="91" t="s">
         <v>150</v>
       </c>
-      <c r="D85" s="108"/>
+      <c r="D85" s="92"/>
       <c r="E85" s="48">
         <v>312.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="62"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="106" t="s">
+      <c r="A86" s="96"/>
+      <c r="B86" s="97"/>
+      <c r="C86" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="109"/>
+      <c r="D86" s="93"/>
       <c r="E86" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="64"/>
-      <c r="B87" s="65"/>
-      <c r="C87" s="69" t="s">
+      <c r="A87" s="98"/>
+      <c r="B87" s="99"/>
+      <c r="C87" s="91" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="108"/>
+      <c r="D87" s="92"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="56" t="s">
+      <c r="A88" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="56"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="57"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="86"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="58" t="s">
+      <c r="C89" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="58"/>
+      <c r="D89" s="89"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
         <v>14.839999999999691</v>
@@ -8134,89 +8197,89 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="90" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="71"/>
-      <c r="C92" s="71"/>
-      <c r="D92" s="71"/>
-      <c r="E92" s="71"/>
+      <c r="B92" s="90"/>
+      <c r="C92" s="90"/>
+      <c r="D92" s="90"/>
+      <c r="E92" s="90"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="72" t="s">
+      <c r="A93" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72" t="s">
+      <c r="B93" s="75"/>
+      <c r="C93" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="72"/>
+      <c r="D93" s="75"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="59" t="s">
+      <c r="A94" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="59"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="57"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="86"/>
+      <c r="D94" s="86"/>
       <c r="E94" s="47">
         <f>E89</f>
         <v>14.839999999999691</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="60" t="s">
+      <c r="A95" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="61"/>
-      <c r="C95" s="104" t="s">
+      <c r="B95" s="95"/>
+      <c r="C95" s="100" t="s">
         <v>148</v>
       </c>
-      <c r="D95" s="105"/>
+      <c r="D95" s="101"/>
       <c r="E95" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="62"/>
-      <c r="B96" s="63"/>
-      <c r="C96" s="104" t="s">
+      <c r="A96" s="96"/>
+      <c r="B96" s="97"/>
+      <c r="C96" s="100" t="s">
         <v>147</v>
       </c>
-      <c r="D96" s="105"/>
+      <c r="D96" s="101"/>
       <c r="E96" s="45">
         <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="64"/>
-      <c r="B97" s="65"/>
-      <c r="C97" s="104"/>
-      <c r="D97" s="105"/>
+      <c r="A97" s="98"/>
+      <c r="B97" s="99"/>
+      <c r="C97" s="100"/>
+      <c r="D97" s="101"/>
       <c r="E97" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="56" t="s">
+      <c r="A98" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="57"/>
-      <c r="D98" s="57"/>
+      <c r="B98" s="78"/>
+      <c r="C98" s="86"/>
+      <c r="D98" s="86"/>
       <c r="E98" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="58" t="s">
+      <c r="C99" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="58"/>
+      <c r="D99" s="89"/>
       <c r="E99" s="47">
         <f>(E30+E94)-SUM(E95:E98)</f>
         <v>1274.8399999999997</v>
@@ -11968,48 +12031,15 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A95:B97"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12022,33 +12052,5042 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E78 E82 E89 E94 E99">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7D833F-4941-DA48-8974-C05250C51A36}">
+  <dimension ref="A1:Y1031"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="24.5" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="25" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9">
+        <f>'April 2026 - June 2026'!C3</f>
+        <v>19.04</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+    </row>
+    <row r="4" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9">
+        <f>'April 2026 - June 2026'!C4</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+    </row>
+    <row r="5" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9">
+        <f>'April 2026 - June 2026'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+    </row>
+    <row r="6" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9">
+        <f>'April 2026 - June 2026'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+    </row>
+    <row r="7" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9">
+        <f>'April 2026 - June 2026'!C7</f>
+        <v>-6.4</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+    </row>
+    <row r="8" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9">
+        <f>'April 2026 - June 2026'!C8</f>
+        <v>14.839999999999998</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+    </row>
+    <row r="9" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+    </row>
+    <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+    </row>
+    <row r="11" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="58"/>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="52">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="26">
+        <f>SUM(E12:E13)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+    </row>
+    <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="63"/>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="61"/>
+      <c r="E18" s="29">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="26">
+        <f>SUM(E18:E19)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+    </row>
+    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+    </row>
+    <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="63"/>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="61"/>
+      <c r="E24" s="33">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="35">
+        <f>SUM(E24:E25)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+    </row>
+    <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+    </row>
+    <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="37"/>
+    </row>
+    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+    </row>
+    <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="33">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="38">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7"/>
+      <c r="B34" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="39">
+        <f>SUM(C31:C33)</f>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+    </row>
+    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="73"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+    </row>
+    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="39">
+        <f>SUM(C37:C40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+    </row>
+    <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="39">
+        <f>SUM(C43:C44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="72"/>
+      <c r="C46" s="72"/>
+    </row>
+    <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="39">
+        <f>SUM(C47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="39">
+        <f>SUM(C50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="74"/>
+      <c r="C52" s="74"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="29">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="39">
+        <f>SUM(C53:C58)</f>
+        <v>955</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="74"/>
+      <c r="C60" s="74"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="19">
+        <f>SUM(C61:C62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="6"/>
+      <c r="B64" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="41">
+        <f>C34+C41+C45+C48+C51+C59</f>
+        <v>1171</v>
+      </c>
+      <c r="H64" s="42"/>
+    </row>
+    <row r="65" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+    </row>
+    <row r="66" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+    </row>
+    <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="75"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+    </row>
+    <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="76"/>
+      <c r="C68" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="76"/>
+      <c r="E68" s="44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="B69" s="77"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="47">
+        <f>'July 2026- September 2026'!E99</f>
+        <v>1274.8399999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="79"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="79"/>
+      <c r="B71" s="79"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="79"/>
+      <c r="B72" s="79"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="79"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="84"/>
+      <c r="E73" s="46">
+        <f>C64</f>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D74" s="85"/>
+      <c r="E74" s="47">
+        <f>(E14+E69)-SUM(E70:E73)</f>
+        <v>2588.8399999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="75"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+    </row>
+    <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="75"/>
+      <c r="E77" s="43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="77"/>
+      <c r="C78" s="86"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="47">
+        <f>E74</f>
+        <v>2588.8399999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="95"/>
+      <c r="C79" s="87"/>
+      <c r="D79" s="88"/>
+      <c r="E79" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="96"/>
+      <c r="B80" s="97"/>
+      <c r="C80" s="80"/>
+      <c r="D80" s="80"/>
+      <c r="E80" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="87"/>
+      <c r="D82" s="93"/>
+      <c r="E82" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="98"/>
+      <c r="B83" s="99"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="92"/>
+      <c r="E83" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="78"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="45">
+        <f>C64</f>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C85" s="89" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" s="89"/>
+      <c r="E85" s="47">
+        <f>(E20+E78)-SUM(E79:E84)</f>
+        <v>3902.84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="49"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="49"/>
+      <c r="E86" s="49"/>
+    </row>
+    <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+    </row>
+    <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="90" t="s">
+        <v>164</v>
+      </c>
+      <c r="B88" s="90"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="90"/>
+      <c r="E88" s="90"/>
+    </row>
+    <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" s="75"/>
+      <c r="C89" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="75"/>
+      <c r="E89" s="43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" s="77"/>
+      <c r="C90" s="86"/>
+      <c r="D90" s="86"/>
+      <c r="E90" s="47">
+        <f>E85</f>
+        <v>3902.84</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="95"/>
+      <c r="C91" s="100"/>
+      <c r="D91" s="101"/>
+      <c r="E91" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="96"/>
+      <c r="B92" s="97"/>
+      <c r="C92" s="100"/>
+      <c r="D92" s="101"/>
+      <c r="E92" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="98"/>
+      <c r="B93" s="99"/>
+      <c r="C93" s="100"/>
+      <c r="D93" s="101"/>
+      <c r="E93" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="78"/>
+      <c r="C94" s="86"/>
+      <c r="D94" s="86"/>
+      <c r="E94" s="45">
+        <f>C64</f>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C95" s="89" t="s">
+        <v>96</v>
+      </c>
+      <c r="D95" s="89"/>
+      <c r="E95" s="47">
+        <f>(E26+E90)-SUM(E91:E94)</f>
+        <v>5216.84</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="24"/>
+      <c r="B96" s="24"/>
+    </row>
+    <row r="97" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="24"/>
+      <c r="B97" s="24"/>
+    </row>
+    <row r="98" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="24"/>
+      <c r="B98" s="24"/>
+    </row>
+    <row r="99" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="24"/>
+      <c r="B99" s="24"/>
+    </row>
+    <row r="100" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="24"/>
+      <c r="B100" s="24"/>
+    </row>
+    <row r="101" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="24"/>
+      <c r="B101" s="24"/>
+    </row>
+    <row r="102" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="24"/>
+      <c r="B102" s="24"/>
+    </row>
+    <row r="103" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="24"/>
+      <c r="B103" s="24"/>
+    </row>
+    <row r="104" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="24"/>
+      <c r="B104" s="24"/>
+    </row>
+    <row r="105" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="24"/>
+      <c r="B105" s="24"/>
+    </row>
+    <row r="106" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="24"/>
+      <c r="B106" s="24"/>
+    </row>
+    <row r="107" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="24"/>
+      <c r="B107" s="24"/>
+    </row>
+    <row r="108" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="24"/>
+      <c r="B108" s="24"/>
+    </row>
+    <row r="109" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="24"/>
+      <c r="B109" s="24"/>
+    </row>
+    <row r="110" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="24"/>
+      <c r="B110" s="24"/>
+    </row>
+    <row r="111" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="24"/>
+      <c r="B111" s="24"/>
+    </row>
+    <row r="112" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="24"/>
+      <c r="B112" s="24"/>
+    </row>
+    <row r="113" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="24"/>
+      <c r="B113" s="24"/>
+    </row>
+    <row r="114" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="24"/>
+      <c r="B114" s="24"/>
+    </row>
+    <row r="115" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="24"/>
+      <c r="B115" s="24"/>
+    </row>
+    <row r="116" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="24"/>
+      <c r="B116" s="24"/>
+    </row>
+    <row r="117" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="24"/>
+      <c r="B117" s="24"/>
+    </row>
+    <row r="118" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="24"/>
+      <c r="B118" s="24"/>
+    </row>
+    <row r="119" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="24"/>
+      <c r="B119" s="24"/>
+    </row>
+    <row r="120" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="24"/>
+      <c r="B120" s="24"/>
+    </row>
+    <row r="121" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="24"/>
+      <c r="B121" s="24"/>
+    </row>
+    <row r="122" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="24"/>
+      <c r="B122" s="24"/>
+    </row>
+    <row r="123" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="24"/>
+      <c r="B123" s="24"/>
+    </row>
+    <row r="124" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="24"/>
+      <c r="B124" s="24"/>
+    </row>
+    <row r="125" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="24"/>
+      <c r="B125" s="24"/>
+    </row>
+    <row r="126" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="24"/>
+      <c r="B126" s="24"/>
+    </row>
+    <row r="127" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="24"/>
+      <c r="B127" s="24"/>
+    </row>
+    <row r="128" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="24"/>
+      <c r="B128" s="24"/>
+    </row>
+    <row r="129" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="24"/>
+      <c r="B129" s="24"/>
+    </row>
+    <row r="130" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="24"/>
+      <c r="B130" s="24"/>
+    </row>
+    <row r="131" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="24"/>
+      <c r="B131" s="24"/>
+    </row>
+    <row r="132" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="24"/>
+      <c r="B132" s="24"/>
+    </row>
+    <row r="133" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="24"/>
+      <c r="B133" s="24"/>
+    </row>
+    <row r="134" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="24"/>
+      <c r="B134" s="24"/>
+    </row>
+    <row r="135" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="24"/>
+      <c r="B135" s="24"/>
+    </row>
+    <row r="136" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="24"/>
+      <c r="B136" s="24"/>
+    </row>
+    <row r="137" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="24"/>
+      <c r="B137" s="24"/>
+    </row>
+    <row r="138" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="24"/>
+      <c r="B138" s="24"/>
+    </row>
+    <row r="139" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="24"/>
+      <c r="B139" s="24"/>
+    </row>
+    <row r="140" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="24"/>
+      <c r="B140" s="24"/>
+    </row>
+    <row r="141" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="24"/>
+      <c r="B141" s="24"/>
+    </row>
+    <row r="142" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="24"/>
+      <c r="B142" s="24"/>
+    </row>
+    <row r="143" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="24"/>
+      <c r="B143" s="24"/>
+    </row>
+    <row r="144" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="24"/>
+      <c r="B144" s="24"/>
+    </row>
+    <row r="145" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="24"/>
+      <c r="B145" s="24"/>
+    </row>
+    <row r="146" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="24"/>
+      <c r="B146" s="24"/>
+    </row>
+    <row r="147" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="24"/>
+      <c r="B147" s="24"/>
+    </row>
+    <row r="148" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="24"/>
+      <c r="B148" s="24"/>
+    </row>
+    <row r="149" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="24"/>
+      <c r="B149" s="24"/>
+    </row>
+    <row r="150" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="24"/>
+      <c r="B150" s="24"/>
+    </row>
+    <row r="151" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="24"/>
+      <c r="B151" s="24"/>
+    </row>
+    <row r="152" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="24"/>
+      <c r="B152" s="24"/>
+    </row>
+    <row r="153" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="24"/>
+      <c r="B153" s="24"/>
+    </row>
+    <row r="154" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="24"/>
+      <c r="B154" s="24"/>
+    </row>
+    <row r="155" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="24"/>
+      <c r="B155" s="24"/>
+    </row>
+    <row r="156" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="24"/>
+      <c r="B156" s="24"/>
+    </row>
+    <row r="157" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="24"/>
+      <c r="B157" s="24"/>
+    </row>
+    <row r="158" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="24"/>
+      <c r="B158" s="24"/>
+    </row>
+    <row r="159" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="24"/>
+      <c r="B159" s="24"/>
+    </row>
+    <row r="160" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="24"/>
+      <c r="B160" s="24"/>
+    </row>
+    <row r="161" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="24"/>
+      <c r="B161" s="24"/>
+    </row>
+    <row r="162" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="24"/>
+      <c r="B162" s="24"/>
+    </row>
+    <row r="163" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="24"/>
+      <c r="B163" s="24"/>
+    </row>
+    <row r="164" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="24"/>
+      <c r="B164" s="24"/>
+    </row>
+    <row r="165" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="24"/>
+      <c r="B165" s="24"/>
+    </row>
+    <row r="166" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="24"/>
+      <c r="B166" s="24"/>
+    </row>
+    <row r="167" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="24"/>
+      <c r="B167" s="24"/>
+    </row>
+    <row r="168" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="24"/>
+      <c r="B168" s="24"/>
+    </row>
+    <row r="169" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="24"/>
+      <c r="B169" s="24"/>
+    </row>
+    <row r="170" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="24"/>
+      <c r="B170" s="24"/>
+    </row>
+    <row r="171" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="24"/>
+      <c r="B171" s="24"/>
+    </row>
+    <row r="172" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="24"/>
+      <c r="B172" s="24"/>
+    </row>
+    <row r="173" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="24"/>
+      <c r="B173" s="24"/>
+    </row>
+    <row r="174" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="24"/>
+      <c r="B174" s="24"/>
+    </row>
+    <row r="175" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="24"/>
+      <c r="B175" s="24"/>
+    </row>
+    <row r="176" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="24"/>
+      <c r="B176" s="24"/>
+    </row>
+    <row r="177" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="24"/>
+      <c r="B177" s="24"/>
+    </row>
+    <row r="178" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="24"/>
+      <c r="B178" s="24"/>
+    </row>
+    <row r="179" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="24"/>
+      <c r="B179" s="24"/>
+    </row>
+    <row r="180" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="24"/>
+      <c r="B180" s="24"/>
+    </row>
+    <row r="181" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="24"/>
+      <c r="B181" s="24"/>
+    </row>
+    <row r="182" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="24"/>
+      <c r="B182" s="24"/>
+    </row>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="24"/>
+      <c r="B183" s="24"/>
+    </row>
+    <row r="184" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="24"/>
+      <c r="B184" s="24"/>
+    </row>
+    <row r="185" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="24"/>
+      <c r="B185" s="24"/>
+    </row>
+    <row r="186" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="24"/>
+      <c r="B186" s="24"/>
+    </row>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="24"/>
+      <c r="B187" s="24"/>
+    </row>
+    <row r="188" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="24"/>
+      <c r="B188" s="24"/>
+    </row>
+    <row r="189" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="24"/>
+      <c r="B189" s="24"/>
+    </row>
+    <row r="190" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="24"/>
+      <c r="B190" s="24"/>
+    </row>
+    <row r="191" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="24"/>
+      <c r="B191" s="24"/>
+    </row>
+    <row r="192" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="24"/>
+      <c r="B192" s="24"/>
+    </row>
+    <row r="193" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="24"/>
+      <c r="B193" s="24"/>
+    </row>
+    <row r="194" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="24"/>
+      <c r="B194" s="24"/>
+    </row>
+    <row r="195" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="24"/>
+      <c r="B195" s="24"/>
+    </row>
+    <row r="196" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="24"/>
+      <c r="B196" s="24"/>
+    </row>
+    <row r="197" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="24"/>
+      <c r="B197" s="24"/>
+    </row>
+    <row r="198" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="24"/>
+      <c r="B198" s="24"/>
+    </row>
+    <row r="199" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="24"/>
+      <c r="B199" s="24"/>
+    </row>
+    <row r="200" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="24"/>
+      <c r="B200" s="24"/>
+    </row>
+    <row r="201" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="24"/>
+      <c r="B201" s="24"/>
+    </row>
+    <row r="202" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="24"/>
+      <c r="B202" s="24"/>
+    </row>
+    <row r="203" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="24"/>
+      <c r="B203" s="24"/>
+    </row>
+    <row r="204" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="24"/>
+      <c r="B204" s="24"/>
+    </row>
+    <row r="205" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="24"/>
+      <c r="B205" s="24"/>
+    </row>
+    <row r="206" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="24"/>
+      <c r="B206" s="24"/>
+    </row>
+    <row r="207" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="24"/>
+      <c r="B207" s="24"/>
+    </row>
+    <row r="208" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="24"/>
+      <c r="B208" s="24"/>
+    </row>
+    <row r="209" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="24"/>
+      <c r="B209" s="24"/>
+    </row>
+    <row r="210" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="24"/>
+      <c r="B210" s="24"/>
+    </row>
+    <row r="211" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="24"/>
+      <c r="B211" s="24"/>
+    </row>
+    <row r="212" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="24"/>
+      <c r="B212" s="24"/>
+    </row>
+    <row r="213" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="24"/>
+      <c r="B213" s="24"/>
+    </row>
+    <row r="214" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="24"/>
+      <c r="B214" s="24"/>
+    </row>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="24"/>
+      <c r="B215" s="24"/>
+    </row>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="24"/>
+      <c r="B216" s="24"/>
+    </row>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="24"/>
+      <c r="B217" s="24"/>
+    </row>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="24"/>
+      <c r="B218" s="24"/>
+    </row>
+    <row r="219" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="24"/>
+      <c r="B219" s="24"/>
+    </row>
+    <row r="220" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="24"/>
+      <c r="B220" s="24"/>
+    </row>
+    <row r="221" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="24"/>
+      <c r="B221" s="24"/>
+    </row>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="24"/>
+      <c r="B222" s="24"/>
+    </row>
+    <row r="223" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="24"/>
+      <c r="B223" s="24"/>
+    </row>
+    <row r="224" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="24"/>
+      <c r="B224" s="24"/>
+    </row>
+    <row r="225" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="24"/>
+      <c r="B225" s="24"/>
+    </row>
+    <row r="226" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="24"/>
+      <c r="B226" s="24"/>
+    </row>
+    <row r="227" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="24"/>
+      <c r="B227" s="24"/>
+    </row>
+    <row r="228" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="24"/>
+      <c r="B228" s="24"/>
+    </row>
+    <row r="229" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="24"/>
+      <c r="B229" s="24"/>
+    </row>
+    <row r="230" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="24"/>
+      <c r="B230" s="24"/>
+    </row>
+    <row r="231" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="24"/>
+      <c r="B231" s="24"/>
+    </row>
+    <row r="232" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="24"/>
+      <c r="B232" s="24"/>
+    </row>
+    <row r="233" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="24"/>
+      <c r="B233" s="24"/>
+    </row>
+    <row r="234" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="24"/>
+      <c r="B234" s="24"/>
+    </row>
+    <row r="235" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="24"/>
+      <c r="B235" s="24"/>
+    </row>
+    <row r="236" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="24"/>
+      <c r="B236" s="24"/>
+    </row>
+    <row r="237" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="24"/>
+      <c r="B237" s="24"/>
+    </row>
+    <row r="238" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="24"/>
+      <c r="B238" s="24"/>
+    </row>
+    <row r="239" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="24"/>
+      <c r="B239" s="24"/>
+    </row>
+    <row r="240" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="24"/>
+      <c r="B240" s="24"/>
+    </row>
+    <row r="241" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="24"/>
+      <c r="B241" s="24"/>
+    </row>
+    <row r="242" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="24"/>
+      <c r="B242" s="24"/>
+    </row>
+    <row r="243" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="24"/>
+      <c r="B243" s="24"/>
+    </row>
+    <row r="244" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="24"/>
+      <c r="B244" s="24"/>
+    </row>
+    <row r="245" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="24"/>
+      <c r="B245" s="24"/>
+    </row>
+    <row r="246" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="24"/>
+      <c r="B246" s="24"/>
+    </row>
+    <row r="247" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="24"/>
+      <c r="B247" s="24"/>
+    </row>
+    <row r="248" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="24"/>
+      <c r="B248" s="24"/>
+    </row>
+    <row r="249" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="24"/>
+      <c r="B249" s="24"/>
+    </row>
+    <row r="250" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="24"/>
+      <c r="B250" s="24"/>
+    </row>
+    <row r="251" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="24"/>
+      <c r="B251" s="24"/>
+    </row>
+    <row r="252" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="24"/>
+      <c r="B252" s="24"/>
+    </row>
+    <row r="253" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="24"/>
+      <c r="B253" s="24"/>
+    </row>
+    <row r="254" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="24"/>
+      <c r="B254" s="24"/>
+    </row>
+    <row r="255" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="24"/>
+      <c r="B255" s="24"/>
+    </row>
+    <row r="256" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="24"/>
+      <c r="B256" s="24"/>
+    </row>
+    <row r="257" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="24"/>
+      <c r="B257" s="24"/>
+    </row>
+    <row r="258" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="24"/>
+      <c r="B258" s="24"/>
+    </row>
+    <row r="259" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="24"/>
+      <c r="B259" s="24"/>
+    </row>
+    <row r="260" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="24"/>
+      <c r="B260" s="24"/>
+    </row>
+    <row r="261" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="24"/>
+      <c r="B261" s="24"/>
+    </row>
+    <row r="262" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="24"/>
+      <c r="B262" s="24"/>
+    </row>
+    <row r="263" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="24"/>
+      <c r="B263" s="24"/>
+    </row>
+    <row r="264" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="24"/>
+      <c r="B264" s="24"/>
+    </row>
+    <row r="265" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="24"/>
+      <c r="B265" s="24"/>
+    </row>
+    <row r="266" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="24"/>
+      <c r="B266" s="24"/>
+    </row>
+    <row r="267" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="24"/>
+      <c r="B267" s="24"/>
+    </row>
+    <row r="268" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="24"/>
+      <c r="B268" s="24"/>
+    </row>
+    <row r="269" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="24"/>
+      <c r="B269" s="24"/>
+    </row>
+    <row r="270" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="24"/>
+      <c r="B270" s="24"/>
+    </row>
+    <row r="271" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="24"/>
+      <c r="B271" s="24"/>
+    </row>
+    <row r="272" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="24"/>
+      <c r="B272" s="24"/>
+    </row>
+    <row r="273" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="24"/>
+      <c r="B273" s="24"/>
+    </row>
+    <row r="274" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="24"/>
+      <c r="B274" s="24"/>
+    </row>
+    <row r="275" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="24"/>
+      <c r="B275" s="24"/>
+    </row>
+    <row r="276" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="24"/>
+      <c r="B276" s="24"/>
+    </row>
+    <row r="277" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="24"/>
+      <c r="B277" s="24"/>
+    </row>
+    <row r="278" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="24"/>
+      <c r="B278" s="24"/>
+    </row>
+    <row r="279" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="24"/>
+      <c r="B279" s="24"/>
+    </row>
+    <row r="280" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="24"/>
+      <c r="B280" s="24"/>
+    </row>
+    <row r="281" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="24"/>
+      <c r="B281" s="24"/>
+    </row>
+    <row r="282" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="24"/>
+      <c r="B282" s="24"/>
+    </row>
+    <row r="283" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="24"/>
+      <c r="B283" s="24"/>
+    </row>
+    <row r="284" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="24"/>
+      <c r="B284" s="24"/>
+    </row>
+    <row r="285" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="24"/>
+      <c r="B285" s="24"/>
+    </row>
+    <row r="286" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="24"/>
+      <c r="B286" s="24"/>
+    </row>
+    <row r="287" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="24"/>
+      <c r="B287" s="24"/>
+    </row>
+    <row r="288" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="24"/>
+      <c r="B288" s="24"/>
+    </row>
+    <row r="289" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="24"/>
+      <c r="B289" s="24"/>
+    </row>
+    <row r="290" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="24"/>
+      <c r="B290" s="24"/>
+    </row>
+    <row r="291" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="24"/>
+      <c r="B291" s="24"/>
+    </row>
+    <row r="292" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="24"/>
+      <c r="B292" s="24"/>
+    </row>
+    <row r="293" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="24"/>
+      <c r="B293" s="24"/>
+    </row>
+    <row r="294" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="24"/>
+      <c r="B294" s="24"/>
+    </row>
+    <row r="295" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="24"/>
+      <c r="B295" s="24"/>
+    </row>
+    <row r="296" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="24"/>
+      <c r="B296" s="24"/>
+    </row>
+    <row r="297" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="24"/>
+      <c r="B297" s="24"/>
+    </row>
+    <row r="298" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="24"/>
+      <c r="B298" s="24"/>
+    </row>
+    <row r="299" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="24"/>
+      <c r="B299" s="24"/>
+    </row>
+    <row r="300" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="24"/>
+      <c r="B300" s="24"/>
+    </row>
+    <row r="301" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="24"/>
+      <c r="B301" s="24"/>
+    </row>
+    <row r="302" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="24"/>
+      <c r="B302" s="24"/>
+    </row>
+    <row r="303" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="24"/>
+      <c r="B303" s="24"/>
+    </row>
+    <row r="304" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="24"/>
+      <c r="B304" s="24"/>
+    </row>
+    <row r="305" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="24"/>
+      <c r="B305" s="24"/>
+    </row>
+    <row r="306" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="24"/>
+      <c r="B306" s="24"/>
+    </row>
+    <row r="307" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="24"/>
+      <c r="B307" s="24"/>
+    </row>
+    <row r="308" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="24"/>
+      <c r="B308" s="24"/>
+    </row>
+    <row r="309" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="24"/>
+      <c r="B309" s="24"/>
+    </row>
+    <row r="310" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="24"/>
+      <c r="B310" s="24"/>
+    </row>
+    <row r="311" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="24"/>
+      <c r="B311" s="24"/>
+    </row>
+    <row r="312" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="24"/>
+      <c r="B312" s="24"/>
+    </row>
+    <row r="313" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="24"/>
+      <c r="B313" s="24"/>
+    </row>
+    <row r="314" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="24"/>
+      <c r="B314" s="24"/>
+    </row>
+    <row r="315" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="24"/>
+      <c r="B315" s="24"/>
+    </row>
+    <row r="316" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="24"/>
+      <c r="B316" s="24"/>
+    </row>
+    <row r="317" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="24"/>
+      <c r="B317" s="24"/>
+    </row>
+    <row r="318" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="24"/>
+      <c r="B318" s="24"/>
+    </row>
+    <row r="319" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="24"/>
+      <c r="B319" s="24"/>
+    </row>
+    <row r="320" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="24"/>
+      <c r="B320" s="24"/>
+    </row>
+    <row r="321" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="24"/>
+      <c r="B321" s="24"/>
+    </row>
+    <row r="322" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="24"/>
+      <c r="B322" s="24"/>
+    </row>
+    <row r="323" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="24"/>
+      <c r="B323" s="24"/>
+    </row>
+    <row r="324" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="24"/>
+      <c r="B324" s="24"/>
+    </row>
+    <row r="325" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="24"/>
+      <c r="B325" s="24"/>
+    </row>
+    <row r="326" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="24"/>
+      <c r="B326" s="24"/>
+    </row>
+    <row r="327" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="24"/>
+      <c r="B327" s="24"/>
+    </row>
+    <row r="328" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="24"/>
+      <c r="B328" s="24"/>
+    </row>
+    <row r="329" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="24"/>
+      <c r="B329" s="24"/>
+    </row>
+    <row r="330" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="24"/>
+      <c r="B330" s="24"/>
+    </row>
+    <row r="331" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="24"/>
+      <c r="B331" s="24"/>
+    </row>
+    <row r="332" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="24"/>
+      <c r="B332" s="24"/>
+    </row>
+    <row r="333" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="24"/>
+      <c r="B333" s="24"/>
+    </row>
+    <row r="334" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="24"/>
+      <c r="B334" s="24"/>
+    </row>
+    <row r="335" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="24"/>
+      <c r="B335" s="24"/>
+    </row>
+    <row r="336" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="24"/>
+      <c r="B336" s="24"/>
+    </row>
+    <row r="337" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="24"/>
+      <c r="B337" s="24"/>
+    </row>
+    <row r="338" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="24"/>
+      <c r="B338" s="24"/>
+    </row>
+    <row r="339" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="24"/>
+      <c r="B339" s="24"/>
+    </row>
+    <row r="340" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="24"/>
+      <c r="B340" s="24"/>
+    </row>
+    <row r="341" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="24"/>
+      <c r="B341" s="24"/>
+    </row>
+    <row r="342" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="24"/>
+      <c r="B342" s="24"/>
+    </row>
+    <row r="343" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="24"/>
+      <c r="B343" s="24"/>
+    </row>
+    <row r="344" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="24"/>
+      <c r="B344" s="24"/>
+    </row>
+    <row r="345" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="24"/>
+      <c r="B345" s="24"/>
+    </row>
+    <row r="346" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="24"/>
+      <c r="B346" s="24"/>
+    </row>
+    <row r="347" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="24"/>
+      <c r="B347" s="24"/>
+    </row>
+    <row r="348" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348" s="24"/>
+      <c r="B348" s="24"/>
+    </row>
+    <row r="349" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="24"/>
+      <c r="B349" s="24"/>
+    </row>
+    <row r="350" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="24"/>
+      <c r="B350" s="24"/>
+    </row>
+    <row r="351" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="24"/>
+      <c r="B351" s="24"/>
+    </row>
+    <row r="352" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="24"/>
+      <c r="B352" s="24"/>
+    </row>
+    <row r="353" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="24"/>
+      <c r="B353" s="24"/>
+    </row>
+    <row r="354" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="24"/>
+      <c r="B354" s="24"/>
+    </row>
+    <row r="355" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355" s="24"/>
+      <c r="B355" s="24"/>
+    </row>
+    <row r="356" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A356" s="24"/>
+      <c r="B356" s="24"/>
+    </row>
+    <row r="357" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A357" s="24"/>
+      <c r="B357" s="24"/>
+    </row>
+    <row r="358" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A358" s="24"/>
+      <c r="B358" s="24"/>
+    </row>
+    <row r="359" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A359" s="24"/>
+      <c r="B359" s="24"/>
+    </row>
+    <row r="360" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A360" s="24"/>
+      <c r="B360" s="24"/>
+    </row>
+    <row r="361" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A361" s="24"/>
+      <c r="B361" s="24"/>
+    </row>
+    <row r="362" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A362" s="24"/>
+      <c r="B362" s="24"/>
+    </row>
+    <row r="363" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363" s="24"/>
+      <c r="B363" s="24"/>
+    </row>
+    <row r="364" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" s="24"/>
+      <c r="B364" s="24"/>
+    </row>
+    <row r="365" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365" s="24"/>
+      <c r="B365" s="24"/>
+    </row>
+    <row r="366" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="24"/>
+      <c r="B366" s="24"/>
+    </row>
+    <row r="367" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="24"/>
+      <c r="B367" s="24"/>
+    </row>
+    <row r="368" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368" s="24"/>
+      <c r="B368" s="24"/>
+    </row>
+    <row r="369" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369" s="24"/>
+      <c r="B369" s="24"/>
+    </row>
+    <row r="370" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370" s="24"/>
+      <c r="B370" s="24"/>
+    </row>
+    <row r="371" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A371" s="24"/>
+      <c r="B371" s="24"/>
+    </row>
+    <row r="372" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372" s="24"/>
+      <c r="B372" s="24"/>
+    </row>
+    <row r="373" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A373" s="24"/>
+      <c r="B373" s="24"/>
+    </row>
+    <row r="374" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A374" s="24"/>
+      <c r="B374" s="24"/>
+    </row>
+    <row r="375" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A375" s="24"/>
+      <c r="B375" s="24"/>
+    </row>
+    <row r="376" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A376" s="24"/>
+      <c r="B376" s="24"/>
+    </row>
+    <row r="377" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A377" s="24"/>
+      <c r="B377" s="24"/>
+    </row>
+    <row r="378" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A378" s="24"/>
+      <c r="B378" s="24"/>
+    </row>
+    <row r="379" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A379" s="24"/>
+      <c r="B379" s="24"/>
+    </row>
+    <row r="380" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A380" s="24"/>
+      <c r="B380" s="24"/>
+    </row>
+    <row r="381" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A381" s="24"/>
+      <c r="B381" s="24"/>
+    </row>
+    <row r="382" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A382" s="24"/>
+      <c r="B382" s="24"/>
+    </row>
+    <row r="383" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A383" s="24"/>
+      <c r="B383" s="24"/>
+    </row>
+    <row r="384" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A384" s="24"/>
+      <c r="B384" s="24"/>
+    </row>
+    <row r="385" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A385" s="24"/>
+      <c r="B385" s="24"/>
+    </row>
+    <row r="386" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A386" s="24"/>
+      <c r="B386" s="24"/>
+    </row>
+    <row r="387" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A387" s="24"/>
+      <c r="B387" s="24"/>
+    </row>
+    <row r="388" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A388" s="24"/>
+      <c r="B388" s="24"/>
+    </row>
+    <row r="389" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A389" s="24"/>
+      <c r="B389" s="24"/>
+    </row>
+    <row r="390" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A390" s="24"/>
+      <c r="B390" s="24"/>
+    </row>
+    <row r="391" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A391" s="24"/>
+      <c r="B391" s="24"/>
+    </row>
+    <row r="392" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A392" s="24"/>
+      <c r="B392" s="24"/>
+    </row>
+    <row r="393" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A393" s="24"/>
+      <c r="B393" s="24"/>
+    </row>
+    <row r="394" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A394" s="24"/>
+      <c r="B394" s="24"/>
+    </row>
+    <row r="395" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A395" s="24"/>
+      <c r="B395" s="24"/>
+    </row>
+    <row r="396" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A396" s="24"/>
+      <c r="B396" s="24"/>
+    </row>
+    <row r="397" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A397" s="24"/>
+      <c r="B397" s="24"/>
+    </row>
+    <row r="398" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A398" s="24"/>
+      <c r="B398" s="24"/>
+    </row>
+    <row r="399" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A399" s="24"/>
+      <c r="B399" s="24"/>
+    </row>
+    <row r="400" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A400" s="24"/>
+      <c r="B400" s="24"/>
+    </row>
+    <row r="401" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A401" s="24"/>
+      <c r="B401" s="24"/>
+    </row>
+    <row r="402" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A402" s="24"/>
+      <c r="B402" s="24"/>
+    </row>
+    <row r="403" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A403" s="24"/>
+      <c r="B403" s="24"/>
+    </row>
+    <row r="404" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A404" s="24"/>
+      <c r="B404" s="24"/>
+    </row>
+    <row r="405" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A405" s="24"/>
+      <c r="B405" s="24"/>
+    </row>
+    <row r="406" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A406" s="24"/>
+      <c r="B406" s="24"/>
+    </row>
+    <row r="407" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A407" s="24"/>
+      <c r="B407" s="24"/>
+    </row>
+    <row r="408" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A408" s="24"/>
+      <c r="B408" s="24"/>
+    </row>
+    <row r="409" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A409" s="24"/>
+      <c r="B409" s="24"/>
+    </row>
+    <row r="410" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A410" s="24"/>
+      <c r="B410" s="24"/>
+    </row>
+    <row r="411" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A411" s="24"/>
+      <c r="B411" s="24"/>
+    </row>
+    <row r="412" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A412" s="24"/>
+      <c r="B412" s="24"/>
+    </row>
+    <row r="413" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A413" s="24"/>
+      <c r="B413" s="24"/>
+    </row>
+    <row r="414" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A414" s="24"/>
+      <c r="B414" s="24"/>
+    </row>
+    <row r="415" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A415" s="24"/>
+      <c r="B415" s="24"/>
+    </row>
+    <row r="416" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A416" s="24"/>
+      <c r="B416" s="24"/>
+    </row>
+    <row r="417" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A417" s="24"/>
+      <c r="B417" s="24"/>
+    </row>
+    <row r="418" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A418" s="24"/>
+      <c r="B418" s="24"/>
+    </row>
+    <row r="419" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A419" s="24"/>
+      <c r="B419" s="24"/>
+    </row>
+    <row r="420" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A420" s="24"/>
+      <c r="B420" s="24"/>
+    </row>
+    <row r="421" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A421" s="24"/>
+      <c r="B421" s="24"/>
+    </row>
+    <row r="422" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A422" s="24"/>
+      <c r="B422" s="24"/>
+    </row>
+    <row r="423" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A423" s="24"/>
+      <c r="B423" s="24"/>
+    </row>
+    <row r="424" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A424" s="24"/>
+      <c r="B424" s="24"/>
+    </row>
+    <row r="425" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A425" s="24"/>
+      <c r="B425" s="24"/>
+    </row>
+    <row r="426" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A426" s="24"/>
+      <c r="B426" s="24"/>
+    </row>
+    <row r="427" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A427" s="24"/>
+      <c r="B427" s="24"/>
+    </row>
+    <row r="428" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A428" s="24"/>
+      <c r="B428" s="24"/>
+    </row>
+    <row r="429" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A429" s="24"/>
+      <c r="B429" s="24"/>
+    </row>
+    <row r="430" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A430" s="24"/>
+      <c r="B430" s="24"/>
+    </row>
+    <row r="431" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A431" s="24"/>
+      <c r="B431" s="24"/>
+    </row>
+    <row r="432" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A432" s="24"/>
+      <c r="B432" s="24"/>
+    </row>
+    <row r="433" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A433" s="24"/>
+      <c r="B433" s="24"/>
+    </row>
+    <row r="434" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A434" s="24"/>
+      <c r="B434" s="24"/>
+    </row>
+    <row r="435" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A435" s="24"/>
+      <c r="B435" s="24"/>
+    </row>
+    <row r="436" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A436" s="24"/>
+      <c r="B436" s="24"/>
+    </row>
+    <row r="437" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A437" s="24"/>
+      <c r="B437" s="24"/>
+    </row>
+    <row r="438" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A438" s="24"/>
+      <c r="B438" s="24"/>
+    </row>
+    <row r="439" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A439" s="24"/>
+      <c r="B439" s="24"/>
+    </row>
+    <row r="440" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A440" s="24"/>
+      <c r="B440" s="24"/>
+    </row>
+    <row r="441" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A441" s="24"/>
+      <c r="B441" s="24"/>
+    </row>
+    <row r="442" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A442" s="24"/>
+      <c r="B442" s="24"/>
+    </row>
+    <row r="443" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A443" s="24"/>
+      <c r="B443" s="24"/>
+    </row>
+    <row r="444" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A444" s="24"/>
+      <c r="B444" s="24"/>
+    </row>
+    <row r="445" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A445" s="24"/>
+      <c r="B445" s="24"/>
+    </row>
+    <row r="446" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A446" s="24"/>
+      <c r="B446" s="24"/>
+    </row>
+    <row r="447" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A447" s="24"/>
+      <c r="B447" s="24"/>
+    </row>
+    <row r="448" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A448" s="24"/>
+      <c r="B448" s="24"/>
+    </row>
+    <row r="449" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A449" s="24"/>
+      <c r="B449" s="24"/>
+    </row>
+    <row r="450" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A450" s="24"/>
+      <c r="B450" s="24"/>
+    </row>
+    <row r="451" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A451" s="24"/>
+      <c r="B451" s="24"/>
+    </row>
+    <row r="452" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A452" s="24"/>
+      <c r="B452" s="24"/>
+    </row>
+    <row r="453" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A453" s="24"/>
+      <c r="B453" s="24"/>
+    </row>
+    <row r="454" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A454" s="24"/>
+      <c r="B454" s="24"/>
+    </row>
+    <row r="455" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A455" s="24"/>
+      <c r="B455" s="24"/>
+    </row>
+    <row r="456" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A456" s="24"/>
+      <c r="B456" s="24"/>
+    </row>
+    <row r="457" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A457" s="24"/>
+      <c r="B457" s="24"/>
+    </row>
+    <row r="458" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A458" s="24"/>
+      <c r="B458" s="24"/>
+    </row>
+    <row r="459" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A459" s="24"/>
+      <c r="B459" s="24"/>
+    </row>
+    <row r="460" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A460" s="24"/>
+      <c r="B460" s="24"/>
+    </row>
+    <row r="461" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A461" s="24"/>
+      <c r="B461" s="24"/>
+    </row>
+    <row r="462" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A462" s="24"/>
+      <c r="B462" s="24"/>
+    </row>
+    <row r="463" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A463" s="24"/>
+      <c r="B463" s="24"/>
+    </row>
+    <row r="464" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A464" s="24"/>
+      <c r="B464" s="24"/>
+    </row>
+    <row r="465" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" s="24"/>
+      <c r="B465" s="24"/>
+    </row>
+    <row r="466" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" s="24"/>
+      <c r="B466" s="24"/>
+    </row>
+    <row r="467" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A467" s="24"/>
+      <c r="B467" s="24"/>
+    </row>
+    <row r="468" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A468" s="24"/>
+      <c r="B468" s="24"/>
+    </row>
+    <row r="469" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A469" s="24"/>
+      <c r="B469" s="24"/>
+    </row>
+    <row r="470" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A470" s="24"/>
+      <c r="B470" s="24"/>
+    </row>
+    <row r="471" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A471" s="24"/>
+      <c r="B471" s="24"/>
+    </row>
+    <row r="472" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A472" s="24"/>
+      <c r="B472" s="24"/>
+    </row>
+    <row r="473" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A473" s="24"/>
+      <c r="B473" s="24"/>
+    </row>
+    <row r="474" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A474" s="24"/>
+      <c r="B474" s="24"/>
+    </row>
+    <row r="475" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A475" s="24"/>
+      <c r="B475" s="24"/>
+    </row>
+    <row r="476" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A476" s="24"/>
+      <c r="B476" s="24"/>
+    </row>
+    <row r="477" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A477" s="24"/>
+      <c r="B477" s="24"/>
+    </row>
+    <row r="478" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A478" s="24"/>
+      <c r="B478" s="24"/>
+    </row>
+    <row r="479" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A479" s="24"/>
+      <c r="B479" s="24"/>
+    </row>
+    <row r="480" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A480" s="24"/>
+      <c r="B480" s="24"/>
+    </row>
+    <row r="481" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481" s="24"/>
+      <c r="B481" s="24"/>
+    </row>
+    <row r="482" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A482" s="24"/>
+      <c r="B482" s="24"/>
+    </row>
+    <row r="483" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A483" s="24"/>
+      <c r="B483" s="24"/>
+    </row>
+    <row r="484" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484" s="24"/>
+      <c r="B484" s="24"/>
+    </row>
+    <row r="485" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A485" s="24"/>
+      <c r="B485" s="24"/>
+    </row>
+    <row r="486" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A486" s="24"/>
+      <c r="B486" s="24"/>
+    </row>
+    <row r="487" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A487" s="24"/>
+      <c r="B487" s="24"/>
+    </row>
+    <row r="488" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A488" s="24"/>
+      <c r="B488" s="24"/>
+    </row>
+    <row r="489" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A489" s="24"/>
+      <c r="B489" s="24"/>
+    </row>
+    <row r="490" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A490" s="24"/>
+      <c r="B490" s="24"/>
+    </row>
+    <row r="491" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A491" s="24"/>
+      <c r="B491" s="24"/>
+    </row>
+    <row r="492" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A492" s="24"/>
+      <c r="B492" s="24"/>
+    </row>
+    <row r="493" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A493" s="24"/>
+      <c r="B493" s="24"/>
+    </row>
+    <row r="494" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A494" s="24"/>
+      <c r="B494" s="24"/>
+    </row>
+    <row r="495" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A495" s="24"/>
+      <c r="B495" s="24"/>
+    </row>
+    <row r="496" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A496" s="24"/>
+      <c r="B496" s="24"/>
+    </row>
+    <row r="497" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A497" s="24"/>
+      <c r="B497" s="24"/>
+    </row>
+    <row r="498" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A498" s="24"/>
+      <c r="B498" s="24"/>
+    </row>
+    <row r="499" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A499" s="24"/>
+      <c r="B499" s="24"/>
+    </row>
+    <row r="500" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A500" s="24"/>
+      <c r="B500" s="24"/>
+    </row>
+    <row r="501" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A501" s="24"/>
+      <c r="B501" s="24"/>
+    </row>
+    <row r="502" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A502" s="24"/>
+      <c r="B502" s="24"/>
+    </row>
+    <row r="503" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A503" s="24"/>
+      <c r="B503" s="24"/>
+    </row>
+    <row r="504" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A504" s="24"/>
+      <c r="B504" s="24"/>
+    </row>
+    <row r="505" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A505" s="24"/>
+      <c r="B505" s="24"/>
+    </row>
+    <row r="506" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A506" s="24"/>
+      <c r="B506" s="24"/>
+    </row>
+    <row r="507" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A507" s="24"/>
+      <c r="B507" s="24"/>
+    </row>
+    <row r="508" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A508" s="24"/>
+      <c r="B508" s="24"/>
+    </row>
+    <row r="509" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A509" s="24"/>
+      <c r="B509" s="24"/>
+    </row>
+    <row r="510" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A510" s="24"/>
+      <c r="B510" s="24"/>
+    </row>
+    <row r="511" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A511" s="24"/>
+      <c r="B511" s="24"/>
+    </row>
+    <row r="512" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A512" s="24"/>
+      <c r="B512" s="24"/>
+    </row>
+    <row r="513" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A513" s="24"/>
+      <c r="B513" s="24"/>
+    </row>
+    <row r="514" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A514" s="24"/>
+      <c r="B514" s="24"/>
+    </row>
+    <row r="515" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A515" s="24"/>
+      <c r="B515" s="24"/>
+    </row>
+    <row r="516" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A516" s="24"/>
+      <c r="B516" s="24"/>
+    </row>
+    <row r="517" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A517" s="24"/>
+      <c r="B517" s="24"/>
+    </row>
+    <row r="518" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A518" s="24"/>
+      <c r="B518" s="24"/>
+    </row>
+    <row r="519" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A519" s="24"/>
+      <c r="B519" s="24"/>
+    </row>
+    <row r="520" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A520" s="24"/>
+      <c r="B520" s="24"/>
+    </row>
+    <row r="521" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A521" s="24"/>
+      <c r="B521" s="24"/>
+    </row>
+    <row r="522" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A522" s="24"/>
+      <c r="B522" s="24"/>
+    </row>
+    <row r="523" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A523" s="24"/>
+      <c r="B523" s="24"/>
+    </row>
+    <row r="524" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A524" s="24"/>
+      <c r="B524" s="24"/>
+    </row>
+    <row r="525" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A525" s="24"/>
+      <c r="B525" s="24"/>
+    </row>
+    <row r="526" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A526" s="24"/>
+      <c r="B526" s="24"/>
+    </row>
+    <row r="527" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A527" s="24"/>
+      <c r="B527" s="24"/>
+    </row>
+    <row r="528" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A528" s="24"/>
+      <c r="B528" s="24"/>
+    </row>
+    <row r="529" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A529" s="24"/>
+      <c r="B529" s="24"/>
+    </row>
+    <row r="530" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A530" s="24"/>
+      <c r="B530" s="24"/>
+    </row>
+    <row r="531" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A531" s="24"/>
+      <c r="B531" s="24"/>
+    </row>
+    <row r="532" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A532" s="24"/>
+      <c r="B532" s="24"/>
+    </row>
+    <row r="533" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A533" s="24"/>
+      <c r="B533" s="24"/>
+    </row>
+    <row r="534" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A534" s="24"/>
+      <c r="B534" s="24"/>
+    </row>
+    <row r="535" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A535" s="24"/>
+      <c r="B535" s="24"/>
+    </row>
+    <row r="536" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A536" s="24"/>
+      <c r="B536" s="24"/>
+    </row>
+    <row r="537" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A537" s="24"/>
+      <c r="B537" s="24"/>
+    </row>
+    <row r="538" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A538" s="24"/>
+      <c r="B538" s="24"/>
+    </row>
+    <row r="539" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A539" s="24"/>
+      <c r="B539" s="24"/>
+    </row>
+    <row r="540" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A540" s="24"/>
+      <c r="B540" s="24"/>
+    </row>
+    <row r="541" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A541" s="24"/>
+      <c r="B541" s="24"/>
+    </row>
+    <row r="542" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A542" s="24"/>
+      <c r="B542" s="24"/>
+    </row>
+    <row r="543" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A543" s="24"/>
+      <c r="B543" s="24"/>
+    </row>
+    <row r="544" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A544" s="24"/>
+      <c r="B544" s="24"/>
+    </row>
+    <row r="545" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A545" s="24"/>
+      <c r="B545" s="24"/>
+    </row>
+    <row r="546" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A546" s="24"/>
+      <c r="B546" s="24"/>
+    </row>
+    <row r="547" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A547" s="24"/>
+      <c r="B547" s="24"/>
+    </row>
+    <row r="548" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A548" s="24"/>
+      <c r="B548" s="24"/>
+    </row>
+    <row r="549" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A549" s="24"/>
+      <c r="B549" s="24"/>
+    </row>
+    <row r="550" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A550" s="24"/>
+      <c r="B550" s="24"/>
+    </row>
+    <row r="551" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A551" s="24"/>
+      <c r="B551" s="24"/>
+    </row>
+    <row r="552" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A552" s="24"/>
+      <c r="B552" s="24"/>
+    </row>
+    <row r="553" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A553" s="24"/>
+      <c r="B553" s="24"/>
+    </row>
+    <row r="554" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A554" s="24"/>
+      <c r="B554" s="24"/>
+    </row>
+    <row r="555" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A555" s="24"/>
+      <c r="B555" s="24"/>
+    </row>
+    <row r="556" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A556" s="24"/>
+      <c r="B556" s="24"/>
+    </row>
+    <row r="557" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A557" s="24"/>
+      <c r="B557" s="24"/>
+    </row>
+    <row r="558" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A558" s="24"/>
+      <c r="B558" s="24"/>
+    </row>
+    <row r="559" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A559" s="24"/>
+      <c r="B559" s="24"/>
+    </row>
+    <row r="560" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A560" s="24"/>
+      <c r="B560" s="24"/>
+    </row>
+    <row r="561" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A561" s="24"/>
+      <c r="B561" s="24"/>
+    </row>
+    <row r="562" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A562" s="24"/>
+      <c r="B562" s="24"/>
+    </row>
+    <row r="563" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A563" s="24"/>
+      <c r="B563" s="24"/>
+    </row>
+    <row r="564" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A564" s="24"/>
+      <c r="B564" s="24"/>
+    </row>
+    <row r="565" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A565" s="24"/>
+      <c r="B565" s="24"/>
+    </row>
+    <row r="566" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A566" s="24"/>
+      <c r="B566" s="24"/>
+    </row>
+    <row r="567" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A567" s="24"/>
+      <c r="B567" s="24"/>
+    </row>
+    <row r="568" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A568" s="24"/>
+      <c r="B568" s="24"/>
+    </row>
+    <row r="569" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A569" s="24"/>
+      <c r="B569" s="24"/>
+    </row>
+    <row r="570" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A570" s="24"/>
+      <c r="B570" s="24"/>
+    </row>
+    <row r="571" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A571" s="24"/>
+      <c r="B571" s="24"/>
+    </row>
+    <row r="572" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A572" s="24"/>
+      <c r="B572" s="24"/>
+    </row>
+    <row r="573" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A573" s="24"/>
+      <c r="B573" s="24"/>
+    </row>
+    <row r="574" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A574" s="24"/>
+      <c r="B574" s="24"/>
+    </row>
+    <row r="575" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A575" s="24"/>
+      <c r="B575" s="24"/>
+    </row>
+    <row r="576" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A576" s="24"/>
+      <c r="B576" s="24"/>
+    </row>
+    <row r="577" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A577" s="24"/>
+      <c r="B577" s="24"/>
+    </row>
+    <row r="578" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A578" s="24"/>
+      <c r="B578" s="24"/>
+    </row>
+    <row r="579" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" s="24"/>
+      <c r="B579" s="24"/>
+    </row>
+    <row r="580" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A580" s="24"/>
+      <c r="B580" s="24"/>
+    </row>
+    <row r="581" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A581" s="24"/>
+      <c r="B581" s="24"/>
+    </row>
+    <row r="582" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A582" s="24"/>
+      <c r="B582" s="24"/>
+    </row>
+    <row r="583" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A583" s="24"/>
+      <c r="B583" s="24"/>
+    </row>
+    <row r="584" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" s="24"/>
+      <c r="B584" s="24"/>
+    </row>
+    <row r="585" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A585" s="24"/>
+      <c r="B585" s="24"/>
+    </row>
+    <row r="586" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" s="24"/>
+      <c r="B586" s="24"/>
+    </row>
+    <row r="587" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" s="24"/>
+      <c r="B587" s="24"/>
+    </row>
+    <row r="588" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" s="24"/>
+      <c r="B588" s="24"/>
+    </row>
+    <row r="589" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A589" s="24"/>
+      <c r="B589" s="24"/>
+    </row>
+    <row r="590" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A590" s="24"/>
+      <c r="B590" s="24"/>
+    </row>
+    <row r="591" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A591" s="24"/>
+      <c r="B591" s="24"/>
+    </row>
+    <row r="592" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A592" s="24"/>
+      <c r="B592" s="24"/>
+    </row>
+    <row r="593" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A593" s="24"/>
+      <c r="B593" s="24"/>
+    </row>
+    <row r="594" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A594" s="24"/>
+      <c r="B594" s="24"/>
+    </row>
+    <row r="595" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" s="24"/>
+      <c r="B595" s="24"/>
+    </row>
+    <row r="596" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" s="24"/>
+      <c r="B596" s="24"/>
+    </row>
+    <row r="597" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" s="24"/>
+      <c r="B597" s="24"/>
+    </row>
+    <row r="598" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A598" s="24"/>
+      <c r="B598" s="24"/>
+    </row>
+    <row r="599" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A599" s="24"/>
+      <c r="B599" s="24"/>
+    </row>
+    <row r="600" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A600" s="24"/>
+      <c r="B600" s="24"/>
+    </row>
+    <row r="601" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A601" s="24"/>
+      <c r="B601" s="24"/>
+    </row>
+    <row r="602" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A602" s="24"/>
+      <c r="B602" s="24"/>
+    </row>
+    <row r="603" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A603" s="24"/>
+      <c r="B603" s="24"/>
+    </row>
+    <row r="604" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A604" s="24"/>
+      <c r="B604" s="24"/>
+    </row>
+    <row r="605" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A605" s="24"/>
+      <c r="B605" s="24"/>
+    </row>
+    <row r="606" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A606" s="24"/>
+      <c r="B606" s="24"/>
+    </row>
+    <row r="607" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A607" s="24"/>
+      <c r="B607" s="24"/>
+    </row>
+    <row r="608" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A608" s="24"/>
+      <c r="B608" s="24"/>
+    </row>
+    <row r="609" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A609" s="24"/>
+      <c r="B609" s="24"/>
+    </row>
+    <row r="610" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A610" s="24"/>
+      <c r="B610" s="24"/>
+    </row>
+    <row r="611" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A611" s="24"/>
+      <c r="B611" s="24"/>
+    </row>
+    <row r="612" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A612" s="24"/>
+      <c r="B612" s="24"/>
+    </row>
+    <row r="613" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A613" s="24"/>
+      <c r="B613" s="24"/>
+    </row>
+    <row r="614" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A614" s="24"/>
+      <c r="B614" s="24"/>
+    </row>
+    <row r="615" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A615" s="24"/>
+      <c r="B615" s="24"/>
+    </row>
+    <row r="616" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A616" s="24"/>
+      <c r="B616" s="24"/>
+    </row>
+    <row r="617" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A617" s="24"/>
+      <c r="B617" s="24"/>
+    </row>
+    <row r="618" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A618" s="24"/>
+      <c r="B618" s="24"/>
+    </row>
+    <row r="619" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A619" s="24"/>
+      <c r="B619" s="24"/>
+    </row>
+    <row r="620" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A620" s="24"/>
+      <c r="B620" s="24"/>
+    </row>
+    <row r="621" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A621" s="24"/>
+      <c r="B621" s="24"/>
+    </row>
+    <row r="622" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A622" s="24"/>
+      <c r="B622" s="24"/>
+    </row>
+    <row r="623" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A623" s="24"/>
+      <c r="B623" s="24"/>
+    </row>
+    <row r="624" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A624" s="24"/>
+      <c r="B624" s="24"/>
+    </row>
+    <row r="625" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A625" s="24"/>
+      <c r="B625" s="24"/>
+    </row>
+    <row r="626" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A626" s="24"/>
+      <c r="B626" s="24"/>
+    </row>
+    <row r="627" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A627" s="24"/>
+      <c r="B627" s="24"/>
+    </row>
+    <row r="628" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A628" s="24"/>
+      <c r="B628" s="24"/>
+    </row>
+    <row r="629" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A629" s="24"/>
+      <c r="B629" s="24"/>
+    </row>
+    <row r="630" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A630" s="24"/>
+      <c r="B630" s="24"/>
+    </row>
+    <row r="631" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A631" s="24"/>
+      <c r="B631" s="24"/>
+    </row>
+    <row r="632" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A632" s="24"/>
+      <c r="B632" s="24"/>
+    </row>
+    <row r="633" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A633" s="24"/>
+      <c r="B633" s="24"/>
+    </row>
+    <row r="634" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A634" s="24"/>
+      <c r="B634" s="24"/>
+    </row>
+    <row r="635" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A635" s="24"/>
+      <c r="B635" s="24"/>
+    </row>
+    <row r="636" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A636" s="24"/>
+      <c r="B636" s="24"/>
+    </row>
+    <row r="637" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A637" s="24"/>
+      <c r="B637" s="24"/>
+    </row>
+    <row r="638" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A638" s="24"/>
+      <c r="B638" s="24"/>
+    </row>
+    <row r="639" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A639" s="24"/>
+      <c r="B639" s="24"/>
+    </row>
+    <row r="640" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A640" s="24"/>
+      <c r="B640" s="24"/>
+    </row>
+    <row r="641" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A641" s="24"/>
+      <c r="B641" s="24"/>
+    </row>
+    <row r="642" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A642" s="24"/>
+      <c r="B642" s="24"/>
+    </row>
+    <row r="643" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A643" s="24"/>
+      <c r="B643" s="24"/>
+    </row>
+    <row r="644" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A644" s="24"/>
+      <c r="B644" s="24"/>
+    </row>
+    <row r="645" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A645" s="24"/>
+      <c r="B645" s="24"/>
+    </row>
+    <row r="646" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A646" s="24"/>
+      <c r="B646" s="24"/>
+    </row>
+    <row r="647" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A647" s="24"/>
+      <c r="B647" s="24"/>
+    </row>
+    <row r="648" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A648" s="24"/>
+      <c r="B648" s="24"/>
+    </row>
+    <row r="649" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A649" s="24"/>
+      <c r="B649" s="24"/>
+    </row>
+    <row r="650" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A650" s="24"/>
+      <c r="B650" s="24"/>
+    </row>
+    <row r="651" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A651" s="24"/>
+      <c r="B651" s="24"/>
+    </row>
+    <row r="652" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A652" s="24"/>
+      <c r="B652" s="24"/>
+    </row>
+    <row r="653" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A653" s="24"/>
+      <c r="B653" s="24"/>
+    </row>
+    <row r="654" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A654" s="24"/>
+      <c r="B654" s="24"/>
+    </row>
+    <row r="655" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A655" s="24"/>
+      <c r="B655" s="24"/>
+    </row>
+    <row r="656" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A656" s="24"/>
+      <c r="B656" s="24"/>
+    </row>
+    <row r="657" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A657" s="24"/>
+      <c r="B657" s="24"/>
+    </row>
+    <row r="658" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A658" s="24"/>
+      <c r="B658" s="24"/>
+    </row>
+    <row r="659" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A659" s="24"/>
+      <c r="B659" s="24"/>
+    </row>
+    <row r="660" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A660" s="24"/>
+      <c r="B660" s="24"/>
+    </row>
+    <row r="661" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A661" s="24"/>
+      <c r="B661" s="24"/>
+    </row>
+    <row r="662" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A662" s="24"/>
+      <c r="B662" s="24"/>
+    </row>
+    <row r="663" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A663" s="24"/>
+      <c r="B663" s="24"/>
+    </row>
+    <row r="664" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A664" s="24"/>
+      <c r="B664" s="24"/>
+    </row>
+    <row r="665" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A665" s="24"/>
+      <c r="B665" s="24"/>
+    </row>
+    <row r="666" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A666" s="24"/>
+      <c r="B666" s="24"/>
+    </row>
+    <row r="667" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A667" s="24"/>
+      <c r="B667" s="24"/>
+    </row>
+    <row r="668" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A668" s="24"/>
+      <c r="B668" s="24"/>
+    </row>
+    <row r="669" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A669" s="24"/>
+      <c r="B669" s="24"/>
+    </row>
+    <row r="670" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A670" s="24"/>
+      <c r="B670" s="24"/>
+    </row>
+    <row r="671" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A671" s="24"/>
+      <c r="B671" s="24"/>
+    </row>
+    <row r="672" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A672" s="24"/>
+      <c r="B672" s="24"/>
+    </row>
+    <row r="673" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A673" s="24"/>
+      <c r="B673" s="24"/>
+    </row>
+    <row r="674" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A674" s="24"/>
+      <c r="B674" s="24"/>
+    </row>
+    <row r="675" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A675" s="24"/>
+      <c r="B675" s="24"/>
+    </row>
+    <row r="676" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A676" s="24"/>
+      <c r="B676" s="24"/>
+    </row>
+    <row r="677" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A677" s="24"/>
+      <c r="B677" s="24"/>
+    </row>
+    <row r="678" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A678" s="24"/>
+      <c r="B678" s="24"/>
+    </row>
+    <row r="679" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A679" s="24"/>
+      <c r="B679" s="24"/>
+    </row>
+    <row r="680" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A680" s="24"/>
+      <c r="B680" s="24"/>
+    </row>
+    <row r="681" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A681" s="24"/>
+      <c r="B681" s="24"/>
+    </row>
+    <row r="682" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A682" s="24"/>
+      <c r="B682" s="24"/>
+    </row>
+    <row r="683" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A683" s="24"/>
+      <c r="B683" s="24"/>
+    </row>
+    <row r="684" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A684" s="24"/>
+      <c r="B684" s="24"/>
+    </row>
+    <row r="685" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A685" s="24"/>
+      <c r="B685" s="24"/>
+    </row>
+    <row r="686" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A686" s="24"/>
+      <c r="B686" s="24"/>
+    </row>
+    <row r="687" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A687" s="24"/>
+      <c r="B687" s="24"/>
+    </row>
+    <row r="688" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A688" s="24"/>
+      <c r="B688" s="24"/>
+    </row>
+    <row r="689" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A689" s="24"/>
+      <c r="B689" s="24"/>
+    </row>
+    <row r="690" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A690" s="24"/>
+      <c r="B690" s="24"/>
+    </row>
+    <row r="691" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A691" s="24"/>
+      <c r="B691" s="24"/>
+    </row>
+    <row r="692" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="24"/>
+      <c r="B692" s="24"/>
+    </row>
+    <row r="693" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="24"/>
+      <c r="B693" s="24"/>
+    </row>
+    <row r="694" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A694" s="24"/>
+      <c r="B694" s="24"/>
+    </row>
+    <row r="695" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A695" s="24"/>
+      <c r="B695" s="24"/>
+    </row>
+    <row r="696" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A696" s="24"/>
+      <c r="B696" s="24"/>
+    </row>
+    <row r="697" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A697" s="24"/>
+      <c r="B697" s="24"/>
+    </row>
+    <row r="698" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A698" s="24"/>
+      <c r="B698" s="24"/>
+    </row>
+    <row r="699" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A699" s="24"/>
+      <c r="B699" s="24"/>
+    </row>
+    <row r="700" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A700" s="24"/>
+      <c r="B700" s="24"/>
+    </row>
+    <row r="701" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A701" s="24"/>
+      <c r="B701" s="24"/>
+    </row>
+    <row r="702" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A702" s="24"/>
+      <c r="B702" s="24"/>
+    </row>
+    <row r="703" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A703" s="24"/>
+      <c r="B703" s="24"/>
+    </row>
+    <row r="704" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A704" s="24"/>
+      <c r="B704" s="24"/>
+    </row>
+    <row r="705" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A705" s="24"/>
+      <c r="B705" s="24"/>
+    </row>
+    <row r="706" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A706" s="24"/>
+      <c r="B706" s="24"/>
+    </row>
+    <row r="707" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A707" s="24"/>
+      <c r="B707" s="24"/>
+    </row>
+    <row r="708" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A708" s="24"/>
+      <c r="B708" s="24"/>
+    </row>
+    <row r="709" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A709" s="24"/>
+      <c r="B709" s="24"/>
+    </row>
+    <row r="710" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A710" s="24"/>
+      <c r="B710" s="24"/>
+    </row>
+    <row r="711" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A711" s="24"/>
+      <c r="B711" s="24"/>
+    </row>
+    <row r="712" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A712" s="24"/>
+      <c r="B712" s="24"/>
+    </row>
+    <row r="713" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A713" s="24"/>
+      <c r="B713" s="24"/>
+    </row>
+    <row r="714" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A714" s="24"/>
+      <c r="B714" s="24"/>
+    </row>
+    <row r="715" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A715" s="24"/>
+      <c r="B715" s="24"/>
+    </row>
+    <row r="716" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A716" s="24"/>
+      <c r="B716" s="24"/>
+    </row>
+    <row r="717" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A717" s="24"/>
+      <c r="B717" s="24"/>
+    </row>
+    <row r="718" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A718" s="24"/>
+      <c r="B718" s="24"/>
+    </row>
+    <row r="719" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A719" s="24"/>
+      <c r="B719" s="24"/>
+    </row>
+    <row r="720" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A720" s="24"/>
+      <c r="B720" s="24"/>
+    </row>
+    <row r="721" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A721" s="24"/>
+      <c r="B721" s="24"/>
+    </row>
+    <row r="722" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A722" s="24"/>
+      <c r="B722" s="24"/>
+    </row>
+    <row r="723" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A723" s="24"/>
+      <c r="B723" s="24"/>
+    </row>
+    <row r="724" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A724" s="24"/>
+      <c r="B724" s="24"/>
+    </row>
+    <row r="725" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A725" s="24"/>
+      <c r="B725" s="24"/>
+    </row>
+    <row r="726" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A726" s="24"/>
+      <c r="B726" s="24"/>
+    </row>
+    <row r="727" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A727" s="24"/>
+      <c r="B727" s="24"/>
+    </row>
+    <row r="728" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A728" s="24"/>
+      <c r="B728" s="24"/>
+    </row>
+    <row r="729" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A729" s="24"/>
+      <c r="B729" s="24"/>
+    </row>
+    <row r="730" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A730" s="24"/>
+      <c r="B730" s="24"/>
+    </row>
+    <row r="731" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A731" s="24"/>
+      <c r="B731" s="24"/>
+    </row>
+    <row r="732" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A732" s="24"/>
+      <c r="B732" s="24"/>
+    </row>
+    <row r="733" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A733" s="24"/>
+      <c r="B733" s="24"/>
+    </row>
+    <row r="734" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A734" s="24"/>
+      <c r="B734" s="24"/>
+    </row>
+    <row r="735" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A735" s="24"/>
+      <c r="B735" s="24"/>
+    </row>
+    <row r="736" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A736" s="24"/>
+      <c r="B736" s="24"/>
+    </row>
+    <row r="737" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A737" s="24"/>
+      <c r="B737" s="24"/>
+    </row>
+    <row r="738" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A738" s="24"/>
+      <c r="B738" s="24"/>
+    </row>
+    <row r="739" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A739" s="24"/>
+      <c r="B739" s="24"/>
+    </row>
+    <row r="740" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A740" s="24"/>
+      <c r="B740" s="24"/>
+    </row>
+    <row r="741" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A741" s="24"/>
+      <c r="B741" s="24"/>
+    </row>
+    <row r="742" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A742" s="24"/>
+      <c r="B742" s="24"/>
+    </row>
+    <row r="743" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A743" s="24"/>
+      <c r="B743" s="24"/>
+    </row>
+    <row r="744" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A744" s="24"/>
+      <c r="B744" s="24"/>
+    </row>
+    <row r="745" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A745" s="24"/>
+      <c r="B745" s="24"/>
+    </row>
+    <row r="746" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A746" s="24"/>
+      <c r="B746" s="24"/>
+    </row>
+    <row r="747" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A747" s="24"/>
+      <c r="B747" s="24"/>
+    </row>
+    <row r="748" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A748" s="24"/>
+      <c r="B748" s="24"/>
+    </row>
+    <row r="749" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A749" s="24"/>
+      <c r="B749" s="24"/>
+    </row>
+    <row r="750" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A750" s="24"/>
+      <c r="B750" s="24"/>
+    </row>
+    <row r="751" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A751" s="24"/>
+      <c r="B751" s="24"/>
+    </row>
+    <row r="752" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A752" s="24"/>
+      <c r="B752" s="24"/>
+    </row>
+    <row r="753" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A753" s="24"/>
+      <c r="B753" s="24"/>
+    </row>
+    <row r="754" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A754" s="24"/>
+      <c r="B754" s="24"/>
+    </row>
+    <row r="755" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A755" s="24"/>
+      <c r="B755" s="24"/>
+    </row>
+    <row r="756" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A756" s="24"/>
+      <c r="B756" s="24"/>
+    </row>
+    <row r="757" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A757" s="24"/>
+      <c r="B757" s="24"/>
+    </row>
+    <row r="758" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A758" s="24"/>
+      <c r="B758" s="24"/>
+    </row>
+    <row r="759" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A759" s="24"/>
+      <c r="B759" s="24"/>
+    </row>
+    <row r="760" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A760" s="24"/>
+      <c r="B760" s="24"/>
+    </row>
+    <row r="761" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A761" s="24"/>
+      <c r="B761" s="24"/>
+    </row>
+    <row r="762" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A762" s="24"/>
+      <c r="B762" s="24"/>
+    </row>
+    <row r="763" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A763" s="24"/>
+      <c r="B763" s="24"/>
+    </row>
+    <row r="764" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A764" s="24"/>
+      <c r="B764" s="24"/>
+    </row>
+    <row r="765" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A765" s="24"/>
+      <c r="B765" s="24"/>
+    </row>
+    <row r="766" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A766" s="24"/>
+      <c r="B766" s="24"/>
+    </row>
+    <row r="767" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A767" s="24"/>
+      <c r="B767" s="24"/>
+    </row>
+    <row r="768" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A768" s="24"/>
+      <c r="B768" s="24"/>
+    </row>
+    <row r="769" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A769" s="24"/>
+      <c r="B769" s="24"/>
+    </row>
+    <row r="770" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A770" s="24"/>
+      <c r="B770" s="24"/>
+    </row>
+    <row r="771" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A771" s="24"/>
+      <c r="B771" s="24"/>
+    </row>
+    <row r="772" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A772" s="24"/>
+      <c r="B772" s="24"/>
+    </row>
+    <row r="773" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A773" s="24"/>
+      <c r="B773" s="24"/>
+    </row>
+    <row r="774" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A774" s="24"/>
+      <c r="B774" s="24"/>
+    </row>
+    <row r="775" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A775" s="24"/>
+      <c r="B775" s="24"/>
+    </row>
+    <row r="776" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A776" s="24"/>
+      <c r="B776" s="24"/>
+    </row>
+    <row r="777" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A777" s="24"/>
+      <c r="B777" s="24"/>
+    </row>
+    <row r="778" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A778" s="24"/>
+      <c r="B778" s="24"/>
+    </row>
+    <row r="779" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A779" s="24"/>
+      <c r="B779" s="24"/>
+    </row>
+    <row r="780" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A780" s="24"/>
+      <c r="B780" s="24"/>
+    </row>
+    <row r="781" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A781" s="24"/>
+      <c r="B781" s="24"/>
+    </row>
+    <row r="782" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A782" s="24"/>
+      <c r="B782" s="24"/>
+    </row>
+    <row r="783" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A783" s="24"/>
+      <c r="B783" s="24"/>
+    </row>
+    <row r="784" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A784" s="24"/>
+      <c r="B784" s="24"/>
+    </row>
+    <row r="785" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A785" s="24"/>
+      <c r="B785" s="24"/>
+    </row>
+    <row r="786" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A786" s="24"/>
+      <c r="B786" s="24"/>
+    </row>
+    <row r="787" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A787" s="24"/>
+      <c r="B787" s="24"/>
+    </row>
+    <row r="788" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A788" s="24"/>
+      <c r="B788" s="24"/>
+    </row>
+    <row r="789" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A789" s="24"/>
+      <c r="B789" s="24"/>
+    </row>
+    <row r="790" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A790" s="24"/>
+      <c r="B790" s="24"/>
+    </row>
+    <row r="791" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A791" s="24"/>
+      <c r="B791" s="24"/>
+    </row>
+    <row r="792" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A792" s="24"/>
+      <c r="B792" s="24"/>
+    </row>
+    <row r="793" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A793" s="24"/>
+      <c r="B793" s="24"/>
+    </row>
+    <row r="794" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A794" s="24"/>
+      <c r="B794" s="24"/>
+    </row>
+    <row r="795" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A795" s="24"/>
+      <c r="B795" s="24"/>
+    </row>
+    <row r="796" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A796" s="24"/>
+      <c r="B796" s="24"/>
+    </row>
+    <row r="797" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A797" s="24"/>
+      <c r="B797" s="24"/>
+    </row>
+    <row r="798" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A798" s="24"/>
+      <c r="B798" s="24"/>
+    </row>
+    <row r="799" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A799" s="24"/>
+      <c r="B799" s="24"/>
+    </row>
+    <row r="800" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A800" s="24"/>
+      <c r="B800" s="24"/>
+    </row>
+    <row r="801" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A801" s="24"/>
+      <c r="B801" s="24"/>
+    </row>
+    <row r="802" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A802" s="24"/>
+      <c r="B802" s="24"/>
+    </row>
+    <row r="803" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A803" s="24"/>
+      <c r="B803" s="24"/>
+    </row>
+    <row r="804" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A804" s="24"/>
+      <c r="B804" s="24"/>
+    </row>
+    <row r="805" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A805" s="24"/>
+      <c r="B805" s="24"/>
+    </row>
+    <row r="806" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A806" s="24"/>
+      <c r="B806" s="24"/>
+    </row>
+    <row r="807" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A807" s="24"/>
+      <c r="B807" s="24"/>
+    </row>
+    <row r="808" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A808" s="24"/>
+      <c r="B808" s="24"/>
+    </row>
+    <row r="809" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A809" s="24"/>
+      <c r="B809" s="24"/>
+    </row>
+    <row r="810" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A810" s="24"/>
+      <c r="B810" s="24"/>
+    </row>
+    <row r="811" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A811" s="24"/>
+      <c r="B811" s="24"/>
+    </row>
+    <row r="812" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A812" s="24"/>
+      <c r="B812" s="24"/>
+    </row>
+    <row r="813" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A813" s="24"/>
+      <c r="B813" s="24"/>
+    </row>
+    <row r="814" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A814" s="24"/>
+      <c r="B814" s="24"/>
+    </row>
+    <row r="815" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A815" s="24"/>
+      <c r="B815" s="24"/>
+    </row>
+    <row r="816" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A816" s="24"/>
+      <c r="B816" s="24"/>
+    </row>
+    <row r="817" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A817" s="24"/>
+      <c r="B817" s="24"/>
+    </row>
+    <row r="818" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A818" s="24"/>
+      <c r="B818" s="24"/>
+    </row>
+    <row r="819" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A819" s="24"/>
+      <c r="B819" s="24"/>
+    </row>
+    <row r="820" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A820" s="24"/>
+      <c r="B820" s="24"/>
+    </row>
+    <row r="821" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A821" s="24"/>
+      <c r="B821" s="24"/>
+    </row>
+    <row r="822" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A822" s="24"/>
+      <c r="B822" s="24"/>
+    </row>
+    <row r="823" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A823" s="24"/>
+      <c r="B823" s="24"/>
+    </row>
+    <row r="824" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A824" s="24"/>
+      <c r="B824" s="24"/>
+    </row>
+    <row r="825" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A825" s="24"/>
+      <c r="B825" s="24"/>
+    </row>
+    <row r="826" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A826" s="24"/>
+      <c r="B826" s="24"/>
+    </row>
+    <row r="827" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A827" s="24"/>
+      <c r="B827" s="24"/>
+    </row>
+    <row r="828" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A828" s="24"/>
+      <c r="B828" s="24"/>
+    </row>
+    <row r="829" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A829" s="24"/>
+      <c r="B829" s="24"/>
+    </row>
+    <row r="830" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A830" s="24"/>
+      <c r="B830" s="24"/>
+    </row>
+    <row r="831" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A831" s="24"/>
+      <c r="B831" s="24"/>
+    </row>
+    <row r="832" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A832" s="24"/>
+      <c r="B832" s="24"/>
+    </row>
+    <row r="833" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A833" s="24"/>
+      <c r="B833" s="24"/>
+    </row>
+    <row r="834" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A834" s="24"/>
+      <c r="B834" s="24"/>
+    </row>
+    <row r="835" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A835" s="24"/>
+      <c r="B835" s="24"/>
+    </row>
+    <row r="836" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A836" s="24"/>
+      <c r="B836" s="24"/>
+    </row>
+    <row r="837" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A837" s="24"/>
+      <c r="B837" s="24"/>
+    </row>
+    <row r="838" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A838" s="24"/>
+      <c r="B838" s="24"/>
+    </row>
+    <row r="839" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A839" s="24"/>
+      <c r="B839" s="24"/>
+    </row>
+    <row r="840" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A840" s="24"/>
+      <c r="B840" s="24"/>
+    </row>
+    <row r="841" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A841" s="24"/>
+      <c r="B841" s="24"/>
+    </row>
+    <row r="842" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A842" s="24"/>
+      <c r="B842" s="24"/>
+    </row>
+    <row r="843" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A843" s="24"/>
+      <c r="B843" s="24"/>
+    </row>
+    <row r="844" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A844" s="24"/>
+      <c r="B844" s="24"/>
+    </row>
+    <row r="845" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A845" s="24"/>
+      <c r="B845" s="24"/>
+    </row>
+    <row r="846" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A846" s="24"/>
+      <c r="B846" s="24"/>
+    </row>
+    <row r="847" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A847" s="24"/>
+      <c r="B847" s="24"/>
+    </row>
+    <row r="848" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A848" s="24"/>
+      <c r="B848" s="24"/>
+    </row>
+    <row r="849" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A849" s="24"/>
+      <c r="B849" s="24"/>
+    </row>
+    <row r="850" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A850" s="24"/>
+      <c r="B850" s="24"/>
+    </row>
+    <row r="851" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A851" s="24"/>
+      <c r="B851" s="24"/>
+    </row>
+    <row r="852" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A852" s="24"/>
+      <c r="B852" s="24"/>
+    </row>
+    <row r="853" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A853" s="24"/>
+      <c r="B853" s="24"/>
+    </row>
+    <row r="854" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A854" s="24"/>
+      <c r="B854" s="24"/>
+    </row>
+    <row r="855" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A855" s="24"/>
+      <c r="B855" s="24"/>
+    </row>
+    <row r="856" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A856" s="24"/>
+      <c r="B856" s="24"/>
+    </row>
+    <row r="857" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A857" s="24"/>
+      <c r="B857" s="24"/>
+    </row>
+    <row r="858" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A858" s="24"/>
+      <c r="B858" s="24"/>
+    </row>
+    <row r="859" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A859" s="24"/>
+      <c r="B859" s="24"/>
+    </row>
+    <row r="860" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A860" s="24"/>
+      <c r="B860" s="24"/>
+    </row>
+    <row r="861" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A861" s="24"/>
+      <c r="B861" s="24"/>
+    </row>
+    <row r="862" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A862" s="24"/>
+      <c r="B862" s="24"/>
+    </row>
+    <row r="863" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A863" s="24"/>
+      <c r="B863" s="24"/>
+    </row>
+    <row r="864" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A864" s="24"/>
+      <c r="B864" s="24"/>
+    </row>
+    <row r="865" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A865" s="24"/>
+      <c r="B865" s="24"/>
+    </row>
+    <row r="866" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A866" s="24"/>
+      <c r="B866" s="24"/>
+    </row>
+    <row r="867" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A867" s="24"/>
+      <c r="B867" s="24"/>
+    </row>
+    <row r="868" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A868" s="24"/>
+      <c r="B868" s="24"/>
+    </row>
+    <row r="869" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A869" s="24"/>
+      <c r="B869" s="24"/>
+    </row>
+    <row r="870" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A870" s="24"/>
+      <c r="B870" s="24"/>
+    </row>
+    <row r="871" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A871" s="24"/>
+      <c r="B871" s="24"/>
+    </row>
+    <row r="872" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A872" s="24"/>
+      <c r="B872" s="24"/>
+    </row>
+    <row r="873" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A873" s="24"/>
+      <c r="B873" s="24"/>
+    </row>
+    <row r="874" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A874" s="24"/>
+      <c r="B874" s="24"/>
+    </row>
+    <row r="875" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A875" s="24"/>
+      <c r="B875" s="24"/>
+    </row>
+    <row r="876" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A876" s="24"/>
+      <c r="B876" s="24"/>
+    </row>
+    <row r="877" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A877" s="24"/>
+      <c r="B877" s="24"/>
+    </row>
+    <row r="878" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A878" s="24"/>
+      <c r="B878" s="24"/>
+    </row>
+    <row r="879" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A879" s="24"/>
+      <c r="B879" s="24"/>
+    </row>
+    <row r="880" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A880" s="24"/>
+      <c r="B880" s="24"/>
+    </row>
+    <row r="881" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A881" s="24"/>
+      <c r="B881" s="24"/>
+    </row>
+    <row r="882" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A882" s="24"/>
+      <c r="B882" s="24"/>
+    </row>
+    <row r="883" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A883" s="24"/>
+      <c r="B883" s="24"/>
+    </row>
+    <row r="884" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A884" s="24"/>
+      <c r="B884" s="24"/>
+    </row>
+    <row r="885" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A885" s="24"/>
+      <c r="B885" s="24"/>
+    </row>
+    <row r="886" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A886" s="24"/>
+      <c r="B886" s="24"/>
+    </row>
+    <row r="887" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A887" s="24"/>
+      <c r="B887" s="24"/>
+    </row>
+    <row r="888" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A888" s="24"/>
+      <c r="B888" s="24"/>
+    </row>
+    <row r="889" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A889" s="24"/>
+      <c r="B889" s="24"/>
+    </row>
+    <row r="890" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A890" s="24"/>
+      <c r="B890" s="24"/>
+    </row>
+    <row r="891" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A891" s="24"/>
+      <c r="B891" s="24"/>
+    </row>
+    <row r="892" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="24"/>
+      <c r="B892" s="24"/>
+    </row>
+    <row r="893" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="24"/>
+      <c r="B893" s="24"/>
+    </row>
+    <row r="894" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="24"/>
+      <c r="B894" s="24"/>
+    </row>
+    <row r="895" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="24"/>
+      <c r="B895" s="24"/>
+    </row>
+    <row r="896" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="24"/>
+      <c r="B896" s="24"/>
+    </row>
+    <row r="897" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A897" s="24"/>
+      <c r="B897" s="24"/>
+    </row>
+    <row r="898" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A898" s="24"/>
+      <c r="B898" s="24"/>
+    </row>
+    <row r="899" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A899" s="24"/>
+      <c r="B899" s="24"/>
+    </row>
+    <row r="900" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A900" s="24"/>
+      <c r="B900" s="24"/>
+    </row>
+    <row r="901" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A901" s="24"/>
+      <c r="B901" s="24"/>
+    </row>
+    <row r="902" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A902" s="24"/>
+      <c r="B902" s="24"/>
+    </row>
+    <row r="903" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A903" s="24"/>
+      <c r="B903" s="24"/>
+    </row>
+    <row r="904" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A904" s="24"/>
+      <c r="B904" s="24"/>
+    </row>
+    <row r="905" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A905" s="24"/>
+      <c r="B905" s="24"/>
+    </row>
+    <row r="906" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A906" s="24"/>
+      <c r="B906" s="24"/>
+    </row>
+    <row r="907" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A907" s="24"/>
+      <c r="B907" s="24"/>
+    </row>
+    <row r="908" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A908" s="24"/>
+      <c r="B908" s="24"/>
+    </row>
+    <row r="909" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A909" s="24"/>
+      <c r="B909" s="24"/>
+    </row>
+    <row r="910" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A910" s="24"/>
+      <c r="B910" s="24"/>
+    </row>
+    <row r="911" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A911" s="24"/>
+      <c r="B911" s="24"/>
+    </row>
+    <row r="912" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A912" s="24"/>
+      <c r="B912" s="24"/>
+    </row>
+    <row r="913" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A913" s="24"/>
+      <c r="B913" s="24"/>
+    </row>
+    <row r="914" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A914" s="24"/>
+      <c r="B914" s="24"/>
+    </row>
+    <row r="915" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A915" s="24"/>
+      <c r="B915" s="24"/>
+    </row>
+    <row r="916" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A916" s="24"/>
+      <c r="B916" s="24"/>
+    </row>
+    <row r="917" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A917" s="24"/>
+      <c r="B917" s="24"/>
+    </row>
+    <row r="918" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A918" s="24"/>
+      <c r="B918" s="24"/>
+    </row>
+    <row r="919" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A919" s="24"/>
+      <c r="B919" s="24"/>
+    </row>
+    <row r="920" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A920" s="24"/>
+      <c r="B920" s="24"/>
+    </row>
+    <row r="921" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A921" s="24"/>
+      <c r="B921" s="24"/>
+    </row>
+    <row r="922" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A922" s="24"/>
+      <c r="B922" s="24"/>
+    </row>
+    <row r="923" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A923" s="24"/>
+      <c r="B923" s="24"/>
+    </row>
+    <row r="924" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A924" s="24"/>
+      <c r="B924" s="24"/>
+    </row>
+    <row r="925" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A925" s="24"/>
+      <c r="B925" s="24"/>
+    </row>
+    <row r="926" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A926" s="24"/>
+      <c r="B926" s="24"/>
+    </row>
+    <row r="927" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A927" s="24"/>
+      <c r="B927" s="24"/>
+    </row>
+    <row r="928" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A928" s="24"/>
+      <c r="B928" s="24"/>
+    </row>
+    <row r="929" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A929" s="24"/>
+      <c r="B929" s="24"/>
+    </row>
+    <row r="930" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A930" s="24"/>
+      <c r="B930" s="24"/>
+    </row>
+    <row r="931" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A931" s="24"/>
+      <c r="B931" s="24"/>
+    </row>
+    <row r="932" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A932" s="24"/>
+      <c r="B932" s="24"/>
+    </row>
+    <row r="933" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A933" s="24"/>
+      <c r="B933" s="24"/>
+    </row>
+    <row r="934" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A934" s="24"/>
+      <c r="B934" s="24"/>
+    </row>
+    <row r="935" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A935" s="24"/>
+      <c r="B935" s="24"/>
+    </row>
+    <row r="936" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A936" s="24"/>
+      <c r="B936" s="24"/>
+    </row>
+    <row r="937" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A937" s="24"/>
+      <c r="B937" s="24"/>
+    </row>
+    <row r="938" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A938" s="24"/>
+      <c r="B938" s="24"/>
+    </row>
+    <row r="939" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A939" s="24"/>
+      <c r="B939" s="24"/>
+    </row>
+    <row r="940" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A940" s="24"/>
+      <c r="B940" s="24"/>
+    </row>
+    <row r="941" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A941" s="24"/>
+      <c r="B941" s="24"/>
+    </row>
+    <row r="942" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A942" s="24"/>
+      <c r="B942" s="24"/>
+    </row>
+    <row r="943" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A943" s="24"/>
+      <c r="B943" s="24"/>
+    </row>
+    <row r="944" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A944" s="24"/>
+      <c r="B944" s="24"/>
+    </row>
+    <row r="945" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A945" s="24"/>
+      <c r="B945" s="24"/>
+    </row>
+    <row r="946" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A946" s="24"/>
+      <c r="B946" s="24"/>
+    </row>
+    <row r="947" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A947" s="24"/>
+      <c r="B947" s="24"/>
+    </row>
+    <row r="948" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A948" s="24"/>
+      <c r="B948" s="24"/>
+    </row>
+    <row r="949" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A949" s="24"/>
+      <c r="B949" s="24"/>
+    </row>
+    <row r="950" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A950" s="24"/>
+      <c r="B950" s="24"/>
+    </row>
+    <row r="951" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A951" s="24"/>
+      <c r="B951" s="24"/>
+    </row>
+    <row r="952" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A952" s="24"/>
+      <c r="B952" s="24"/>
+    </row>
+    <row r="953" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A953" s="24"/>
+      <c r="B953" s="24"/>
+    </row>
+    <row r="954" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A954" s="24"/>
+      <c r="B954" s="24"/>
+    </row>
+    <row r="955" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A955" s="24"/>
+      <c r="B955" s="24"/>
+    </row>
+    <row r="956" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A956" s="24"/>
+      <c r="B956" s="24"/>
+    </row>
+    <row r="957" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A957" s="24"/>
+      <c r="B957" s="24"/>
+    </row>
+    <row r="958" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A958" s="24"/>
+      <c r="B958" s="24"/>
+    </row>
+    <row r="959" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A959" s="24"/>
+      <c r="B959" s="24"/>
+    </row>
+    <row r="960" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A960" s="24"/>
+      <c r="B960" s="24"/>
+    </row>
+    <row r="961" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A961" s="24"/>
+      <c r="B961" s="24"/>
+    </row>
+    <row r="962" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A962" s="24"/>
+      <c r="B962" s="24"/>
+    </row>
+    <row r="963" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A963" s="24"/>
+      <c r="B963" s="24"/>
+    </row>
+    <row r="964" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A964" s="24"/>
+      <c r="B964" s="24"/>
+    </row>
+    <row r="965" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A965" s="24"/>
+      <c r="B965" s="24"/>
+    </row>
+    <row r="966" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A966" s="24"/>
+      <c r="B966" s="24"/>
+    </row>
+    <row r="967" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A967" s="24"/>
+      <c r="B967" s="24"/>
+    </row>
+    <row r="968" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A968" s="24"/>
+      <c r="B968" s="24"/>
+    </row>
+    <row r="969" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A969" s="24"/>
+      <c r="B969" s="24"/>
+    </row>
+    <row r="970" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A970" s="24"/>
+      <c r="B970" s="24"/>
+    </row>
+    <row r="971" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A971" s="24"/>
+      <c r="B971" s="24"/>
+    </row>
+    <row r="972" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A972" s="24"/>
+      <c r="B972" s="24"/>
+    </row>
+    <row r="973" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A973" s="24"/>
+      <c r="B973" s="24"/>
+    </row>
+    <row r="974" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A974" s="24"/>
+      <c r="B974" s="24"/>
+    </row>
+    <row r="975" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A975" s="24"/>
+      <c r="B975" s="24"/>
+    </row>
+    <row r="976" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A976" s="24"/>
+      <c r="B976" s="24"/>
+    </row>
+    <row r="977" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A977" s="24"/>
+      <c r="B977" s="24"/>
+    </row>
+    <row r="978" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A978" s="24"/>
+      <c r="B978" s="24"/>
+    </row>
+    <row r="979" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A979" s="24"/>
+      <c r="B979" s="24"/>
+    </row>
+    <row r="980" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A980" s="24"/>
+      <c r="B980" s="24"/>
+    </row>
+    <row r="981" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A981" s="24"/>
+      <c r="B981" s="24"/>
+    </row>
+    <row r="982" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A982" s="24"/>
+      <c r="B982" s="24"/>
+    </row>
+    <row r="983" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A983" s="24"/>
+      <c r="B983" s="24"/>
+    </row>
+    <row r="984" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A984" s="24"/>
+      <c r="B984" s="24"/>
+    </row>
+    <row r="985" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A985" s="24"/>
+      <c r="B985" s="24"/>
+    </row>
+    <row r="986" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A986" s="24"/>
+      <c r="B986" s="24"/>
+    </row>
+    <row r="987" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A987" s="24"/>
+      <c r="B987" s="24"/>
+    </row>
+    <row r="988" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A988" s="24"/>
+      <c r="B988" s="24"/>
+    </row>
+    <row r="989" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A989" s="24"/>
+      <c r="B989" s="24"/>
+    </row>
+    <row r="990" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A990" s="24"/>
+      <c r="B990" s="24"/>
+    </row>
+    <row r="991" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A991" s="24"/>
+      <c r="B991" s="24"/>
+    </row>
+    <row r="992" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A992" s="24"/>
+      <c r="B992" s="24"/>
+    </row>
+    <row r="993" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A993" s="24"/>
+      <c r="B993" s="24"/>
+    </row>
+    <row r="994" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A994" s="24"/>
+      <c r="B994" s="24"/>
+    </row>
+    <row r="995" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A995" s="24"/>
+      <c r="B995" s="24"/>
+    </row>
+    <row r="996" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A996" s="24"/>
+      <c r="B996" s="24"/>
+    </row>
+    <row r="997" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A997" s="24"/>
+      <c r="B997" s="24"/>
+    </row>
+    <row r="998" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A998" s="24"/>
+      <c r="B998" s="24"/>
+    </row>
+    <row r="999" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A999" s="24"/>
+      <c r="B999" s="24"/>
+    </row>
+    <row r="1000" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1000" s="24"/>
+      <c r="B1000" s="24"/>
+    </row>
+    <row r="1001" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1001" s="24"/>
+      <c r="B1001" s="24"/>
+    </row>
+    <row r="1002" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1002" s="24"/>
+      <c r="B1002" s="24"/>
+    </row>
+    <row r="1003" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1003" s="24"/>
+      <c r="B1003" s="24"/>
+    </row>
+    <row r="1004" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1004" s="24"/>
+      <c r="B1004" s="24"/>
+    </row>
+    <row r="1005" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1005" s="24"/>
+      <c r="B1005" s="24"/>
+    </row>
+    <row r="1006" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1006" s="24"/>
+      <c r="B1006" s="24"/>
+    </row>
+    <row r="1007" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1007" s="24"/>
+      <c r="B1007" s="24"/>
+    </row>
+    <row r="1008" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1008" s="24"/>
+      <c r="B1008" s="24"/>
+    </row>
+    <row r="1009" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1009" s="24"/>
+      <c r="B1009" s="24"/>
+    </row>
+    <row r="1010" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1010" s="24"/>
+      <c r="B1010" s="24"/>
+    </row>
+    <row r="1011" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1011" s="24"/>
+      <c r="B1011" s="24"/>
+    </row>
+    <row r="1012" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1012" s="24"/>
+      <c r="B1012" s="24"/>
+    </row>
+    <row r="1013" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1013" s="24"/>
+      <c r="B1013" s="24"/>
+    </row>
+    <row r="1014" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1014" s="24"/>
+      <c r="B1014" s="24"/>
+    </row>
+    <row r="1015" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1015" s="24"/>
+      <c r="B1015" s="24"/>
+    </row>
+    <row r="1016" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1016" s="24"/>
+      <c r="B1016" s="24"/>
+    </row>
+    <row r="1017" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1017" s="24"/>
+      <c r="B1017" s="24"/>
+    </row>
+    <row r="1018" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1018" s="24"/>
+      <c r="B1018" s="24"/>
+    </row>
+    <row r="1019" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1019" s="24"/>
+      <c r="B1019" s="24"/>
+    </row>
+    <row r="1020" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1020" s="24"/>
+      <c r="B1020" s="24"/>
+    </row>
+    <row r="1021" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1021" s="24"/>
+      <c r="B1021" s="24"/>
+    </row>
+    <row r="1022" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1022" s="24"/>
+      <c r="B1022" s="24"/>
+    </row>
+    <row r="1023" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1023" s="24"/>
+      <c r="B1023" s="24"/>
+    </row>
+    <row r="1024" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1024" s="24"/>
+      <c r="B1024" s="24"/>
+    </row>
+    <row r="1025" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1025" s="24"/>
+      <c r="B1025" s="24"/>
+    </row>
+    <row r="1026" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1026" s="24"/>
+      <c r="B1026" s="24"/>
+    </row>
+    <row r="1027" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1027" s="24"/>
+      <c r="B1027" s="24"/>
+    </row>
+    <row r="1028" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1028" s="24"/>
+      <c r="B1028" s="24"/>
+    </row>
+    <row r="1029" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1029" s="24"/>
+      <c r="B1029" s="24"/>
+    </row>
+    <row r="1030" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1030" s="24"/>
+      <c r="B1030" s="24"/>
+    </row>
+    <row r="1031" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1031" s="24"/>
+      <c r="B1031" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="59">
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C7:C8 E69">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74 E78 E85 E90 E95">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DA9FCD-D7F1-3A46-8DC6-303761A161C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF771F51-3A7B-3340-9984-770C75BBA4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="170">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -652,9 +652,6 @@
     <t>Brother</t>
   </si>
   <si>
-    <t>1. A gift for birthday $1000 from Lawrence</t>
-  </si>
-  <si>
     <t>~ Payback $100 to Mom
 ~ Payback $670.4 to Mom (HKTVmall Online Shopping)
 ~ Payback $60 to Mom</t>
@@ -670,10 +667,6 @@
 ~ Watsons Revlon color silk 17/09 - $59.9</t>
   </si>
   <si>
-    <t>~ Additional transport fees for e-cigarette 17/09 - $50
-~ Round Trip to East Kowloon hospital 02/10 - $4</t>
-  </si>
-  <si>
     <t>Partial Food And Snack Prepaid on the Previous Month
 ~ Food
 ~ Snack And Drinks</t>
@@ -681,16 +674,6 @@
   <si>
     <t>1. Top up $50 for Octopus
 2. Top up $50 for Octopus 03/09</t>
-  </si>
-  <si>
-    <t>~ Debit For Octopus Card ($50). 20/08
-~ OK Store buy additional 1 packet cigarette 20/08 - $78
-~ Mail Chuk Yuen Post Office - $2.4
-~ Additional transport fees for e-cigarette 20/08 - $50
-~ Paid Water Supplies Fees 20/08 - $74.1
-~ Round Trip to East Kowloon hospital 31/08 - $4
-~ Round Trip to East Kowloon hospital 03/09 - $4
-~ Debit For Octopus Card ($50). 03/09</t>
   </si>
   <si>
     <t>Partial Food And Snack Prepaid on the Previous Month
@@ -743,6 +726,38 @@
   </si>
   <si>
     <t>Blance Brough Forward From September 2026</t>
+  </si>
+  <si>
+    <t>1. A gift for birthday $1000 from Lawrence
+2. Borrow $500</t>
+  </si>
+  <si>
+    <t>~ Food
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>~ Round Trip to East Kowloon hospital - $4</t>
+  </si>
+  <si>
+    <t>~ Additional fees for cigarette (change e-cigarette to cigarette) 18/09 - $380
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>~ Payback $500 to Lawrence</t>
+  </si>
+  <si>
+    <t>~ Debit For Octopus Card ($50). 20/08
+~ OK Store buy additional 1 packet cigarette 20/08 - $78
+~ Mail Chuk Yuen Post Office - $2.4
+~ Additional transport fees for e-cigarette 20/08 - $50
+~ Paid Water Supplies Fees 20/08 - $74.1
+~ Round Trip to East Kowloon hospital 31/08 - $4
+~ Round Trip to East Kowloon hospital 03/09 - $4
+~ Debit For Octopus Card ($50). 03/09
+~ OK Store buy additional 6 packet cigarette 11/09 - $468</t>
+  </si>
+  <si>
+    <t>Cigarette - 4 pack - each pack has 10 packages. $320 per pack</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1273,119 +1288,29 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1405,16 +1330,124 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1429,32 +1462,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1793,13 +1805,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1820,7 +1832,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>19.04</v>
+        <v>441.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1976,7 +1988,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>14.839999999999998</v>
+        <v>436.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2029,13 +2041,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2063,10 +2075,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2078,10 +2090,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="114"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2093,10 +2105,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="103"/>
+      <c r="D13" s="115"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2106,10 +2118,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2119,10 +2131,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="61"/>
+      <c r="D15" s="88"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2132,10 +2144,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2147,10 +2159,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="104"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2160,10 +2172,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="105"/>
+      <c r="D18" s="111"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2175,10 +2187,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="112"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2199,13 +2211,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2233,10 +2245,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="107"/>
+      <c r="D23" s="113"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2248,10 +2260,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2263,10 +2275,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2276,10 +2288,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="104"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2291,10 +2303,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="105" t="s">
+      <c r="C27" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="105"/>
+      <c r="D27" s="111"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2304,10 +2316,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="108" t="s">
+      <c r="C28" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="108"/>
+      <c r="D28" s="101"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2329,13 +2341,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2363,10 +2375,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="87"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2378,10 +2390,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2391,10 +2403,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2404,10 +2416,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="67"/>
+      <c r="D35" s="94"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2417,7 +2429,7 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="93" t="s">
         <v>115</v>
       </c>
       <c r="D36" s="109"/>
@@ -2430,10 +2442,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2455,11 +2467,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2474,11 +2486,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="72" t="s">
+      <c r="A42" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2524,16 +2536,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="73"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2582,11 +2594,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="72" t="s">
+      <c r="A54" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="86"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2621,11 +2633,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="72" t="s">
+      <c r="A58" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2649,11 +2661,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="86"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="83"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="74" t="s">
+      <c r="A72" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
+      <c r="B72" s="83"/>
+      <c r="C72" s="83"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2779,7 +2791,7 @@
       </c>
       <c r="B74" s="7"/>
       <c r="C74" s="19">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2789,7 +2801,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2812,167 +2824,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="75" t="s">
+      <c r="A79" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="75"/>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
-      <c r="E79" s="75"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="72"/>
+      <c r="E79" s="72"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="76"/>
-      <c r="C80" s="76" t="s">
+      <c r="B80" s="84"/>
+      <c r="C80" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="76"/>
+      <c r="D80" s="84"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="78"/>
+      <c r="B81" s="105"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="78" t="s">
+      <c r="A82" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="78"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="59"/>
+      <c r="C82" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="106"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="78"/>
-      <c r="B83" s="78"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="106"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="78"/>
-      <c r="B84" s="78"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="106"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="78"/>
-      <c r="B85" s="78"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="107"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="78"/>
-      <c r="B86" s="78"/>
-      <c r="C86" s="83" t="s">
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="83"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="78"/>
-      <c r="B87" s="78"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="107"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="78"/>
-      <c r="B88" s="78"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="106"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="78"/>
-      <c r="B89" s="78"/>
-      <c r="C89" s="83" t="s">
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="83"/>
+      <c r="D89" s="81"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="78"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="83" t="s">
+      <c r="A90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="83"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="78"/>
-      <c r="B91" s="78"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="59"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="108"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="79"/>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="85" t="s">
+      <c r="C93" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="85"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2980,113 +2992,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="75"/>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="75"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="75" t="s">
+      <c r="A96" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="75"/>
-      <c r="C96" s="75" t="s">
+      <c r="B96" s="72"/>
+      <c r="C96" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="75"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="77" t="s">
+      <c r="A97" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="77"/>
-      <c r="C97" s="86"/>
-      <c r="D97" s="86"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="78" t="s">
+      <c r="A98" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="78"/>
-      <c r="C98" s="82" t="s">
+      <c r="B98" s="59"/>
+      <c r="C98" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="82"/>
+      <c r="D98" s="80"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="78"/>
-      <c r="B99" s="78"/>
-      <c r="C99" s="80" t="s">
+      <c r="A99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="80"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="78"/>
-      <c r="B100" s="78"/>
-      <c r="C100" s="80" t="s">
+      <c r="A100" s="59"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="80"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="78"/>
-      <c r="B101" s="78"/>
-      <c r="C101" s="80" t="s">
+      <c r="A101" s="59"/>
+      <c r="B101" s="59"/>
+      <c r="C101" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="80"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="78"/>
-      <c r="B102" s="78"/>
-      <c r="C102" s="91" t="s">
+      <c r="A102" s="59"/>
+      <c r="B102" s="59"/>
+      <c r="C102" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="104"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="78" t="s">
+      <c r="A103" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="78"/>
-      <c r="C103" s="86"/>
-      <c r="D103" s="86"/>
+      <c r="B103" s="59"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="89" t="s">
+      <c r="C104" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="89"/>
+      <c r="D104" s="56"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3107,91 +3119,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="90" t="s">
+      <c r="A107" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="90"/>
-      <c r="C107" s="90"/>
-      <c r="D107" s="90"/>
-      <c r="E107" s="90"/>
+      <c r="B107" s="71"/>
+      <c r="C107" s="71"/>
+      <c r="D107" s="71"/>
+      <c r="E107" s="71"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="75" t="s">
+      <c r="A108" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="75"/>
-      <c r="C108" s="75" t="s">
+      <c r="B108" s="72"/>
+      <c r="C108" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="75"/>
+      <c r="D108" s="72"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="77" t="s">
+      <c r="A109" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="77"/>
-      <c r="C109" s="86"/>
-      <c r="D109" s="86"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="94" t="s">
+      <c r="A110" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="95"/>
-      <c r="C110" s="108" t="s">
+      <c r="B110" s="65"/>
+      <c r="C110" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="108"/>
+      <c r="D110" s="101"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="96"/>
-      <c r="B111" s="97"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="66"/>
+      <c r="B111" s="67"/>
+      <c r="C111" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="103"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="98"/>
-      <c r="B112" s="99"/>
-      <c r="C112" s="91" t="s">
+      <c r="A112" s="68"/>
+      <c r="B112" s="69"/>
+      <c r="C112" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="104"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="78" t="s">
+      <c r="A113" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="78"/>
-      <c r="C113" s="86"/>
-      <c r="D113" s="86"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="89" t="s">
+      <c r="C114" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="89"/>
+      <c r="D114" s="56"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6943,35 +6955,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6985,42 +7004,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7045,7 +7057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y1035"/>
+  <dimension ref="A1:Y1036"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -7060,13 +7072,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7088,7 +7100,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>19.04</v>
+        <v>441.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7248,7 +7260,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>14.839999999999998</v>
+        <v>436.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7301,13 +7313,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7335,10 +7347,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7350,10 +7362,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="99"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7365,10 +7377,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7380,10 +7392,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7404,13 +7416,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7438,10 +7450,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="87"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7453,10 +7465,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="88"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7468,10 +7480,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="66" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="67"/>
+      <c r="C20" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="94"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7483,10 +7495,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="91" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="65"/>
+      <c r="D21" s="92"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7498,27 +7510,27 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="95" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="67"/>
+      <c r="D22" s="94"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
         <v>141</v>
       </c>
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="69"/>
+      <c r="C23" s="93" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="94"/>
       <c r="E23" s="29">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7530,7 +7542,7 @@
       </c>
       <c r="E24" s="26">
         <f>SUM(E19:E23)</f>
-        <v>3648.08</v>
+        <v>4148.08</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7538,13 +7550,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7572,10 +7584,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="63"/>
+      <c r="D27" s="87"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7587,10 +7599,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="61"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7598,8 +7610,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7621,11 +7633,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="71" t="s">
+      <c r="A32" s="89" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7640,11 +7652,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7690,16 +7702,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="73"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7748,11 +7760,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
+      <c r="B46" s="86"/>
+      <c r="C46" s="86"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7787,11 +7799,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="72"/>
-      <c r="C50" s="72"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7815,11 +7827,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="72" t="s">
+      <c r="A53" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7843,11 +7855,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="74" t="s">
+      <c r="A56" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="83"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7924,11 +7936,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="83"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7945,7 +7957,7 @@
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7955,7 +7967,7 @@
       </c>
       <c r="C67" s="19">
         <f>SUM(C65:C66)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7978,91 +7990,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="75" t="s">
+      <c r="A71" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="75"/>
-      <c r="C71" s="75"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="72"/>
+      <c r="E71" s="72"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="76" t="s">
+      <c r="A72" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="76"/>
-      <c r="C72" s="76" t="s">
+      <c r="B72" s="84"/>
+      <c r="C72" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="76"/>
+      <c r="D72" s="84"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="77" t="s">
+      <c r="A73" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="77"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="78"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="79" t="s">
+      <c r="A74" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="79"/>
-      <c r="C74" s="80" t="s">
+      <c r="B74" s="78"/>
+      <c r="C74" s="73" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="80"/>
+      <c r="D74" s="73"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="79"/>
-      <c r="B75" s="79"/>
-      <c r="C75" s="81" t="s">
+      <c r="A75" s="78"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="82"/>
+      <c r="D75" s="80"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="79"/>
-      <c r="B76" s="79"/>
-      <c r="C76" s="81" t="s">
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="83"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="79" t="s">
+      <c r="A77" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="79"/>
-      <c r="C77" s="84"/>
-      <c r="D77" s="84"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="85" t="s">
+      <c r="C78" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="85"/>
+      <c r="D78" s="77"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8070,116 +8082,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="72"/>
+      <c r="E80" s="72"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="75" t="s">
+      <c r="A81" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="75"/>
-      <c r="C81" s="75" t="s">
+      <c r="B81" s="72"/>
+      <c r="C81" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="75"/>
+      <c r="D81" s="72"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="94" t="s">
+      <c r="A83" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="95"/>
-      <c r="C83" s="87" t="s">
-        <v>144</v>
-      </c>
-      <c r="D83" s="88"/>
+      <c r="B83" s="65"/>
+      <c r="C83" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" s="63"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="96"/>
-      <c r="B84" s="97"/>
-      <c r="C84" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D84" s="80"/>
+      <c r="A84" s="66"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="D84" s="73"/>
       <c r="E84" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="137" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="96"/>
-      <c r="B85" s="97"/>
-      <c r="C85" s="91" t="s">
-        <v>150</v>
-      </c>
-      <c r="D85" s="92"/>
+    <row r="85" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="66"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="75"/>
       <c r="E85" s="48">
-        <v>312.5</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="96"/>
-      <c r="B86" s="97"/>
-      <c r="C86" s="87" t="s">
-        <v>146</v>
-      </c>
-      <c r="D86" s="93"/>
+      <c r="A86" s="66"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86" s="76"/>
       <c r="E86" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="98"/>
-      <c r="B87" s="99"/>
-      <c r="C87" s="91" t="s">
-        <v>145</v>
-      </c>
-      <c r="D87" s="92"/>
+      <c r="A87" s="68"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" s="75"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="78" t="s">
+      <c r="A88" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="78"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="86"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="89" t="s">
+      <c r="C89" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="89"/>
+      <c r="D89" s="56"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>14.839999999999691</v>
+        <v>46.840000000000146</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8197,97 +8209,104 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="90" t="s">
+      <c r="A92" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="90"/>
-      <c r="C92" s="90"/>
-      <c r="D92" s="90"/>
-      <c r="E92" s="90"/>
+      <c r="B92" s="71"/>
+      <c r="C92" s="71"/>
+      <c r="D92" s="71"/>
+      <c r="E92" s="71"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="75" t="s">
+      <c r="A93" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="75"/>
-      <c r="C93" s="75" t="s">
+      <c r="B93" s="72"/>
+      <c r="C93" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="75"/>
+      <c r="D93" s="72"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="77" t="s">
+      <c r="A94" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="86"/>
-      <c r="D94" s="86"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>14.839999999999691</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="94" t="s">
+        <v>46.840000000000146</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="95"/>
-      <c r="C95" s="100" t="s">
-        <v>148</v>
-      </c>
-      <c r="D95" s="101"/>
+      <c r="B95" s="65"/>
+      <c r="C95" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="D95" s="63"/>
       <c r="E95" s="45">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="66"/>
+      <c r="B96" s="67"/>
+      <c r="C96" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="61"/>
+      <c r="E96" s="45">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="66"/>
+      <c r="B97" s="67"/>
+      <c r="C97" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" s="61"/>
+      <c r="E97" s="45">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="68"/>
+      <c r="B98" s="69"/>
+      <c r="C98" s="60"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="96"/>
-      <c r="B96" s="97"/>
-      <c r="C96" s="100" t="s">
-        <v>147</v>
-      </c>
-      <c r="D96" s="101"/>
-      <c r="E96" s="45">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="98"/>
-      <c r="B97" s="99"/>
-      <c r="C97" s="100"/>
-      <c r="D97" s="101"/>
-      <c r="E97" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="78" t="s">
+    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="78"/>
-      <c r="C98" s="86"/>
-      <c r="D98" s="86"/>
-      <c r="E98" s="45">
+      <c r="B99" s="59"/>
+      <c r="C99" s="58"/>
+      <c r="D99" s="58"/>
+      <c r="E99" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C99" s="89" t="s">
+    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C100" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D99" s="89"/>
-      <c r="E99" s="47">
-        <f>(E30+E94)-SUM(E95:E98)</f>
-        <v>1274.8399999999997</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="24"/>
-      <c r="B100" s="24"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="47">
+        <f>(E30+E94)-SUM(E95:E99)</f>
+        <v>76.840000000000146</v>
+      </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="24"/>
@@ -12029,17 +12048,54 @@
       <c r="A1035" s="24"/>
       <c r="B1035" s="24"/>
     </row>
+    <row r="1036" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1036" s="24"/>
+      <c r="B1036" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A95:B97"/>
+  <mergeCells count="64">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12052,48 +12108,16 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A95:B98"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12103,7 +12127,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78 E82 E89 E94 E99">
+  <conditionalFormatting sqref="E78 E82 E89 E94 E100">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -12133,13 +12157,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="A1" s="96" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12161,7 +12185,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>19.04</v>
+        <v>441.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12321,7 +12345,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>14.839999999999998</v>
+        <v>436.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12374,13 +12398,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="A10" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12408,25 +12432,25 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="99"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12434,8 +12458,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12456,13 +12480,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="62" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
+      <c r="A16" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12490,25 +12514,25 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="63"/>
+      <c r="D17" s="87"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12516,8 +12540,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="65"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="92"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12539,13 +12563,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="A22" s="90" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12573,25 +12597,25 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="63"/>
+      <c r="D23" s="87"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12599,8 +12623,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12622,11 +12646,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="71" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
+      <c r="A28" s="89" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12641,11 +12665,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="72" t="s">
+      <c r="A30" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12691,16 +12715,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="73"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="73"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="85"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12749,11 +12773,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="72" t="s">
+      <c r="A42" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12788,11 +12812,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="72" t="s">
+      <c r="A46" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="72"/>
+      <c r="B46" s="86"/>
+      <c r="C46" s="86"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12816,11 +12840,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="72" t="s">
+      <c r="A49" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12844,11 +12868,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="74" t="s">
+      <c r="A52" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="74"/>
-      <c r="C52" s="74"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12861,15 +12885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>18</v>
+      <c r="B54" s="50" t="s">
+        <v>169</v>
       </c>
       <c r="C54" s="29">
-        <v>900</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -12921,15 +12945,15 @@
       </c>
       <c r="C59" s="39">
         <f>SUM(C53:C58)</f>
-        <v>955</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="74" t="s">
+      <c r="A60" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="74"/>
-      <c r="C60" s="74"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -12966,7 +12990,7 @@
       </c>
       <c r="C64" s="41">
         <f>C34+C41+C45+C48+C51+C59</f>
-        <v>1171</v>
+        <v>1551</v>
       </c>
       <c r="H64" s="42"/>
     </row>
@@ -12979,192 +13003,200 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="B67" s="75"/>
-      <c r="C67" s="75"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="75"/>
+      <c r="A67" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="72"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="76" t="s">
+      <c r="A68" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="76"/>
-      <c r="C68" s="76" t="s">
+      <c r="B68" s="84"/>
+      <c r="C68" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="76"/>
+      <c r="D68" s="84"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B69" s="77"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
+      <c r="A69" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" s="57"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
       <c r="E69" s="47">
-        <f>'July 2026- September 2026'!E99</f>
-        <v>1274.8399999999997</v>
+        <f>'July 2026- September 2026'!E100</f>
+        <v>76.840000000000146</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="79" t="s">
+      <c r="A70" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
       <c r="E70" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="79"/>
-      <c r="B71" s="79"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="82"/>
+    <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="78"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="79" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" s="80"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="79"/>
-      <c r="B72" s="79"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="83"/>
+      <c r="A72" s="78"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" s="81"/>
       <c r="E72" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="79" t="s">
+      <c r="A73" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="79"/>
-      <c r="C73" s="84"/>
-      <c r="D73" s="84"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
       <c r="E73" s="46">
         <f>C64</f>
-        <v>1171</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="85" t="s">
+      <c r="C74" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="85"/>
+      <c r="D74" s="77"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>2588.8399999999997</v>
+        <v>1006.8400000000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="B76" s="75"/>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="75"/>
+      <c r="A76" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="72"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="72"/>
+      <c r="E76" s="72"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="75" t="s">
+      <c r="A77" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="75"/>
-      <c r="C77" s="75" t="s">
+      <c r="B77" s="72"/>
+      <c r="C77" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="75"/>
+      <c r="D77" s="72"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="77" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="77"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="86"/>
+      <c r="A78" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" s="57"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>2588.8399999999997</v>
+        <v>1006.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="94" t="s">
+      <c r="A79" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="95"/>
-      <c r="C79" s="87"/>
-      <c r="D79" s="88"/>
+      <c r="B79" s="65"/>
+      <c r="C79" s="70"/>
+      <c r="D79" s="63"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="96"/>
-      <c r="B80" s="97"/>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
+    <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="66"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="D80" s="73"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="96"/>
-      <c r="B81" s="97"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="92"/>
+      <c r="A81" s="66"/>
+      <c r="B81" s="67"/>
+      <c r="C81" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="D81" s="75"/>
       <c r="E81" s="48">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="87"/>
-      <c r="D82" s="93"/>
+      <c r="A82" s="66"/>
+      <c r="B82" s="67"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="76"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="98"/>
-      <c r="B83" s="99"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="92"/>
+      <c r="A83" s="68"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="75"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="78" t="s">
+      <c r="A84" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="78"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="86"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="58"/>
       <c r="E84" s="45">
         <f>C64</f>
-        <v>1171</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="89" t="s">
+      <c r="C85" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="89"/>
+      <c r="D85" s="56"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>3902.84</v>
+        <v>1936.8400000000001</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13182,88 +13214,92 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="90" t="s">
-        <v>164</v>
-      </c>
-      <c r="B88" s="90"/>
-      <c r="C88" s="90"/>
-      <c r="D88" s="90"/>
-      <c r="E88" s="90"/>
+      <c r="A88" s="71" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" s="71"/>
+      <c r="C88" s="71"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="71"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="75" t="s">
+      <c r="A89" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="75"/>
-      <c r="C89" s="75" t="s">
+      <c r="B89" s="72"/>
+      <c r="C89" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="75"/>
+      <c r="D89" s="72"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77" t="s">
-        <v>162</v>
-      </c>
-      <c r="B90" s="77"/>
-      <c r="C90" s="86"/>
-      <c r="D90" s="86"/>
+      <c r="A90" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="B90" s="57"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>3902.84</v>
+        <v>1936.8400000000001</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="94" t="s">
+      <c r="A91" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="95"/>
-      <c r="C91" s="100"/>
-      <c r="D91" s="101"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="60"/>
+      <c r="D91" s="61"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="96"/>
-      <c r="B92" s="97"/>
-      <c r="C92" s="100"/>
-      <c r="D92" s="101"/>
+    <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="66"/>
+      <c r="B92" s="67"/>
+      <c r="C92" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" s="61"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="98"/>
-      <c r="B93" s="99"/>
-      <c r="C93" s="100"/>
-      <c r="D93" s="101"/>
+      <c r="A93" s="68"/>
+      <c r="B93" s="69"/>
+      <c r="C93" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="D93" s="61"/>
       <c r="E93" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="78" t="s">
+      <c r="A94" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="78"/>
-      <c r="C94" s="86"/>
-      <c r="D94" s="86"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="45">
         <f>C64</f>
-        <v>1171</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="89" t="s">
+      <c r="C95" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="89"/>
+      <c r="D95" s="56"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>5216.84</v>
+        <v>2866.84</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17012,6 +17048,56 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="C94:D94"/>
     <mergeCell ref="C95:D95"/>
@@ -17021,56 +17107,6 @@
     <mergeCell ref="C91:D91"/>
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF771F51-3A7B-3340-9984-770C75BBA4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C172F-24B8-CB49-940A-FE80ECBC9541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="170">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -743,9 +743,6 @@
 ~ Round Trip to East Kowloon hospital 02/10 - $4</t>
   </si>
   <si>
-    <t>~ Payback $500 to Lawrence</t>
-  </si>
-  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
@@ -758,6 +755,9 @@
   </si>
   <si>
     <t>Cigarette - 4 pack - each pack has 10 packages. $320 per pack</t>
+  </si>
+  <si>
+    <t>~ Payback $250 to Lawrence</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1288,100 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1297,20 +1390,23 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1330,68 +1426,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1400,72 +1442,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1805,13 +1805,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2041,13 +2041,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2075,10 +2075,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2090,10 +2090,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="114"/>
+      <c r="D12" s="59"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2105,10 +2105,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="115"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2118,10 +2118,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2131,10 +2131,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="88"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2144,10 +2144,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="88"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2159,10 +2159,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="110" t="s">
+      <c r="C17" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="110"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2172,10 +2172,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="111"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2187,10 +2187,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="112" t="s">
+      <c r="C19" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="112"/>
+      <c r="D19" s="64"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2211,13 +2211,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2245,10 +2245,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="113"/>
+      <c r="D23" s="66"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2260,10 +2260,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2275,10 +2275,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="88"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2288,10 +2288,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="110"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2303,10 +2303,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="111"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2316,10 +2316,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="101"/>
+      <c r="D28" s="68"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2341,13 +2341,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2375,10 +2375,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="87" t="s">
+      <c r="C32" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="87"/>
+      <c r="D32" s="69"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2390,10 +2390,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="88"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2403,10 +2403,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="88"/>
+      <c r="D34" s="61"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2416,10 +2416,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="93" t="s">
+      <c r="C35" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="94"/>
+      <c r="D35" s="71"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2429,10 +2429,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="72"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2442,10 +2442,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="100" t="s">
+      <c r="C37" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="88"/>
+      <c r="D37" s="61"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2467,11 +2467,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="89" t="s">
+      <c r="A40" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2486,11 +2486,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="86" t="s">
+      <c r="A42" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2536,16 +2536,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
+      <c r="A48" s="75"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2594,11 +2594,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="86" t="s">
+      <c r="A54" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2633,11 +2633,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="86" t="s">
+      <c r="A58" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2661,11 +2661,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="86" t="s">
+      <c r="A61" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="86"/>
-      <c r="C61" s="86"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2689,11 +2689,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="83" t="s">
+      <c r="A64" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="83"/>
-      <c r="C64" s="83"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2770,11 +2770,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="83"/>
-      <c r="C72" s="83"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="76"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2824,167 +2824,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
+      <c r="E79" s="77"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="84"/>
-      <c r="C80" s="84" t="s">
+      <c r="B80" s="78"/>
+      <c r="C80" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="84"/>
+      <c r="D80" s="78"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="105" t="s">
+      <c r="A81" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="105"/>
-      <c r="C81" s="59"/>
-      <c r="D81" s="59"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="80"/>
+      <c r="D81" s="80"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="59" t="s">
+      <c r="A82" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="106" t="s">
+      <c r="B82" s="80"/>
+      <c r="C82" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="106"/>
+      <c r="D82" s="81"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="59"/>
-      <c r="B83" s="59"/>
-      <c r="C83" s="106" t="s">
+      <c r="A83" s="80"/>
+      <c r="B83" s="80"/>
+      <c r="C83" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="106"/>
+      <c r="D83" s="81"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="59"/>
-      <c r="B84" s="59"/>
-      <c r="C84" s="106" t="s">
+      <c r="A84" s="80"/>
+      <c r="B84" s="80"/>
+      <c r="C84" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="106"/>
+      <c r="D84" s="81"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="59"/>
-      <c r="B85" s="59"/>
-      <c r="C85" s="107" t="s">
+      <c r="A85" s="80"/>
+      <c r="B85" s="80"/>
+      <c r="C85" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="107"/>
+      <c r="D85" s="82"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="59"/>
-      <c r="B86" s="59"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="80"/>
+      <c r="B86" s="80"/>
+      <c r="C86" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="81"/>
+      <c r="D86" s="83"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="59"/>
-      <c r="B87" s="59"/>
-      <c r="C87" s="107" t="s">
+      <c r="A87" s="80"/>
+      <c r="B87" s="80"/>
+      <c r="C87" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="107"/>
+      <c r="D87" s="82"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59"/>
-      <c r="B88" s="59"/>
-      <c r="C88" s="106" t="s">
+      <c r="A88" s="80"/>
+      <c r="B88" s="80"/>
+      <c r="C88" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="106"/>
+      <c r="D88" s="81"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="59"/>
-      <c r="B89" s="59"/>
-      <c r="C89" s="81" t="s">
+      <c r="A89" s="80"/>
+      <c r="B89" s="80"/>
+      <c r="C89" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="81"/>
+      <c r="D89" s="83"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="59"/>
-      <c r="B90" s="59"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="80"/>
+      <c r="B90" s="80"/>
+      <c r="C90" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="81"/>
+      <c r="D90" s="83"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="59"/>
-      <c r="B91" s="59"/>
-      <c r="C91" s="108" t="s">
+      <c r="A91" s="80"/>
+      <c r="B91" s="80"/>
+      <c r="C91" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="108"/>
+      <c r="D91" s="84"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="82"/>
-      <c r="D92" s="82"/>
+      <c r="B92" s="85"/>
+      <c r="C92" s="86"/>
+      <c r="D92" s="86"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="87"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2992,113 +2992,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="72" t="s">
+      <c r="A95" s="77" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="72"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="77"/>
+      <c r="D95" s="77"/>
+      <c r="E95" s="77"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="72" t="s">
+      <c r="A96" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="72"/>
-      <c r="C96" s="72" t="s">
+      <c r="B96" s="77"/>
+      <c r="C96" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="72"/>
+      <c r="D96" s="77"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
+      <c r="B97" s="88"/>
+      <c r="C97" s="89"/>
+      <c r="D97" s="89"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="59" t="s">
+      <c r="A98" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="59"/>
-      <c r="C98" s="80" t="s">
+      <c r="B98" s="80"/>
+      <c r="C98" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="80"/>
+      <c r="D98" s="90"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="59"/>
-      <c r="B99" s="59"/>
-      <c r="C99" s="73" t="s">
+      <c r="A99" s="80"/>
+      <c r="B99" s="80"/>
+      <c r="C99" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="91"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="59"/>
-      <c r="B100" s="59"/>
-      <c r="C100" s="73" t="s">
+      <c r="A100" s="80"/>
+      <c r="B100" s="80"/>
+      <c r="C100" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="91"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="59"/>
-      <c r="B101" s="59"/>
-      <c r="C101" s="73" t="s">
+      <c r="A101" s="80"/>
+      <c r="B101" s="80"/>
+      <c r="C101" s="91" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="73"/>
+      <c r="D101" s="91"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="59"/>
-      <c r="B102" s="59"/>
-      <c r="C102" s="74" t="s">
+      <c r="A102" s="80"/>
+      <c r="B102" s="80"/>
+      <c r="C102" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="104"/>
+      <c r="D102" s="93"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="59" t="s">
+      <c r="A103" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="59"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
+      <c r="B103" s="80"/>
+      <c r="C103" s="89"/>
+      <c r="D103" s="89"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="56" t="s">
+      <c r="C104" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="56"/>
+      <c r="D104" s="94"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3119,55 +3119,55 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="71" t="s">
+      <c r="A107" s="95" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="71"/>
-      <c r="C107" s="71"/>
-      <c r="D107" s="71"/>
-      <c r="E107" s="71"/>
+      <c r="B107" s="95"/>
+      <c r="C107" s="95"/>
+      <c r="D107" s="95"/>
+      <c r="E107" s="95"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="72" t="s">
+      <c r="A108" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="72"/>
-      <c r="C108" s="72" t="s">
+      <c r="B108" s="77"/>
+      <c r="C108" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="72"/>
+      <c r="D108" s="77"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
+      <c r="B109" s="88"/>
+      <c r="C109" s="89"/>
+      <c r="D109" s="89"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="64" t="s">
+      <c r="A110" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="65"/>
-      <c r="C110" s="101" t="s">
+      <c r="B110" s="97"/>
+      <c r="C110" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="101"/>
+      <c r="D110" s="68"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="66"/>
-      <c r="B111" s="67"/>
+      <c r="A111" s="98"/>
+      <c r="B111" s="99"/>
       <c r="C111" s="102" t="s">
         <v>116</v>
       </c>
@@ -3177,33 +3177,33 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
-      <c r="C112" s="74" t="s">
+      <c r="A112" s="100"/>
+      <c r="B112" s="101"/>
+      <c r="C112" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="104"/>
+      <c r="D112" s="93"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="59" t="s">
+      <c r="A113" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="59"/>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
+      <c r="B113" s="80"/>
+      <c r="C113" s="89"/>
+      <c r="D113" s="89"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="56" t="s">
+      <c r="C114" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="56"/>
+      <c r="D114" s="94"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6955,42 +6955,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7004,35 +6997,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7072,13 +7072,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7313,13 +7313,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7347,10 +7347,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7362,10 +7362,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="99"/>
+      <c r="D12" s="104"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7377,10 +7377,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="88"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7392,10 +7392,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="100" t="s">
+      <c r="C14" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="88"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7416,13 +7416,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7450,10 +7450,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="87"/>
+      <c r="D18" s="69"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7465,10 +7465,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="88"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7480,10 +7480,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="94"/>
+      <c r="D20" s="71"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7495,10 +7495,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="92"/>
+      <c r="D21" s="106"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7510,10 +7510,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="95" t="s">
+      <c r="C22" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="94"/>
+      <c r="D22" s="71"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7525,10 +7525,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="93" t="s">
+      <c r="C23" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="94"/>
+      <c r="D23" s="71"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7550,13 +7550,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7584,10 +7584,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="87" t="s">
+      <c r="C27" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="87"/>
+      <c r="D27" s="69"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7599,10 +7599,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="88"/>
+      <c r="D28" s="61"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7610,8 +7610,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7633,11 +7633,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="89" t="s">
+      <c r="A32" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7652,11 +7652,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="86" t="s">
+      <c r="A34" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7702,16 +7702,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="85" t="s">
+      <c r="A39" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="85"/>
+      <c r="A40" s="75"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="75"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7760,11 +7760,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="86" t="s">
+      <c r="A46" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7799,11 +7799,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7827,11 +7827,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="86" t="s">
+      <c r="A53" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="74"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7855,11 +7855,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="83" t="s">
+      <c r="A56" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="83"/>
-      <c r="C56" s="83"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="76"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7936,11 +7936,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="83" t="s">
+      <c r="A64" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="83"/>
-      <c r="C64" s="83"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7990,91 +7990,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="72" t="s">
+      <c r="A71" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="72"/>
-      <c r="C71" s="72"/>
-      <c r="D71" s="72"/>
-      <c r="E71" s="72"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="84" t="s">
+      <c r="B72" s="78"/>
+      <c r="C72" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="84"/>
+      <c r="D72" s="78"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="57" t="s">
+      <c r="A73" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="57"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="59"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="80"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="78" t="s">
+      <c r="A74" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="73" t="s">
+      <c r="B74" s="85"/>
+      <c r="C74" s="91" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="73"/>
+      <c r="D74" s="91"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78"/>
-      <c r="B75" s="78"/>
-      <c r="C75" s="79" t="s">
+      <c r="A75" s="85"/>
+      <c r="B75" s="85"/>
+      <c r="C75" s="108" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="80"/>
+      <c r="D75" s="90"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="79" t="s">
+      <c r="A76" s="85"/>
+      <c r="B76" s="85"/>
+      <c r="C76" s="108" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="81"/>
+      <c r="D76" s="83"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78" t="s">
+      <c r="A77" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="82"/>
-      <c r="D77" s="82"/>
+      <c r="B77" s="85"/>
+      <c r="C77" s="86"/>
+      <c r="D77" s="86"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="77" t="s">
+      <c r="C78" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="77"/>
+      <c r="D78" s="87"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8082,113 +8082,113 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="72" t="s">
+      <c r="A81" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72" t="s">
+      <c r="B81" s="77"/>
+      <c r="C81" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="72"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
+      <c r="B82" s="88"/>
+      <c r="C82" s="89"/>
+      <c r="D82" s="89"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="64" t="s">
+      <c r="A83" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="65"/>
-      <c r="C83" s="70" t="s">
+      <c r="B83" s="97"/>
+      <c r="C83" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="63"/>
+      <c r="D83" s="110"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="66"/>
-      <c r="B84" s="67"/>
-      <c r="C84" s="73" t="s">
+      <c r="A84" s="98"/>
+      <c r="B84" s="99"/>
+      <c r="C84" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="73"/>
+      <c r="D84" s="91"/>
       <c r="E84" s="48">
         <v>721.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="66"/>
-      <c r="B85" s="67"/>
-      <c r="C85" s="74" t="s">
-        <v>168</v>
-      </c>
-      <c r="D85" s="75"/>
+      <c r="A85" s="98"/>
+      <c r="B85" s="99"/>
+      <c r="C85" s="92" t="s">
+        <v>167</v>
+      </c>
+      <c r="D85" s="111"/>
       <c r="E85" s="48">
         <v>780.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="66"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="70" t="s">
+      <c r="A86" s="98"/>
+      <c r="B86" s="99"/>
+      <c r="C86" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="76"/>
+      <c r="D86" s="112"/>
       <c r="E86" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="68"/>
-      <c r="B87" s="69"/>
-      <c r="C87" s="74" t="s">
+      <c r="A87" s="100"/>
+      <c r="B87" s="101"/>
+      <c r="C87" s="92" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="75"/>
+      <c r="D87" s="111"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="59" t="s">
+      <c r="A88" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="59"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
+      <c r="B88" s="80"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="89"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="56" t="s">
+      <c r="C89" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="56"/>
+      <c r="D89" s="94"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
         <v>46.840000000000146</v>
@@ -8209,103 +8209,103 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="95" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="71"/>
-      <c r="C92" s="71"/>
-      <c r="D92" s="71"/>
-      <c r="E92" s="71"/>
+      <c r="B92" s="95"/>
+      <c r="C92" s="95"/>
+      <c r="D92" s="95"/>
+      <c r="E92" s="95"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="72" t="s">
+      <c r="A93" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72" t="s">
+      <c r="B93" s="77"/>
+      <c r="C93" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="72"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="57" t="s">
+      <c r="A94" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="88"/>
+      <c r="C94" s="89"/>
+      <c r="D94" s="89"/>
       <c r="E94" s="47">
         <f>E89</f>
         <v>46.840000000000146</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="64" t="s">
+      <c r="A95" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="65"/>
-      <c r="C95" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="D95" s="63"/>
+      <c r="B95" s="97"/>
+      <c r="C95" s="115" t="s">
+        <v>169</v>
+      </c>
+      <c r="D95" s="110"/>
       <c r="E95" s="45">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="66"/>
-      <c r="B96" s="67"/>
-      <c r="C96" s="60" t="s">
+      <c r="A96" s="98"/>
+      <c r="B96" s="99"/>
+      <c r="C96" s="113" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="61"/>
+      <c r="D96" s="114"/>
       <c r="E96" s="45">
         <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="66"/>
-      <c r="B97" s="67"/>
-      <c r="C97" s="60" t="s">
+      <c r="A97" s="98"/>
+      <c r="B97" s="99"/>
+      <c r="C97" s="113" t="s">
         <v>166</v>
       </c>
-      <c r="D97" s="61"/>
+      <c r="D97" s="114"/>
       <c r="E97" s="45">
         <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="68"/>
-      <c r="B98" s="69"/>
-      <c r="C98" s="60"/>
-      <c r="D98" s="61"/>
+      <c r="A98" s="100"/>
+      <c r="B98" s="101"/>
+      <c r="C98" s="113"/>
+      <c r="D98" s="114"/>
       <c r="E98" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="59" t="s">
+      <c r="A99" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="59"/>
-      <c r="C99" s="58"/>
-      <c r="D99" s="58"/>
+      <c r="B99" s="80"/>
+      <c r="C99" s="89"/>
+      <c r="D99" s="89"/>
       <c r="E99" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="56" t="s">
+      <c r="C100" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D100" s="56"/>
+      <c r="D100" s="94"/>
       <c r="E100" s="47">
         <f>(E30+E94)-SUM(E95:E99)</f>
-        <v>76.840000000000146</v>
+        <v>326.84000000000015</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12054,48 +12054,16 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A95:B98"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12108,16 +12076,48 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A95:B98"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12157,13 +12157,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12398,13 +12398,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12432,10 +12432,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12447,10 +12447,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="99"/>
+      <c r="D12" s="104"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12458,8 +12458,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12480,13 +12480,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12514,10 +12514,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="87"/>
+      <c r="D17" s="69"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12529,10 +12529,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="88"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12540,8 +12540,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="92"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12563,13 +12563,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12597,10 +12597,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="87"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12612,10 +12612,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12623,8 +12623,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12646,11 +12646,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12665,11 +12665,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12715,16 +12715,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="75"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="75"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12773,11 +12773,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="86" t="s">
+      <c r="A42" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12812,11 +12812,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="86" t="s">
+      <c r="A46" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12840,11 +12840,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="86" t="s">
+      <c r="A49" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="74"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12868,11 +12868,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="83"/>
-      <c r="C52" s="83"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="76"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12890,7 +12890,7 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C54" s="29">
         <v>1280</v>
@@ -12949,11 +12949,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="83" t="s">
+      <c r="A60" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="83"/>
-      <c r="C60" s="83"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13003,89 +13003,91 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="72" t="s">
+      <c r="A67" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="77"/>
+      <c r="D67" s="77"/>
+      <c r="E67" s="77"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="84" t="s">
+      <c r="A68" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="84"/>
-      <c r="C68" s="84" t="s">
+      <c r="B68" s="78"/>
+      <c r="C68" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="84"/>
+      <c r="D68" s="78"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="57" t="s">
+      <c r="A69" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="57"/>
-      <c r="C69" s="59"/>
-      <c r="D69" s="59"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="80"/>
+      <c r="D69" s="80"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E100</f>
-        <v>76.840000000000146</v>
+        <v>326.84000000000015</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="73"/>
+      <c r="B70" s="85"/>
+      <c r="C70" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="91"/>
       <c r="E70" s="45">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="78"/>
-      <c r="B71" s="78"/>
-      <c r="C71" s="79" t="s">
+      <c r="A71" s="85"/>
+      <c r="B71" s="85"/>
+      <c r="C71" s="108" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="80"/>
+      <c r="D71" s="90"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="78"/>
-      <c r="B72" s="78"/>
-      <c r="C72" s="79" t="s">
+      <c r="A72" s="85"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="108" t="s">
         <v>165</v>
       </c>
-      <c r="D72" s="81"/>
+      <c r="D72" s="83"/>
       <c r="E72" s="45">
         <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="78" t="s">
+      <c r="A73" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="82"/>
-      <c r="D73" s="82"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="86"/>
       <c r="E73" s="46">
         <f>C64</f>
         <v>1551</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="77" t="s">
+      <c r="C74" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="77"/>
+      <c r="D74" s="87"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
         <v>1006.8400000000001</v>
@@ -13093,107 +13095,107 @@
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="72" t="s">
+      <c r="A76" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="72"/>
-      <c r="C76" s="72"/>
-      <c r="D76" s="72"/>
-      <c r="E76" s="72"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="77"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="72" t="s">
+      <c r="A77" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="72"/>
-      <c r="C77" s="72" t="s">
+      <c r="B77" s="77"/>
+      <c r="C77" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="72"/>
+      <c r="D77" s="77"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="57"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
+      <c r="B78" s="88"/>
+      <c r="C78" s="89"/>
+      <c r="D78" s="89"/>
       <c r="E78" s="47">
         <f>E74</f>
         <v>1006.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="64" t="s">
+      <c r="A79" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="65"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="63"/>
+      <c r="B79" s="97"/>
+      <c r="C79" s="109"/>
+      <c r="D79" s="110"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="66"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="73" t="s">
+      <c r="A80" s="98"/>
+      <c r="B80" s="99"/>
+      <c r="C80" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="73"/>
+      <c r="D80" s="91"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="66"/>
-      <c r="B81" s="67"/>
-      <c r="C81" s="74" t="s">
+      <c r="A81" s="98"/>
+      <c r="B81" s="99"/>
+      <c r="C81" s="92" t="s">
         <v>165</v>
       </c>
-      <c r="D81" s="75"/>
+      <c r="D81" s="111"/>
       <c r="E81" s="48">
         <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="66"/>
-      <c r="B82" s="67"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="76"/>
+      <c r="A82" s="98"/>
+      <c r="B82" s="99"/>
+      <c r="C82" s="109"/>
+      <c r="D82" s="112"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="68"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="75"/>
+      <c r="A83" s="100"/>
+      <c r="B83" s="101"/>
+      <c r="C83" s="92"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="59" t="s">
+      <c r="A84" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="59"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
+      <c r="B84" s="80"/>
+      <c r="C84" s="89"/>
+      <c r="D84" s="89"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1551</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="56" t="s">
+      <c r="C85" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="56"/>
+      <c r="D85" s="94"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
         <v>1936.8400000000001</v>
@@ -13214,89 +13216,89 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="71" t="s">
+      <c r="A88" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="71"/>
-      <c r="C88" s="71"/>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
+      <c r="B88" s="95"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="72" t="s">
+      <c r="A89" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="72"/>
-      <c r="C89" s="72" t="s">
+      <c r="B89" s="77"/>
+      <c r="C89" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="72"/>
+      <c r="D89" s="77"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57" t="s">
+      <c r="A90" s="88" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="57"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
+      <c r="B90" s="88"/>
+      <c r="C90" s="89"/>
+      <c r="D90" s="89"/>
       <c r="E90" s="47">
         <f>E85</f>
         <v>1936.8400000000001</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="64" t="s">
+      <c r="A91" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="65"/>
-      <c r="C91" s="60"/>
-      <c r="D91" s="61"/>
+      <c r="B91" s="97"/>
+      <c r="C91" s="113"/>
+      <c r="D91" s="114"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="66"/>
-      <c r="B92" s="67"/>
-      <c r="C92" s="60" t="s">
+      <c r="A92" s="98"/>
+      <c r="B92" s="99"/>
+      <c r="C92" s="113" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="61"/>
+      <c r="D92" s="114"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="68"/>
-      <c r="B93" s="69"/>
-      <c r="C93" s="60" t="s">
+      <c r="A93" s="100"/>
+      <c r="B93" s="101"/>
+      <c r="C93" s="113" t="s">
         <v>165</v>
       </c>
-      <c r="D93" s="61"/>
+      <c r="D93" s="114"/>
       <c r="E93" s="45">
         <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="59" t="s">
+      <c r="A94" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="59"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="80"/>
+      <c r="C94" s="89"/>
+      <c r="D94" s="89"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1551</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="56" t="s">
+      <c r="C95" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="56"/>
+      <c r="D95" s="94"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
         <v>2866.84</v>
@@ -17048,15 +17050,45 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17068,45 +17100,15 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C172F-24B8-CB49-940A-FE80ECBC9541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584049BE-EF2B-C548-90E7-9217FEA77DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="171">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -736,13 +736,6 @@
 ~ Snack And Drinks</t>
   </si>
   <si>
-    <t>~ Round Trip to East Kowloon hospital - $4</t>
-  </si>
-  <si>
-    <t>~ Additional fees for cigarette (change e-cigarette to cigarette) 18/09 - $380
-~ Round Trip to East Kowloon hospital 02/10 - $4</t>
-  </si>
-  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
@@ -751,13 +744,24 @@
 ~ Round Trip to East Kowloon hospital 31/08 - $4
 ~ Round Trip to East Kowloon hospital 03/09 - $4
 ~ Debit For Octopus Card ($50). 03/09
-~ OK Store buy additional 6 packet cigarette 11/09 - $468</t>
+~ OK Store buy additional 1 packet cigarette 11/09 - $78</t>
   </si>
   <si>
-    <t>Cigarette - 4 pack - each pack has 10 packages. $320 per pack</t>
+    <t>~ Payback $500 to Lawrence</t>
   </si>
   <si>
-    <t>~ Payback $250 to Lawrence</t>
+    <t>e-cigarette plus transport fees</t>
+  </si>
+  <si>
+    <t>Vist Psychology Doctor plus transport</t>
+  </si>
+  <si>
+    <t>~ Additional fees for e-cigarette machine 18/09 - $250
+~ Additional transport fees for e-cigarette 18/09 - $50
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>~ iHerb Aveeno Lotion 18/09 - $136.64</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1288,124 +1292,19 @@
     <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1426,14 +1325,143 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1444,28 +1472,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1805,13 +1812,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2041,13 +2048,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2075,10 +2082,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2090,10 +2097,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="59"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2105,10 +2112,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="60"/>
+      <c r="D13" s="104"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2118,10 +2125,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2131,10 +2138,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="61"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2144,10 +2151,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2159,10 +2166,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="62"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2172,10 +2179,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2187,10 +2194,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="64" t="s">
+      <c r="C19" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="64"/>
+      <c r="D19" s="98"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2211,13 +2218,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2245,10 +2252,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="66"/>
+      <c r="D23" s="99"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2260,10 +2267,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2275,10 +2282,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2288,10 +2295,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="62"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2303,10 +2310,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="63"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2316,10 +2323,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="67"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2341,13 +2348,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2375,10 +2382,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="69"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2390,10 +2397,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2403,10 +2410,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="61"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2416,10 +2423,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="71"/>
+      <c r="D35" s="91"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2429,10 +2436,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="72"/>
+      <c r="D36" s="92"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2442,10 +2449,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
+      <c r="C37" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="61"/>
+      <c r="D37" s="89"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2467,11 +2474,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2486,11 +2493,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2536,16 +2543,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="88"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="75"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2594,11 +2601,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="74" t="s">
+      <c r="A54" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2633,11 +2640,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="84"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2661,11 +2668,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="74" t="s">
+      <c r="A61" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="84"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2689,11 +2696,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="85"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2770,11 +2777,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="76" t="s">
+      <c r="A72" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="76"/>
-      <c r="C72" s="76"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="85"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2824,23 +2831,23 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="77" t="s">
+      <c r="A79" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="77"/>
-      <c r="C79" s="77"/>
-      <c r="D79" s="77"/>
-      <c r="E79" s="77"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78" t="s">
+      <c r="B80" s="86"/>
+      <c r="C80" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="78"/>
+      <c r="D80" s="86"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
@@ -2850,141 +2857,141 @@
         <v>84</v>
       </c>
       <c r="B81" s="79"/>
-      <c r="C81" s="80"/>
-      <c r="D81" s="80"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="80" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="80"/>
-      <c r="C82" s="81" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="81"/>
+      <c r="D82" s="80"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="80"/>
-      <c r="B83" s="80"/>
-      <c r="C83" s="81" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="81"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="80"/>
-      <c r="B84" s="80"/>
-      <c r="C84" s="81" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="81"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="80"/>
-      <c r="B85" s="80"/>
-      <c r="C85" s="82" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="82"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="80"/>
-      <c r="B86" s="80"/>
-      <c r="C86" s="83" t="s">
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="83"/>
+      <c r="D86" s="82"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="80"/>
-      <c r="B87" s="80"/>
-      <c r="C87" s="82" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="82"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="80"/>
-      <c r="B88" s="80"/>
-      <c r="C88" s="81" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="81"/>
+      <c r="D88" s="80"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="80"/>
-      <c r="B89" s="80"/>
-      <c r="C89" s="83" t="s">
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="83"/>
+      <c r="D89" s="82"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="80"/>
-      <c r="B90" s="80"/>
-      <c r="C90" s="83" t="s">
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="83"/>
+      <c r="D90" s="82"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="80"/>
-      <c r="B91" s="80"/>
-      <c r="C91" s="84" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="84"/>
+      <c r="D91" s="83"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="85" t="s">
+      <c r="A92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="85"/>
-      <c r="C92" s="86"/>
-      <c r="D92" s="86"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="87" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="87"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2992,113 +2999,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="77" t="s">
+      <c r="A95" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="77"/>
-      <c r="C95" s="77"/>
-      <c r="D95" s="77"/>
-      <c r="E95" s="77"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="77" t="s">
+      <c r="A96" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="77"/>
-      <c r="C96" s="77" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="77"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="88" t="s">
+      <c r="A97" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="88"/>
-      <c r="C97" s="89"/>
-      <c r="D97" s="89"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="80" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="80"/>
-      <c r="C98" s="90" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="90"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="80"/>
-      <c r="B99" s="80"/>
-      <c r="C99" s="91" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="91"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="80"/>
-      <c r="B100" s="80"/>
-      <c r="C100" s="91" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="91"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="80"/>
-      <c r="B101" s="80"/>
-      <c r="C101" s="91" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="91"/>
+      <c r="D101" s="75"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="80"/>
-      <c r="B102" s="80"/>
-      <c r="C102" s="92" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="93"/>
+      <c r="D102" s="71"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="80" t="s">
+      <c r="A103" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="80"/>
-      <c r="C103" s="89"/>
-      <c r="D103" s="89"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="94" t="s">
+      <c r="C104" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="94"/>
+      <c r="D104" s="59"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3119,91 +3126,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="95" t="s">
+      <c r="A107" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="95"/>
-      <c r="C107" s="95"/>
-      <c r="D107" s="95"/>
-      <c r="E107" s="95"/>
+      <c r="B107" s="72"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="72"/>
+      <c r="E107" s="72"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="77" t="s">
+      <c r="A108" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="77"/>
-      <c r="C108" s="77" t="s">
+      <c r="B108" s="73"/>
+      <c r="C108" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="77"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="88" t="s">
+      <c r="A109" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="88"/>
-      <c r="C109" s="89"/>
-      <c r="D109" s="89"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="96" t="s">
+      <c r="A110" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="97"/>
-      <c r="C110" s="68" t="s">
+      <c r="B110" s="62"/>
+      <c r="C110" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="68"/>
+      <c r="D110" s="67"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="98"/>
-      <c r="B111" s="99"/>
-      <c r="C111" s="102" t="s">
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="103"/>
+      <c r="D111" s="69"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="100"/>
-      <c r="B112" s="101"/>
-      <c r="C112" s="92" t="s">
+      <c r="A112" s="65"/>
+      <c r="B112" s="66"/>
+      <c r="C112" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="93"/>
+      <c r="D112" s="71"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="80" t="s">
+      <c r="A113" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="80"/>
-      <c r="C113" s="89"/>
-      <c r="D113" s="89"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="94" t="s">
+      <c r="C114" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="94"/>
+      <c r="D114" s="59"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6955,35 +6962,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6997,42 +7011,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7072,13 +7079,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7313,13 +7320,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7347,10 +7354,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7362,10 +7369,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="104"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7377,10 +7384,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7392,10 +7399,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7416,13 +7423,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7450,10 +7457,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="69"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7465,10 +7472,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7480,10 +7487,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="71"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7495,10 +7502,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="106"/>
+      <c r="D21" s="114"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7510,10 +7517,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="107" t="s">
+      <c r="C22" s="115" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="71"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7525,10 +7532,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="90" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="71"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7550,13 +7557,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7584,10 +7591,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="69"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7599,10 +7606,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="61"/>
+      <c r="D28" s="89"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7610,8 +7617,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7633,11 +7640,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="73" t="s">
+      <c r="A32" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7652,11 +7659,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="74" t="s">
+      <c r="A34" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="84"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7702,16 +7709,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="75" t="s">
+      <c r="A39" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="75"/>
-      <c r="C39" s="75"/>
+      <c r="B39" s="88"/>
+      <c r="C39" s="88"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="75"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="75"/>
+      <c r="A40" s="88"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7760,11 +7767,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7799,11 +7806,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="84"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7827,11 +7834,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="74" t="s">
+      <c r="A53" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="74"/>
+      <c r="B53" s="84"/>
+      <c r="C53" s="84"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7855,11 +7862,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="76" t="s">
+      <c r="A56" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="76"/>
-      <c r="C56" s="76"/>
+      <c r="B56" s="85"/>
+      <c r="C56" s="85"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7936,11 +7943,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="85"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7957,7 +7964,7 @@
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7967,7 +7974,7 @@
       </c>
       <c r="C67" s="19">
         <f>SUM(C65:C66)</f>
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7990,91 +7997,91 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="77" t="s">
+      <c r="A71" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="77"/>
-      <c r="C71" s="77"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="77"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="73"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="73"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="78" t="s">
+      <c r="A72" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78" t="s">
+      <c r="B72" s="86"/>
+      <c r="C72" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="78"/>
+      <c r="D72" s="86"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="88" t="s">
+      <c r="A73" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="88"/>
-      <c r="C73" s="80"/>
-      <c r="D73" s="80"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="85" t="s">
+      <c r="A74" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="85"/>
-      <c r="C74" s="91" t="s">
+      <c r="B74" s="76"/>
+      <c r="C74" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="91"/>
+      <c r="D74" s="75"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="85"/>
-      <c r="B75" s="85"/>
-      <c r="C75" s="108" t="s">
+      <c r="A75" s="76"/>
+      <c r="B75" s="76"/>
+      <c r="C75" s="112" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="90"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="85"/>
-      <c r="B76" s="85"/>
-      <c r="C76" s="108" t="s">
+      <c r="A76" s="76"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="112" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="83"/>
+      <c r="D76" s="82"/>
       <c r="E76" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="85"/>
-      <c r="C77" s="86"/>
-      <c r="D77" s="86"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="77"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="87" t="s">
+      <c r="C78" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="87"/>
+      <c r="D78" s="78"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8082,116 +8089,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="77"/>
-      <c r="C80" s="77"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="77"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="73"/>
+      <c r="D80" s="73"/>
+      <c r="E80" s="73"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="77" t="s">
+      <c r="A81" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="77"/>
-      <c r="C81" s="77" t="s">
+      <c r="B81" s="73"/>
+      <c r="C81" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="77"/>
+      <c r="D81" s="73"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="88" t="s">
+      <c r="A82" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="88"/>
-      <c r="C82" s="89"/>
-      <c r="D82" s="89"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="96" t="s">
+      <c r="A83" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="97"/>
+      <c r="B83" s="62"/>
       <c r="C83" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="110"/>
+      <c r="D83" s="108"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="98"/>
-      <c r="B84" s="99"/>
-      <c r="C84" s="91" t="s">
+      <c r="A84" s="63"/>
+      <c r="B84" s="64"/>
+      <c r="C84" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="91"/>
+      <c r="D84" s="75"/>
       <c r="E84" s="48">
         <v>721.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="98"/>
-      <c r="B85" s="99"/>
-      <c r="C85" s="92" t="s">
-        <v>167</v>
-      </c>
-      <c r="D85" s="111"/>
+      <c r="A85" s="63"/>
+      <c r="B85" s="64"/>
+      <c r="C85" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="D85" s="110"/>
       <c r="E85" s="48">
-        <v>780.5</v>
+        <v>390.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="98"/>
-      <c r="B86" s="99"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="64"/>
       <c r="C86" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="112"/>
+      <c r="D86" s="111"/>
       <c r="E86" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="100"/>
-      <c r="B87" s="101"/>
-      <c r="C87" s="92" t="s">
+      <c r="A87" s="65"/>
+      <c r="B87" s="66"/>
+      <c r="C87" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="111"/>
+      <c r="D87" s="110"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="80" t="s">
+      <c r="A88" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="80"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="89"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="94" t="s">
+      <c r="C89" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="94"/>
+      <c r="D89" s="59"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>46.840000000000146</v>
+        <v>436.84000000000015</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8209,103 +8216,105 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="95" t="s">
+      <c r="A92" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="95"/>
-      <c r="C92" s="95"/>
-      <c r="D92" s="95"/>
-      <c r="E92" s="95"/>
+      <c r="B92" s="72"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="72"/>
+      <c r="E92" s="72"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="77" t="s">
+      <c r="A93" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="77"/>
-      <c r="C93" s="77" t="s">
+      <c r="B93" s="73"/>
+      <c r="C93" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="73"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="88" t="s">
+      <c r="A94" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="88"/>
-      <c r="C94" s="89"/>
-      <c r="D94" s="89"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>46.840000000000146</v>
+        <v>436.84000000000015</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="96" t="s">
+      <c r="A95" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="97"/>
-      <c r="C95" s="115" t="s">
+      <c r="B95" s="62"/>
+      <c r="C95" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" s="108"/>
+      <c r="E95" s="45">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="63"/>
+      <c r="B96" s="64"/>
+      <c r="C96" s="105" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="106"/>
+      <c r="E96" s="45">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="63"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="D95" s="110"/>
-      <c r="E95" s="45">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="98"/>
-      <c r="B96" s="99"/>
-      <c r="C96" s="113" t="s">
-        <v>146</v>
-      </c>
-      <c r="D96" s="114"/>
-      <c r="E96" s="45">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="98"/>
-      <c r="B97" s="99"/>
-      <c r="C97" s="113" t="s">
-        <v>166</v>
-      </c>
-      <c r="D97" s="114"/>
+      <c r="D97" s="106"/>
       <c r="E97" s="45">
-        <v>384</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="100"/>
-      <c r="B98" s="101"/>
-      <c r="C98" s="113"/>
-      <c r="D98" s="114"/>
+      <c r="A98" s="65"/>
+      <c r="B98" s="66"/>
+      <c r="C98" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" s="106"/>
       <c r="E98" s="45">
-        <v>0</v>
+        <v>136.63999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="80" t="s">
+      <c r="A99" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="80"/>
-      <c r="C99" s="89"/>
-      <c r="D99" s="89"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="58"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="94" t="s">
+      <c r="C100" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D100" s="94"/>
+      <c r="D100" s="59"/>
       <c r="E100" s="47">
         <f>(E30+E94)-SUM(E95:E99)</f>
-        <v>326.84000000000015</v>
+        <v>210.20000000000027</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12054,16 +12063,48 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A95:B98"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12076,48 +12117,16 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A95:B98"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12157,13 +12166,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="100" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12398,13 +12407,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12432,10 +12441,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12447,10 +12456,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="104"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12458,8 +12467,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12480,13 +12489,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12514,10 +12523,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="69"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12529,10 +12538,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="89"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12540,8 +12549,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="106"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="114"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12563,13 +12572,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12597,10 +12606,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="69"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12612,10 +12621,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12623,8 +12632,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12646,11 +12655,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="73" t="s">
+      <c r="A28" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12665,11 +12674,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12715,16 +12724,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="75"/>
-      <c r="C35" s="75"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="75"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="75"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12773,11 +12782,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12812,11 +12821,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12840,11 +12849,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="74" t="s">
+      <c r="A49" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="74"/>
-      <c r="C49" s="74"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12868,11 +12877,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
+      <c r="B52" s="85"/>
+      <c r="C52" s="85"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12890,10 +12899,10 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C54" s="29">
-        <v>1280</v>
+        <v>950</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -12931,11 +12940,11 @@
       <c r="A58" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>77</v>
+      <c r="B58" s="56" t="s">
+        <v>168</v>
       </c>
       <c r="C58" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12945,15 +12954,15 @@
       </c>
       <c r="C59" s="39">
         <f>SUM(C53:C58)</f>
-        <v>1335</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
+      <c r="B60" s="85"/>
+      <c r="C60" s="85"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -12990,7 +12999,7 @@
       </c>
       <c r="C64" s="41">
         <f>C34+C41+C45+C48+C51+C59</f>
-        <v>1551</v>
+        <v>1225</v>
       </c>
       <c r="H64" s="42"/>
     </row>
@@ -13003,202 +13012,196 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="77" t="s">
+      <c r="A67" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="77"/>
-      <c r="C67" s="77"/>
-      <c r="D67" s="77"/>
-      <c r="E67" s="77"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="78" t="s">
+      <c r="A68" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="78"/>
-      <c r="C68" s="78" t="s">
+      <c r="B68" s="86"/>
+      <c r="C68" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="78"/>
+      <c r="D68" s="86"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="88" t="s">
+      <c r="A69" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="88"/>
-      <c r="C69" s="80"/>
-      <c r="D69" s="80"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E100</f>
-        <v>326.84000000000015</v>
+        <v>210.20000000000027</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="85" t="s">
+      <c r="A70" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="85"/>
-      <c r="C70" s="91" t="s">
-        <v>169</v>
-      </c>
-      <c r="D70" s="91"/>
+      <c r="B70" s="76"/>
+      <c r="C70" s="75"/>
+      <c r="D70" s="75"/>
       <c r="E70" s="45">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="85"/>
-      <c r="B71" s="85"/>
-      <c r="C71" s="108" t="s">
+      <c r="A71" s="76"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="112" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="90"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="85"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="108" t="s">
-        <v>165</v>
-      </c>
-      <c r="D72" s="83"/>
+      <c r="A72" s="76"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="82"/>
       <c r="E72" s="45">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="85" t="s">
+      <c r="A73" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="85"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="86"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="46">
         <f>C64</f>
-        <v>1551</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="87" t="s">
+      <c r="C74" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="87"/>
+      <c r="D74" s="78"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1006.8400000000001</v>
+        <v>1470.2000000000003</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="77" t="s">
+      <c r="A76" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="77"/>
-      <c r="C76" s="77"/>
-      <c r="D76" s="77"/>
-      <c r="E76" s="77"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="77" t="s">
+      <c r="A77" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="77"/>
-      <c r="C77" s="77" t="s">
+      <c r="B77" s="73"/>
+      <c r="C77" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="77"/>
+      <c r="D77" s="73"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="88" t="s">
+      <c r="A78" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="88"/>
-      <c r="C78" s="89"/>
-      <c r="D78" s="89"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1006.8400000000001</v>
+        <v>1470.2000000000003</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="96" t="s">
+      <c r="A79" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="97"/>
+      <c r="B79" s="62"/>
       <c r="C79" s="109"/>
-      <c r="D79" s="110"/>
+      <c r="D79" s="108"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="98"/>
-      <c r="B80" s="99"/>
-      <c r="C80" s="91" t="s">
+      <c r="A80" s="63"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="91"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="98"/>
-      <c r="B81" s="99"/>
-      <c r="C81" s="92" t="s">
-        <v>165</v>
-      </c>
-      <c r="D81" s="111"/>
+      <c r="A81" s="63"/>
+      <c r="B81" s="64"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="110"/>
       <c r="E81" s="48">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="98"/>
-      <c r="B82" s="99"/>
+      <c r="A82" s="63"/>
+      <c r="B82" s="64"/>
       <c r="C82" s="109"/>
-      <c r="D82" s="112"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="100"/>
-      <c r="B83" s="101"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="111"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="110"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="80" t="s">
+      <c r="A84" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="80"/>
-      <c r="C84" s="89"/>
-      <c r="D84" s="89"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="58"/>
       <c r="E84" s="45">
         <f>C64</f>
-        <v>1551</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="94" t="s">
+      <c r="C85" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="94"/>
+      <c r="D85" s="59"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>1936.8400000000001</v>
+        <v>2730.2000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13216,92 +13219,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="95" t="s">
+      <c r="A88" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="95"/>
-      <c r="C88" s="95"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77" t="s">
+      <c r="A89" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="77"/>
-      <c r="C89" s="77" t="s">
+      <c r="B89" s="73"/>
+      <c r="C89" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="77"/>
+      <c r="D89" s="73"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="88" t="s">
+      <c r="A90" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="88"/>
-      <c r="C90" s="89"/>
-      <c r="D90" s="89"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>1936.8400000000001</v>
+        <v>2730.2000000000003</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="96" t="s">
+      <c r="A91" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="97"/>
-      <c r="C91" s="113"/>
-      <c r="D91" s="114"/>
+      <c r="B91" s="62"/>
+      <c r="C91" s="105"/>
+      <c r="D91" s="106"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="98"/>
-      <c r="B92" s="99"/>
-      <c r="C92" s="113" t="s">
+      <c r="A92" s="63"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="114"/>
+      <c r="D92" s="106"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="100"/>
-      <c r="B93" s="101"/>
-      <c r="C93" s="113" t="s">
-        <v>165</v>
-      </c>
-      <c r="D93" s="114"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="66"/>
+      <c r="C93" s="105"/>
+      <c r="D93" s="106"/>
       <c r="E93" s="45">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="80" t="s">
+      <c r="A94" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="80"/>
-      <c r="C94" s="89"/>
-      <c r="D94" s="89"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="45">
         <f>C64</f>
-        <v>1551</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="94" t="s">
+      <c r="C95" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="94"/>
+      <c r="D95" s="59"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>2866.84</v>
+        <v>3990.2000000000007</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17050,45 +17051,15 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17100,15 +17071,45 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584049BE-EF2B-C548-90E7-9217FEA77DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32E729A-6250-9B42-A6A1-9207A0CF6997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="170">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -736,20 +736,6 @@
 ~ Snack And Drinks</t>
   </si>
   <si>
-    <t>~ Debit For Octopus Card ($50). 20/08
-~ OK Store buy additional 1 packet cigarette 20/08 - $78
-~ Mail Chuk Yuen Post Office - $2.4
-~ Additional transport fees for e-cigarette 20/08 - $50
-~ Paid Water Supplies Fees 20/08 - $74.1
-~ Round Trip to East Kowloon hospital 31/08 - $4
-~ Round Trip to East Kowloon hospital 03/09 - $4
-~ Debit For Octopus Card ($50). 03/09
-~ OK Store buy additional 1 packet cigarette 11/09 - $78</t>
-  </si>
-  <si>
-    <t>~ Payback $500 to Lawrence</t>
-  </si>
-  <si>
     <t>e-cigarette plus transport fees</t>
   </si>
   <si>
@@ -761,7 +747,19 @@
 ~ Round Trip to East Kowloon hospital 02/10 - $4</t>
   </si>
   <si>
-    <t>~ iHerb Aveeno Lotion 18/09 - $136.64</t>
+    <t>~ Debit For Octopus Card ($50). 20/08
+~ OK Store buy additional 1 packet cigarette 20/08 - $78
+~ Mail Chuk Yuen Post Office - $2.4
+~ Additional transport fees for e-cigarette 20/08 - $50
+~ Paid Water Supplies Fees 20/08 - $74.1
+~ Round Trip to East Kowloon hospital 31/08 - $4
+~ Round Trip to East Kowloon hospital 03/09 - $4
+~ Debit For Octopus Card ($50). 03/09
+~ OK Store buy additional 1 packet cigarette 11/09 - $78
+~ OK Store buy additional 1 packet cigarette 12/09 - $78</t>
+  </si>
+  <si>
+    <t>~ Payback $250 to Lawrence</t>
   </si>
 </sst>
 </file>
@@ -1295,17 +1293,113 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1325,41 +1419,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1370,110 +1461,17 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1812,13 +1810,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1839,7 +1837,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>441.04</v>
+        <v>363.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1995,7 +1993,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>436.84000000000003</v>
+        <v>358.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2048,13 +2046,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2082,10 +2080,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2097,10 +2095,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="103"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2112,10 +2110,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="104"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2125,10 +2123,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2138,10 +2136,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="89"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2151,10 +2149,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="89"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2166,10 +2164,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="94"/>
+      <c r="D17" s="104"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2179,10 +2177,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2194,10 +2192,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="98" t="s">
+      <c r="C19" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="98"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2218,13 +2216,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2252,10 +2250,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="99" t="s">
+      <c r="C23" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="99"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2267,10 +2265,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2282,10 +2280,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="89"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2295,10 +2293,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="94"/>
+      <c r="D26" s="104"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2310,10 +2308,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2323,10 +2321,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="67"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2348,13 +2346,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2382,10 +2380,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="97"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2397,10 +2395,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="89"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2410,10 +2408,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="89"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2423,10 +2421,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C35" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="91"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2436,10 +2434,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="90" t="s">
+      <c r="C36" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="92"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2449,10 +2447,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="93" t="s">
+      <c r="C37" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="89"/>
+      <c r="D37" s="62"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2474,11 +2472,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2493,11 +2491,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2543,16 +2541,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="88"/>
-      <c r="C47" s="88"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="88"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="88"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2601,11 +2599,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="84" t="s">
+      <c r="A54" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="84"/>
-      <c r="C54" s="84"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2640,11 +2638,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="84"/>
-      <c r="C58" s="84"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2668,11 +2666,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="84" t="s">
+      <c r="A61" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="84"/>
-      <c r="C61" s="84"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2696,11 +2694,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="85" t="s">
+      <c r="A64" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2777,11 +2775,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="85" t="s">
+      <c r="A72" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="85"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2831,87 +2829,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="73" t="s">
+      <c r="A79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="86" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="86"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="79" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="79"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="80" t="s">
+      <c r="B82" s="77"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="80"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="57"/>
-      <c r="B83" s="57"/>
-      <c r="C83" s="80" t="s">
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="80"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="57"/>
-      <c r="B84" s="57"/>
-      <c r="C84" s="80" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="80"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
-      <c r="B85" s="57"/>
-      <c r="C85" s="81" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="81"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="57"/>
-      <c r="B86" s="57"/>
+      <c r="A86" s="77"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2921,30 +2919,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="57"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="81" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="81"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="57"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="80" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="80"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="57"/>
-      <c r="B89" s="57"/>
+      <c r="A89" s="77"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2954,8 +2952,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57"/>
-      <c r="B90" s="57"/>
+      <c r="A90" s="77"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2965,33 +2963,33 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57"/>
-      <c r="B91" s="57"/>
-      <c r="C91" s="83" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="83"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="76"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="78" t="s">
+      <c r="C93" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="78"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2999,113 +2997,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="73"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="73"/>
-      <c r="E95" s="73"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="73"/>
-      <c r="C96" s="73" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="73"/>
+      <c r="D96" s="74"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="60" t="s">
+      <c r="A97" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="60"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="57" t="s">
+      <c r="A98" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="74" t="s">
+      <c r="B98" s="77"/>
+      <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="74"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="57"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="75" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="75"/>
+      <c r="D99" s="79"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="57"/>
-      <c r="B100" s="57"/>
-      <c r="C100" s="75" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="75"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="57"/>
-      <c r="B101" s="57"/>
-      <c r="C101" s="75" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="75"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="57"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="70" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="71"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="57" t="s">
+      <c r="A103" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="57"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="59" t="s">
+      <c r="C104" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="59"/>
+      <c r="D104" s="88"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3126,91 +3124,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="72" t="s">
+      <c r="A107" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="72"/>
-      <c r="C107" s="72"/>
-      <c r="D107" s="72"/>
-      <c r="E107" s="72"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
+      <c r="D107" s="89"/>
+      <c r="E107" s="89"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="73" t="s">
+      <c r="A108" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="73"/>
-      <c r="C108" s="73" t="s">
+      <c r="B108" s="74"/>
+      <c r="C108" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="73"/>
+      <c r="D108" s="74"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="60" t="s">
+      <c r="A109" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="60"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
+      <c r="B109" s="76"/>
+      <c r="C109" s="85"/>
+      <c r="D109" s="85"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="61" t="s">
+      <c r="A110" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="62"/>
-      <c r="C110" s="67" t="s">
+      <c r="B110" s="94"/>
+      <c r="C110" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="67"/>
+      <c r="D110" s="108"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="63"/>
-      <c r="B111" s="64"/>
-      <c r="C111" s="68" t="s">
+      <c r="A111" s="95"/>
+      <c r="B111" s="96"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="69"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="65"/>
-      <c r="B112" s="66"/>
-      <c r="C112" s="70" t="s">
+      <c r="A112" s="97"/>
+      <c r="B112" s="98"/>
+      <c r="C112" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="71"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="57" t="s">
+      <c r="A113" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="85"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="59"/>
+      <c r="D114" s="88"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6962,42 +6960,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7011,35 +7002,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7079,13 +7077,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7107,7 +7105,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>441.04</v>
+        <v>363.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7267,7 +7265,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>436.84000000000003</v>
+        <v>358.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7320,13 +7318,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7354,10 +7352,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7369,10 +7367,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7384,10 +7382,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="89"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7399,10 +7397,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7423,13 +7421,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7457,10 +7455,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="97"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7472,10 +7470,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="89"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7487,10 +7485,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="91"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7502,10 +7500,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="114"/>
+      <c r="D21" s="66"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7517,10 +7515,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="91"/>
+      <c r="D22" s="68"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7532,10 +7530,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="91"/>
+      <c r="D23" s="68"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7557,13 +7555,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="96" t="s">
+      <c r="A26" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7591,10 +7589,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="97" t="s">
+      <c r="C27" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="97"/>
+      <c r="D27" s="64"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7606,10 +7604,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="89"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7617,8 +7615,8 @@
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="29">
         <v>0</v>
       </c>
@@ -7640,11 +7638,11 @@
       <c r="B31" s="24"/>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -7659,11 +7657,11 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="84" t="s">
+      <c r="A34" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="84"/>
-      <c r="C34" s="84"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50" t="s">
@@ -7709,16 +7707,16 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="88"/>
-      <c r="C39" s="88"/>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="88"/>
-      <c r="B40" s="88"/>
-      <c r="C40" s="88"/>
+      <c r="A40" s="72"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -7767,11 +7765,11 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -7806,11 +7804,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="84" t="s">
+      <c r="A50" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="84"/>
-      <c r="C50" s="84"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="71"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7834,11 +7832,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="84" t="s">
+      <c r="A53" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="84"/>
-      <c r="C53" s="84"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="71"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
@@ -7862,11 +7860,11 @@
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="85" t="s">
+      <c r="A56" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="85"/>
-      <c r="C56" s="85"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="17" t="s">
@@ -7943,11 +7941,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="85" t="s">
+      <c r="A64" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
@@ -7964,7 +7962,7 @@
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7974,7 +7972,7 @@
       </c>
       <c r="C67" s="19">
         <f>SUM(C65:C66)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7997,67 +7995,67 @@
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="73" t="s">
+      <c r="A71" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="73"/>
-      <c r="C71" s="73"/>
-      <c r="D71" s="73"/>
-      <c r="E71" s="73"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="86"/>
-      <c r="C72" s="86" t="s">
+      <c r="B72" s="75"/>
+      <c r="C72" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="86"/>
+      <c r="D72" s="75"/>
       <c r="E72" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="60" t="s">
+      <c r="A73" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="60"/>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="76" t="s">
+      <c r="A74" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="76"/>
-      <c r="C74" s="75" t="s">
+      <c r="B74" s="78"/>
+      <c r="C74" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="75"/>
+      <c r="D74" s="79"/>
       <c r="E74" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="76"/>
-      <c r="B75" s="76"/>
-      <c r="C75" s="112" t="s">
+      <c r="A75" s="78"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="74"/>
+      <c r="D75" s="81"/>
       <c r="E75" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="76"/>
-      <c r="B76" s="76"/>
-      <c r="C76" s="112" t="s">
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="80" t="s">
         <v>134</v>
       </c>
       <c r="D76" s="82"/>
@@ -8066,22 +8064,22 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="76" t="s">
+      <c r="A77" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="76"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="77"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="83"/>
       <c r="E77" s="46">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="78" t="s">
+      <c r="C78" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="78"/>
+      <c r="D78" s="84"/>
       <c r="E78" s="47">
         <f>(E15+E73)-SUM(E74:E77)</f>
         <v>24.599999999999909</v>
@@ -8089,116 +8087,116 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="73"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
     </row>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="73"/>
-      <c r="C81" s="73" t="s">
+      <c r="B81" s="74"/>
+      <c r="C81" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="73"/>
+      <c r="D81" s="74"/>
       <c r="E81" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="60"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
+      <c r="B82" s="76"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
       <c r="E82" s="47">
         <f>E78</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="61" t="s">
+      <c r="A83" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="62"/>
-      <c r="C83" s="109" t="s">
+      <c r="B83" s="94"/>
+      <c r="C83" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="108"/>
+      <c r="D83" s="87"/>
       <c r="E83" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="63"/>
-      <c r="B84" s="64"/>
-      <c r="C84" s="75" t="s">
+      <c r="A84" s="95"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="75"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="63"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D85" s="110"/>
+    <row r="85" spans="1:5" ht="176" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="90" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="91"/>
       <c r="E85" s="48">
-        <v>390.5</v>
+        <v>468.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="63"/>
-      <c r="B86" s="64"/>
-      <c r="C86" s="109" t="s">
+      <c r="A86" s="95"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="111"/>
+      <c r="D86" s="92"/>
       <c r="E86" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="65"/>
-      <c r="B87" s="66"/>
-      <c r="C87" s="70" t="s">
+      <c r="A87" s="97"/>
+      <c r="B87" s="98"/>
+      <c r="C87" s="90" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="110"/>
+      <c r="D87" s="91"/>
       <c r="E87" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="57" t="s">
+      <c r="A88" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="57"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="85"/>
       <c r="E88" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="59" t="s">
+      <c r="C89" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="59"/>
+      <c r="D89" s="88"/>
       <c r="E89" s="47">
         <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>436.84000000000015</v>
+        <v>358.84000000000015</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8216,105 +8214,103 @@
       <c r="E91" s="49"/>
     </row>
     <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="72" t="s">
+      <c r="A92" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="72"/>
-      <c r="C92" s="72"/>
-      <c r="D92" s="72"/>
-      <c r="E92" s="72"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="89"/>
+      <c r="D92" s="89"/>
+      <c r="E92" s="89"/>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="73" t="s">
+      <c r="A93" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="73"/>
-      <c r="C93" s="73" t="s">
+      <c r="B93" s="74"/>
+      <c r="C93" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="73"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="60" t="s">
+      <c r="A94" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="60"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="76"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="47">
         <f>E89</f>
-        <v>436.84000000000015</v>
+        <v>358.84000000000015</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="61" t="s">
+      <c r="A95" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="62"/>
-      <c r="C95" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="D95" s="108"/>
+      <c r="B95" s="94"/>
+      <c r="C95" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="D95" s="87"/>
       <c r="E95" s="45">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="63"/>
-      <c r="B96" s="64"/>
-      <c r="C96" s="105" t="s">
+      <c r="A96" s="95"/>
+      <c r="B96" s="96"/>
+      <c r="C96" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="106"/>
+      <c r="D96" s="100"/>
       <c r="E96" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="63"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="D97" s="106"/>
+      <c r="A97" s="95"/>
+      <c r="B97" s="96"/>
+      <c r="C97" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="D97" s="100"/>
       <c r="E97" s="45">
         <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="65"/>
-      <c r="B98" s="66"/>
-      <c r="C98" s="105" t="s">
-        <v>170</v>
-      </c>
-      <c r="D98" s="106"/>
+      <c r="A98" s="97"/>
+      <c r="B98" s="98"/>
+      <c r="C98" s="99"/>
+      <c r="D98" s="100"/>
       <c r="E98" s="45">
-        <v>136.63999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="57" t="s">
+      <c r="A99" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="57"/>
-      <c r="C99" s="58"/>
-      <c r="D99" s="58"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="85"/>
+      <c r="D99" s="85"/>
       <c r="E99" s="45">
         <f>C68</f>
         <v>1171</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="59" t="s">
+      <c r="C100" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D100" s="59"/>
+      <c r="D100" s="88"/>
       <c r="E100" s="47">
         <f>(E30+E94)-SUM(E95:E99)</f>
-        <v>210.20000000000027</v>
+        <v>518.84000000000015</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12063,48 +12059,16 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A95:B98"/>
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="A92:E92"/>
@@ -12117,16 +12081,48 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A95:B98"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A74:B76"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E73">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12166,13 +12162,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12194,7 +12190,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>441.04</v>
+        <v>363.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12354,7 +12350,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>436.84000000000003</v>
+        <v>358.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12407,13 +12403,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12441,10 +12437,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12456,10 +12452,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12467,8 +12463,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12489,13 +12485,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12523,10 +12519,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="97"/>
+      <c r="D17" s="64"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12538,10 +12534,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="89"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12549,8 +12545,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12572,13 +12568,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12606,10 +12602,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="97"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12621,10 +12617,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12632,8 +12628,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12655,11 +12651,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="87"/>
-      <c r="C28" s="87"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12674,11 +12670,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12724,16 +12720,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="88"/>
-      <c r="C35" s="88"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="88"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12782,11 +12778,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12821,11 +12817,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12849,11 +12845,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="84"/>
-      <c r="C49" s="84"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="71"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12877,11 +12873,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="85"/>
-      <c r="C52" s="85"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12899,7 +12895,7 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C54" s="29">
         <v>950</v>
@@ -12941,7 +12937,7 @@
         <v>76</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C58" s="19">
         <v>4</v>
@@ -12958,11 +12954,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="85"/>
-      <c r="C60" s="85"/>
+      <c r="B60" s="73"/>
+      <c r="C60" s="73"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13012,196 +13008,198 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73" t="s">
+      <c r="A67" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="86" t="s">
+      <c r="A68" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="86"/>
-      <c r="C68" s="86" t="s">
+      <c r="B68" s="75"/>
+      <c r="C68" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="86"/>
+      <c r="D68" s="75"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="60" t="s">
+      <c r="A69" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="60"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E100</f>
-        <v>210.20000000000027</v>
+        <v>518.84000000000015</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="76" t="s">
+      <c r="A70" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="76"/>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="79"/>
       <c r="E70" s="45">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="76"/>
-      <c r="B71" s="76"/>
-      <c r="C71" s="112" t="s">
+      <c r="A71" s="78"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="80" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="74"/>
+      <c r="D71" s="81"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="76"/>
-      <c r="B72" s="76"/>
-      <c r="C72" s="112"/>
+      <c r="A72" s="78"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="80"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+      <c r="A73" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
       <c r="E73" s="46">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="78" t="s">
+      <c r="C74" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="78"/>
+      <c r="D74" s="84"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1470.2000000000003</v>
+        <v>1528.8400000000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="73" t="s">
+      <c r="A76" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
+      <c r="B76" s="74"/>
+      <c r="C76" s="74"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="73"/>
-      <c r="C77" s="73" t="s">
+      <c r="B77" s="74"/>
+      <c r="C77" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="73"/>
+      <c r="D77" s="74"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="60" t="s">
+      <c r="A78" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="60"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="85"/>
+      <c r="D78" s="85"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1470.2000000000003</v>
+        <v>1528.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="61" t="s">
+      <c r="A79" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="62"/>
-      <c r="C79" s="109"/>
-      <c r="D79" s="108"/>
+      <c r="B79" s="94"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="87"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="63"/>
-      <c r="B80" s="64"/>
-      <c r="C80" s="75" t="s">
+      <c r="A80" s="95"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="79"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="63"/>
-      <c r="B81" s="64"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="110"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="91"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="63"/>
-      <c r="B82" s="64"/>
-      <c r="C82" s="109"/>
-      <c r="D82" s="111"/>
+      <c r="A82" s="95"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="92"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="65"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="110"/>
+      <c r="A83" s="97"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="90"/>
+      <c r="D83" s="91"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="57" t="s">
+      <c r="A84" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="57"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="85"/>
+      <c r="D84" s="85"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="59" t="s">
+      <c r="C85" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="59"/>
+      <c r="D85" s="88"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>2730.2000000000003</v>
+        <v>2788.84</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13219,90 +13217,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="72" t="s">
+      <c r="A88" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="72"/>
-      <c r="C88" s="72"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
+      <c r="B88" s="89"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="89"/>
+      <c r="E88" s="89"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73" t="s">
+      <c r="B89" s="74"/>
+      <c r="C89" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="73"/>
+      <c r="D89" s="74"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="60" t="s">
+      <c r="A90" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="60"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>2730.2000000000003</v>
+        <v>2788.84</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="61" t="s">
+      <c r="A91" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="62"/>
-      <c r="C91" s="105"/>
-      <c r="D91" s="106"/>
+      <c r="B91" s="94"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="100"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="63"/>
-      <c r="B92" s="64"/>
-      <c r="C92" s="105" t="s">
+      <c r="A92" s="95"/>
+      <c r="B92" s="96"/>
+      <c r="C92" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="106"/>
+      <c r="D92" s="100"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="65"/>
-      <c r="B93" s="66"/>
-      <c r="C93" s="105"/>
-      <c r="D93" s="106"/>
+      <c r="A93" s="97"/>
+      <c r="B93" s="98"/>
+      <c r="C93" s="99"/>
+      <c r="D93" s="100"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="57" t="s">
+      <c r="A94" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="59" t="s">
+      <c r="C95" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="59"/>
+      <c r="D95" s="88"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>3990.2000000000007</v>
+        <v>4048.84</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17051,15 +17049,45 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17071,45 +17099,15 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32E729A-6250-9B42-A6A1-9207A0CF6997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8DE8B5-158A-8C4E-B960-FE9DE09F371A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="171">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -742,11 +742,6 @@
     <t>Vist Psychology Doctor plus transport</t>
   </si>
   <si>
-    <t>~ Additional fees for e-cigarette machine 18/09 - $250
-~ Additional transport fees for e-cigarette 18/09 - $50
-~ Round Trip to East Kowloon hospital 02/10 - $4</t>
-  </si>
-  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
@@ -756,10 +751,20 @@
 ~ Round Trip to East Kowloon hospital 03/09 - $4
 ~ Debit For Octopus Card ($50). 03/09
 ~ OK Store buy additional 1 packet cigarette 11/09 - $78
-~ OK Store buy additional 1 packet cigarette 12/09 - $78</t>
+~ OK Store buy additional 1 packet cigarette 12/09 - $78
+~ OK Store buy additional 1 packet cigarette 13/09 - $78</t>
   </si>
   <si>
-    <t>~ Payback $250 to Lawrence</t>
+    <t>~ Additional fees for e-cigarette machine 18/09 - $250
+~ Additional fees for e-cigarette 18/09 - $400
+~ Additional transport fees for e-cigarette 18/09 - $50
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>~ Payback $300 to Lawrence</t>
+  </si>
+  <si>
+    <t>~ Payback $200 to Lawrence</t>
   </si>
 </sst>
 </file>
@@ -1293,113 +1298,17 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1419,38 +1328,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1461,17 +1373,110 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1810,13 +1815,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1837,7 +1842,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>363.04</v>
+        <v>285.04000000000002</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1993,7 +1998,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>358.84000000000003</v>
+        <v>280.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2046,13 +2051,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2080,10 +2085,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2095,10 +2100,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2110,10 +2115,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="103"/>
+      <c r="D13" s="104"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2123,10 +2128,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2136,10 +2141,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="62"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2149,10 +2154,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="62"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2164,10 +2169,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="104"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2177,10 +2182,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="105"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2192,10 +2197,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="98"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2216,13 +2221,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2250,10 +2255,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="107"/>
+      <c r="D23" s="99"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2265,10 +2270,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2280,10 +2285,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="62"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2293,10 +2298,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="104"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2308,10 +2313,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="105" t="s">
+      <c r="C27" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="105"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2321,10 +2326,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="108" t="s">
+      <c r="C28" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="108"/>
+      <c r="D28" s="67"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2346,13 +2351,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2380,10 +2385,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="64"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2395,10 +2400,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="62"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2408,10 +2413,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="62"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2421,10 +2426,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="91"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2434,10 +2439,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="92"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2447,10 +2452,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="62"/>
+      <c r="D37" s="89"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2472,11 +2477,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2491,11 +2496,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2541,16 +2546,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="88"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2599,11 +2604,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2638,11 +2643,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="84"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2666,11 +2671,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="84"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2694,11 +2699,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="85"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2775,11 +2780,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="85"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2829,87 +2834,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75" t="s">
+      <c r="B80" s="86"/>
+      <c r="C80" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="86"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="80"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2919,30 +2924,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="80"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2952,8 +2957,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2963,33 +2968,33 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="83"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="84"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2997,113 +3002,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="74"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="74" t="s">
+      <c r="A96" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="74"/>
-      <c r="C96" s="74" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="74"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
+      <c r="A97" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="77"/>
-      <c r="C98" s="81" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="81"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="79"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="79"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="77"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="79"/>
+      <c r="D101" s="75"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="71"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="88"/>
+      <c r="D104" s="59"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3124,91 +3129,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
+      <c r="B107" s="72"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="72"/>
+      <c r="E107" s="72"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="74"/>
-      <c r="C108" s="74" t="s">
+      <c r="B108" s="73"/>
+      <c r="C108" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="74"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="76" t="s">
+      <c r="A109" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="76"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="93" t="s">
+      <c r="A110" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="94"/>
-      <c r="C110" s="108" t="s">
+      <c r="B110" s="62"/>
+      <c r="C110" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="108"/>
+      <c r="D110" s="67"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="95"/>
-      <c r="B111" s="96"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="69"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="65"/>
+      <c r="B112" s="66"/>
+      <c r="C112" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="71"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="88"/>
+      <c r="D114" s="59"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6960,35 +6965,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7002,42 +7014,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7062,7 +7067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y1036"/>
+  <dimension ref="A1:Y1037"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -7077,13 +7082,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7105,7 +7110,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>363.04</v>
+        <v>285.04000000000002</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7265,7 +7270,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>358.84000000000003</v>
+        <v>280.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7318,13 +7323,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7352,10 +7357,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7367,10 +7372,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7382,10 +7387,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="62"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7397,10 +7402,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7421,13 +7426,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7455,10 +7460,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="64"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7470,10 +7475,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="62"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7485,10 +7490,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7500,10 +7505,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="66"/>
+      <c r="D21" s="114"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7515,10 +7520,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="115" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7530,10 +7535,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="90" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7555,13 +7560,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7589,10 +7594,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="64"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7604,141 +7609,147 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="62"/>
+      <c r="D28" s="89"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
+      <c r="A29" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="89" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="89"/>
       <c r="E29" s="29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="35">
-        <f>SUM(E28:E29)</f>
-        <v>2485</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="24"/>
       <c r="B31" s="24"/>
-    </row>
-    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="70" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="35">
+        <f>SUM(E28:E30)</f>
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-    </row>
-    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+    </row>
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C34" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="37"/>
-    </row>
-    <row r="34" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="71" t="s">
+      <c r="D34" s="37"/>
+    </row>
+    <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-    </row>
-    <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="50" t="s">
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
+    </row>
+    <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="50" t="s">
+      <c r="B36" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C36" s="33">
         <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="38">
-        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B38" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="38">
+      <c r="C38" s="38">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="6" t="s">
+    <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7"/>
+      <c r="B39" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="39">
-        <f>SUM(C35:C37)</f>
+      <c r="C39" s="39">
+        <f>SUM(C36:C38)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="72" t="s">
+    <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
-    </row>
-    <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="29">
-        <v>0</v>
-      </c>
+      <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="6"/>
-      <c r="C42" s="19">
+      <c r="C42" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="19">
@@ -7747,7 +7758,7 @@
     </row>
     <row r="44" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="19">
@@ -7755,156 +7766,154 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6" t="s">
+      <c r="A45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="39">
-        <f>SUM(C41:C44)</f>
+      <c r="C46" s="39">
+        <f>SUM(C42:C45)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+    <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-    </row>
-    <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="33">
-        <v>0</v>
-      </c>
+      <c r="B47" s="84"/>
+      <c r="C47" s="84"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C48" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6"/>
+      <c r="A49" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="B49" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="39">
-        <f>SUM(C47:C48)</f>
+      <c r="C50" s="39">
+        <f>SUM(C48:C49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="71" t="s">
+    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="71"/>
-      <c r="C50" s="71"/>
-    </row>
-    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="B51" s="84"/>
+      <c r="C51" s="84"/>
+    </row>
+    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B52" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17" t="s">
+    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="39">
-        <f>SUM(C51)</f>
+      <c r="C53" s="39">
+        <f>SUM(C52)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="71" t="s">
+    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
-    </row>
-    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
+    </row>
+    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6" t="s">
+    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="39">
-        <f>SUM(C54)</f>
+      <c r="C56" s="39">
+        <f>SUM(C55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="73" t="s">
+    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
-    </row>
-    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="17" t="s">
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
+    </row>
+    <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="40">
+      <c r="C58" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+    <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <v>900</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
+    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B60" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C59" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="C60" s="29">
         <v>0</v>
@@ -7912,299 +7921,303 @@
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="29">
+      <c r="B62" s="6"/>
+      <c r="C62" s="29">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B63" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C62" s="19">
+      <c r="C63" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7" t="s">
+    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C63" s="39">
-        <f>SUM(C57:C62)</f>
+      <c r="C64" s="39">
+        <f>SUM(C58:C63)</f>
         <v>955</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
-    </row>
-    <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="19">
-        <v>0</v>
-      </c>
+      <c r="B65" s="85"/>
+      <c r="C65" s="85"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7" t="s">
+      <c r="A67" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="19">
-        <f>SUM(C65:C66)</f>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6"/>
-      <c r="B68" s="34" t="s">
+      <c r="C68" s="19">
+        <f>SUM(C66:C67)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6"/>
+      <c r="B69" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C68" s="41">
-        <f>C38+C45+C49+C52+C55+C63</f>
+      <c r="C69" s="41">
+        <f>C39+C46+C50+C53+C56+C64</f>
         <v>1171</v>
       </c>
-      <c r="H68" s="42"/>
-    </row>
-    <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="24"/>
-      <c r="B69" s="24"/>
+      <c r="H69" s="42"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
       <c r="B70" s="24"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="74" t="s">
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+    </row>
+    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-    </row>
-    <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="75" t="s">
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
+    </row>
+    <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="75"/>
-      <c r="C72" s="75" t="s">
+      <c r="B73" s="86"/>
+      <c r="C73" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="75"/>
-      <c r="E72" s="44" t="s">
+      <c r="D73" s="86"/>
+      <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+    <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
-      <c r="E73" s="47">
+      <c r="B74" s="60"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="78" t="s">
+    <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="79" t="s">
+      <c r="B75" s="76"/>
+      <c r="C75" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="79"/>
-      <c r="E74" s="45">
+      <c r="D75" s="75"/>
+      <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78"/>
-      <c r="B75" s="78"/>
-      <c r="C75" s="80" t="s">
+    <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="76"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="112" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="81"/>
-      <c r="E75" s="45">
+      <c r="D76" s="74"/>
+      <c r="E76" s="45">
         <v>1117.5</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="80" t="s">
+    <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="76"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="112" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="82"/>
-      <c r="E76" s="45">
+      <c r="D77" s="82"/>
+      <c r="E77" s="45">
         <v>508</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78" t="s">
+    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="78"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="46">
-        <f>C68</f>
+      <c r="B78" s="76"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="77"/>
+      <c r="E78" s="46">
+        <f>C69</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C78" s="84" t="s">
+    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="84"/>
-      <c r="E78" s="47">
-        <f>(E15+E73)-SUM(E74:E77)</f>
+      <c r="D79" s="78"/>
+      <c r="E79" s="47">
+        <f>(E15+E74)-SUM(E75:E78)</f>
         <v>24.599999999999909</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="74" t="s">
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-    </row>
-    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="B81" s="73"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
+    </row>
+    <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74" t="s">
+      <c r="B82" s="73"/>
+      <c r="C82" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D81" s="74"/>
-      <c r="E81" s="43" t="s">
+      <c r="D82" s="73"/>
+      <c r="E82" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="76" t="s">
+    <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="76"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
-      <c r="E82" s="47">
-        <f>E78</f>
+      <c r="B83" s="60"/>
+      <c r="C83" s="58"/>
+      <c r="D83" s="58"/>
+      <c r="E83" s="47">
+        <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="93" t="s">
+    <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B83" s="94"/>
-      <c r="C83" s="86" t="s">
+      <c r="B84" s="62"/>
+      <c r="C84" s="109" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="87"/>
-      <c r="E83" s="48">
+      <c r="D84" s="108"/>
+      <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="95"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="79" t="s">
+    <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="63"/>
+      <c r="B85" s="64"/>
+      <c r="C85" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="79"/>
-      <c r="E84" s="48">
+      <c r="D85" s="75"/>
+      <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="176" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="90" t="s">
-        <v>168</v>
-      </c>
-      <c r="D85" s="91"/>
-      <c r="E85" s="48">
-        <v>468.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="95"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="86" t="s">
+    <row r="86" spans="1:5" ht="189" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="63"/>
+      <c r="B86" s="64"/>
+      <c r="C86" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="D86" s="110"/>
+      <c r="E86" s="48">
+        <v>546.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="63"/>
+      <c r="B87" s="64"/>
+      <c r="C87" s="109" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="92"/>
-      <c r="E86" s="48">
+      <c r="D87" s="111"/>
+      <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="97"/>
-      <c r="B87" s="98"/>
-      <c r="C87" s="90" t="s">
+    <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="65"/>
+      <c r="B88" s="66"/>
+      <c r="C88" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="91"/>
-      <c r="E87" s="55">
+      <c r="D88" s="110"/>
+      <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77" t="s">
+    <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="77"/>
-      <c r="C88" s="85"/>
-      <c r="D88" s="85"/>
-      <c r="E88" s="45">
-        <f>C68</f>
+      <c r="B89" s="57"/>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="45">
+        <f>C69</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="88" t="s">
+    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C90" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D89" s="88"/>
-      <c r="E89" s="47">
-        <f>(E24+E82)-SUM(E83:E88)</f>
-        <v>358.84000000000015</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="49"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="49"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="49"/>
+      <c r="D90" s="59"/>
+      <c r="E90" s="47">
+        <f>(E24+E83)-SUM(E84:E89)</f>
+        <v>280.84000000000015</v>
+      </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="49"/>
@@ -8213,109 +8226,112 @@
       <c r="D91" s="49"/>
       <c r="E91" s="49"/>
     </row>
-    <row r="92" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="89" t="s">
+    <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49"/>
+      <c r="E92" s="49"/>
+    </row>
+    <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="89"/>
-      <c r="C92" s="89"/>
-      <c r="D92" s="89"/>
-      <c r="E92" s="89"/>
-    </row>
-    <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="74" t="s">
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
+    </row>
+    <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="74"/>
-      <c r="C93" s="74" t="s">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D93" s="74"/>
-      <c r="E93" s="43" t="s">
+      <c r="D94" s="73"/>
+      <c r="E94" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="76" t="s">
+    <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="76"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
-      <c r="E94" s="47">
-        <f>E89</f>
-        <v>358.84000000000015</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="93" t="s">
+      <c r="B95" s="60"/>
+      <c r="C95" s="58"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="47">
+        <f>E90</f>
+        <v>280.84000000000015</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="94"/>
-      <c r="C95" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="D95" s="87"/>
-      <c r="E95" s="45">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="95"/>
-      <c r="B96" s="96"/>
-      <c r="C96" s="99" t="s">
+      <c r="B96" s="62"/>
+      <c r="C96" s="107" t="s">
+        <v>170</v>
+      </c>
+      <c r="D96" s="108"/>
+      <c r="E96" s="45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="63"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="D96" s="100"/>
-      <c r="E96" s="45">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="95"/>
-      <c r="B97" s="96"/>
-      <c r="C97" s="99" t="s">
-        <v>167</v>
-      </c>
-      <c r="D97" s="100"/>
+      <c r="D97" s="106"/>
       <c r="E97" s="45">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="97"/>
-      <c r="B98" s="98"/>
-      <c r="C98" s="99"/>
-      <c r="D98" s="100"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="74" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="63"/>
+      <c r="B98" s="64"/>
+      <c r="C98" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="D98" s="106"/>
       <c r="E98" s="45">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="65"/>
+      <c r="B99" s="66"/>
+      <c r="C99" s="105"/>
+      <c r="D99" s="106"/>
+      <c r="E99" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77" t="s">
+    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B99" s="77"/>
-      <c r="C99" s="85"/>
-      <c r="D99" s="85"/>
-      <c r="E99" s="45">
-        <f>C68</f>
+      <c r="B100" s="57"/>
+      <c r="C100" s="58"/>
+      <c r="D100" s="58"/>
+      <c r="E100" s="45">
+        <f>C69</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C100" s="88" t="s">
+    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D100" s="88"/>
-      <c r="E100" s="47">
-        <f>(E30+E94)-SUM(E95:E99)</f>
-        <v>518.84000000000015</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="24"/>
-      <c r="B101" s="24"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="47">
+        <f>(E31+E95)-SUM(E96:E100)</f>
+        <v>295.84000000000015</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="24"/>
@@ -12057,58 +12073,18 @@
       <c r="A1036" s="24"/>
       <c r="B1036" s="24"/>
     </row>
+    <row r="1037" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1037" s="24"/>
+      <c r="B1037" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A95:B98"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A92:E92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="A83:B87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A74:B76"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
+  <mergeCells count="65">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -12117,14 +12093,59 @@
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B77"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A84:B88"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A96:B99"/>
   </mergeCells>
-  <conditionalFormatting sqref="C7:C8 E73">
+  <conditionalFormatting sqref="C7:C8 E74">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -12132,7 +12153,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78 E82 E89 E94 E100">
+  <conditionalFormatting sqref="E79 E83 E90 E95 E101">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -12162,13 +12183,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="100" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12190,7 +12211,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>363.04</v>
+        <v>285.04000000000002</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12350,7 +12371,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>358.84000000000003</v>
+        <v>280.84000000000003</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12403,13 +12424,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12437,10 +12458,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12452,10 +12473,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="116"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12463,8 +12484,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12485,13 +12506,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12519,10 +12540,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C17" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="64"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12534,10 +12555,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="89"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12545,8 +12566,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="114"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12568,13 +12589,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12602,10 +12623,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="64"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12617,10 +12638,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12628,8 +12649,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12651,11 +12672,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12670,11 +12691,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="71" t="s">
+      <c r="A30" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12720,16 +12741,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12778,11 +12799,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12817,11 +12838,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12845,11 +12866,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="71" t="s">
+      <c r="A49" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="71"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12873,11 +12894,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
+      <c r="B52" s="85"/>
+      <c r="C52" s="85"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12954,11 +12975,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="73"/>
-      <c r="C60" s="73"/>
+      <c r="B60" s="85"/>
+      <c r="C60" s="85"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13008,198 +13029,198 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="74" t="s">
+      <c r="A67" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="74"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="75"/>
-      <c r="C68" s="75" t="s">
+      <c r="B68" s="86"/>
+      <c r="C68" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="75"/>
+      <c r="D68" s="86"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="76" t="s">
+      <c r="A69" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
       <c r="E69" s="47">
-        <f>'July 2026- September 2026'!E100</f>
-        <v>518.84000000000015</v>
+        <f>'July 2026- September 2026'!E101</f>
+        <v>295.84000000000015</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="79" t="s">
+      <c r="B70" s="76"/>
+      <c r="C70" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="D70" s="79"/>
+      <c r="D70" s="75"/>
       <c r="E70" s="45">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="78"/>
-      <c r="B71" s="78"/>
-      <c r="C71" s="80" t="s">
+      <c r="A71" s="76"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="112" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="81"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="78"/>
-      <c r="B72" s="78"/>
-      <c r="C72" s="80"/>
+      <c r="A72" s="76"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="112"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="78" t="s">
+      <c r="A73" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="83"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
       <c r="E73" s="46">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="84"/>
+      <c r="D74" s="78"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1528.8400000000001</v>
+        <v>1255.8400000000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="74" t="s">
+      <c r="A76" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="74" t="s">
+      <c r="A77" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="74"/>
-      <c r="C77" s="74" t="s">
+      <c r="B77" s="73"/>
+      <c r="C77" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="74"/>
+      <c r="D77" s="73"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="76" t="s">
+      <c r="A78" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="76"/>
-      <c r="C78" s="85"/>
-      <c r="D78" s="85"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1528.8400000000001</v>
+        <v>1255.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="93" t="s">
+      <c r="A79" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="94"/>
-      <c r="C79" s="86"/>
-      <c r="D79" s="87"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="109"/>
+      <c r="D79" s="108"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="95"/>
-      <c r="B80" s="96"/>
-      <c r="C80" s="79" t="s">
+      <c r="A80" s="63"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="79"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="95"/>
-      <c r="B81" s="96"/>
-      <c r="C81" s="90"/>
-      <c r="D81" s="91"/>
+      <c r="A81" s="63"/>
+      <c r="B81" s="64"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="110"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="95"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="92"/>
+      <c r="A82" s="63"/>
+      <c r="B82" s="64"/>
+      <c r="C82" s="109"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="97"/>
-      <c r="B83" s="98"/>
-      <c r="C83" s="90"/>
-      <c r="D83" s="91"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="110"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="77" t="s">
+      <c r="A84" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="77"/>
-      <c r="C84" s="85"/>
-      <c r="D84" s="85"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="58"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="88" t="s">
+      <c r="C85" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="88"/>
+      <c r="D85" s="59"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>2788.84</v>
+        <v>2515.84</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13217,90 +13238,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="89" t="s">
+      <c r="A88" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="89"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="89"/>
-      <c r="E88" s="89"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="74" t="s">
+      <c r="A89" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="74"/>
-      <c r="C89" s="74" t="s">
+      <c r="B89" s="73"/>
+      <c r="C89" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="73"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="76" t="s">
+      <c r="A90" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="76"/>
-      <c r="C90" s="85"/>
-      <c r="D90" s="85"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>2788.84</v>
+        <v>2515.84</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="93" t="s">
+      <c r="A91" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="94"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="100"/>
+      <c r="B91" s="62"/>
+      <c r="C91" s="105"/>
+      <c r="D91" s="106"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="95"/>
-      <c r="B92" s="96"/>
-      <c r="C92" s="99" t="s">
+      <c r="A92" s="63"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="100"/>
+      <c r="D92" s="106"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="97"/>
-      <c r="B93" s="98"/>
-      <c r="C93" s="99"/>
-      <c r="D93" s="100"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="66"/>
+      <c r="C93" s="105"/>
+      <c r="D93" s="106"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="77" t="s">
+      <c r="A94" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1225</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="88" t="s">
+      <c r="C95" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="88"/>
+      <c r="D95" s="59"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>4048.84</v>
+        <v>3775.84</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17049,45 +17070,15 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17099,15 +17090,45 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8DE8B5-158A-8C4E-B960-FE9DE09F371A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C90A264-2B15-D34A-8075-129EB80AA265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="170">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -736,9 +736,6 @@
 ~ Snack And Drinks</t>
   </si>
   <si>
-    <t>e-cigarette plus transport fees</t>
-  </si>
-  <si>
     <t>Vist Psychology Doctor plus transport</t>
   </si>
   <si>
@@ -755,16 +752,14 @@
 ~ OK Store buy additional 1 packet cigarette 13/09 - $78</t>
   </si>
   <si>
-    <t>~ Additional fees for e-cigarette machine 18/09 - $250
-~ Additional fees for e-cigarette 18/09 - $400
-~ Additional transport fees for e-cigarette 18/09 - $50
+    <t>~ Additional fees for cigarette (change from e-cigarette to cigarette) 18/09 - $380
 ~ Round Trip to East Kowloon hospital 02/10 - $4</t>
   </si>
   <si>
-    <t>~ Payback $300 to Lawrence</t>
+    <t>~ Payback $500 to Lawrence</t>
   </si>
   <si>
-    <t>~ Payback $200 to Lawrence</t>
+    <t>cigarette - 4 packs each pack has 10 packets of cigarette</t>
   </si>
 </sst>
 </file>
@@ -1298,17 +1293,113 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1328,41 +1419,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1373,110 +1461,17 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1815,13 +1810,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2051,13 +2046,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2085,10 +2080,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2100,10 +2095,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="103"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2115,10 +2110,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="104"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2128,10 +2123,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2141,10 +2136,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="89"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2154,10 +2149,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="89"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2169,10 +2164,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="94"/>
+      <c r="D17" s="104"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2182,10 +2177,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2197,10 +2192,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="98" t="s">
+      <c r="C19" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="98"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2221,13 +2216,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2255,10 +2250,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="99" t="s">
+      <c r="C23" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="99"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2270,10 +2265,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2285,10 +2280,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="89"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2298,10 +2293,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="94"/>
+      <c r="D26" s="104"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2313,10 +2308,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2326,10 +2321,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="67"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2351,13 +2346,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2385,10 +2380,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="97"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2400,10 +2395,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="89"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2413,10 +2408,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="89"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2426,10 +2421,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="90" t="s">
+      <c r="C35" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="91"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2439,10 +2434,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="90" t="s">
+      <c r="C36" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="92"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2452,10 +2447,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="93" t="s">
+      <c r="C37" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="89"/>
+      <c r="D37" s="62"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2477,11 +2472,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2496,11 +2491,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2546,16 +2541,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="88"/>
-      <c r="C47" s="88"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="88"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="88"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2604,11 +2599,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="84" t="s">
+      <c r="A54" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="84"/>
-      <c r="C54" s="84"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2643,11 +2638,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="84"/>
-      <c r="C58" s="84"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2671,11 +2666,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="84" t="s">
+      <c r="A61" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="84"/>
-      <c r="C61" s="84"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2699,11 +2694,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="85" t="s">
+      <c r="A64" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2780,11 +2775,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="85" t="s">
+      <c r="A72" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="85"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2834,87 +2829,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="73" t="s">
+      <c r="A79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="86" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="86"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="79" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="79"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="80" t="s">
+      <c r="B82" s="77"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="80"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="57"/>
-      <c r="B83" s="57"/>
-      <c r="C83" s="80" t="s">
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="80"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="57"/>
-      <c r="B84" s="57"/>
-      <c r="C84" s="80" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="80"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
-      <c r="B85" s="57"/>
-      <c r="C85" s="81" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="81"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="57"/>
-      <c r="B86" s="57"/>
+      <c r="A86" s="77"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2924,30 +2919,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="57"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="81" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="81"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="57"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="80" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="80"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="57"/>
-      <c r="B89" s="57"/>
+      <c r="A89" s="77"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2957,8 +2952,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57"/>
-      <c r="B90" s="57"/>
+      <c r="A90" s="77"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2968,33 +2963,33 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57"/>
-      <c r="B91" s="57"/>
-      <c r="C91" s="83" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="83"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="76"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="78" t="s">
+      <c r="C93" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="78"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -3002,113 +2997,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="73"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="73"/>
-      <c r="E95" s="73"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="73"/>
-      <c r="C96" s="73" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="73"/>
+      <c r="D96" s="74"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="60" t="s">
+      <c r="A97" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="60"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="57" t="s">
+      <c r="A98" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="74" t="s">
+      <c r="B98" s="77"/>
+      <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="74"/>
+      <c r="D98" s="81"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="57"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="75" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="75"/>
+      <c r="D99" s="79"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="57"/>
-      <c r="B100" s="57"/>
-      <c r="C100" s="75" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="75"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="57"/>
-      <c r="B101" s="57"/>
-      <c r="C101" s="75" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="75"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="57"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="70" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="71"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="57" t="s">
+      <c r="A103" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="57"/>
-      <c r="C103" s="58"/>
-      <c r="D103" s="58"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="59" t="s">
+      <c r="C104" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="59"/>
+      <c r="D104" s="88"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3129,91 +3124,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="72" t="s">
+      <c r="A107" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="72"/>
-      <c r="C107" s="72"/>
-      <c r="D107" s="72"/>
-      <c r="E107" s="72"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
+      <c r="D107" s="89"/>
+      <c r="E107" s="89"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="73" t="s">
+      <c r="A108" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="73"/>
-      <c r="C108" s="73" t="s">
+      <c r="B108" s="74"/>
+      <c r="C108" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="73"/>
+      <c r="D108" s="74"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="60" t="s">
+      <c r="A109" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="60"/>
-      <c r="C109" s="58"/>
-      <c r="D109" s="58"/>
+      <c r="B109" s="76"/>
+      <c r="C109" s="85"/>
+      <c r="D109" s="85"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="61" t="s">
+      <c r="A110" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="62"/>
-      <c r="C110" s="67" t="s">
+      <c r="B110" s="94"/>
+      <c r="C110" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="67"/>
+      <c r="D110" s="108"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="63"/>
-      <c r="B111" s="64"/>
-      <c r="C111" s="68" t="s">
+      <c r="A111" s="95"/>
+      <c r="B111" s="96"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="69"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="65"/>
-      <c r="B112" s="66"/>
-      <c r="C112" s="70" t="s">
+      <c r="A112" s="97"/>
+      <c r="B112" s="98"/>
+      <c r="C112" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="71"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="57" t="s">
+      <c r="A113" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="58"/>
-      <c r="D113" s="58"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="85"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="59"/>
+      <c r="D114" s="88"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6965,42 +6960,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7014,35 +7002,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7082,13 +7077,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7323,13 +7318,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7357,10 +7352,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7372,10 +7367,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7387,10 +7382,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="89"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7402,10 +7397,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7426,13 +7421,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7460,10 +7455,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="97" t="s">
+      <c r="C18" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="97"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7475,10 +7470,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="89"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7490,10 +7485,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="91"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7505,10 +7500,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="114"/>
+      <c r="D21" s="66"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7520,10 +7515,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="91"/>
+      <c r="D22" s="68"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7535,10 +7530,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="91"/>
+      <c r="D23" s="68"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7560,13 +7555,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="96" t="s">
+      <c r="A26" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7594,10 +7589,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="97" t="s">
+      <c r="C27" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="97"/>
+      <c r="D27" s="64"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7609,10 +7604,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="89"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7624,10 +7619,10 @@
       <c r="B29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="89" t="s">
+      <c r="C29" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="89"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="29">
         <v>55</v>
       </c>
@@ -7635,8 +7630,8 @@
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="29">
         <v>0</v>
       </c>
@@ -7658,11 +7653,11 @@
       <c r="B32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="87" t="s">
+      <c r="A33" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -7677,11 +7672,11 @@
       <c r="D34" s="37"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
     </row>
     <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50" t="s">
@@ -7727,16 +7722,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="88" t="s">
+      <c r="A40" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="88"/>
-      <c r="C40" s="88"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="88"/>
-      <c r="B41" s="88"/>
-      <c r="C41" s="88"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -7785,11 +7780,11 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="84"/>
-      <c r="C47" s="84"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7824,11 +7819,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="84" t="s">
+      <c r="A51" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="84"/>
-      <c r="C51" s="84"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="71"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7852,11 +7847,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="84" t="s">
+      <c r="A54" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="84"/>
-      <c r="C54" s="84"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -7880,11 +7875,11 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="85" t="s">
+      <c r="A57" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
@@ -7961,11 +7956,11 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="85" t="s">
+      <c r="A65" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="85"/>
-      <c r="C65" s="85"/>
+      <c r="B65" s="73"/>
+      <c r="C65" s="73"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
@@ -7982,7 +7977,7 @@
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="19">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7992,7 +7987,7 @@
       </c>
       <c r="C68" s="19">
         <f>SUM(C66:C67)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8015,67 +8010,67 @@
       <c r="B71" s="24"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
-      <c r="D72" s="73"/>
-      <c r="E72" s="73"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="86" t="s">
+      <c r="A73" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="86"/>
-      <c r="C73" s="86" t="s">
+      <c r="B73" s="75"/>
+      <c r="C73" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="86"/>
+      <c r="D73" s="75"/>
       <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="60" t="s">
+      <c r="A74" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="60"/>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="77"/>
       <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="76" t="s">
+      <c r="A75" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="76"/>
-      <c r="C75" s="75" t="s">
+      <c r="B75" s="78"/>
+      <c r="C75" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="75"/>
+      <c r="D75" s="79"/>
       <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="76"/>
-      <c r="B76" s="76"/>
-      <c r="C76" s="112" t="s">
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="D76" s="74"/>
+      <c r="D76" s="81"/>
       <c r="E76" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="76"/>
-      <c r="B77" s="76"/>
-      <c r="C77" s="112" t="s">
+      <c r="A77" s="78"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="80" t="s">
         <v>134</v>
       </c>
       <c r="D77" s="82"/>
@@ -8084,22 +8079,22 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="76" t="s">
+      <c r="A78" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="76"/>
-      <c r="C78" s="77"/>
-      <c r="D78" s="77"/>
+      <c r="B78" s="78"/>
+      <c r="C78" s="83"/>
+      <c r="D78" s="83"/>
       <c r="E78" s="46">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="78" t="s">
+      <c r="C79" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="78"/>
+      <c r="D79" s="84"/>
       <c r="E79" s="47">
         <f>(E15+E74)-SUM(E75:E78)</f>
         <v>24.599999999999909</v>
@@ -8107,113 +8102,113 @@
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="B81" s="73"/>
-      <c r="C81" s="73"/>
-      <c r="D81" s="73"/>
-      <c r="E81" s="73"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="73" t="s">
+      <c r="A82" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="73"/>
-      <c r="C82" s="73" t="s">
+      <c r="B82" s="74"/>
+      <c r="C82" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="73"/>
+      <c r="D82" s="74"/>
       <c r="E82" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="60"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="85"/>
+      <c r="D83" s="85"/>
       <c r="E83" s="47">
         <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="61" t="s">
+      <c r="A84" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="62"/>
-      <c r="C84" s="109" t="s">
+      <c r="B84" s="94"/>
+      <c r="C84" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="D84" s="108"/>
+      <c r="D84" s="87"/>
       <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="63"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="75" t="s">
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="D85" s="75"/>
+      <c r="D85" s="79"/>
       <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="189" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="63"/>
-      <c r="B86" s="64"/>
-      <c r="C86" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="D86" s="110"/>
+      <c r="A86" s="95"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="90" t="s">
+        <v>166</v>
+      </c>
+      <c r="D86" s="91"/>
       <c r="E86" s="48">
         <v>546.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="63"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="109" t="s">
+      <c r="A87" s="95"/>
+      <c r="B87" s="96"/>
+      <c r="C87" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="111"/>
+      <c r="D87" s="92"/>
       <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="65"/>
-      <c r="B88" s="66"/>
-      <c r="C88" s="70" t="s">
+      <c r="A88" s="97"/>
+      <c r="B88" s="98"/>
+      <c r="C88" s="90" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="110"/>
+      <c r="D88" s="91"/>
       <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="57" t="s">
+      <c r="A89" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="57"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="85"/>
+      <c r="D89" s="85"/>
       <c r="E89" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="59" t="s">
+      <c r="C90" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="59"/>
+      <c r="D90" s="88"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
         <v>280.84000000000015</v>
@@ -8234,103 +8229,103 @@
       <c r="E92" s="49"/>
     </row>
     <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="72" t="s">
+      <c r="A93" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
+      <c r="B93" s="89"/>
+      <c r="C93" s="89"/>
+      <c r="D93" s="89"/>
+      <c r="E93" s="89"/>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="73" t="s">
+      <c r="A94" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="73"/>
-      <c r="C94" s="73" t="s">
+      <c r="B94" s="74"/>
+      <c r="C94" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D94" s="73"/>
+      <c r="D94" s="74"/>
       <c r="E94" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="60" t="s">
+      <c r="A95" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="60"/>
-      <c r="C95" s="58"/>
-      <c r="D95" s="58"/>
+      <c r="B95" s="76"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
       <c r="E95" s="47">
         <f>E90</f>
         <v>280.84000000000015</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="61" t="s">
+      <c r="A96" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="62"/>
-      <c r="C96" s="107" t="s">
-        <v>170</v>
-      </c>
-      <c r="D96" s="108"/>
+      <c r="B96" s="94"/>
+      <c r="C96" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="D96" s="87"/>
       <c r="E96" s="45">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="63"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="105" t="s">
+      <c r="A97" s="95"/>
+      <c r="B97" s="96"/>
+      <c r="C97" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="D97" s="106"/>
+      <c r="D97" s="100"/>
       <c r="E97" s="45">
         <v>450</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="74" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="63"/>
-      <c r="B98" s="64"/>
-      <c r="C98" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="D98" s="106"/>
+    <row r="98" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="95"/>
+      <c r="B98" s="96"/>
+      <c r="C98" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="D98" s="100"/>
       <c r="E98" s="45">
-        <v>704</v>
+        <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="65"/>
-      <c r="B99" s="66"/>
-      <c r="C99" s="105"/>
-      <c r="D99" s="106"/>
+      <c r="A99" s="97"/>
+      <c r="B99" s="98"/>
+      <c r="C99" s="99"/>
+      <c r="D99" s="100"/>
       <c r="E99" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="57" t="s">
+      <c r="A100" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="57"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="58"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="85"/>
+      <c r="D100" s="85"/>
       <c r="E100" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="59" t="s">
+      <c r="C101" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="59"/>
+      <c r="D101" s="88"/>
       <c r="E101" s="47">
         <f>(E31+E95)-SUM(E96:E100)</f>
-        <v>295.84000000000015</v>
+        <v>315.84000000000015</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12079,49 +12074,16 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B77"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A96:B99"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="A93:E93"/>
@@ -12134,16 +12096,49 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A84:B88"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A96:B99"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A75:B77"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E74">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12183,13 +12178,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12424,13 +12419,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12458,10 +12453,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="102"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12473,10 +12468,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="116"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12484,8 +12479,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12506,13 +12501,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12540,10 +12535,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="97"/>
+      <c r="D17" s="64"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12555,10 +12550,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="89"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12566,8 +12561,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12589,13 +12584,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12623,10 +12618,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="97"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12638,10 +12633,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12649,8 +12644,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12672,11 +12667,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="87"/>
-      <c r="C28" s="87"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12691,11 +12686,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12741,16 +12736,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="88"/>
-      <c r="C35" s="88"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="88"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12799,11 +12794,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12838,11 +12833,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12866,11 +12861,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="84"/>
-      <c r="C49" s="84"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="71"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12894,11 +12889,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="85"/>
-      <c r="C52" s="85"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12916,10 +12911,10 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C54" s="29">
-        <v>950</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="32" x14ac:dyDescent="0.2">
@@ -12958,7 +12953,7 @@
         <v>76</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="19">
         <v>4</v>
@@ -12971,15 +12966,15 @@
       </c>
       <c r="C59" s="39">
         <f>SUM(C53:C58)</f>
-        <v>1009</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="85"/>
-      <c r="C60" s="85"/>
+      <c r="B60" s="73"/>
+      <c r="C60" s="73"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13016,7 +13011,7 @@
       </c>
       <c r="C64" s="41">
         <f>C34+C41+C45+C48+C51+C59</f>
-        <v>1225</v>
+        <v>1555</v>
       </c>
       <c r="H64" s="42"/>
     </row>
@@ -13029,198 +13024,196 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73" t="s">
+      <c r="A67" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="86" t="s">
+      <c r="A68" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="86"/>
-      <c r="C68" s="86" t="s">
+      <c r="B68" s="75"/>
+      <c r="C68" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="86"/>
+      <c r="D68" s="75"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="60" t="s">
+      <c r="A69" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="60"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E101</f>
-        <v>295.84000000000015</v>
+        <v>315.84000000000015</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="76" t="s">
+      <c r="A70" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="76"/>
-      <c r="C70" s="75" t="s">
-        <v>169</v>
-      </c>
-      <c r="D70" s="75"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
       <c r="E70" s="45">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="76"/>
-      <c r="B71" s="76"/>
-      <c r="C71" s="112" t="s">
+      <c r="A71" s="78"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="80" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="74"/>
+      <c r="D71" s="81"/>
       <c r="E71" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="76"/>
-      <c r="B72" s="76"/>
-      <c r="C72" s="112"/>
+      <c r="A72" s="78"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="80"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="76" t="s">
+      <c r="A73" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
       <c r="E73" s="46">
         <f>C64</f>
-        <v>1225</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="78" t="s">
+      <c r="C74" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="78"/>
+      <c r="D74" s="84"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1255.8400000000001</v>
+        <v>1245.8400000000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="73" t="s">
+      <c r="A76" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
+      <c r="B76" s="74"/>
+      <c r="C76" s="74"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="73"/>
-      <c r="C77" s="73" t="s">
+      <c r="B77" s="74"/>
+      <c r="C77" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="73"/>
+      <c r="D77" s="74"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="60" t="s">
+      <c r="A78" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="60"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="85"/>
+      <c r="D78" s="85"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1255.8400000000001</v>
+        <v>1245.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="61" t="s">
+      <c r="A79" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="62"/>
-      <c r="C79" s="109"/>
-      <c r="D79" s="108"/>
+      <c r="B79" s="94"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="87"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="63"/>
-      <c r="B80" s="64"/>
-      <c r="C80" s="75" t="s">
+      <c r="A80" s="95"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="79"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="63"/>
-      <c r="B81" s="64"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="110"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="91"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="63"/>
-      <c r="B82" s="64"/>
-      <c r="C82" s="109"/>
-      <c r="D82" s="111"/>
+      <c r="A82" s="95"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="92"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="65"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="110"/>
+      <c r="A83" s="97"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="90"/>
+      <c r="D83" s="91"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="57" t="s">
+      <c r="A84" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="57"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="85"/>
+      <c r="D84" s="85"/>
       <c r="E84" s="45">
         <f>C64</f>
-        <v>1225</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="59" t="s">
+      <c r="C85" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="59"/>
+      <c r="D85" s="88"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>2515.84</v>
+        <v>2175.84</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13238,90 +13231,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="72" t="s">
+      <c r="A88" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="72"/>
-      <c r="C88" s="72"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
+      <c r="B88" s="89"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="89"/>
+      <c r="E88" s="89"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73" t="s">
+      <c r="B89" s="74"/>
+      <c r="C89" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="73"/>
+      <c r="D89" s="74"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="60" t="s">
+      <c r="A90" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="60"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>2515.84</v>
+        <v>2175.84</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="61" t="s">
+      <c r="A91" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="62"/>
-      <c r="C91" s="105"/>
-      <c r="D91" s="106"/>
+      <c r="B91" s="94"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="100"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="63"/>
-      <c r="B92" s="64"/>
-      <c r="C92" s="105" t="s">
+      <c r="A92" s="95"/>
+      <c r="B92" s="96"/>
+      <c r="C92" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="106"/>
+      <c r="D92" s="100"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="65"/>
-      <c r="B93" s="66"/>
-      <c r="C93" s="105"/>
-      <c r="D93" s="106"/>
+      <c r="A93" s="97"/>
+      <c r="B93" s="98"/>
+      <c r="C93" s="99"/>
+      <c r="D93" s="100"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="57" t="s">
+      <c r="A94" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="45">
         <f>C64</f>
-        <v>1225</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="59" t="s">
+      <c r="C95" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="59"/>
+      <c r="D95" s="88"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>3775.84</v>
+        <v>3105.84</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17070,15 +17063,45 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17090,45 +17113,15 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C90A264-2B15-D34A-8075-129EB80AA265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C408B9A-56A2-E84F-A740-0617C15BC699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -739,6 +739,16 @@
     <t>Vist Psychology Doctor plus transport</t>
   </si>
   <si>
+    <t>~ Additional fees for cigarette (change from e-cigarette to cigarette) 18/09 - $380
+~ Round Trip to East Kowloon hospital 02/10 - $4</t>
+  </si>
+  <si>
+    <t>~ Payback $500 to Lawrence</t>
+  </si>
+  <si>
+    <t>cigarette - 4 packs each pack has 10 packets of cigarette</t>
+  </si>
+  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
@@ -749,17 +759,8 @@
 ~ Debit For Octopus Card ($50). 03/09
 ~ OK Store buy additional 1 packet cigarette 11/09 - $78
 ~ OK Store buy additional 1 packet cigarette 12/09 - $78
-~ OK Store buy additional 1 packet cigarette 13/09 - $78</t>
-  </si>
-  <si>
-    <t>~ Additional fees for cigarette (change from e-cigarette to cigarette) 18/09 - $380
-~ Round Trip to East Kowloon hospital 02/10 - $4</t>
-  </si>
-  <si>
-    <t>~ Payback $500 to Lawrence</t>
-  </si>
-  <si>
-    <t>cigarette - 4 packs each pack has 10 packets of cigarette</t>
+~ OK Store buy additional 1 packet cigarette 13/09 - $78
+~ OK Store buy additional 1 packet cigarette 14/09 - $78</t>
   </si>
 </sst>
 </file>
@@ -1293,113 +1294,29 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1419,19 +1336,124 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1446,32 +1468,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1810,13 +1811,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1837,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>285.04000000000002</v>
+        <v>207.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1993,7 +1994,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>280.84000000000003</v>
+        <v>202.83999999999997</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2046,13 +2047,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2080,10 +2081,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2095,10 +2096,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="115"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2110,10 +2111,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="103"/>
+      <c r="D13" s="116"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2123,10 +2124,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2136,10 +2137,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="62"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2149,10 +2150,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="62"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2164,10 +2165,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="104"/>
+      <c r="D17" s="111"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2177,10 +2178,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="105"/>
+      <c r="D18" s="112"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2192,10 +2193,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="113"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2216,13 +2217,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2250,10 +2251,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="107"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2265,10 +2266,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2280,10 +2281,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="62"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2293,10 +2294,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="104"/>
+      <c r="D26" s="111"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2308,10 +2309,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="105" t="s">
+      <c r="C27" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="105"/>
+      <c r="D27" s="112"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2321,10 +2322,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="108" t="s">
+      <c r="C28" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="108"/>
+      <c r="D28" s="102"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2346,13 +2347,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2380,10 +2381,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="64"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2395,10 +2396,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="62"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2408,10 +2409,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="62"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2421,10 +2422,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="94" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="95"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2434,10 +2435,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="110"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2447,10 +2448,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="62"/>
+      <c r="D37" s="89"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2472,11 +2473,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2491,11 +2492,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2541,16 +2542,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2599,11 +2600,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2638,11 +2639,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="87"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2666,11 +2667,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2694,11 +2695,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="84"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2775,11 +2776,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
+      <c r="B72" s="84"/>
+      <c r="C72" s="84"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2829,87 +2830,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="85"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
+      <c r="B81" s="106"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="60"/>
+      <c r="C82" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="107"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="60"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="107"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="60"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="107"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="60"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="108"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
+      <c r="A86" s="60"/>
+      <c r="B86" s="60"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2919,30 +2920,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="60"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="108"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="60"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="107"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
+      <c r="A89" s="60"/>
+      <c r="B89" s="60"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2952,8 +2953,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
+      <c r="A90" s="60"/>
+      <c r="B90" s="60"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2963,21 +2964,21 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="60"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="109" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="109"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
+      <c r="B92" s="79"/>
       <c r="C92" s="83"/>
       <c r="D92" s="83"/>
       <c r="E92" s="46">
@@ -2986,10 +2987,10 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="84"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2997,44 +2998,44 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="74"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="74" t="s">
+      <c r="A96" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="74"/>
-      <c r="C96" s="74" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="74"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
+      <c r="A97" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="59"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="77"/>
+      <c r="B98" s="60"/>
       <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
@@ -3044,66 +3045,66 @@
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79" t="s">
+      <c r="A99" s="60"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="79"/>
+      <c r="D99" s="74"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79" t="s">
+      <c r="A100" s="60"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="79"/>
+      <c r="D100" s="74"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="77"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79" t="s">
+      <c r="A101" s="60"/>
+      <c r="B101" s="60"/>
+      <c r="C101" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="79"/>
+      <c r="D101" s="74"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="60"/>
+      <c r="B102" s="60"/>
+      <c r="C102" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="105"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="59"/>
+      <c r="D103" s="59"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="88"/>
+      <c r="D104" s="57"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3124,91 +3125,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
+      <c r="B107" s="72"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="72"/>
+      <c r="E107" s="72"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="74"/>
-      <c r="C108" s="74" t="s">
+      <c r="B108" s="73"/>
+      <c r="C108" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="74"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="76" t="s">
+      <c r="A109" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="76"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="58"/>
+      <c r="C109" s="59"/>
+      <c r="D109" s="59"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="93" t="s">
+      <c r="A110" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="94"/>
-      <c r="C110" s="108" t="s">
+      <c r="B110" s="66"/>
+      <c r="C110" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="108"/>
+      <c r="D110" s="102"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="95"/>
-      <c r="B111" s="96"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="67"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="104"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="69"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="105"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="60"/>
+      <c r="C113" s="59"/>
+      <c r="D113" s="59"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="88"/>
+      <c r="D114" s="57"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6960,35 +6961,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7002,42 +7010,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7077,13 +7078,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7105,7 +7106,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>285.04000000000002</v>
+        <v>207.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7265,7 +7266,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>280.84000000000003</v>
+        <v>202.83999999999997</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7318,13 +7319,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7352,10 +7353,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7367,10 +7368,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="100"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7382,10 +7383,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="62"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7397,10 +7398,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="101" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7421,13 +7422,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7455,10 +7456,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="64"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7470,10 +7471,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="62"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7485,10 +7486,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C20" s="94" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="95"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7500,10 +7501,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="66"/>
+      <c r="D21" s="93"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7515,10 +7516,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="96" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="95"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7530,10 +7531,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="67" t="s">
+      <c r="C23" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7555,13 +7556,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7589,10 +7590,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="64"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7604,10 +7605,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="62"/>
+      <c r="D28" s="89"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7619,10 +7620,10 @@
       <c r="B29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="62"/>
+      <c r="D29" s="89"/>
       <c r="E29" s="29">
         <v>55</v>
       </c>
@@ -7630,8 +7631,8 @@
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
       <c r="E30" s="29">
         <v>0</v>
       </c>
@@ -7653,11 +7654,11 @@
       <c r="B32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -7672,11 +7673,11 @@
       <c r="D34" s="37"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
     </row>
     <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50" t="s">
@@ -7722,16 +7723,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="72"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="72"/>
+      <c r="A41" s="86"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -7780,11 +7781,11 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="71" t="s">
+      <c r="A47" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7819,11 +7820,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="71" t="s">
+      <c r="A51" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="71"/>
-      <c r="C51" s="71"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="87"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7847,11 +7848,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -7875,11 +7876,11 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
+      <c r="B57" s="84"/>
+      <c r="C57" s="84"/>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
@@ -7956,11 +7957,11 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="73" t="s">
+      <c r="A65" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="73"/>
-      <c r="C65" s="73"/>
+      <c r="B65" s="84"/>
+      <c r="C65" s="84"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
@@ -8010,55 +8011,55 @@
       <c r="B71" s="24"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="74" t="s">
+      <c r="A72" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="75"/>
-      <c r="C73" s="75" t="s">
+      <c r="B73" s="85"/>
+      <c r="C73" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="75"/>
+      <c r="D73" s="85"/>
       <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="76" t="s">
+      <c r="A74" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="76"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="77"/>
+      <c r="B74" s="58"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
       <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78" t="s">
+      <c r="A75" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="79" t="s">
+      <c r="B75" s="79"/>
+      <c r="C75" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="79"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
+      <c r="A76" s="79"/>
+      <c r="B76" s="79"/>
       <c r="C76" s="80" t="s">
         <v>133</v>
       </c>
@@ -8068,8 +8069,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78"/>
-      <c r="B77" s="78"/>
+      <c r="A77" s="79"/>
+      <c r="B77" s="79"/>
       <c r="C77" s="80" t="s">
         <v>134</v>
       </c>
@@ -8079,10 +8080,10 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="78" t="s">
+      <c r="A78" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="78"/>
+      <c r="B78" s="79"/>
       <c r="C78" s="83"/>
       <c r="D78" s="83"/>
       <c r="E78" s="46">
@@ -8091,10 +8092,10 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="84" t="s">
+      <c r="C79" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="84"/>
+      <c r="D79" s="78"/>
       <c r="E79" s="47">
         <f>(E15+E74)-SUM(E75:E78)</f>
         <v>24.599999999999909</v>
@@ -8102,116 +8103,116 @@
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
+      <c r="B81" s="73"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="74" t="s">
+      <c r="A82" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="74"/>
-      <c r="C82" s="74" t="s">
+      <c r="B82" s="73"/>
+      <c r="C82" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="74"/>
+      <c r="D82" s="73"/>
       <c r="E82" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="76" t="s">
+      <c r="A83" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="76"/>
-      <c r="C83" s="85"/>
-      <c r="D83" s="85"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
       <c r="E83" s="47">
         <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="94"/>
-      <c r="C84" s="86" t="s">
+      <c r="B84" s="66"/>
+      <c r="C84" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="D84" s="87"/>
+      <c r="D84" s="64"/>
       <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="79" t="s">
+      <c r="A85" s="67"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="D85" s="79"/>
+      <c r="D85" s="74"/>
       <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="189" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="95"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="90" t="s">
-        <v>166</v>
-      </c>
-      <c r="D86" s="91"/>
+    <row r="86" spans="1:5" ht="209" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="67"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="75" t="s">
+        <v>169</v>
+      </c>
+      <c r="D86" s="76"/>
       <c r="E86" s="48">
-        <v>546.5</v>
+        <v>624.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="95"/>
-      <c r="B87" s="96"/>
-      <c r="C87" s="86" t="s">
+      <c r="A87" s="67"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="92"/>
+      <c r="D87" s="77"/>
       <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="97"/>
-      <c r="B88" s="98"/>
-      <c r="C88" s="90" t="s">
+      <c r="A88" s="69"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="91"/>
+      <c r="D88" s="76"/>
       <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77" t="s">
+      <c r="A89" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="77"/>
-      <c r="C89" s="85"/>
-      <c r="D89" s="85"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="59"/>
       <c r="E89" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="88" t="s">
+      <c r="C90" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="88"/>
+      <c r="D90" s="57"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>280.84000000000015</v>
+        <v>202.84000000000015</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8229,103 +8230,103 @@
       <c r="E92" s="49"/>
     </row>
     <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="89" t="s">
+      <c r="A93" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="89"/>
-      <c r="C93" s="89"/>
-      <c r="D93" s="89"/>
-      <c r="E93" s="89"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="74" t="s">
+      <c r="A94" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="74"/>
-      <c r="C94" s="74" t="s">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D94" s="74"/>
+      <c r="D94" s="73"/>
       <c r="E94" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="76" t="s">
+      <c r="A95" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="76"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
+      <c r="B95" s="58"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
       <c r="E95" s="47">
         <f>E90</f>
-        <v>280.84000000000015</v>
+        <v>202.84000000000015</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="93" t="s">
+      <c r="A96" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="94"/>
-      <c r="C96" s="101" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="87"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" s="64"/>
       <c r="E96" s="45">
         <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="95"/>
-      <c r="B97" s="96"/>
-      <c r="C97" s="99" t="s">
+      <c r="A97" s="67"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="D97" s="100"/>
+      <c r="D97" s="62"/>
       <c r="E97" s="45">
         <v>450</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="95"/>
-      <c r="B98" s="96"/>
-      <c r="C98" s="99" t="s">
-        <v>167</v>
-      </c>
-      <c r="D98" s="100"/>
+      <c r="A98" s="67"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="D98" s="62"/>
       <c r="E98" s="45">
         <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="97"/>
-      <c r="B99" s="98"/>
-      <c r="C99" s="99"/>
-      <c r="D99" s="100"/>
+      <c r="A99" s="69"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="62"/>
       <c r="E99" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77" t="s">
+      <c r="A100" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="77"/>
-      <c r="C100" s="85"/>
-      <c r="D100" s="85"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
       <c r="E100" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="88" t="s">
+      <c r="C101" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="88"/>
+      <c r="D101" s="57"/>
       <c r="E101" s="47">
         <f>(E31+E95)-SUM(E96:E100)</f>
-        <v>315.84000000000015</v>
+        <v>237.84000000000015</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12074,16 +12075,49 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A96:B99"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B77"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="A93:E93"/>
@@ -12096,49 +12130,16 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A84:B88"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A75:B77"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A96:B99"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E74">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12178,13 +12179,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="97" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12206,7 +12207,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>285.04000000000002</v>
+        <v>207.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12366,7 +12367,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>280.84000000000003</v>
+        <v>202.83999999999997</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12419,13 +12420,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="98" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12453,10 +12454,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12468,10 +12469,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="100"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12479,8 +12480,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12501,13 +12502,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12535,10 +12536,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C17" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="64"/>
+      <c r="D17" s="88"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12550,10 +12551,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="89"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12561,8 +12562,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12584,13 +12585,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="91" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12618,10 +12619,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="64"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12633,10 +12634,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12644,8 +12645,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12667,11 +12668,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12686,11 +12687,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="71" t="s">
+      <c r="A30" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12736,16 +12737,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
+      <c r="A36" s="86"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12794,11 +12795,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12833,11 +12834,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="87"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12861,11 +12862,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="71" t="s">
+      <c r="A49" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="71"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="87"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12889,11 +12890,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="84"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12911,7 +12912,7 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C54" s="29">
         <v>1280</v>
@@ -12970,11 +12971,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="73"/>
-      <c r="C60" s="73"/>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13024,53 +13025,53 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="74" t="s">
+      <c r="A67" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="74"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="75"/>
-      <c r="C68" s="75" t="s">
+      <c r="B68" s="85"/>
+      <c r="C68" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="75"/>
+      <c r="D68" s="85"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="76" t="s">
+      <c r="A69" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
+      <c r="B69" s="58"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E101</f>
-        <v>315.84000000000015</v>
+        <v>237.84000000000015</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="74"/>
       <c r="E70" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="78"/>
-      <c r="B71" s="78"/>
+      <c r="A71" s="79"/>
+      <c r="B71" s="79"/>
       <c r="C71" s="80" t="s">
         <v>164</v>
       </c>
@@ -13080,8 +13081,8 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="78"/>
-      <c r="B72" s="78"/>
+      <c r="A72" s="79"/>
+      <c r="B72" s="79"/>
       <c r="C72" s="80"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
@@ -13089,10 +13090,10 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="78" t="s">
+      <c r="A73" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="78"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="83"/>
       <c r="D73" s="83"/>
       <c r="E73" s="46">
@@ -13101,119 +13102,119 @@
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="84"/>
+      <c r="D74" s="78"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1245.8400000000001</v>
+        <v>1167.8400000000001</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="74" t="s">
+      <c r="A76" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="74" t="s">
+      <c r="A77" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="74"/>
-      <c r="C77" s="74" t="s">
+      <c r="B77" s="73"/>
+      <c r="C77" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="74"/>
+      <c r="D77" s="73"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="76" t="s">
+      <c r="A78" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="76"/>
-      <c r="C78" s="85"/>
-      <c r="D78" s="85"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1245.8400000000001</v>
+        <v>1167.8400000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="93" t="s">
+      <c r="A79" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="94"/>
-      <c r="C79" s="86"/>
-      <c r="D79" s="87"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="64"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="95"/>
-      <c r="B80" s="96"/>
-      <c r="C80" s="79" t="s">
+      <c r="A80" s="67"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="79"/>
+      <c r="D80" s="74"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="95"/>
-      <c r="B81" s="96"/>
-      <c r="C81" s="90"/>
-      <c r="D81" s="91"/>
+      <c r="A81" s="67"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="76"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="95"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="92"/>
+      <c r="A82" s="67"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="77"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="97"/>
-      <c r="B83" s="98"/>
-      <c r="C83" s="90"/>
-      <c r="D83" s="91"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="76"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="77" t="s">
+      <c r="A84" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="77"/>
-      <c r="C84" s="85"/>
-      <c r="D84" s="85"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="88" t="s">
+      <c r="C85" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="88"/>
+      <c r="D85" s="57"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>2175.84</v>
+        <v>2097.84</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13231,90 +13232,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="89" t="s">
+      <c r="A88" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="89"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="89"/>
-      <c r="E88" s="89"/>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="74" t="s">
+      <c r="A89" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="74"/>
-      <c r="C89" s="74" t="s">
+      <c r="B89" s="73"/>
+      <c r="C89" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="73"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="76" t="s">
+      <c r="A90" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="76"/>
-      <c r="C90" s="85"/>
-      <c r="D90" s="85"/>
+      <c r="B90" s="58"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>2175.84</v>
+        <v>2097.84</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="93" t="s">
+      <c r="A91" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="94"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="100"/>
+      <c r="B91" s="66"/>
+      <c r="C91" s="61"/>
+      <c r="D91" s="62"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="95"/>
-      <c r="B92" s="96"/>
-      <c r="C92" s="99" t="s">
+      <c r="A92" s="67"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="100"/>
+      <c r="D92" s="62"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="97"/>
-      <c r="B93" s="98"/>
-      <c r="C93" s="99"/>
-      <c r="D93" s="100"/>
+      <c r="A93" s="69"/>
+      <c r="B93" s="70"/>
+      <c r="C93" s="61"/>
+      <c r="D93" s="62"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="77" t="s">
+      <c r="A94" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="88" t="s">
+      <c r="C95" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="88"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>3105.84</v>
+        <v>3027.84</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17063,45 +17064,15 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17113,15 +17084,45 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C408B9A-56A2-E84F-A740-0617C15BC699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C8124-DE03-8C42-AFED-6D380E1150D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="171">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -743,9 +743,6 @@
 ~ Round Trip to East Kowloon hospital 02/10 - $4</t>
   </si>
   <si>
-    <t>~ Payback $500 to Lawrence</t>
-  </si>
-  <si>
     <t>cigarette - 4 packs each pack has 10 packets of cigarette</t>
   </si>
   <si>
@@ -760,7 +757,13 @@
 ~ OK Store buy additional 1 packet cigarette 11/09 - $78
 ~ OK Store buy additional 1 packet cigarette 12/09 - $78
 ~ OK Store buy additional 1 packet cigarette 13/09 - $78
-~ OK Store buy additional 1 packet cigarette 14/09 - $78</t>
+~ OK Store buy additional 3 packet cigarette 14/09 - $234</t>
+  </si>
+  <si>
+    <t>~ Payback $250 to Lawrence</t>
+  </si>
+  <si>
+    <t>~ iHerb Aveeno Lotion - $136.64</t>
   </si>
 </sst>
 </file>
@@ -1294,29 +1297,113 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1336,124 +1423,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1468,11 +1450,32 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1811,13 +1814,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1838,7 +1841,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>207.04</v>
+        <v>51.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1994,7 +1997,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>202.83999999999997</v>
+        <v>46.84</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2047,13 +2050,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2081,10 +2084,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2096,10 +2099,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="115"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2111,10 +2114,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="116" t="s">
+      <c r="C13" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="116"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2124,10 +2127,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2137,10 +2140,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="89"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2150,10 +2153,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="89"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2165,10 +2168,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="111" t="s">
+      <c r="C17" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="111"/>
+      <c r="D17" s="104"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2178,10 +2181,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="112"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2193,10 +2196,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="113"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2217,13 +2220,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2251,10 +2254,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="114"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2266,10 +2269,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2281,10 +2284,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="89"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2294,10 +2297,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="111"/>
+      <c r="D26" s="104"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2309,10 +2312,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="112"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2322,10 +2325,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="102" t="s">
+      <c r="C28" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="102"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2347,13 +2350,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="91" t="s">
+      <c r="A31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2381,10 +2384,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="88"/>
+      <c r="D32" s="64"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2396,10 +2399,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="89"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2409,10 +2412,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="89"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2422,10 +2425,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="94" t="s">
+      <c r="C35" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="95"/>
+      <c r="D35" s="68"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2435,10 +2438,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="94" t="s">
+      <c r="C36" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="110"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2448,10 +2451,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="101" t="s">
+      <c r="C37" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="89"/>
+      <c r="D37" s="62"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2473,11 +2476,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="90"/>
-      <c r="C40" s="90"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2492,11 +2495,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2542,16 +2545,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="72"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="86"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2600,11 +2603,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2639,11 +2642,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="87"/>
-      <c r="C58" s="87"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="71"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2667,11 +2670,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="87"/>
-      <c r="C61" s="87"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2695,11 +2698,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="84"/>
-      <c r="C64" s="84"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2776,11 +2779,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="84"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2830,87 +2833,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="73" t="s">
+      <c r="A79" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="85" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="85"/>
+      <c r="D80" s="75"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="106" t="s">
+      <c r="A81" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="106"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="60"/>
+      <c r="B81" s="110"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="60"/>
-      <c r="C82" s="107" t="s">
+      <c r="B82" s="77"/>
+      <c r="C82" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="107"/>
+      <c r="D82" s="111"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="107" t="s">
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="107"/>
+      <c r="D83" s="111"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="60"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="107" t="s">
+      <c r="A84" s="77"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="107"/>
+      <c r="D84" s="111"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="60"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="108" t="s">
+      <c r="A85" s="77"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="108"/>
+      <c r="D85" s="112"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="60"/>
-      <c r="B86" s="60"/>
+      <c r="A86" s="77"/>
+      <c r="B86" s="77"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2920,30 +2923,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="60"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="108" t="s">
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="112" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="108"/>
+      <c r="D87" s="112"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="60"/>
-      <c r="B88" s="60"/>
-      <c r="C88" s="107" t="s">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="107"/>
+      <c r="D88" s="111"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="60"/>
-      <c r="B89" s="60"/>
+      <c r="A89" s="77"/>
+      <c r="B89" s="77"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2953,8 +2956,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="60"/>
-      <c r="B90" s="60"/>
+      <c r="A90" s="77"/>
+      <c r="B90" s="77"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2964,21 +2967,21 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="60"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="109" t="s">
+      <c r="A91" s="77"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="109"/>
+      <c r="D91" s="113"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="79"/>
+      <c r="B92" s="78"/>
       <c r="C92" s="83"/>
       <c r="D92" s="83"/>
       <c r="E92" s="46">
@@ -2987,10 +2990,10 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="78" t="s">
+      <c r="C93" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="78"/>
+      <c r="D93" s="84"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2998,44 +3001,44 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="73"/>
-      <c r="C95" s="73"/>
-      <c r="D95" s="73"/>
-      <c r="E95" s="73"/>
+      <c r="B95" s="74"/>
+      <c r="C95" s="74"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="73"/>
-      <c r="C96" s="73" t="s">
+      <c r="B96" s="74"/>
+      <c r="C96" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="73"/>
+      <c r="D96" s="74"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="58" t="s">
+      <c r="A97" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="58"/>
-      <c r="C97" s="59"/>
-      <c r="D97" s="59"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="60" t="s">
+      <c r="A98" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="60"/>
+      <c r="B98" s="77"/>
       <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
@@ -3045,66 +3048,66 @@
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="60"/>
-      <c r="B99" s="60"/>
-      <c r="C99" s="74" t="s">
+      <c r="A99" s="77"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="74"/>
+      <c r="D99" s="79"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="60"/>
-      <c r="B100" s="60"/>
-      <c r="C100" s="74" t="s">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="79" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="74"/>
+      <c r="D100" s="79"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="60"/>
-      <c r="B101" s="60"/>
-      <c r="C101" s="74" t="s">
+      <c r="A101" s="77"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="79"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="60"/>
-      <c r="B102" s="60"/>
-      <c r="C102" s="75" t="s">
+      <c r="A102" s="77"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="105"/>
+      <c r="D102" s="114"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="60" t="s">
+      <c r="A103" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="60"/>
-      <c r="C103" s="59"/>
-      <c r="D103" s="59"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="57"/>
+      <c r="D104" s="88"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3125,91 +3128,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="72" t="s">
+      <c r="A107" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="72"/>
-      <c r="C107" s="72"/>
-      <c r="D107" s="72"/>
-      <c r="E107" s="72"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
+      <c r="D107" s="89"/>
+      <c r="E107" s="89"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="73" t="s">
+      <c r="A108" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="73"/>
-      <c r="C108" s="73" t="s">
+      <c r="B108" s="74"/>
+      <c r="C108" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="73"/>
+      <c r="D108" s="74"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="58"/>
-      <c r="C109" s="59"/>
-      <c r="D109" s="59"/>
+      <c r="B109" s="76"/>
+      <c r="C109" s="85"/>
+      <c r="D109" s="85"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="65" t="s">
+      <c r="A110" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="66"/>
-      <c r="C110" s="102" t="s">
+      <c r="B110" s="94"/>
+      <c r="C110" s="108" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="102"/>
+      <c r="D110" s="108"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="67"/>
-      <c r="B111" s="68"/>
-      <c r="C111" s="103" t="s">
+      <c r="A111" s="95"/>
+      <c r="B111" s="96"/>
+      <c r="C111" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="104"/>
+      <c r="D111" s="116"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="69"/>
-      <c r="B112" s="70"/>
-      <c r="C112" s="75" t="s">
+      <c r="A112" s="97"/>
+      <c r="B112" s="98"/>
+      <c r="C112" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="105"/>
+      <c r="D112" s="114"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="60" t="s">
+      <c r="A113" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="60"/>
-      <c r="C113" s="59"/>
-      <c r="D113" s="59"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="85"/>
+      <c r="D113" s="85"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="57" t="s">
+      <c r="C114" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="57"/>
+      <c r="D114" s="88"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6961,42 +6964,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7010,35 +7006,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7078,13 +7081,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7106,7 +7109,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>207.04</v>
+        <v>51.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7266,7 +7269,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>202.83999999999997</v>
+        <v>46.84</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7319,13 +7322,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7353,10 +7356,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7368,10 +7371,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="100" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="100"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7383,10 +7386,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="89"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7398,10 +7401,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7422,13 +7425,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7456,10 +7459,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="88"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7471,10 +7474,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="89"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7486,10 +7489,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="95"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7501,10 +7504,10 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="93"/>
+      <c r="D21" s="66"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
@@ -7516,10 +7519,10 @@
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="96" t="s">
+      <c r="C22" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="95"/>
+      <c r="D22" s="68"/>
       <c r="E22" s="29">
         <v>60</v>
       </c>
@@ -7531,10 +7534,10 @@
       <c r="B23" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="D23" s="95"/>
+      <c r="D23" s="68"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7556,13 +7559,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7590,10 +7593,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="88"/>
+      <c r="D27" s="64"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7605,10 +7608,10 @@
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="89"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
@@ -7620,10 +7623,10 @@
       <c r="B29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="89" t="s">
+      <c r="C29" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="89"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="29">
         <v>55</v>
       </c>
@@ -7631,8 +7634,8 @@
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="29">
         <v>0</v>
       </c>
@@ -7654,11 +7657,11 @@
       <c r="B32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+      <c r="A33" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -7673,11 +7676,11 @@
       <c r="D34" s="37"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="87"/>
-      <c r="C35" s="87"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
     </row>
     <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50" t="s">
@@ -7723,16 +7726,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="86"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -7781,11 +7784,11 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7820,11 +7823,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="87"/>
-      <c r="C51" s="87"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="71"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7848,11 +7851,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -7876,11 +7879,11 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="84"/>
-      <c r="C57" s="84"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
@@ -7957,11 +7960,11 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="84" t="s">
+      <c r="A65" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="84"/>
-      <c r="C65" s="84"/>
+      <c r="B65" s="73"/>
+      <c r="C65" s="73"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
@@ -7978,7 +7981,7 @@
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="19">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7988,7 +7991,7 @@
       </c>
       <c r="C68" s="19">
         <f>SUM(C66:C67)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8011,55 +8014,55 @@
       <c r="B71" s="24"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
-      <c r="D72" s="73"/>
-      <c r="E72" s="73"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="85" t="s">
+      <c r="A73" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85" t="s">
+      <c r="B73" s="75"/>
+      <c r="C73" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="85"/>
+      <c r="D73" s="75"/>
       <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="58" t="s">
+      <c r="A74" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="58"/>
-      <c r="C74" s="60"/>
-      <c r="D74" s="60"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="77"/>
       <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="79"/>
-      <c r="C75" s="74" t="s">
+      <c r="B75" s="78"/>
+      <c r="C75" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="74"/>
+      <c r="D75" s="79"/>
       <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="79"/>
-      <c r="B76" s="79"/>
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
       <c r="C76" s="80" t="s">
         <v>133</v>
       </c>
@@ -8069,8 +8072,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="79"/>
-      <c r="B77" s="79"/>
+      <c r="A77" s="78"/>
+      <c r="B77" s="78"/>
       <c r="C77" s="80" t="s">
         <v>134</v>
       </c>
@@ -8080,10 +8083,10 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="79"/>
+      <c r="B78" s="78"/>
       <c r="C78" s="83"/>
       <c r="D78" s="83"/>
       <c r="E78" s="46">
@@ -8092,10 +8095,10 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="78" t="s">
+      <c r="C79" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="78"/>
+      <c r="D79" s="84"/>
       <c r="E79" s="47">
         <f>(E15+E74)-SUM(E75:E78)</f>
         <v>24.599999999999909</v>
@@ -8103,116 +8106,116 @@
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="B81" s="73"/>
-      <c r="C81" s="73"/>
-      <c r="D81" s="73"/>
-      <c r="E81" s="73"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="73" t="s">
+      <c r="A82" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="73"/>
-      <c r="C82" s="73" t="s">
+      <c r="B82" s="74"/>
+      <c r="C82" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="73"/>
+      <c r="D82" s="74"/>
       <c r="E82" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="58"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
+      <c r="B83" s="76"/>
+      <c r="C83" s="85"/>
+      <c r="D83" s="85"/>
       <c r="E83" s="47">
         <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="65" t="s">
+      <c r="A84" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="66"/>
-      <c r="C84" s="71" t="s">
+      <c r="B84" s="94"/>
+      <c r="C84" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="D84" s="64"/>
+      <c r="D84" s="87"/>
       <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="67"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="74" t="s">
+      <c r="A85" s="95"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="D85" s="74"/>
+      <c r="D85" s="79"/>
       <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="209" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="67"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="75" t="s">
-        <v>169</v>
-      </c>
-      <c r="D86" s="76"/>
+      <c r="A86" s="95"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="90" t="s">
+        <v>168</v>
+      </c>
+      <c r="D86" s="91"/>
       <c r="E86" s="48">
-        <v>624.5</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="67"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="71" t="s">
+      <c r="A87" s="95"/>
+      <c r="B87" s="96"/>
+      <c r="C87" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="77"/>
+      <c r="D87" s="92"/>
       <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="75" t="s">
+      <c r="A88" s="97"/>
+      <c r="B88" s="98"/>
+      <c r="C88" s="90" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="76"/>
+      <c r="D88" s="91"/>
       <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="60" t="s">
+      <c r="A89" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="60"/>
-      <c r="C89" s="59"/>
-      <c r="D89" s="59"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="85"/>
+      <c r="D89" s="85"/>
       <c r="E89" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="57" t="s">
+      <c r="C90" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="57"/>
+      <c r="D90" s="88"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>202.84000000000015</v>
+        <v>46.840000000000146</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8230,103 +8233,105 @@
       <c r="E92" s="49"/>
     </row>
     <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="72" t="s">
+      <c r="A93" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
+      <c r="B93" s="89"/>
+      <c r="C93" s="89"/>
+      <c r="D93" s="89"/>
+      <c r="E93" s="89"/>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="73" t="s">
+      <c r="A94" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="73"/>
-      <c r="C94" s="73" t="s">
+      <c r="B94" s="74"/>
+      <c r="C94" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D94" s="73"/>
+      <c r="D94" s="74"/>
       <c r="E94" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="58" t="s">
+      <c r="A95" s="76" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="58"/>
-      <c r="C95" s="59"/>
-      <c r="D95" s="59"/>
+      <c r="B95" s="76"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
       <c r="E95" s="47">
         <f>E90</f>
-        <v>202.84000000000015</v>
+        <v>46.840000000000146</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="65" t="s">
+      <c r="A96" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="63" t="s">
-        <v>167</v>
-      </c>
-      <c r="D96" s="64"/>
+      <c r="B96" s="94"/>
+      <c r="C96" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="D96" s="87"/>
       <c r="E96" s="45">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="95"/>
+      <c r="B97" s="96"/>
+      <c r="C97" s="99" t="s">
+        <v>146</v>
+      </c>
+      <c r="D97" s="100"/>
+      <c r="E97" s="45">
         <v>500</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="67"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="D97" s="62"/>
-      <c r="E97" s="45">
-        <v>450</v>
-      </c>
-    </row>
     <row r="98" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="67"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="61" t="s">
+      <c r="A98" s="95"/>
+      <c r="B98" s="96"/>
+      <c r="C98" s="99" t="s">
         <v>166</v>
       </c>
-      <c r="D98" s="62"/>
+      <c r="D98" s="100"/>
       <c r="E98" s="45">
         <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="69"/>
-      <c r="B99" s="70"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="62"/>
+      <c r="A99" s="97"/>
+      <c r="B99" s="98"/>
+      <c r="C99" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="100"/>
       <c r="E99" s="45">
-        <v>0</v>
+        <v>136.63999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="60" t="s">
+      <c r="A100" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="60"/>
-      <c r="C100" s="59"/>
-      <c r="D100" s="59"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="85"/>
+      <c r="D100" s="85"/>
       <c r="E100" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="57" t="s">
+      <c r="C101" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="57"/>
+      <c r="D101" s="88"/>
       <c r="E101" s="47">
         <f>(E31+E95)-SUM(E96:E100)</f>
-        <v>237.84000000000015</v>
+        <v>145.20000000000027</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12075,49 +12080,16 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B77"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A96:B99"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="A93:E93"/>
@@ -12130,16 +12102,49 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A84:B88"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A96:B99"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A75:B77"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E74">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12179,13 +12184,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12207,7 +12212,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>207.04</v>
+        <v>51.04</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12367,7 +12372,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>202.83999999999997</v>
+        <v>46.84</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12420,13 +12425,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12454,10 +12459,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12469,10 +12474,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="100" t="s">
+      <c r="C12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="100"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12480,8 +12485,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12502,13 +12507,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12536,10 +12541,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="88"/>
+      <c r="D17" s="64"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12551,10 +12556,10 @@
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="89"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12562,8 +12567,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12585,13 +12590,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12619,10 +12624,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="88"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12634,10 +12639,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12645,8 +12650,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12668,11 +12673,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12687,11 +12692,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12737,16 +12742,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="72"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="86"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="72"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12795,11 +12800,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12834,11 +12839,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="87" t="s">
+      <c r="A46" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="87"/>
-      <c r="C46" s="87"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12862,11 +12867,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="87"/>
-      <c r="C49" s="87"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="71"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12890,11 +12895,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="84" t="s">
+      <c r="A52" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="84"/>
-      <c r="C52" s="84"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12912,7 +12917,7 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C54" s="29">
         <v>1280</v>
@@ -12971,11 +12976,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="84"/>
-      <c r="C60" s="84"/>
+      <c r="B60" s="73"/>
+      <c r="C60" s="73"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13025,53 +13030,55 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73" t="s">
+      <c r="A67" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="85"/>
-      <c r="C68" s="85" t="s">
+      <c r="B68" s="75"/>
+      <c r="C68" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="85"/>
+      <c r="D68" s="75"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="58" t="s">
+      <c r="A69" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E101</f>
-        <v>237.84000000000015</v>
+        <v>145.20000000000027</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="79" t="s">
+      <c r="A70" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="74"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="79"/>
       <c r="E70" s="45">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="79"/>
-      <c r="B71" s="79"/>
+      <c r="A71" s="78"/>
+      <c r="B71" s="78"/>
       <c r="C71" s="80" t="s">
         <v>164</v>
       </c>
@@ -13081,8 +13088,8 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="79"/>
-      <c r="B72" s="79"/>
+      <c r="A72" s="78"/>
+      <c r="B72" s="78"/>
       <c r="C72" s="80"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
@@ -13090,10 +13097,10 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="79" t="s">
+      <c r="A73" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="79"/>
+      <c r="B73" s="78"/>
       <c r="C73" s="83"/>
       <c r="D73" s="83"/>
       <c r="E73" s="46">
@@ -13102,119 +13109,119 @@
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="78" t="s">
+      <c r="C74" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="78"/>
+      <c r="D74" s="84"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>1167.8400000000001</v>
+        <v>825.20000000000027</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="73" t="s">
+      <c r="A76" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
+      <c r="B76" s="74"/>
+      <c r="C76" s="74"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="73"/>
-      <c r="C77" s="73" t="s">
+      <c r="B77" s="74"/>
+      <c r="C77" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="73"/>
+      <c r="D77" s="74"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="58" t="s">
+      <c r="A78" s="76" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="58"/>
-      <c r="C78" s="59"/>
-      <c r="D78" s="59"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="85"/>
+      <c r="D78" s="85"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>1167.8400000000001</v>
+        <v>825.20000000000027</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="65" t="s">
+      <c r="A79" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="66"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="64"/>
+      <c r="B79" s="94"/>
+      <c r="C79" s="86"/>
+      <c r="D79" s="87"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="67"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="74" t="s">
+      <c r="A80" s="95"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="74"/>
+      <c r="D80" s="79"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="67"/>
-      <c r="B81" s="68"/>
-      <c r="C81" s="75"/>
-      <c r="D81" s="76"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="90"/>
+      <c r="D81" s="91"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="67"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="77"/>
+      <c r="A82" s="95"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="86"/>
+      <c r="D82" s="92"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="69"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="75"/>
-      <c r="D83" s="76"/>
+      <c r="A83" s="97"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="90"/>
+      <c r="D83" s="91"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="60" t="s">
+      <c r="A84" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="60"/>
-      <c r="C84" s="59"/>
-      <c r="D84" s="59"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="85"/>
+      <c r="D84" s="85"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="57" t="s">
+      <c r="C85" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="57"/>
+      <c r="D85" s="88"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>2097.84</v>
+        <v>1755.2000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13232,90 +13239,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="72" t="s">
+      <c r="A88" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="72"/>
-      <c r="C88" s="72"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
+      <c r="B88" s="89"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="89"/>
+      <c r="E88" s="89"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73" t="s">
+      <c r="B89" s="74"/>
+      <c r="C89" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="73"/>
+      <c r="D89" s="74"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="58" t="s">
+      <c r="A90" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="58"/>
-      <c r="C90" s="59"/>
-      <c r="D90" s="59"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>2097.84</v>
+        <v>1755.2000000000003</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="65" t="s">
+      <c r="A91" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="66"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="62"/>
+      <c r="B91" s="94"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="100"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="67"/>
-      <c r="B92" s="68"/>
-      <c r="C92" s="61" t="s">
+      <c r="A92" s="95"/>
+      <c r="B92" s="96"/>
+      <c r="C92" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="62"/>
+      <c r="D92" s="100"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="69"/>
-      <c r="B93" s="70"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="62"/>
+      <c r="A93" s="97"/>
+      <c r="B93" s="98"/>
+      <c r="C93" s="99"/>
+      <c r="D93" s="100"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="60" t="s">
+      <c r="A94" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="60"/>
-      <c r="C94" s="59"/>
-      <c r="D94" s="59"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="57" t="s">
+      <c r="C95" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="57"/>
+      <c r="D95" s="88"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>3027.84</v>
+        <v>2685.2000000000007</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17064,15 +17071,45 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17084,45 +17121,15 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9C8124-DE03-8C42-AFED-6D380E1150D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44812AF1-33CF-A249-8AC8-035FD221CDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -640,9 +640,6 @@
     <t>2nd September 2026</t>
   </si>
   <si>
-    <t>1. Borrow $60</t>
-  </si>
-  <si>
     <t>18th September 2026</t>
   </si>
   <si>
@@ -665,11 +662,6 @@
   <si>
     <t>~ iHerb Aveeno Lotion 23/08 - $136.64
 ~ Watsons Revlon color silk 17/09 - $59.9</t>
-  </si>
-  <si>
-    <t>Partial Food And Snack Prepaid on the Previous Month
-~ Food
-~ Snack And Drinks</t>
   </si>
   <si>
     <t>1. Top up $50 for Octopus
@@ -746,6 +738,22 @@
     <t>cigarette - 4 packs each pack has 10 packets of cigarette</t>
   </si>
   <si>
+    <t>~ iHerb Aveeno Lotion - $136.64</t>
+  </si>
+  <si>
+    <t>~ Payback $250 to Lawrence</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+   ~ HKTV mall 18/09 - $339.9
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>1. Borrow $60
+2. Payback Water bill through Alipay $74.1.</t>
+  </si>
+  <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
@@ -757,13 +765,8 @@
 ~ OK Store buy additional 1 packet cigarette 11/09 - $78
 ~ OK Store buy additional 1 packet cigarette 12/09 - $78
 ~ OK Store buy additional 1 packet cigarette 13/09 - $78
-~ OK Store buy additional 3 packet cigarette 14/09 - $234</t>
-  </si>
-  <si>
-    <t>~ Payback $250 to Lawrence</t>
-  </si>
-  <si>
-    <t>~ iHerb Aveeno Lotion - $136.64</t>
+~ OK Store buy additional 3 packet cigarette 14/09 - $234
+~ OK Store buy additional 1 packet cigarette 16/09 - $78</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1297,113 +1300,29 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1423,19 +1342,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1450,32 +1471,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1814,13 +1814,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1841,7 +1841,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>51.04</v>
+        <v>47.14</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>46.84</v>
+        <v>42.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2050,13 +2050,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2084,10 +2084,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2099,10 +2099,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="114"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2114,10 +2114,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="103"/>
+      <c r="D13" s="115"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2127,10 +2127,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -2140,10 +2140,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="62"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -2153,10 +2153,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="62"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2168,10 +2168,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="104"/>
+      <c r="D17" s="110"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2181,10 +2181,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="105"/>
+      <c r="D18" s="111"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2196,10 +2196,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="112"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2220,13 +2220,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2254,10 +2254,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="107"/>
+      <c r="D23" s="113"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2269,10 +2269,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2284,10 +2284,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="62"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2297,10 +2297,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="104"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2312,10 +2312,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="105" t="s">
+      <c r="C27" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="105"/>
+      <c r="D27" s="111"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2325,10 +2325,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="108" t="s">
+      <c r="C28" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="108"/>
+      <c r="D28" s="101"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2350,13 +2350,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2384,10 +2384,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="64"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2399,10 +2399,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="62"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2412,10 +2412,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="62"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2425,10 +2425,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="94" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="95"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="94" t="s">
         <v>115</v>
       </c>
       <c r="D36" s="109"/>
@@ -2451,10 +2451,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="62"/>
+      <c r="D37" s="89"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2476,11 +2476,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2495,11 +2495,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2545,16 +2545,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="72"/>
-      <c r="C47" s="72"/>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2603,11 +2603,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2642,11 +2642,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="87"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2670,11 +2670,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2698,11 +2698,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73" t="s">
+      <c r="A64" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="84"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2779,11 +2779,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="73"/>
+      <c r="B72" s="84"/>
+      <c r="C72" s="84"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2833,87 +2833,87 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="74" t="s">
+      <c r="A79" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
+      <c r="B79" s="73"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="75"/>
+      <c r="D80" s="85"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="110" t="s">
+      <c r="A81" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="110"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
+      <c r="B81" s="105"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="111" t="s">
+      <c r="B82" s="60"/>
+      <c r="C82" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="111"/>
+      <c r="D82" s="106"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="111" t="s">
+      <c r="A83" s="60"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="111"/>
+      <c r="D83" s="106"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="111" t="s">
+      <c r="A84" s="60"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="111"/>
+      <c r="D84" s="106"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="60"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="112"/>
+      <c r="D85" s="107"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="77"/>
-      <c r="B86" s="77"/>
+      <c r="A86" s="60"/>
+      <c r="B86" s="60"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2923,30 +2923,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="77"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="112" t="s">
+      <c r="A87" s="60"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="112"/>
+      <c r="D87" s="107"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="111" t="s">
+      <c r="A88" s="60"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="111"/>
+      <c r="D88" s="106"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
+      <c r="A89" s="60"/>
+      <c r="B89" s="60"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2956,8 +2956,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="77"/>
-      <c r="B90" s="77"/>
+      <c r="A90" s="60"/>
+      <c r="B90" s="60"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2967,21 +2967,21 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="113" t="s">
+      <c r="A91" s="60"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="113"/>
+      <c r="D91" s="108"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="78"/>
+      <c r="B92" s="79"/>
       <c r="C92" s="83"/>
       <c r="D92" s="83"/>
       <c r="E92" s="46">
@@ -2990,10 +2990,10 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="84"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -3001,44 +3001,44 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="74" t="s">
+      <c r="A95" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="74"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="74"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="74" t="s">
+      <c r="A96" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="74"/>
-      <c r="C96" s="74" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="74"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="76" t="s">
+      <c r="A97" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="76"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="59"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="77" t="s">
+      <c r="A98" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="77"/>
+      <c r="B98" s="60"/>
       <c r="C98" s="81" t="s">
         <v>98</v>
       </c>
@@ -3048,66 +3048,66 @@
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="77"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="79" t="s">
+      <c r="A99" s="60"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="79"/>
+      <c r="D99" s="74"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="79" t="s">
+      <c r="A100" s="60"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="79"/>
+      <c r="D100" s="74"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="77"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="79" t="s">
+      <c r="A101" s="60"/>
+      <c r="B101" s="60"/>
+      <c r="C101" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="79"/>
+      <c r="D101" s="74"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="77"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="60"/>
+      <c r="B102" s="60"/>
+      <c r="C102" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="114"/>
+      <c r="D102" s="104"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="77" t="s">
+      <c r="A103" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="77"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="59"/>
+      <c r="D103" s="59"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="88"/>
+      <c r="D104" s="57"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3128,91 +3128,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="B107" s="89"/>
-      <c r="C107" s="89"/>
-      <c r="D107" s="89"/>
-      <c r="E107" s="89"/>
+      <c r="B107" s="72"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="72"/>
+      <c r="E107" s="72"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="74"/>
-      <c r="C108" s="74" t="s">
+      <c r="B108" s="73"/>
+      <c r="C108" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="74"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="76" t="s">
+      <c r="A109" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="76"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="58"/>
+      <c r="C109" s="59"/>
+      <c r="D109" s="59"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="93" t="s">
+      <c r="A110" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="94"/>
-      <c r="C110" s="108" t="s">
+      <c r="B110" s="66"/>
+      <c r="C110" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="108"/>
+      <c r="D110" s="101"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="95"/>
-      <c r="B111" s="96"/>
-      <c r="C111" s="115" t="s">
+      <c r="A111" s="67"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="116"/>
+      <c r="D111" s="103"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="98"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="69"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="114"/>
+      <c r="D112" s="104"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="77" t="s">
+      <c r="A113" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="77"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="60"/>
+      <c r="C113" s="59"/>
+      <c r="D113" s="59"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="88"/>
+      <c r="D114" s="57"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6964,35 +6964,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -7006,42 +7013,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThanOrEqual">
@@ -7081,13 +7081,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="96" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>51.04</v>
+        <v>47.14</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>46.84</v>
+        <v>42.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7322,13 +7322,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7356,10 +7356,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7371,10 +7371,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="99"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7386,10 +7386,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="62"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7401,10 +7401,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7425,13 +7425,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7459,10 +7459,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="64"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7474,10 +7474,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="62"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7489,10 +7489,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="68"/>
+      <c r="C20" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="95"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7504,40 +7504,40 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="66"/>
+      <c r="D21" s="93"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
         <v>138</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="D22" s="68"/>
+      <c r="C22" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="95"/>
       <c r="E22" s="29">
-        <v>60</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" s="68"/>
+      <c r="C23" s="94" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="95"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E24" s="26">
         <f>SUM(E19:E23)</f>
-        <v>4148.08</v>
+        <v>4222.18</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7559,13 +7559,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7593,40 +7593,40 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="64"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="62"/>
+      <c r="D28" s="89"/>
       <c r="E28" s="33">
         <v>2485</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="62"/>
+      <c r="D29" s="89"/>
       <c r="E29" s="29">
         <v>55</v>
       </c>
@@ -7634,8 +7634,8 @@
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
       <c r="E30" s="29">
         <v>0</v>
       </c>
@@ -7657,11 +7657,11 @@
       <c r="B32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -7676,11 +7676,11 @@
       <c r="D34" s="37"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
     </row>
     <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50" t="s">
@@ -7726,16 +7726,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="72"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="72"/>
+      <c r="A41" s="86"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -7784,11 +7784,11 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="71" t="s">
+      <c r="A47" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7823,11 +7823,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="71" t="s">
+      <c r="A51" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="71"/>
-      <c r="C51" s="71"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="87"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7851,11 +7851,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="71" t="s">
+      <c r="A54" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -7879,11 +7879,11 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
+      <c r="B57" s="84"/>
+      <c r="C57" s="84"/>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
@@ -7960,11 +7960,11 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="73" t="s">
+      <c r="A65" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="73"/>
-      <c r="C65" s="73"/>
+      <c r="B65" s="84"/>
+      <c r="C65" s="84"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
@@ -8014,55 +8014,55 @@
       <c r="B71" s="24"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="74" t="s">
+      <c r="A72" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="75"/>
-      <c r="C73" s="75" t="s">
+      <c r="B73" s="85"/>
+      <c r="C73" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="75"/>
+      <c r="D73" s="85"/>
       <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="76" t="s">
+      <c r="A74" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="76"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="77"/>
+      <c r="B74" s="58"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
       <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="78" t="s">
+      <c r="A75" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="79" t="s">
+      <c r="B75" s="79"/>
+      <c r="C75" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="79"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
+      <c r="A76" s="79"/>
+      <c r="B76" s="79"/>
       <c r="C76" s="80" t="s">
         <v>133</v>
       </c>
@@ -8072,8 +8072,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="78"/>
-      <c r="B77" s="78"/>
+      <c r="A77" s="79"/>
+      <c r="B77" s="79"/>
       <c r="C77" s="80" t="s">
         <v>134</v>
       </c>
@@ -8083,10 +8083,10 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="78" t="s">
+      <c r="A78" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="78"/>
+      <c r="B78" s="79"/>
       <c r="C78" s="83"/>
       <c r="D78" s="83"/>
       <c r="E78" s="46">
@@ -8095,10 +8095,10 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="84" t="s">
+      <c r="C79" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D79" s="84"/>
+      <c r="D79" s="78"/>
       <c r="E79" s="47">
         <f>(E15+E74)-SUM(E75:E78)</f>
         <v>24.599999999999909</v>
@@ -8106,116 +8106,116 @@
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
+      <c r="B81" s="73"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
     </row>
     <row r="82" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="74" t="s">
+      <c r="A82" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="74"/>
-      <c r="C82" s="74" t="s">
+      <c r="B82" s="73"/>
+      <c r="C82" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="74"/>
+      <c r="D82" s="73"/>
       <c r="E82" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="76" t="s">
+      <c r="A83" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="76"/>
-      <c r="C83" s="85"/>
-      <c r="D83" s="85"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
       <c r="E83" s="47">
         <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="94"/>
-      <c r="C84" s="86" t="s">
-        <v>143</v>
-      </c>
-      <c r="D84" s="87"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D84" s="64"/>
       <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="95"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="D85" s="79"/>
+      <c r="A85" s="67"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="D85" s="74"/>
       <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="209" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="95"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="90" t="s">
-        <v>168</v>
-      </c>
-      <c r="D86" s="91"/>
+    <row r="86" spans="1:5" ht="221" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="67"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="75" t="s">
+        <v>170</v>
+      </c>
+      <c r="D86" s="76"/>
       <c r="E86" s="48">
-        <v>780.5</v>
+        <v>858.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="95"/>
-      <c r="B87" s="96"/>
-      <c r="C87" s="86" t="s">
-        <v>145</v>
-      </c>
-      <c r="D87" s="92"/>
+      <c r="A87" s="67"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" s="77"/>
       <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="97"/>
-      <c r="B88" s="98"/>
-      <c r="C88" s="90" t="s">
-        <v>144</v>
-      </c>
-      <c r="D88" s="91"/>
+      <c r="A88" s="69"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D88" s="76"/>
       <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="77" t="s">
+      <c r="A89" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="77"/>
-      <c r="C89" s="85"/>
-      <c r="D89" s="85"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="59"/>
       <c r="E89" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="88" t="s">
+      <c r="C90" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="88"/>
+      <c r="D90" s="57"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>46.840000000000146</v>
+        <v>42.940000000000509</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8233,105 +8233,105 @@
       <c r="E92" s="49"/>
     </row>
     <row r="93" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="89" t="s">
+      <c r="A93" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="89"/>
-      <c r="C93" s="89"/>
-      <c r="D93" s="89"/>
-      <c r="E93" s="89"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="74" t="s">
+      <c r="A94" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="74"/>
-      <c r="C94" s="74" t="s">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D94" s="74"/>
+      <c r="D94" s="73"/>
       <c r="E94" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="76" t="s">
+      <c r="A95" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="76"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
+      <c r="B95" s="58"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
       <c r="E95" s="47">
         <f>E90</f>
-        <v>46.840000000000146</v>
+        <v>42.940000000000509</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="93" t="s">
+      <c r="A96" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="94"/>
-      <c r="C96" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="D96" s="87"/>
+      <c r="B96" s="66"/>
+      <c r="C96" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" s="64"/>
       <c r="E96" s="45">
         <v>250</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="95"/>
-      <c r="B97" s="96"/>
-      <c r="C97" s="99" t="s">
-        <v>146</v>
-      </c>
-      <c r="D97" s="100"/>
+    <row r="97" spans="1:5" ht="71" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="67"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" s="62"/>
       <c r="E97" s="45">
-        <v>500</v>
+        <v>339.9</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="95"/>
-      <c r="B98" s="96"/>
-      <c r="C98" s="99" t="s">
-        <v>166</v>
-      </c>
-      <c r="D98" s="100"/>
+      <c r="A98" s="67"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D98" s="62"/>
       <c r="E98" s="45">
         <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="97"/>
-      <c r="B99" s="98"/>
-      <c r="C99" s="99" t="s">
-        <v>170</v>
-      </c>
-      <c r="D99" s="100"/>
+      <c r="A99" s="69"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" s="62"/>
       <c r="E99" s="45">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="77" t="s">
+      <c r="A100" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="77"/>
-      <c r="C100" s="85"/>
-      <c r="D100" s="85"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
       <c r="E100" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="88" t="s">
+      <c r="C101" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="88"/>
+      <c r="D101" s="57"/>
       <c r="E101" s="47">
         <f>(E31+E95)-SUM(E96:E100)</f>
-        <v>145.20000000000027</v>
+        <v>301.40000000000055</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12080,16 +12080,49 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A96:B99"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A40:C41"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B77"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:D83"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="A93:E93"/>
@@ -12102,49 +12135,16 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C87:D87"/>
     <mergeCell ref="A84:B88"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="A75:B77"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A40:C41"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A96:B99"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E74">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -12184,13 +12184,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="96" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>51.04</v>
+        <v>47.14</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>46.84</v>
+        <v>42.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12425,13 +12425,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="A10" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12459,25 +12459,25 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="59"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="60"/>
+      <c r="D12" s="99"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12485,8 +12485,8 @@
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="29">
         <v>0</v>
       </c>
@@ -12507,13 +12507,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="A16" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12541,25 +12541,25 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C17" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="64"/>
+      <c r="D17" s="88"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="89"/>
       <c r="E18" s="29">
         <v>2485</v>
       </c>
@@ -12567,8 +12567,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="66"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12590,13 +12590,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="A22" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="91"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12624,25 +12624,25 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="64"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="89"/>
       <c r="E24" s="33">
         <v>2485</v>
       </c>
@@ -12650,8 +12650,8 @@
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
       <c r="E25" s="29">
         <v>0</v>
       </c>
@@ -12673,11 +12673,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
+      <c r="A28" s="90" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12692,11 +12692,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="71" t="s">
+      <c r="A30" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12742,16 +12742,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="72"/>
+      <c r="A36" s="86"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12800,11 +12800,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12839,11 +12839,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="71" t="s">
+      <c r="A46" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="87"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12867,11 +12867,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="71" t="s">
+      <c r="A49" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="71"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="87"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
@@ -12895,11 +12895,11 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="84"/>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
@@ -12917,7 +12917,7 @@
         <v>70</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C54" s="29">
         <v>1280</v>
@@ -12959,7 +12959,7 @@
         <v>76</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C58" s="19">
         <v>4</v>
@@ -12976,11 +12976,11 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="73"/>
-      <c r="C60" s="73"/>
+      <c r="B60" s="84"/>
+      <c r="C60" s="84"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
@@ -13030,57 +13030,57 @@
       <c r="B66" s="24"/>
     </row>
     <row r="67" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="74" t="s">
-        <v>157</v>
-      </c>
-      <c r="B67" s="74"/>
-      <c r="C67" s="74"/>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
+      <c r="A67" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
     </row>
     <row r="68" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="75"/>
-      <c r="C68" s="75" t="s">
+      <c r="B68" s="85"/>
+      <c r="C68" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="75"/>
+      <c r="D68" s="85"/>
       <c r="E68" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="76" t="s">
-        <v>162</v>
-      </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
+      <c r="A69" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="58"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
       <c r="E69" s="47">
         <f>'July 2026- September 2026'!E101</f>
-        <v>145.20000000000027</v>
+        <v>301.40000000000055</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="79" t="s">
-        <v>169</v>
-      </c>
-      <c r="D70" s="79"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="74" t="s">
+        <v>167</v>
+      </c>
+      <c r="D70" s="74"/>
       <c r="E70" s="45">
         <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="78"/>
-      <c r="B71" s="78"/>
+      <c r="A71" s="79"/>
+      <c r="B71" s="79"/>
       <c r="C71" s="80" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D71" s="81"/>
       <c r="E71" s="45">
@@ -13088,8 +13088,8 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="78"/>
-      <c r="B72" s="78"/>
+      <c r="A72" s="79"/>
+      <c r="B72" s="79"/>
       <c r="C72" s="80"/>
       <c r="D72" s="82"/>
       <c r="E72" s="45">
@@ -13097,10 +13097,10 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="78" t="s">
+      <c r="A73" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="78"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="83"/>
       <c r="D73" s="83"/>
       <c r="E73" s="46">
@@ -13109,119 +13109,119 @@
       </c>
     </row>
     <row r="74" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D74" s="84"/>
+      <c r="D74" s="78"/>
       <c r="E74" s="47">
         <f>(E14+E69)-SUM(E70:E73)</f>
-        <v>825.20000000000027</v>
+        <v>981.40000000000055</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="74" t="s">
-        <v>158</v>
-      </c>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
+      <c r="A76" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="73"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
     </row>
     <row r="77" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="74" t="s">
+      <c r="A77" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="74"/>
-      <c r="C77" s="74" t="s">
+      <c r="B77" s="73"/>
+      <c r="C77" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="74"/>
+      <c r="D77" s="73"/>
       <c r="E77" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="76" t="s">
-        <v>150</v>
-      </c>
-      <c r="B78" s="76"/>
-      <c r="C78" s="85"/>
-      <c r="D78" s="85"/>
+      <c r="A78" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" s="58"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
       <c r="E78" s="47">
         <f>E74</f>
-        <v>825.20000000000027</v>
+        <v>981.40000000000055</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="93" t="s">
+      <c r="A79" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B79" s="94"/>
-      <c r="C79" s="86"/>
-      <c r="D79" s="87"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="64"/>
       <c r="E79" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="95"/>
-      <c r="B80" s="96"/>
-      <c r="C80" s="79" t="s">
-        <v>164</v>
-      </c>
-      <c r="D80" s="79"/>
+      <c r="A80" s="67"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="74" t="s">
+        <v>162</v>
+      </c>
+      <c r="D80" s="74"/>
       <c r="E80" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="95"/>
-      <c r="B81" s="96"/>
-      <c r="C81" s="90"/>
-      <c r="D81" s="91"/>
+      <c r="A81" s="67"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="76"/>
       <c r="E81" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="95"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="92"/>
+      <c r="A82" s="67"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="77"/>
       <c r="E82" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="97"/>
-      <c r="B83" s="98"/>
-      <c r="C83" s="90"/>
-      <c r="D83" s="91"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="76"/>
       <c r="E83" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="77" t="s">
+      <c r="A84" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="77"/>
-      <c r="C84" s="85"/>
-      <c r="D84" s="85"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
       <c r="E84" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="88" t="s">
+      <c r="C85" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="88"/>
+      <c r="D85" s="57"/>
       <c r="E85" s="47">
         <f>(E20+E78)-SUM(E79:E84)</f>
-        <v>1755.2000000000003</v>
+        <v>1911.4000000000005</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -13239,90 +13239,90 @@
       <c r="E87" s="49"/>
     </row>
     <row r="88" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="89" t="s">
-        <v>161</v>
-      </c>
-      <c r="B88" s="89"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="89"/>
-      <c r="E88" s="89"/>
+      <c r="A88" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="72"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="72"/>
+      <c r="E88" s="72"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="74" t="s">
+      <c r="A89" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="74"/>
-      <c r="C89" s="74" t="s">
+      <c r="B89" s="73"/>
+      <c r="C89" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="73"/>
       <c r="E89" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="B90" s="76"/>
-      <c r="C90" s="85"/>
-      <c r="D90" s="85"/>
+      <c r="A90" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" s="58"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
       <c r="E90" s="47">
         <f>E85</f>
-        <v>1755.2000000000003</v>
+        <v>1911.4000000000005</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="93" t="s">
+      <c r="A91" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="94"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="100"/>
+      <c r="B91" s="66"/>
+      <c r="C91" s="61"/>
+      <c r="D91" s="62"/>
       <c r="E91" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="95"/>
-      <c r="B92" s="96"/>
-      <c r="C92" s="99" t="s">
-        <v>164</v>
-      </c>
-      <c r="D92" s="100"/>
+      <c r="A92" s="67"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="D92" s="62"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="97"/>
-      <c r="B93" s="98"/>
-      <c r="C93" s="99"/>
-      <c r="D93" s="100"/>
+      <c r="A93" s="69"/>
+      <c r="B93" s="70"/>
+      <c r="C93" s="61"/>
+      <c r="D93" s="62"/>
       <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="77" t="s">
+      <c r="A94" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
       <c r="E94" s="45">
         <f>C64</f>
         <v>1555</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="88" t="s">
+      <c r="C95" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="88"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="47">
         <f>(E26+E90)-SUM(E91:E94)</f>
-        <v>2685.2000000000007</v>
+        <v>2841.4000000000005</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17071,45 +17071,15 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B93"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="A79:B83"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A70:B72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="C23:D23"/>
@@ -17121,15 +17091,45 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B83"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B93"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E69">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44812AF1-33CF-A249-8AC8-035FD221CDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04EED0A-38EB-DC43-830F-0FF2712D31C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="172">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -751,10 +751,15 @@
   </si>
   <si>
     <t>1. Borrow $60
-2. Payback Water bill through Alipay $74.1.</t>
+2. Payback Water bill through Alipay $74.1.
+3. Borrow $100 ~ 16/09</t>
   </si>
   <si>
-    <t>~ Debit For Octopus Card ($50). 20/08
+    <t>~ Payback $250 to Lawrence
+~ Payback $100 to Mom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
 ~ Additional transport fees for e-cigarette 20/08 - $50
@@ -766,7 +771,9 @@
 ~ OK Store buy additional 1 packet cigarette 12/09 - $78
 ~ OK Store buy additional 1 packet cigarette 13/09 - $78
 ~ OK Store buy additional 3 packet cigarette 14/09 - $234
-~ OK Store buy additional 1 packet cigarette 16/09 - $78</t>
+~ OK Store buy additional 2 packet cigarette 16/09 - $156
+~ OK Store 16/09 - $20
+</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1300,29 +1307,17 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1342,7 +1337,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1351,35 +1358,38 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1387,35 +1397,44 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1426,55 +1445,40 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1814,13 +1818,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1872,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>2.2000000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1997,7 +2001,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>42.940000000000005</v>
+        <v>44.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2050,13 +2054,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2084,10 +2088,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2099,10 +2103,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="114"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -2114,10 +2118,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="115"/>
+      <c r="D13" s="104"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -2168,10 +2172,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="110" t="s">
+      <c r="C17" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="110"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2181,10 +2185,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="111"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2196,10 +2200,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="112" t="s">
+      <c r="C19" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="112"/>
+      <c r="D19" s="98"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2220,13 +2224,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2254,10 +2258,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="113" t="s">
+      <c r="C23" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="113"/>
+      <c r="D23" s="99"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2297,10 +2301,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="110"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2312,10 +2316,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="111"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2325,10 +2329,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="101"/>
+      <c r="D28" s="67"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2350,13 +2354,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="91" t="s">
+      <c r="A31" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2384,10 +2388,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="88"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2425,10 +2429,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="94" t="s">
+      <c r="C35" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="95"/>
+      <c r="D35" s="91"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2438,10 +2442,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="94" t="s">
+      <c r="C36" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="109"/>
+      <c r="D36" s="92"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2451,7 +2455,7 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="100" t="s">
+      <c r="C37" s="93" t="s">
         <v>119</v>
       </c>
       <c r="D37" s="89"/>
@@ -2476,11 +2480,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="90"/>
-      <c r="C40" s="90"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2495,11 +2499,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2545,16 +2549,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="88"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="86"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2603,11 +2607,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2642,11 +2646,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="87"/>
-      <c r="C58" s="87"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="84"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2670,11 +2674,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="87"/>
-      <c r="C61" s="87"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="84"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2698,11 +2702,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="84"/>
-      <c r="C64" s="84"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="85"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2779,11 +2783,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="84"/>
+      <c r="B72" s="85"/>
+      <c r="C72" s="85"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2791,7 +2795,7 @@
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2810,7 +2814,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2842,78 +2846,78 @@
       <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="85" t="s">
+      <c r="B80" s="86"/>
+      <c r="C80" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="85"/>
+      <c r="D80" s="86"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="105" t="s">
+      <c r="A81" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="105"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="60"/>
+      <c r="B81" s="79"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="60"/>
-      <c r="C82" s="106" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="106"/>
+      <c r="D82" s="80"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="106" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="106"/>
+      <c r="D83" s="80"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="60"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="106" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="106"/>
+      <c r="D84" s="80"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="60"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="107" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="107"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="60"/>
-      <c r="B86" s="60"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
       <c r="C86" s="82" t="s">
         <v>89</v>
       </c>
@@ -2923,30 +2927,30 @@
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="60"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="107" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="107"/>
+      <c r="D87" s="81"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="60"/>
-      <c r="B88" s="60"/>
-      <c r="C88" s="106" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="106"/>
+      <c r="D88" s="80"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="60"/>
-      <c r="B89" s="60"/>
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
       <c r="C89" s="82" t="s">
         <v>92</v>
       </c>
@@ -2956,8 +2960,8 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="60"/>
-      <c r="B90" s="60"/>
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
       <c r="C90" s="82" t="s">
         <v>93</v>
       </c>
@@ -2967,23 +2971,23 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="60"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="108" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="108"/>
+      <c r="D91" s="83"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="79"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
@@ -3023,91 +3027,91 @@
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="58" t="s">
+      <c r="A97" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="58"/>
-      <c r="C97" s="59"/>
-      <c r="D97" s="59"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="60" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="60"/>
-      <c r="C98" s="81" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="81"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="60"/>
-      <c r="B99" s="60"/>
-      <c r="C99" s="74" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="74"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="60"/>
-      <c r="B100" s="60"/>
-      <c r="C100" s="74" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="74"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="60"/>
-      <c r="B101" s="60"/>
-      <c r="C101" s="74" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="75"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="60"/>
-      <c r="B102" s="60"/>
-      <c r="C102" s="75" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="104"/>
+      <c r="D102" s="71"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="60" t="s">
+      <c r="A103" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="60"/>
-      <c r="C103" s="59"/>
-      <c r="D103" s="59"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="57"/>
+      <c r="D104" s="59"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -3150,69 +3154,69 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="58"/>
-      <c r="C109" s="59"/>
-      <c r="D109" s="59"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="65" t="s">
+      <c r="A110" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="66"/>
-      <c r="C110" s="101" t="s">
+      <c r="B110" s="62"/>
+      <c r="C110" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="101"/>
+      <c r="D110" s="67"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="67"/>
-      <c r="B111" s="68"/>
-      <c r="C111" s="102" t="s">
+      <c r="A111" s="63"/>
+      <c r="B111" s="64"/>
+      <c r="C111" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="103"/>
+      <c r="D111" s="69"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="69"/>
-      <c r="B112" s="70"/>
-      <c r="C112" s="75" t="s">
+      <c r="A112" s="65"/>
+      <c r="B112" s="66"/>
+      <c r="C112" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="104"/>
+      <c r="D112" s="71"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="60" t="s">
+      <c r="A113" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="60"/>
-      <c r="C113" s="59"/>
-      <c r="D113" s="59"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="57" t="s">
+      <c r="C114" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="57"/>
+      <c r="D114" s="59"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -7081,13 +7085,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7141,7 +7145,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>2.2000000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7269,7 +7273,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>42.940000000000005</v>
+        <v>44.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7322,13 +7326,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7356,10 +7360,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7371,10 +7375,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="99"/>
+      <c r="D12" s="114"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7401,7 +7405,7 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="100" t="s">
+      <c r="C14" s="93" t="s">
         <v>132</v>
       </c>
       <c r="D14" s="89"/>
@@ -7425,13 +7429,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7459,10 +7463,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="88"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7489,10 +7493,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="90" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="95"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="29">
         <v>100</v>
       </c>
@@ -7504,27 +7508,27 @@
       <c r="B21" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="112" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="93"/>
+      <c r="D21" s="113"/>
       <c r="E21" s="29">
         <v>3.08</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
         <v>138</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="90" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="95"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="29">
-        <v>134.1</v>
+        <v>234.1</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="37" customHeight="1" x14ac:dyDescent="0.2">
@@ -7534,10 +7538,10 @@
       <c r="B23" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="95"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="29">
         <v>1500</v>
       </c>
@@ -7551,7 +7555,7 @@
       </c>
       <c r="E24" s="26">
         <f>SUM(E19:E23)</f>
-        <v>4222.18</v>
+        <v>4322.18</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7559,13 +7563,13 @@
       <c r="B25" s="24"/>
     </row>
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -7593,10 +7597,10 @@
       <c r="B27" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="88"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
@@ -7657,11 +7661,11 @@
       <c r="B32" s="24"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="90" t="s">
+      <c r="A33" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -7676,11 +7680,11 @@
       <c r="D34" s="37"/>
     </row>
     <row r="35" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="87"/>
-      <c r="C35" s="87"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
     </row>
     <row r="36" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50" t="s">
@@ -7726,16 +7730,16 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
     </row>
     <row r="41" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="86"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
+      <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
     </row>
     <row r="42" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
@@ -7784,11 +7788,11 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="84"/>
     </row>
     <row r="48" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7823,11 +7827,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="87"/>
-      <c r="C51" s="87"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="84"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7851,11 +7855,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -7879,11 +7883,11 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="84"/>
-      <c r="C57" s="84"/>
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
@@ -7960,11 +7964,11 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="84" t="s">
+      <c r="A65" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="84"/>
-      <c r="C65" s="84"/>
+      <c r="B65" s="85"/>
+      <c r="C65" s="85"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
@@ -7972,7 +7976,7 @@
       </c>
       <c r="B66" s="7"/>
       <c r="C66" s="19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7991,7 +7995,7 @@
       </c>
       <c r="C68" s="19">
         <f>SUM(C66:C67)</f>
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8023,58 +8027,58 @@
       <c r="E72" s="73"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="85" t="s">
+      <c r="A73" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85" t="s">
+      <c r="B73" s="86"/>
+      <c r="C73" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="85"/>
+      <c r="D73" s="86"/>
       <c r="E73" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="58" t="s">
+      <c r="A74" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="58"/>
-      <c r="C74" s="60"/>
-      <c r="D74" s="60"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
       <c r="E74" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="79"/>
-      <c r="C75" s="74" t="s">
+      <c r="B75" s="76"/>
+      <c r="C75" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="74"/>
+      <c r="D75" s="75"/>
       <c r="E75" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="79"/>
-      <c r="B76" s="79"/>
-      <c r="C76" s="80" t="s">
+      <c r="A76" s="76"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="111" t="s">
         <v>133</v>
       </c>
-      <c r="D76" s="81"/>
+      <c r="D76" s="74"/>
       <c r="E76" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="79"/>
-      <c r="B77" s="79"/>
-      <c r="C77" s="80" t="s">
+      <c r="A77" s="76"/>
+      <c r="B77" s="76"/>
+      <c r="C77" s="111" t="s">
         <v>134</v>
       </c>
       <c r="D77" s="82"/>
@@ -8083,12 +8087,12 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="79"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="83"/>
+      <c r="B78" s="76"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="77"/>
       <c r="E78" s="46">
         <f>C69</f>
         <v>1171</v>
@@ -8128,94 +8132,94 @@
       </c>
     </row>
     <row r="83" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="58"/>
-      <c r="C83" s="59"/>
-      <c r="D83" s="59"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="58"/>
+      <c r="D83" s="58"/>
       <c r="E83" s="47">
         <f>E79</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="65" t="s">
+      <c r="A84" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B84" s="66"/>
-      <c r="C84" s="71" t="s">
+      <c r="B84" s="62"/>
+      <c r="C84" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="D84" s="64"/>
+      <c r="D84" s="108"/>
       <c r="E84" s="48">
         <v>830.4</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="149" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="67"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="74" t="s">
+      <c r="A85" s="63"/>
+      <c r="B85" s="64"/>
+      <c r="C85" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="D85" s="74"/>
+      <c r="D85" s="75"/>
       <c r="E85" s="48">
         <v>721.4</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="221" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="67"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="75" t="s">
-        <v>170</v>
-      </c>
-      <c r="D86" s="76"/>
+    <row r="86" spans="1:5" ht="234" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="63"/>
+      <c r="B86" s="64"/>
+      <c r="C86" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" s="109"/>
       <c r="E86" s="48">
-        <v>858.5</v>
+        <v>956.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="67"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="71" t="s">
+      <c r="A87" s="63"/>
+      <c r="B87" s="64"/>
+      <c r="C87" s="107" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="77"/>
+      <c r="D87" s="110"/>
       <c r="E87" s="48">
         <v>196.54</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="75" t="s">
+      <c r="A88" s="65"/>
+      <c r="B88" s="66"/>
+      <c r="C88" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="D88" s="76"/>
+      <c r="D88" s="109"/>
       <c r="E88" s="55">
         <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="60" t="s">
+      <c r="A89" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="60"/>
-      <c r="C89" s="59"/>
-      <c r="D89" s="59"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
       <c r="E89" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C90" s="57" t="s">
+      <c r="C90" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="57"/>
+      <c r="D90" s="59"/>
       <c r="E90" s="47">
         <f>(E24+E83)-SUM(E84:E89)</f>
-        <v>42.940000000000509</v>
+        <v>44.940000000000509</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8255,83 +8259,83 @@
       </c>
     </row>
     <row r="95" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="58" t="s">
+      <c r="A95" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="58"/>
-      <c r="C95" s="59"/>
-      <c r="D95" s="59"/>
+      <c r="B95" s="60"/>
+      <c r="C95" s="58"/>
+      <c r="D95" s="58"/>
       <c r="E95" s="47">
         <f>E90</f>
-        <v>42.940000000000509</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="65" t="s">
+        <v>44.940000000000509</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="63" t="s">
+      <c r="B96" s="62"/>
+      <c r="C96" s="107" t="s">
         <v>167</v>
       </c>
-      <c r="D96" s="64"/>
+      <c r="D96" s="108"/>
       <c r="E96" s="45">
         <v>250</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="71" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="67"/>
-      <c r="B97" s="68"/>
-      <c r="C97" s="61" t="s">
+      <c r="A97" s="63"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="105" t="s">
         <v>168</v>
       </c>
-      <c r="D97" s="62"/>
+      <c r="D97" s="106"/>
       <c r="E97" s="45">
         <v>339.9</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="67"/>
-      <c r="B98" s="68"/>
-      <c r="C98" s="61" t="s">
+      <c r="A98" s="63"/>
+      <c r="B98" s="64"/>
+      <c r="C98" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="D98" s="62"/>
+      <c r="D98" s="106"/>
       <c r="E98" s="45">
         <v>384</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="69"/>
-      <c r="B99" s="70"/>
-      <c r="C99" s="61" t="s">
+      <c r="A99" s="65"/>
+      <c r="B99" s="66"/>
+      <c r="C99" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="D99" s="62"/>
+      <c r="D99" s="106"/>
       <c r="E99" s="45">
         <v>136.63999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="60" t="s">
+      <c r="A100" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="60"/>
-      <c r="C100" s="59"/>
-      <c r="D100" s="59"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="58"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="45">
         <f>C69</f>
         <v>1171</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C101" s="57" t="s">
+      <c r="C101" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="57"/>
+      <c r="D101" s="59"/>
       <c r="E101" s="47">
         <f>(E31+E95)-SUM(E96:E100)</f>
-        <v>301.40000000000055</v>
+        <v>303.40000000000055</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -12184,13 +12188,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -12244,7 +12248,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>2.2000000000000002</v>
+        <v>4.2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -12372,7 +12376,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>42.940000000000005</v>
+        <v>44.940000000000005</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -12425,13 +12429,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="101" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -12459,10 +12463,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="98"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -12474,10 +12478,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="99"/>
+      <c r="D12" s="114"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -12507,13 +12511,13 @@
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="96" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -12541,10 +12545,10 @@
       <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="88"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
@@ -12567,8 +12571,8 @@
     <row r="19" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54"/>
       <c r="B19" s="54"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="93"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="113"/>
       <c r="E19" s="29">
         <v>0</v>
       </c>
@@ -12590,13 +12594,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -12624,10 +12628,10 @@
       <c r="B23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="88"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
@@ -12673,11 +12677,11 @@
       <c r="B27" s="24"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="87" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
     </row>
     <row r="29" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -12692,11 +12696,11 @@
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
@@ -12742,16 +12746,16 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="86"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -12800,11 +12804,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -12839,11 +12843,11 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="87" t="s">
+      <c r="A46" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="87"/>
-      <c r="C46" s="87"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
@@ -12867,11 +12871,11 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="87"/>
-      <c r="C49" s="87"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
     </row>
     <row r=